--- a/three_gate/analysis/YM_weekly.xlsx
+++ b/three_gate/analysis/YM_weekly.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X58"/>
+  <dimension ref="A1:X59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5236,13 +5236,13 @@
         <v>51992</v>
       </c>
       <c r="E57" t="n">
-        <v>52576</v>
+        <v>52585</v>
       </c>
       <c r="F57" t="n">
-        <v>-864</v>
+        <v>-855</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0162</v>
+        <v>-0.016</v>
       </c>
       <c r="H57" t="n">
         <v>1344</v>
@@ -5307,31 +5307,113 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="12" t="inlineStr">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>52836</v>
+      </c>
+      <c r="C58" t="n">
+        <v>53090</v>
+      </c>
+      <c r="D58" t="n">
+        <v>52642</v>
+      </c>
+      <c r="E58" t="n">
+        <v>52894</v>
+      </c>
+      <c r="F58" t="n">
+        <v>309</v>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v>0.0059</v>
+      </c>
+      <c r="H58" t="n">
+        <v>448</v>
+      </c>
+      <c r="I58" t="n">
+        <v>50648</v>
+      </c>
+      <c r="J58" t="n">
+        <v>51201.5</v>
+      </c>
+      <c r="K58" t="n">
+        <v>51913</v>
+      </c>
+      <c r="L58" t="n">
+        <v>52624.5</v>
+      </c>
+      <c r="M58" t="n">
+        <v>53257</v>
+      </c>
+      <c r="N58" t="n">
+        <v>53889.5</v>
+      </c>
+      <c r="O58" t="n">
+        <v>54680</v>
+      </c>
+      <c r="P58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S58" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W58" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="12" t="inlineStr">
         <is>
           <t>下週預測</t>
         </is>
       </c>
-      <c r="I58" s="13" t="n">
-        <v>50648</v>
-      </c>
-      <c r="J58" s="13" t="n">
-        <v>51188</v>
-      </c>
-      <c r="K58" s="13" t="n">
-        <v>51904</v>
-      </c>
-      <c r="L58" s="13" t="n">
-        <v>52620</v>
-      </c>
-      <c r="M58" s="13" t="n">
-        <v>53248</v>
-      </c>
-      <c r="N58" s="13" t="n">
-        <v>53876</v>
-      </c>
-      <c r="O58" s="13" t="n">
-        <v>54680</v>
+      <c r="I59" s="13" t="n">
+        <v>52194</v>
+      </c>
+      <c r="J59" s="13" t="n">
+        <v>52460</v>
+      </c>
+      <c r="K59" s="13" t="n">
+        <v>52670</v>
+      </c>
+      <c r="L59" s="13" t="n">
+        <v>52880</v>
+      </c>
+      <c r="M59" s="13" t="n">
+        <v>53118</v>
+      </c>
+      <c r="N59" s="13" t="n">
+        <v>53356</v>
+      </c>
+      <c r="O59" s="13" t="n">
+        <v>53538</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/YM_weekly.xlsx
+++ b/three_gate/analysis/YM_weekly.xlsx
@@ -91,7 +91,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -120,6 +120,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -666,25 +669,25 @@
         <v>1199</v>
       </c>
       <c r="I2" t="n">
-        <v>42639</v>
+        <v>42681</v>
       </c>
       <c r="J2" t="n">
-        <v>43850</v>
+        <v>43865.75</v>
       </c>
       <c r="K2" t="n">
-        <v>44357</v>
+        <v>44367.5</v>
       </c>
       <c r="L2" t="n">
-        <v>44864</v>
+        <v>44869.25</v>
       </c>
       <c r="M2" t="n">
-        <v>45723</v>
+        <v>45712.5</v>
       </c>
       <c r="N2" t="n">
-        <v>46582</v>
+        <v>46555.75</v>
       </c>
       <c r="O2" t="n">
-        <v>46737</v>
+        <v>46716</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -5313,25 +5316,25 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>52836</v>
+        <v>52906</v>
       </c>
       <c r="C58" t="n">
-        <v>53090</v>
+        <v>52906</v>
       </c>
       <c r="D58" t="n">
-        <v>52642</v>
+        <v>52833</v>
       </c>
       <c r="E58" t="n">
-        <v>52894</v>
+        <v/>
       </c>
       <c r="F58" t="n">
-        <v>309</v>
+        <v/>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0059</v>
+        <v/>
       </c>
       <c r="H58" t="n">
-        <v>448</v>
+        <v>73</v>
       </c>
       <c r="I58" t="n">
         <v>50648</v>
@@ -5354,8 +5357,10 @@
       <c r="O58" t="n">
         <v>54680</v>
       </c>
-      <c r="P58" s="6" t="n">
-        <v/>
+      <c r="P58" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q58" s="6" t="n">
         <v/>
@@ -5363,9 +5368,9 @@
       <c r="R58" s="6" t="n">
         <v/>
       </c>
-      <c r="S58" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S58" s="12" t="inlineStr">
+        <is>
+          <t>=</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">
@@ -5389,31 +5394,31 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="12" t="inlineStr">
+      <c r="A59" s="13" t="inlineStr">
         <is>
           <t>下週預測</t>
         </is>
       </c>
-      <c r="I59" s="13" t="n">
-        <v>52194</v>
-      </c>
-      <c r="J59" s="13" t="n">
-        <v>52460</v>
-      </c>
-      <c r="K59" s="13" t="n">
-        <v>52670</v>
-      </c>
-      <c r="L59" s="13" t="n">
-        <v>52880</v>
-      </c>
-      <c r="M59" s="13" t="n">
-        <v>53118</v>
-      </c>
-      <c r="N59" s="13" t="n">
-        <v>53356</v>
-      </c>
-      <c r="O59" s="13" t="n">
-        <v>53538</v>
+      <c r="I59" s="14" t="n">
+        <v>52760</v>
+      </c>
+      <c r="J59" s="14" t="n">
+        <v/>
+      </c>
+      <c r="K59" s="14" t="n">
+        <v/>
+      </c>
+      <c r="L59" s="14" t="n">
+        <v/>
+      </c>
+      <c r="M59" s="14" t="n">
+        <v/>
+      </c>
+      <c r="N59" s="14" t="n">
+        <v/>
+      </c>
+      <c r="O59" s="14" t="n">
+        <v>52979</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/YM_weekly.xlsx
+++ b/three_gate/analysis/YM_weekly.xlsx
@@ -5322,7 +5322,7 @@
         <v>52906</v>
       </c>
       <c r="D58" t="n">
-        <v>52833</v>
+        <v>52803</v>
       </c>
       <c r="E58" t="n">
         <v/>
@@ -5334,7 +5334,7 @@
         <v/>
       </c>
       <c r="H58" t="n">
-        <v>73</v>
+        <v>103</v>
       </c>
       <c r="I58" t="n">
         <v>50648</v>
@@ -5400,7 +5400,7 @@
         </is>
       </c>
       <c r="I59" s="14" t="n">
-        <v>52760</v>
+        <v>52700</v>
       </c>
       <c r="J59" s="14" t="n">
         <v/>
@@ -5418,7 +5418,7 @@
         <v/>
       </c>
       <c r="O59" s="14" t="n">
-        <v>52979</v>
+        <v>53009</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/YM_weekly.xlsx
+++ b/three_gate/analysis/YM_weekly.xlsx
@@ -91,7 +91,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -120,9 +120,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -5316,25 +5313,25 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>52906</v>
+        <v>52376</v>
       </c>
       <c r="C58" t="n">
-        <v>52906</v>
+        <v>52672</v>
       </c>
       <c r="D58" t="n">
-        <v>52803</v>
+        <v>52226</v>
       </c>
       <c r="E58" t="n">
-        <v/>
+        <v>52440</v>
       </c>
       <c r="F58" t="n">
-        <v/>
+        <v>-145</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v/>
+        <v>-0.0028</v>
       </c>
       <c r="H58" t="n">
-        <v>103</v>
+        <v>446</v>
       </c>
       <c r="I58" t="n">
         <v>50648</v>
@@ -5357,10 +5354,8 @@
       <c r="O58" t="n">
         <v>54680</v>
       </c>
-      <c r="P58" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="P58" s="6" t="n">
+        <v/>
       </c>
       <c r="Q58" s="6" t="n">
         <v/>
@@ -5368,9 +5363,9 @@
       <c r="R58" s="6" t="n">
         <v/>
       </c>
-      <c r="S58" s="12" t="inlineStr">
-        <is>
-          <t>=</t>
+      <c r="S58" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">
@@ -5389,36 +5384,36 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="13" t="inlineStr">
+      <c r="A59" s="12" t="inlineStr">
         <is>
           <t>下週預測</t>
         </is>
       </c>
-      <c r="I59" s="14" t="n">
-        <v>52700</v>
-      </c>
-      <c r="J59" s="14" t="n">
-        <v/>
-      </c>
-      <c r="K59" s="14" t="n">
-        <v/>
-      </c>
-      <c r="L59" s="14" t="n">
-        <v/>
-      </c>
-      <c r="M59" s="14" t="n">
-        <v/>
-      </c>
-      <c r="N59" s="14" t="n">
-        <v/>
-      </c>
-      <c r="O59" s="14" t="n">
-        <v>53009</v>
+      <c r="I59" s="13" t="n">
+        <v>51780</v>
+      </c>
+      <c r="J59" s="13" t="n">
+        <v>51989.5</v>
+      </c>
+      <c r="K59" s="13" t="n">
+        <v>52217</v>
+      </c>
+      <c r="L59" s="13" t="n">
+        <v>52444.5</v>
+      </c>
+      <c r="M59" s="13" t="n">
+        <v>52663</v>
+      </c>
+      <c r="N59" s="13" t="n">
+        <v>52881.5</v>
+      </c>
+      <c r="O59" s="13" t="n">
+        <v>53118</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/YM_weekly.xlsx
+++ b/three_gate/analysis/YM_weekly.xlsx
@@ -5316,22 +5316,22 @@
         <v>52376</v>
       </c>
       <c r="C58" t="n">
-        <v>52672</v>
+        <v>52906</v>
       </c>
       <c r="D58" t="n">
         <v>52226</v>
       </c>
       <c r="E58" t="n">
-        <v>52440</v>
+        <v>52713</v>
       </c>
       <c r="F58" t="n">
-        <v>-145</v>
+        <v>128</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0028</v>
+        <v>0.0024</v>
       </c>
       <c r="H58" t="n">
-        <v>446</v>
+        <v>680</v>
       </c>
       <c r="I58" t="n">
         <v>50648</v>
@@ -5363,9 +5363,9 @@
       <c r="R58" s="6" t="n">
         <v/>
       </c>
-      <c r="S58" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S58" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">
@@ -5384,7 +5384,7 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
@@ -5395,25 +5395,25 @@
         </is>
       </c>
       <c r="I59" s="13" t="n">
-        <v>51780</v>
+        <v>51546</v>
       </c>
       <c r="J59" s="13" t="n">
-        <v>51989.5</v>
+        <v>52106.5</v>
       </c>
       <c r="K59" s="13" t="n">
-        <v>52217</v>
+        <v>52373</v>
       </c>
       <c r="L59" s="13" t="n">
-        <v>52444.5</v>
+        <v>52639.5</v>
       </c>
       <c r="M59" s="13" t="n">
-        <v>52663</v>
+        <v>53053</v>
       </c>
       <c r="N59" s="13" t="n">
-        <v>52881.5</v>
+        <v>53466.5</v>
       </c>
       <c r="O59" s="13" t="n">
-        <v>53118</v>
+        <v>53586</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/YM_weekly.xlsx
+++ b/three_gate/analysis/YM_weekly.xlsx
@@ -5322,13 +5322,13 @@
         <v>52226</v>
       </c>
       <c r="E58" t="n">
-        <v>52713</v>
+        <v>52571</v>
       </c>
       <c r="F58" t="n">
-        <v>128</v>
+        <v>-14</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0024</v>
+        <v>-0.0003</v>
       </c>
       <c r="H58" t="n">
         <v>680</v>
@@ -5363,9 +5363,9 @@
       <c r="R58" s="6" t="n">
         <v/>
       </c>
-      <c r="S58" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S58" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">
@@ -5384,7 +5384,7 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
@@ -5398,19 +5398,19 @@
         <v>51546</v>
       </c>
       <c r="J59" s="13" t="n">
-        <v>52106.5</v>
+        <v>51893.5</v>
       </c>
       <c r="K59" s="13" t="n">
-        <v>52373</v>
+        <v>52231</v>
       </c>
       <c r="L59" s="13" t="n">
-        <v>52639.5</v>
+        <v>52568.5</v>
       </c>
       <c r="M59" s="13" t="n">
-        <v>53053</v>
+        <v>52911</v>
       </c>
       <c r="N59" s="13" t="n">
-        <v>53466.5</v>
+        <v>53253.5</v>
       </c>
       <c r="O59" s="13" t="n">
         <v>53586</v>

--- a/three_gate/analysis/YM_weekly.xlsx
+++ b/three_gate/analysis/YM_weekly.xlsx
@@ -666,25 +666,25 @@
         <v>1199</v>
       </c>
       <c r="I2" t="n">
-        <v>42681</v>
+        <v>43637</v>
       </c>
       <c r="J2" t="n">
-        <v>43865.75</v>
+        <v>44224.25</v>
       </c>
       <c r="K2" t="n">
-        <v>44367.5</v>
+        <v>44606.5</v>
       </c>
       <c r="L2" t="n">
-        <v>44869.25</v>
+        <v>44988.75</v>
       </c>
       <c r="M2" t="n">
-        <v>45712.5</v>
+        <v>45473.5</v>
       </c>
       <c r="N2" t="n">
-        <v>46555.75</v>
+        <v>45958.25</v>
       </c>
       <c r="O2" t="n">
-        <v>46716</v>
+        <v>46238</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -5316,22 +5316,22 @@
         <v>52376</v>
       </c>
       <c r="C58" t="n">
-        <v>52906</v>
+        <v>52672</v>
       </c>
       <c r="D58" t="n">
         <v>52226</v>
       </c>
       <c r="E58" t="n">
-        <v>52571</v>
+        <v>52573</v>
       </c>
       <c r="F58" t="n">
-        <v>-14</v>
+        <v>-12</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0003</v>
+        <v>-0.0002</v>
       </c>
       <c r="H58" t="n">
-        <v>680</v>
+        <v>446</v>
       </c>
       <c r="I58" t="n">
         <v>50648</v>
@@ -5395,25 +5395,25 @@
         </is>
       </c>
       <c r="I59" s="13" t="n">
-        <v>51546</v>
+        <v>51780</v>
       </c>
       <c r="J59" s="13" t="n">
-        <v>51893.5</v>
+        <v>52189</v>
       </c>
       <c r="K59" s="13" t="n">
-        <v>52231</v>
+        <v>52350</v>
       </c>
       <c r="L59" s="13" t="n">
-        <v>52568.5</v>
+        <v>52511</v>
       </c>
       <c r="M59" s="13" t="n">
-        <v>52911</v>
+        <v>52796</v>
       </c>
       <c r="N59" s="13" t="n">
-        <v>53253.5</v>
+        <v>53081</v>
       </c>
       <c r="O59" s="13" t="n">
-        <v>53586</v>
+        <v>53118</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/YM_weekly.xlsx
+++ b/three_gate/analysis/YM_weekly.xlsx
@@ -5316,22 +5316,22 @@
         <v>52376</v>
       </c>
       <c r="C58" t="n">
-        <v>52672</v>
+        <v>52678</v>
       </c>
       <c r="D58" t="n">
-        <v>52226</v>
+        <v>51908</v>
       </c>
       <c r="E58" t="n">
-        <v>52573</v>
+        <v>52617</v>
       </c>
       <c r="F58" t="n">
-        <v>-12</v>
+        <v>32</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0002</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="H58" t="n">
-        <v>446</v>
+        <v>770</v>
       </c>
       <c r="I58" t="n">
         <v>50648</v>
@@ -5360,8 +5360,10 @@
       <c r="Q58" s="6" t="n">
         <v/>
       </c>
-      <c r="R58" s="6" t="n">
-        <v/>
+      <c r="R58" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S58" s="10" t="inlineStr">
         <is>
@@ -5395,25 +5397,25 @@
         </is>
       </c>
       <c r="I59" s="13" t="n">
-        <v>51780</v>
+        <v>51138</v>
       </c>
       <c r="J59" s="13" t="n">
-        <v>52189</v>
+        <v>52009</v>
       </c>
       <c r="K59" s="13" t="n">
-        <v>52350</v>
+        <v>52232</v>
       </c>
       <c r="L59" s="13" t="n">
-        <v>52511</v>
+        <v>52455</v>
       </c>
       <c r="M59" s="13" t="n">
-        <v>52796</v>
+        <v>53002</v>
       </c>
       <c r="N59" s="13" t="n">
-        <v>53081</v>
+        <v>53549</v>
       </c>
       <c r="O59" s="13" t="n">
-        <v>53118</v>
+        <v>53448</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/YM_weekly.xlsx
+++ b/three_gate/analysis/YM_weekly.xlsx
@@ -5316,22 +5316,22 @@
         <v>52376</v>
       </c>
       <c r="C58" t="n">
-        <v>52678</v>
+        <v>52687</v>
       </c>
       <c r="D58" t="n">
         <v>51908</v>
       </c>
       <c r="E58" t="n">
-        <v>52617</v>
+        <v>52644</v>
       </c>
       <c r="F58" t="n">
-        <v>32</v>
+        <v>59</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0005999999999999999</v>
+        <v>0.0011</v>
       </c>
       <c r="H58" t="n">
-        <v>770</v>
+        <v>779</v>
       </c>
       <c r="I58" t="n">
         <v>50648</v>
@@ -5365,9 +5365,9 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S58" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S58" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">
@@ -5397,25 +5397,25 @@
         </is>
       </c>
       <c r="I59" s="13" t="n">
-        <v>51138</v>
+        <v>51129</v>
       </c>
       <c r="J59" s="13" t="n">
-        <v>52009</v>
+        <v>52038.25</v>
       </c>
       <c r="K59" s="13" t="n">
-        <v>52232</v>
+        <v>52254.5</v>
       </c>
       <c r="L59" s="13" t="n">
-        <v>52455</v>
+        <v>52470.75</v>
       </c>
       <c r="M59" s="13" t="n">
-        <v>53002</v>
+        <v>53033.5</v>
       </c>
       <c r="N59" s="13" t="n">
-        <v>53549</v>
+        <v>53596.25</v>
       </c>
       <c r="O59" s="13" t="n">
-        <v>53448</v>
+        <v>53466</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/YM_weekly.xlsx
+++ b/three_gate/analysis/YM_weekly.xlsx
@@ -5316,22 +5316,22 @@
         <v>52376</v>
       </c>
       <c r="C58" t="n">
-        <v>52687</v>
+        <v>52697</v>
       </c>
       <c r="D58" t="n">
         <v>51908</v>
       </c>
       <c r="E58" t="n">
-        <v>52644</v>
+        <v>52695</v>
       </c>
       <c r="F58" t="n">
-        <v>59</v>
+        <v>110</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0011</v>
+        <v>0.0021</v>
       </c>
       <c r="H58" t="n">
-        <v>779</v>
+        <v>789</v>
       </c>
       <c r="I58" t="n">
         <v>50648</v>
@@ -5397,25 +5397,25 @@
         </is>
       </c>
       <c r="I59" s="13" t="n">
-        <v>51129</v>
+        <v>51119</v>
       </c>
       <c r="J59" s="13" t="n">
-        <v>52038.25</v>
+        <v>52102.25</v>
       </c>
       <c r="K59" s="13" t="n">
-        <v>52254.5</v>
+        <v>52300.5</v>
       </c>
       <c r="L59" s="13" t="n">
-        <v>52470.75</v>
+        <v>52498.75</v>
       </c>
       <c r="M59" s="13" t="n">
-        <v>53033.5</v>
+        <v>53089.5</v>
       </c>
       <c r="N59" s="13" t="n">
-        <v>53596.25</v>
+        <v>53680.25</v>
       </c>
       <c r="O59" s="13" t="n">
-        <v>53466</v>
+        <v>53486</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/YM_weekly.xlsx
+++ b/three_gate/analysis/YM_weekly.xlsx
@@ -5316,22 +5316,22 @@
         <v>52376</v>
       </c>
       <c r="C58" t="n">
-        <v>52697</v>
+        <v>52709</v>
       </c>
       <c r="D58" t="n">
         <v>51908</v>
       </c>
       <c r="E58" t="n">
-        <v>52695</v>
+        <v>52693</v>
       </c>
       <c r="F58" t="n">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="G58" s="5" t="n">
         <v>0.0021</v>
       </c>
       <c r="H58" t="n">
-        <v>789</v>
+        <v>801</v>
       </c>
       <c r="I58" t="n">
         <v>50648</v>
@@ -5397,25 +5397,25 @@
         </is>
       </c>
       <c r="I59" s="13" t="n">
-        <v>51119</v>
+        <v>51107</v>
       </c>
       <c r="J59" s="13" t="n">
-        <v>52102.25</v>
+        <v>52084.25</v>
       </c>
       <c r="K59" s="13" t="n">
-        <v>52300.5</v>
+        <v>52292.5</v>
       </c>
       <c r="L59" s="13" t="n">
-        <v>52498.75</v>
+        <v>52500.75</v>
       </c>
       <c r="M59" s="13" t="n">
-        <v>53089.5</v>
+        <v>53093.5</v>
       </c>
       <c r="N59" s="13" t="n">
-        <v>53680.25</v>
+        <v>53686.25</v>
       </c>
       <c r="O59" s="13" t="n">
-        <v>53486</v>
+        <v>53510</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/YM_weekly.xlsx
+++ b/three_gate/analysis/YM_weekly.xlsx
@@ -5316,22 +5316,22 @@
         <v>52376</v>
       </c>
       <c r="C58" t="n">
-        <v>52709</v>
+        <v>52672</v>
       </c>
       <c r="D58" t="n">
-        <v>51908</v>
+        <v>51838</v>
       </c>
       <c r="E58" t="n">
-        <v>52693</v>
+        <v>51891</v>
       </c>
       <c r="F58" t="n">
-        <v>108</v>
+        <v>-694</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0021</v>
+        <v>-0.0132</v>
       </c>
       <c r="H58" t="n">
-        <v>801</v>
+        <v>834</v>
       </c>
       <c r="I58" t="n">
         <v>50648</v>
@@ -5362,12 +5362,12 @@
       </c>
       <c r="R58" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S58" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S58" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
@@ -5397,25 +5397,25 @@
         </is>
       </c>
       <c r="I59" s="13" t="n">
-        <v>51107</v>
+        <v>51004</v>
       </c>
       <c r="J59" s="13" t="n">
-        <v>52084.25</v>
+        <v>50875</v>
       </c>
       <c r="K59" s="13" t="n">
-        <v>52292.5</v>
+        <v>51474</v>
       </c>
       <c r="L59" s="13" t="n">
-        <v>52500.75</v>
+        <v>52073</v>
       </c>
       <c r="M59" s="13" t="n">
-        <v>53093.5</v>
+        <v>52308</v>
       </c>
       <c r="N59" s="13" t="n">
-        <v>53686.25</v>
+        <v>52543</v>
       </c>
       <c r="O59" s="13" t="n">
-        <v>53510</v>
+        <v>53506</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/YM_weekly.xlsx
+++ b/three_gate/analysis/YM_weekly.xlsx
@@ -666,25 +666,25 @@
         <v>1199</v>
       </c>
       <c r="I2" t="n">
-        <v>43637</v>
+        <v>44169</v>
       </c>
       <c r="J2" t="n">
-        <v>44224.25</v>
+        <v>44423.75</v>
       </c>
       <c r="K2" t="n">
-        <v>44606.5</v>
+        <v>44739.5</v>
       </c>
       <c r="L2" t="n">
-        <v>44988.75</v>
+        <v>45055.25</v>
       </c>
       <c r="M2" t="n">
-        <v>45473.5</v>
+        <v>45340.5</v>
       </c>
       <c r="N2" t="n">
-        <v>45958.25</v>
+        <v>45625.75</v>
       </c>
       <c r="O2" t="n">
-        <v>46238</v>
+        <v>45972</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -692,8 +692,10 @@
       <c r="Q2" s="6" t="n">
         <v/>
       </c>
-      <c r="R2" s="6" t="n">
-        <v/>
+      <c r="R2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
@@ -702,12 +704,14 @@
       </c>
       <c r="T2" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U2" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U2" s="8" t="n">
-        <v/>
-      </c>
       <c r="V2" s="8" t="n">
         <v/>
       </c>
@@ -716,7 +720,11 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr"/>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -5322,13 +5330,13 @@
         <v>51838</v>
       </c>
       <c r="E58" t="n">
-        <v>51891</v>
+        <v>52203</v>
       </c>
       <c r="F58" t="n">
-        <v>-694</v>
+        <v>-382</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0132</v>
+        <v>-0.0073</v>
       </c>
       <c r="H58" t="n">
         <v>834</v>
@@ -5400,19 +5408,19 @@
         <v>51004</v>
       </c>
       <c r="J59" s="13" t="n">
-        <v>50875</v>
+        <v>51343</v>
       </c>
       <c r="K59" s="13" t="n">
-        <v>51474</v>
+        <v>51786</v>
       </c>
       <c r="L59" s="13" t="n">
-        <v>52073</v>
+        <v>52229</v>
       </c>
       <c r="M59" s="13" t="n">
-        <v>52308</v>
+        <v>52620</v>
       </c>
       <c r="N59" s="13" t="n">
-        <v>52543</v>
+        <v>53011</v>
       </c>
       <c r="O59" s="13" t="n">
         <v>53506</v>

--- a/three_gate/analysis/YM_weekly.xlsx
+++ b/three_gate/analysis/YM_weekly.xlsx
@@ -5327,19 +5327,19 @@
         <v>52672</v>
       </c>
       <c r="D58" t="n">
-        <v>51838</v>
+        <v>51209</v>
       </c>
       <c r="E58" t="n">
-        <v>52203</v>
+        <v>52197</v>
       </c>
       <c r="F58" t="n">
-        <v>-382</v>
+        <v>-388</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0073</v>
+        <v>-0.0074</v>
       </c>
       <c r="H58" t="n">
-        <v>834</v>
+        <v>1463</v>
       </c>
       <c r="I58" t="n">
         <v>50648</v>
@@ -5405,25 +5405,25 @@
         </is>
       </c>
       <c r="I59" s="13" t="n">
-        <v>51004</v>
+        <v>49746</v>
       </c>
       <c r="J59" s="13" t="n">
-        <v>51343</v>
+        <v>50862.25</v>
       </c>
       <c r="K59" s="13" t="n">
-        <v>51786</v>
+        <v>51465.5</v>
       </c>
       <c r="L59" s="13" t="n">
-        <v>52229</v>
+        <v>52068.75</v>
       </c>
       <c r="M59" s="13" t="n">
-        <v>52620</v>
+        <v>52928.5</v>
       </c>
       <c r="N59" s="13" t="n">
-        <v>53011</v>
+        <v>53788.25</v>
       </c>
       <c r="O59" s="13" t="n">
-        <v>53506</v>
+        <v>54135</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/YM_weekly.xlsx
+++ b/three_gate/analysis/YM_weekly.xlsx
@@ -5330,13 +5330,13 @@
         <v>51209</v>
       </c>
       <c r="E58" t="n">
-        <v>52197</v>
+        <v>52174</v>
       </c>
       <c r="F58" t="n">
-        <v>-388</v>
+        <v>-411</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0074</v>
+        <v>-0.0078</v>
       </c>
       <c r="H58" t="n">
         <v>1463</v>
@@ -5408,19 +5408,19 @@
         <v>49746</v>
       </c>
       <c r="J59" s="13" t="n">
-        <v>50862.25</v>
+        <v>50827.75</v>
       </c>
       <c r="K59" s="13" t="n">
-        <v>51465.5</v>
+        <v>51442.5</v>
       </c>
       <c r="L59" s="13" t="n">
-        <v>52068.75</v>
+        <v>52057.25</v>
       </c>
       <c r="M59" s="13" t="n">
-        <v>52928.5</v>
+        <v>52905.5</v>
       </c>
       <c r="N59" s="13" t="n">
-        <v>53788.25</v>
+        <v>53753.75</v>
       </c>
       <c r="O59" s="13" t="n">
         <v>54135</v>

--- a/three_gate/analysis/YM_weekly.xlsx
+++ b/three_gate/analysis/YM_weekly.xlsx
@@ -46,7 +46,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -73,11 +73,6 @@
         <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFE699"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -91,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -120,8 +115,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -487,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X59"/>
+  <dimension ref="A1:X58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -666,25 +659,25 @@
         <v>1199</v>
       </c>
       <c r="I2" t="n">
-        <v>44169</v>
+        <v>44591</v>
       </c>
       <c r="J2" t="n">
-        <v>44423.75</v>
+        <v>44582</v>
       </c>
       <c r="K2" t="n">
-        <v>44739.5</v>
+        <v>44845</v>
       </c>
       <c r="L2" t="n">
-        <v>45055.25</v>
+        <v>45108</v>
       </c>
       <c r="M2" t="n">
-        <v>45340.5</v>
+        <v>45235</v>
       </c>
       <c r="N2" t="n">
-        <v>45625.75</v>
+        <v>45362</v>
       </c>
       <c r="O2" t="n">
-        <v>45972</v>
+        <v>45761</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -709,11 +702,13 @@
       </c>
       <c r="U2" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V2" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="V2" s="8" t="n">
-        <v/>
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
@@ -5330,13 +5325,13 @@
         <v>51209</v>
       </c>
       <c r="E58" t="n">
-        <v>52174</v>
+        <v>52193</v>
       </c>
       <c r="F58" t="n">
-        <v>-411</v>
+        <v>-392</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0078</v>
+        <v>-0.0075</v>
       </c>
       <c r="H58" t="n">
         <v>1463</v>
@@ -5396,34 +5391,6 @@
         <is>
           <t>強警訊</t>
         </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="12" t="inlineStr">
-        <is>
-          <t>下週預測</t>
-        </is>
-      </c>
-      <c r="I59" s="13" t="n">
-        <v>49746</v>
-      </c>
-      <c r="J59" s="13" t="n">
-        <v>50827.75</v>
-      </c>
-      <c r="K59" s="13" t="n">
-        <v>51442.5</v>
-      </c>
-      <c r="L59" s="13" t="n">
-        <v>52057.25</v>
-      </c>
-      <c r="M59" s="13" t="n">
-        <v>52905.5</v>
-      </c>
-      <c r="N59" s="13" t="n">
-        <v>53753.75</v>
-      </c>
-      <c r="O59" s="13" t="n">
-        <v>54135</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/YM_weekly.xlsx
+++ b/three_gate/analysis/YM_weekly.xlsx
@@ -5325,13 +5325,13 @@
         <v>51209</v>
       </c>
       <c r="E58" t="n">
-        <v>52193</v>
+        <v>52205</v>
       </c>
       <c r="F58" t="n">
-        <v>-392</v>
+        <v>-380</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0075</v>
+        <v>-0.0072</v>
       </c>
       <c r="H58" t="n">
         <v>1463</v>

--- a/three_gate/analysis/YM_weekly.xlsx
+++ b/three_gate/analysis/YM_weekly.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X58"/>
+  <dimension ref="A1:X57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,50 +634,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>45029</v>
+        <v>45721</v>
       </c>
       <c r="C2" t="n">
-        <v>45841</v>
+        <v>45801</v>
       </c>
       <c r="D2" t="n">
-        <v>44642</v>
+        <v>45183</v>
       </c>
       <c r="E2" t="n">
-        <v>45715</v>
+        <v>45601</v>
       </c>
       <c r="F2" t="n">
-        <v>675</v>
+        <v>-114</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.015</v>
+        <v>-0.0025</v>
       </c>
       <c r="H2" t="n">
-        <v>1199</v>
+        <v>618</v>
       </c>
       <c r="I2" t="n">
-        <v>44591</v>
+        <v>43443</v>
       </c>
       <c r="J2" t="n">
-        <v>44582</v>
+        <v>44752.75</v>
       </c>
       <c r="K2" t="n">
-        <v>44845</v>
+        <v>45115.5</v>
       </c>
       <c r="L2" t="n">
-        <v>45108</v>
+        <v>45478.25</v>
       </c>
       <c r="M2" t="n">
-        <v>45235</v>
+        <v>46314.5</v>
       </c>
       <c r="N2" t="n">
-        <v>45362</v>
+        <v>47150.75</v>
       </c>
       <c r="O2" t="n">
-        <v>45761</v>
+        <v>47040</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -685,30 +685,22 @@
       <c r="Q2" s="6" t="n">
         <v/>
       </c>
-      <c r="R2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R2" s="6" t="n">
+        <v/>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V2" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U2" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V2" s="8" t="n">
+        <v/>
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
@@ -717,70 +709,74 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>45721</v>
+        <v>45685</v>
       </c>
       <c r="C3" t="n">
-        <v>45801</v>
+        <v>45832</v>
       </c>
       <c r="D3" t="n">
-        <v>45183</v>
+        <v>45000</v>
       </c>
       <c r="E3" t="n">
-        <v>45601</v>
+        <v>45459</v>
       </c>
       <c r="F3" t="n">
-        <v>-114</v>
+        <v>-142</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.0025</v>
+        <v>-0.0031</v>
       </c>
       <c r="H3" t="n">
-        <v>618</v>
+        <v>832</v>
       </c>
       <c r="I3" t="n">
-        <v>43443</v>
+        <v>44565</v>
       </c>
       <c r="J3" t="n">
-        <v>44752.75</v>
+        <v>45037.5</v>
       </c>
       <c r="K3" t="n">
-        <v>45115.5</v>
+        <v>45292</v>
       </c>
       <c r="L3" t="n">
-        <v>45478.25</v>
+        <v>45546.5</v>
       </c>
       <c r="M3" t="n">
-        <v>46314.5</v>
+        <v>45910</v>
       </c>
       <c r="N3" t="n">
-        <v>47150.75</v>
+        <v>46273.5</v>
       </c>
       <c r="O3" t="n">
-        <v>47040</v>
+        <v>46419</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
       </c>
-      <c r="Q3" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R3" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S3" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="Q3" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R3" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S3" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T3" s="8" t="n">
@@ -806,71 +802,69 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>45685</v>
+        <v>45475</v>
       </c>
       <c r="C4" t="n">
-        <v>45832</v>
+        <v>46176</v>
       </c>
       <c r="D4" t="n">
-        <v>45000</v>
+        <v>45321</v>
       </c>
       <c r="E4" t="n">
-        <v>45459</v>
+        <v>45854</v>
       </c>
       <c r="F4" t="n">
-        <v>-142</v>
+        <v>395</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.0031</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="H4" t="n">
-        <v>832</v>
+        <v>855</v>
       </c>
       <c r="I4" t="n">
-        <v>44565</v>
+        <v>44168</v>
       </c>
       <c r="J4" t="n">
-        <v>45037.5</v>
+        <v>44648.5</v>
       </c>
       <c r="K4" t="n">
-        <v>45292</v>
+        <v>45043</v>
       </c>
       <c r="L4" t="n">
-        <v>45546.5</v>
+        <v>45437.5</v>
       </c>
       <c r="M4" t="n">
-        <v>45910</v>
+        <v>45875</v>
       </c>
       <c r="N4" t="n">
-        <v>46273.5</v>
+        <v>46312.5</v>
       </c>
       <c r="O4" t="n">
-        <v>46419</v>
+        <v>46664</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
       </c>
-      <c r="Q4" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R4" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S4" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="n">
-        <v/>
+      <c r="Q4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S4" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U4" s="8" t="n">
         <v/>
@@ -883,59 +877,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>45475</v>
+        <v>45860</v>
       </c>
       <c r="C5" t="n">
-        <v>46176</v>
+        <v>46379</v>
       </c>
       <c r="D5" t="n">
-        <v>45321</v>
+        <v>45680</v>
       </c>
       <c r="E5" t="n">
-        <v>45854</v>
+        <v>46328</v>
       </c>
       <c r="F5" t="n">
-        <v>395</v>
+        <v>474</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.008699999999999999</v>
+        <v>0.0103</v>
       </c>
       <c r="H5" t="n">
-        <v>855</v>
+        <v>699</v>
       </c>
       <c r="I5" t="n">
-        <v>44168</v>
+        <v>44466</v>
       </c>
       <c r="J5" t="n">
-        <v>44648.5</v>
+        <v>45051.75</v>
       </c>
       <c r="K5" t="n">
-        <v>45043</v>
+        <v>45426.5</v>
       </c>
       <c r="L5" t="n">
-        <v>45437.5</v>
+        <v>45801.25</v>
       </c>
       <c r="M5" t="n">
-        <v>45875</v>
+        <v>46281.5</v>
       </c>
       <c r="N5" t="n">
-        <v>46312.5</v>
+        <v>46761.75</v>
       </c>
       <c r="O5" t="n">
-        <v>46664</v>
+        <v>47031</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -972,50 +962,50 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>45860</v>
+        <v>46605</v>
       </c>
       <c r="C6" t="n">
-        <v>46379</v>
+        <v>47055</v>
       </c>
       <c r="D6" t="n">
-        <v>45680</v>
+        <v>46098</v>
       </c>
       <c r="E6" t="n">
-        <v>46328</v>
+        <v>46556</v>
       </c>
       <c r="F6" t="n">
-        <v>474</v>
+        <v>228</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.0103</v>
+        <v>0.0049</v>
       </c>
       <c r="H6" t="n">
-        <v>699</v>
+        <v>957</v>
       </c>
       <c r="I6" t="n">
-        <v>44466</v>
+        <v>44981</v>
       </c>
       <c r="J6" t="n">
-        <v>45051.75</v>
+        <v>45778.25</v>
       </c>
       <c r="K6" t="n">
-        <v>45426.5</v>
+        <v>45978.5</v>
       </c>
       <c r="L6" t="n">
-        <v>45801.25</v>
+        <v>46178.75</v>
       </c>
       <c r="M6" t="n">
-        <v>46281.5</v>
+        <v>46677.5</v>
       </c>
       <c r="N6" t="n">
-        <v>46761.75</v>
+        <v>47176.25</v>
       </c>
       <c r="O6" t="n">
-        <v>47031</v>
+        <v>47078</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1052,50 +1042,50 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>46605</v>
+        <v>46565</v>
       </c>
       <c r="C7" t="n">
-        <v>47055</v>
+        <v>47323</v>
       </c>
       <c r="D7" t="n">
-        <v>46098</v>
+        <v>46335</v>
       </c>
       <c r="E7" t="n">
-        <v>46556</v>
+        <v>47031</v>
       </c>
       <c r="F7" t="n">
-        <v>228</v>
+        <v>475</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.0049</v>
+        <v>0.0102</v>
       </c>
       <c r="H7" t="n">
-        <v>957</v>
+        <v>988</v>
       </c>
       <c r="I7" t="n">
-        <v>44981</v>
+        <v>45141</v>
       </c>
       <c r="J7" t="n">
-        <v>45778.25</v>
+        <v>45588.75</v>
       </c>
       <c r="K7" t="n">
-        <v>45978.5</v>
+        <v>46077.5</v>
       </c>
       <c r="L7" t="n">
-        <v>46178.75</v>
+        <v>46566.25</v>
       </c>
       <c r="M7" t="n">
-        <v>46677.5</v>
+        <v>47034.5</v>
       </c>
       <c r="N7" t="n">
-        <v>47176.25</v>
+        <v>47502.75</v>
       </c>
       <c r="O7" t="n">
-        <v>47078</v>
+        <v>48012</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1132,79 +1122,83 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>46565</v>
+        <v>47048</v>
       </c>
       <c r="C8" t="n">
-        <v>47323</v>
+        <v>47162</v>
       </c>
       <c r="D8" t="n">
-        <v>46335</v>
+        <v>45387</v>
       </c>
       <c r="E8" t="n">
-        <v>47031</v>
+        <v>45706</v>
       </c>
       <c r="F8" t="n">
-        <v>475</v>
+        <v>-1325</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.0102</v>
+        <v>-0.0282</v>
       </c>
       <c r="H8" t="n">
-        <v>988</v>
+        <v>1775</v>
       </c>
       <c r="I8" t="n">
-        <v>45141</v>
+        <v>45347</v>
       </c>
       <c r="J8" t="n">
-        <v>45588.75</v>
+        <v>46144</v>
       </c>
       <c r="K8" t="n">
-        <v>46077.5</v>
+        <v>46537</v>
       </c>
       <c r="L8" t="n">
-        <v>46566.25</v>
+        <v>46930</v>
       </c>
       <c r="M8" t="n">
-        <v>47034.5</v>
+        <v>47525</v>
       </c>
       <c r="N8" t="n">
-        <v>47502.75</v>
+        <v>48120</v>
       </c>
       <c r="O8" t="n">
-        <v>48012</v>
-      </c>
-      <c r="P8" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q8" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R8" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S8" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="inlineStr">
+        <v>48311</v>
+      </c>
+      <c r="P8" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="Q8" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R8" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S8" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="n">
+        <v/>
+      </c>
       <c r="U8" s="8" t="n">
         <v/>
       </c>
       <c r="V8" s="8" t="n">
         <v/>
       </c>
-      <c r="W8" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W8" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X8" t="inlineStr"/>
@@ -1212,74 +1206,70 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>47048</v>
+        <v>45837</v>
       </c>
       <c r="C9" t="n">
-        <v>47162</v>
+        <v>46915</v>
       </c>
       <c r="D9" t="n">
-        <v>45387</v>
+        <v>45605</v>
       </c>
       <c r="E9" t="n">
-        <v>45706</v>
+        <v>46381</v>
       </c>
       <c r="F9" t="n">
-        <v>-1325</v>
+        <v>675</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.0282</v>
+        <v>0.0148</v>
       </c>
       <c r="H9" t="n">
-        <v>1775</v>
+        <v>1310</v>
       </c>
       <c r="I9" t="n">
-        <v>45347</v>
+        <v>43612</v>
       </c>
       <c r="J9" t="n">
-        <v>46144</v>
+        <v>43646.75</v>
       </c>
       <c r="K9" t="n">
-        <v>46537</v>
+        <v>44818.5</v>
       </c>
       <c r="L9" t="n">
-        <v>46930</v>
+        <v>45990.25</v>
       </c>
       <c r="M9" t="n">
-        <v>47525</v>
+        <v>46593.5</v>
       </c>
       <c r="N9" t="n">
-        <v>48120</v>
+        <v>47196.75</v>
       </c>
       <c r="O9" t="n">
-        <v>48311</v>
-      </c>
-      <c r="P9" s="6" t="inlineStr">
+        <v>48937</v>
+      </c>
+      <c r="P9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S9" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q9" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R9" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S9" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="n">
-        <v/>
-      </c>
       <c r="U9" s="8" t="n">
         <v/>
       </c>
@@ -1291,55 +1281,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr"/>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>45837</v>
+        <v>46489</v>
       </c>
       <c r="C10" t="n">
-        <v>46915</v>
+        <v>47508</v>
       </c>
       <c r="D10" t="n">
-        <v>45605</v>
+        <v>46316</v>
       </c>
       <c r="E10" t="n">
-        <v>46381</v>
+        <v>47396</v>
       </c>
       <c r="F10" t="n">
-        <v>675</v>
+        <v>1015</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.0148</v>
+        <v>0.0219</v>
       </c>
       <c r="H10" t="n">
-        <v>1310</v>
+        <v>1192</v>
       </c>
       <c r="I10" t="n">
-        <v>43612</v>
+        <v>44295</v>
       </c>
       <c r="J10" t="n">
-        <v>43646.75</v>
+        <v>45131.5</v>
       </c>
       <c r="K10" t="n">
-        <v>44818.5</v>
+        <v>45726</v>
       </c>
       <c r="L10" t="n">
-        <v>45990.25</v>
+        <v>46320.5</v>
       </c>
       <c r="M10" t="n">
-        <v>46593.5</v>
+        <v>47036</v>
       </c>
       <c r="N10" t="n">
-        <v>47196.75</v>
+        <v>47751.5</v>
       </c>
       <c r="O10" t="n">
-        <v>48937</v>
+        <v>48225</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1357,12 +1351,14 @@
       </c>
       <c r="T10" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U10" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U10" s="8" t="n">
-        <v/>
-      </c>
       <c r="V10" s="8" t="n">
         <v/>
       </c>
@@ -1373,57 +1369,57 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>46489</v>
+        <v>47711</v>
       </c>
       <c r="C11" t="n">
-        <v>47508</v>
+        <v>48214</v>
       </c>
       <c r="D11" t="n">
-        <v>46316</v>
+        <v>47488</v>
       </c>
       <c r="E11" t="n">
-        <v>47396</v>
+        <v>47722</v>
       </c>
       <c r="F11" t="n">
-        <v>1015</v>
+        <v>326</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0219</v>
+        <v>0.0069</v>
       </c>
       <c r="H11" t="n">
-        <v>1192</v>
+        <v>726</v>
       </c>
       <c r="I11" t="n">
-        <v>44295</v>
+        <v>45124</v>
       </c>
       <c r="J11" t="n">
-        <v>45131.5</v>
+        <v>46446</v>
       </c>
       <c r="K11" t="n">
-        <v>45726</v>
+        <v>46800</v>
       </c>
       <c r="L11" t="n">
-        <v>46320.5</v>
+        <v>47154</v>
       </c>
       <c r="M11" t="n">
-        <v>47036</v>
+        <v>47992</v>
       </c>
       <c r="N11" t="n">
-        <v>47751.5</v>
+        <v>48830</v>
       </c>
       <c r="O11" t="n">
-        <v>48225</v>
+        <v>48700</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1441,13 +1437,11 @@
       </c>
       <c r="T11" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U11" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U11" s="8" t="n">
+        <v/>
       </c>
       <c r="V11" s="8" t="n">
         <v/>
@@ -1466,70 +1460,74 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>47711</v>
+        <v>47735</v>
       </c>
       <c r="C12" t="n">
-        <v>48214</v>
+        <v>47869</v>
       </c>
       <c r="D12" t="n">
-        <v>47488</v>
+        <v>46574</v>
       </c>
       <c r="E12" t="n">
-        <v>47722</v>
+        <v>47085</v>
       </c>
       <c r="F12" t="n">
-        <v>326</v>
+        <v>-637</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.0069</v>
+        <v>-0.0133</v>
       </c>
       <c r="H12" t="n">
-        <v>726</v>
+        <v>1295</v>
       </c>
       <c r="I12" t="n">
-        <v>45124</v>
+        <v>46762</v>
       </c>
       <c r="J12" t="n">
-        <v>46446</v>
+        <v>46931.5</v>
       </c>
       <c r="K12" t="n">
-        <v>46800</v>
+        <v>47359</v>
       </c>
       <c r="L12" t="n">
-        <v>47154</v>
+        <v>47786.5</v>
       </c>
       <c r="M12" t="n">
-        <v>47992</v>
+        <v>48085</v>
       </c>
       <c r="N12" t="n">
-        <v>48830</v>
+        <v>48383.5</v>
       </c>
       <c r="O12" t="n">
-        <v>48700</v>
-      </c>
-      <c r="P12" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q12" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R12" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S12" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="inlineStr">
+        <v>48940</v>
+      </c>
+      <c r="P12" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q12" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R12" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S12" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="n">
+        <v/>
+      </c>
       <c r="U12" s="8" t="n">
         <v/>
       </c>
@@ -1541,86 +1539,80 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>47735</v>
+        <v>47208</v>
       </c>
       <c r="C13" t="n">
-        <v>47869</v>
+        <v>48528</v>
       </c>
       <c r="D13" t="n">
-        <v>46574</v>
+        <v>46939</v>
       </c>
       <c r="E13" t="n">
-        <v>47085</v>
+        <v>47229</v>
       </c>
       <c r="F13" t="n">
-        <v>-637</v>
+        <v>144</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.0133</v>
+        <v>0.0031</v>
       </c>
       <c r="H13" t="n">
-        <v>1295</v>
+        <v>1589</v>
       </c>
       <c r="I13" t="n">
-        <v>46762</v>
+        <v>45279</v>
       </c>
       <c r="J13" t="n">
-        <v>46931.5</v>
+        <v>45721.75</v>
       </c>
       <c r="K13" t="n">
-        <v>47359</v>
+        <v>46437.5</v>
       </c>
       <c r="L13" t="n">
-        <v>47786.5</v>
+        <v>47153.25</v>
       </c>
       <c r="M13" t="n">
-        <v>48085</v>
+        <v>47732.5</v>
       </c>
       <c r="N13" t="n">
-        <v>48383.5</v>
+        <v>48311.75</v>
       </c>
       <c r="O13" t="n">
-        <v>48940</v>
-      </c>
-      <c r="P13" s="6" t="inlineStr">
+        <v>49164</v>
+      </c>
+      <c r="P13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S13" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q13" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R13" s="6" t="inlineStr">
+      <c r="U13" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S13" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U13" s="8" t="n">
-        <v/>
-      </c>
       <c r="V13" s="8" t="n">
         <v/>
       </c>
@@ -1629,55 +1621,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr"/>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>47208</v>
+        <v>47237</v>
       </c>
       <c r="C14" t="n">
-        <v>48528</v>
+        <v>47368</v>
       </c>
       <c r="D14" t="n">
-        <v>46939</v>
+        <v>45779</v>
       </c>
       <c r="E14" t="n">
-        <v>47229</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="n">
-        <v>144</v>
+        <v>-908</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0031</v>
+        <v>-0.0192</v>
       </c>
       <c r="H14" t="n">
         <v>1589</v>
       </c>
       <c r="I14" t="n">
-        <v>45279</v>
+        <v>45350</v>
       </c>
       <c r="J14" t="n">
-        <v>45721.75</v>
+        <v>45387.75</v>
       </c>
       <c r="K14" t="n">
-        <v>46437.5</v>
+        <v>46434.5</v>
       </c>
       <c r="L14" t="n">
-        <v>47153.25</v>
+        <v>47481.25</v>
       </c>
       <c r="M14" t="n">
-        <v>47732.5</v>
+        <v>48023.5</v>
       </c>
       <c r="N14" t="n">
-        <v>48311.75</v>
+        <v>48565.75</v>
       </c>
       <c r="O14" t="n">
-        <v>49164</v>
+        <v>50117</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1685,23 +1681,21 @@
       <c r="Q14" s="6" t="n">
         <v/>
       </c>
-      <c r="R14" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S14" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U14" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R14" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S14" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U14" s="8" t="n">
+        <v/>
       </c>
       <c r="V14" s="8" t="n">
         <v/>
@@ -1711,59 +1705,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>47237</v>
+        <v>46504</v>
       </c>
       <c r="C15" t="n">
-        <v>47368</v>
+        <v>47796</v>
       </c>
       <c r="D15" t="n">
-        <v>45779</v>
+        <v>46165</v>
       </c>
       <c r="E15" t="n">
-        <v>46321</v>
+        <v>47743</v>
       </c>
       <c r="F15" t="n">
-        <v>-908</v>
+        <v>1422</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.0192</v>
+        <v>0.0307</v>
       </c>
       <c r="H15" t="n">
-        <v>1589</v>
+        <v>1631</v>
       </c>
       <c r="I15" t="n">
-        <v>45350</v>
+        <v>44190</v>
       </c>
       <c r="J15" t="n">
-        <v>45387.75</v>
+        <v>44605.75</v>
       </c>
       <c r="K15" t="n">
-        <v>46434.5</v>
+        <v>45526.5</v>
       </c>
       <c r="L15" t="n">
-        <v>47481.25</v>
+        <v>46447.25</v>
       </c>
       <c r="M15" t="n">
-        <v>48023.5</v>
+        <v>47115.5</v>
       </c>
       <c r="N15" t="n">
-        <v>48565.75</v>
+        <v>47783.75</v>
       </c>
       <c r="O15" t="n">
-        <v>50117</v>
+        <v>48957</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1771,22 +1761,24 @@
       <c r="Q15" s="6" t="n">
         <v/>
       </c>
-      <c r="R15" s="6" t="inlineStr">
+      <c r="R15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S15" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U15" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S15" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U15" s="8" t="n">
-        <v/>
-      </c>
       <c r="V15" s="8" t="n">
         <v/>
       </c>
@@ -1795,55 +1787,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr"/>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>46504</v>
+        <v>47741</v>
       </c>
       <c r="C16" t="n">
-        <v>47796</v>
+        <v>48184</v>
       </c>
       <c r="D16" t="n">
-        <v>46165</v>
+        <v>47269</v>
       </c>
       <c r="E16" t="n">
-        <v>47743</v>
+        <v>48001</v>
       </c>
       <c r="F16" t="n">
-        <v>1422</v>
+        <v>258</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0307</v>
+        <v>0.0054</v>
       </c>
       <c r="H16" t="n">
-        <v>1631</v>
+        <v>915</v>
       </c>
       <c r="I16" t="n">
-        <v>44190</v>
+        <v>44534</v>
       </c>
       <c r="J16" t="n">
-        <v>44605.75</v>
+        <v>46493.25</v>
       </c>
       <c r="K16" t="n">
-        <v>45526.5</v>
+        <v>46927.5</v>
       </c>
       <c r="L16" t="n">
-        <v>46447.25</v>
+        <v>47361.75</v>
       </c>
       <c r="M16" t="n">
-        <v>47115.5</v>
+        <v>48558.5</v>
       </c>
       <c r="N16" t="n">
-        <v>47783.75</v>
+        <v>49755.25</v>
       </c>
       <c r="O16" t="n">
-        <v>48957</v>
+        <v>49427</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1861,13 +1857,11 @@
       </c>
       <c r="T16" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U16" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U16" s="8" t="n">
+        <v/>
       </c>
       <c r="V16" s="8" t="n">
         <v/>
@@ -1886,50 +1880,50 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>47741</v>
+        <v>48015</v>
       </c>
       <c r="C17" t="n">
-        <v>48184</v>
+        <v>48917</v>
       </c>
       <c r="D17" t="n">
-        <v>47269</v>
+        <v>47504</v>
       </c>
       <c r="E17" t="n">
-        <v>48001</v>
+        <v>48474</v>
       </c>
       <c r="F17" t="n">
-        <v>258</v>
+        <v>473</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0054</v>
+        <v>0.009900000000000001</v>
       </c>
       <c r="H17" t="n">
-        <v>915</v>
+        <v>1413</v>
       </c>
       <c r="I17" t="n">
-        <v>44534</v>
+        <v>46354</v>
       </c>
       <c r="J17" t="n">
-        <v>46493.25</v>
+        <v>47223.25</v>
       </c>
       <c r="K17" t="n">
-        <v>46927.5</v>
+        <v>47543.5</v>
       </c>
       <c r="L17" t="n">
-        <v>47361.75</v>
+        <v>47863.75</v>
       </c>
       <c r="M17" t="n">
-        <v>48558.5</v>
+        <v>48458.5</v>
       </c>
       <c r="N17" t="n">
-        <v>49755.25</v>
+        <v>49053.25</v>
       </c>
       <c r="O17" t="n">
-        <v>49427</v>
+        <v>49099</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1937,8 +1931,10 @@
       <c r="Q17" s="6" t="n">
         <v/>
       </c>
-      <c r="R17" s="6" t="n">
-        <v/>
+      <c r="R17" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S17" s="7" t="inlineStr">
         <is>
@@ -1970,50 +1966,50 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>48015</v>
+        <v>48517</v>
       </c>
       <c r="C18" t="n">
-        <v>48917</v>
+        <v>48745</v>
       </c>
       <c r="D18" t="n">
-        <v>47504</v>
+        <v>47809</v>
       </c>
       <c r="E18" t="n">
-        <v>48474</v>
+        <v>48090</v>
       </c>
       <c r="F18" t="n">
-        <v>473</v>
+        <v>-384</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.009900000000000001</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="H18" t="n">
-        <v>1413</v>
+        <v>936</v>
       </c>
       <c r="I18" t="n">
-        <v>46354</v>
+        <v>46091</v>
       </c>
       <c r="J18" t="n">
-        <v>47223.25</v>
+        <v>47192.75</v>
       </c>
       <c r="K18" t="n">
-        <v>47543.5</v>
+        <v>47767.5</v>
       </c>
       <c r="L18" t="n">
-        <v>47863.75</v>
+        <v>48342.25</v>
       </c>
       <c r="M18" t="n">
-        <v>48458.5</v>
+        <v>49180.5</v>
       </c>
       <c r="N18" t="n">
-        <v>49053.25</v>
+        <v>50018.75</v>
       </c>
       <c r="O18" t="n">
-        <v>49099</v>
+        <v>50330</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2021,20 +2017,16 @@
       <c r="Q18" s="6" t="n">
         <v/>
       </c>
-      <c r="R18" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S18" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S18" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="n">
+        <v/>
       </c>
       <c r="U18" s="8" t="n">
         <v/>
@@ -2049,57 +2041,57 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>48517</v>
+        <v>48600</v>
       </c>
       <c r="C19" t="n">
-        <v>48745</v>
+        <v>49086</v>
       </c>
       <c r="D19" t="n">
-        <v>47809</v>
+        <v>48458</v>
       </c>
       <c r="E19" t="n">
-        <v>48090</v>
+        <v>48998</v>
       </c>
       <c r="F19" t="n">
-        <v>-384</v>
+        <v>908</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-0.007900000000000001</v>
+        <v>0.0189</v>
       </c>
       <c r="H19" t="n">
-        <v>936</v>
+        <v>628</v>
       </c>
       <c r="I19" t="n">
-        <v>46091</v>
+        <v>46873</v>
       </c>
       <c r="J19" t="n">
-        <v>47192.75</v>
+        <v>47060.5</v>
       </c>
       <c r="K19" t="n">
-        <v>47767.5</v>
+        <v>47622</v>
       </c>
       <c r="L19" t="n">
-        <v>48342.25</v>
+        <v>48183.5</v>
       </c>
       <c r="M19" t="n">
-        <v>49180.5</v>
+        <v>48558</v>
       </c>
       <c r="N19" t="n">
-        <v>50018.75</v>
+        <v>48932.5</v>
       </c>
       <c r="O19" t="n">
-        <v>50330</v>
+        <v>49681</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2110,103 +2102,103 @@
       <c r="R19" s="6" t="n">
         <v/>
       </c>
-      <c r="S19" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U19" s="8" t="n">
-        <v/>
+      <c r="S19" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U19" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V19" s="8" t="n">
         <v/>
       </c>
-      <c r="W19" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W19" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>48600</v>
+        <v>48998</v>
       </c>
       <c r="C20" t="n">
-        <v>49086</v>
+        <v>49052</v>
       </c>
       <c r="D20" t="n">
-        <v>48458</v>
+        <v>48092</v>
       </c>
       <c r="E20" t="n">
-        <v>48998</v>
+        <v>48616</v>
       </c>
       <c r="F20" t="n">
-        <v>908</v>
+        <v>-382</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.0189</v>
+        <v>-0.0078</v>
       </c>
       <c r="H20" t="n">
-        <v>628</v>
+        <v>960</v>
       </c>
       <c r="I20" t="n">
-        <v>46873</v>
+        <v>47830</v>
       </c>
       <c r="J20" t="n">
-        <v>47060.5</v>
+        <v>48483</v>
       </c>
       <c r="K20" t="n">
-        <v>47622</v>
+        <v>48684</v>
       </c>
       <c r="L20" t="n">
-        <v>48183.5</v>
+        <v>48885</v>
       </c>
       <c r="M20" t="n">
-        <v>48558</v>
+        <v>49312</v>
       </c>
       <c r="N20" t="n">
-        <v>48932.5</v>
+        <v>49739</v>
       </c>
       <c r="O20" t="n">
-        <v>49681</v>
+        <v>49714</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
       </c>
-      <c r="Q20" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R20" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S20" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="inlineStr">
+      <c r="Q20" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U20" s="8" t="inlineStr">
+      <c r="R20" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S20" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U20" s="8" t="n">
+        <v/>
+      </c>
       <c r="V20" s="8" t="n">
         <v/>
       </c>
@@ -2215,80 +2207,84 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr"/>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>48998</v>
+        <v>48653</v>
       </c>
       <c r="C21" t="n">
-        <v>49052</v>
+        <v>49876</v>
       </c>
       <c r="D21" t="n">
-        <v>48092</v>
+        <v>48556</v>
       </c>
       <c r="E21" t="n">
-        <v>48616</v>
+        <v>49726</v>
       </c>
       <c r="F21" t="n">
-        <v>-382</v>
+        <v>1110</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.0078</v>
+        <v>0.0228</v>
       </c>
       <c r="H21" t="n">
-        <v>960</v>
+        <v>1320</v>
       </c>
       <c r="I21" t="n">
-        <v>47830</v>
+        <v>47132</v>
       </c>
       <c r="J21" t="n">
-        <v>48483</v>
+        <v>47678</v>
       </c>
       <c r="K21" t="n">
-        <v>48684</v>
+        <v>48136</v>
       </c>
       <c r="L21" t="n">
-        <v>48885</v>
+        <v>48594</v>
       </c>
       <c r="M21" t="n">
-        <v>49312</v>
+        <v>49096</v>
       </c>
       <c r="N21" t="n">
-        <v>49739</v>
+        <v>49598</v>
       </c>
       <c r="O21" t="n">
-        <v>49714</v>
+        <v>50012</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
       </c>
-      <c r="Q21" s="6" t="inlineStr">
+      <c r="Q21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S21" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R21" s="6" t="inlineStr">
+      <c r="U21" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S21" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U21" s="8" t="n">
-        <v/>
-      </c>
       <c r="V21" s="8" t="n">
         <v/>
       </c>
@@ -2297,59 +2293,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>48653</v>
+        <v>49720</v>
       </c>
       <c r="C22" t="n">
-        <v>49876</v>
+        <v>49901</v>
       </c>
       <c r="D22" t="n">
-        <v>48556</v>
+        <v>49057</v>
       </c>
       <c r="E22" t="n">
-        <v>49726</v>
+        <v>49547</v>
       </c>
       <c r="F22" t="n">
-        <v>1110</v>
+        <v>-179</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.0228</v>
+        <v>-0.0036</v>
       </c>
       <c r="H22" t="n">
-        <v>1320</v>
+        <v>844</v>
       </c>
       <c r="I22" t="n">
-        <v>47132</v>
+        <v>47236</v>
       </c>
       <c r="J22" t="n">
-        <v>47678</v>
+        <v>48661</v>
       </c>
       <c r="K22" t="n">
-        <v>48136</v>
+        <v>49066</v>
       </c>
       <c r="L22" t="n">
-        <v>48594</v>
+        <v>49471</v>
       </c>
       <c r="M22" t="n">
-        <v>49096</v>
+        <v>50386</v>
       </c>
       <c r="N22" t="n">
-        <v>49598</v>
+        <v>51301</v>
       </c>
       <c r="O22" t="n">
-        <v>50012</v>
+        <v>51196</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2357,23 +2349,21 @@
       <c r="Q22" s="6" t="n">
         <v/>
       </c>
-      <c r="R22" s="6" t="n">
-        <v/>
+      <c r="R22" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S22" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U22" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U22" s="8" t="n">
+        <v/>
       </c>
       <c r="V22" s="8" t="n">
         <v/>
@@ -2383,70 +2373,76 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr"/>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>49720</v>
+        <v>49310</v>
       </c>
       <c r="C23" t="n">
-        <v>49901</v>
+        <v>49795</v>
       </c>
       <c r="D23" t="n">
-        <v>49057</v>
+        <v>48488</v>
       </c>
       <c r="E23" t="n">
-        <v>49547</v>
+        <v>49263</v>
       </c>
       <c r="F23" t="n">
-        <v>-179</v>
+        <v>-284</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-0.0036</v>
+        <v>-0.0057</v>
       </c>
       <c r="H23" t="n">
-        <v>844</v>
+        <v>1307</v>
       </c>
       <c r="I23" t="n">
-        <v>47236</v>
+        <v>48213</v>
       </c>
       <c r="J23" t="n">
-        <v>48661</v>
+        <v>48737</v>
       </c>
       <c r="K23" t="n">
-        <v>49066</v>
+        <v>49125</v>
       </c>
       <c r="L23" t="n">
-        <v>49471</v>
+        <v>49513</v>
       </c>
       <c r="M23" t="n">
-        <v>50386</v>
+        <v>49969</v>
       </c>
       <c r="N23" t="n">
-        <v>51301</v>
+        <v>50425</v>
       </c>
       <c r="O23" t="n">
-        <v>51196</v>
+        <v>50745</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
       </c>
-      <c r="Q23" s="6" t="n">
-        <v/>
+      <c r="Q23" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R23" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S23" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S23" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T23" s="8" t="n">
@@ -2465,74 +2461,72 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>49310</v>
+        <v>49036</v>
       </c>
       <c r="C24" t="n">
-        <v>49795</v>
+        <v>49644</v>
       </c>
       <c r="D24" t="n">
-        <v>48488</v>
+        <v>48571</v>
       </c>
       <c r="E24" t="n">
-        <v>49263</v>
+        <v>49008</v>
       </c>
       <c r="F24" t="n">
-        <v>-284</v>
+        <v>-255</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-0.0057</v>
+        <v>-0.0052</v>
       </c>
       <c r="H24" t="n">
-        <v>1307</v>
+        <v>1073</v>
       </c>
       <c r="I24" t="n">
-        <v>48213</v>
+        <v>47181</v>
       </c>
       <c r="J24" t="n">
-        <v>48737</v>
+        <v>48016.75</v>
       </c>
       <c r="K24" t="n">
-        <v>49125</v>
+        <v>48609.5</v>
       </c>
       <c r="L24" t="n">
-        <v>49513</v>
+        <v>49202.25</v>
       </c>
       <c r="M24" t="n">
-        <v>49969</v>
+        <v>49916.5</v>
       </c>
       <c r="N24" t="n">
-        <v>50425</v>
+        <v>50630.75</v>
       </c>
       <c r="O24" t="n">
-        <v>50745</v>
+        <v>51102</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
       </c>
-      <c r="Q24" s="6" t="inlineStr">
+      <c r="Q24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R24" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R24" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
       <c r="S24" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T24" s="8" t="n">
@@ -2551,57 +2545,57 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>49036</v>
+        <v>48864</v>
       </c>
       <c r="C25" t="n">
-        <v>49644</v>
+        <v>50263</v>
       </c>
       <c r="D25" t="n">
-        <v>48571</v>
+        <v>48506</v>
       </c>
       <c r="E25" t="n">
-        <v>49008</v>
+        <v>50205</v>
       </c>
       <c r="F25" t="n">
-        <v>-255</v>
+        <v>1197</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.0052</v>
+        <v>0.0244</v>
       </c>
       <c r="H25" t="n">
-        <v>1073</v>
+        <v>1757</v>
       </c>
       <c r="I25" t="n">
-        <v>47181</v>
+        <v>47498</v>
       </c>
       <c r="J25" t="n">
-        <v>48016.75</v>
+        <v>47885.25</v>
       </c>
       <c r="K25" t="n">
-        <v>48609.5</v>
+        <v>48471.5</v>
       </c>
       <c r="L25" t="n">
-        <v>49202.25</v>
+        <v>49057.75</v>
       </c>
       <c r="M25" t="n">
-        <v>49916.5</v>
+        <v>49544.5</v>
       </c>
       <c r="N25" t="n">
-        <v>50630.75</v>
+        <v>50031.25</v>
       </c>
       <c r="O25" t="n">
-        <v>51102</v>
+        <v>50717</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2609,21 +2603,23 @@
       <c r="Q25" s="6" t="n">
         <v/>
       </c>
-      <c r="R25" s="6" t="inlineStr">
+      <c r="R25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S25" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S25" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U25" s="8" t="n">
-        <v/>
+      <c r="U25" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V25" s="8" t="n">
         <v/>
@@ -2635,57 +2631,57 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>48864</v>
+        <v>50240</v>
       </c>
       <c r="C26" t="n">
-        <v>50263</v>
+        <v>50611</v>
       </c>
       <c r="D26" t="n">
-        <v>48506</v>
+        <v>49155</v>
       </c>
       <c r="E26" t="n">
-        <v>50205</v>
+        <v>49569</v>
       </c>
       <c r="F26" t="n">
-        <v>1197</v>
+        <v>-636</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.0244</v>
+        <v>-0.0127</v>
       </c>
       <c r="H26" t="n">
-        <v>1757</v>
+        <v>1456</v>
       </c>
       <c r="I26" t="n">
-        <v>47498</v>
+        <v>46749</v>
       </c>
       <c r="J26" t="n">
-        <v>47885.25</v>
+        <v>48858.25</v>
       </c>
       <c r="K26" t="n">
-        <v>48471.5</v>
+        <v>49326.5</v>
       </c>
       <c r="L26" t="n">
-        <v>49057.75</v>
+        <v>49794.75</v>
       </c>
       <c r="M26" t="n">
-        <v>49544.5</v>
+        <v>51083.5</v>
       </c>
       <c r="N26" t="n">
-        <v>50031.25</v>
+        <v>52372.25</v>
       </c>
       <c r="O26" t="n">
-        <v>50717</v>
+        <v>52020</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2693,23 +2689,21 @@
       <c r="Q26" s="6" t="n">
         <v/>
       </c>
-      <c r="R26" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S26" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="inlineStr">
+      <c r="R26" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U26" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S26" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U26" s="8" t="n">
+        <v/>
       </c>
       <c r="V26" s="8" t="n">
         <v/>
@@ -2728,50 +2722,50 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>50240</v>
+        <v>49549</v>
       </c>
       <c r="C27" t="n">
-        <v>50611</v>
+        <v>49967</v>
       </c>
       <c r="D27" t="n">
-        <v>49155</v>
+        <v>49204</v>
       </c>
       <c r="E27" t="n">
-        <v>49569</v>
+        <v>49674</v>
       </c>
       <c r="F27" t="n">
-        <v>-636</v>
+        <v>105</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.0127</v>
+        <v>0.0021</v>
       </c>
       <c r="H27" t="n">
-        <v>1456</v>
+        <v>763</v>
       </c>
       <c r="I27" t="n">
-        <v>46749</v>
+        <v>47699</v>
       </c>
       <c r="J27" t="n">
-        <v>48858.25</v>
+        <v>47956</v>
       </c>
       <c r="K27" t="n">
-        <v>49326.5</v>
+        <v>48841</v>
       </c>
       <c r="L27" t="n">
-        <v>49794.75</v>
+        <v>49726</v>
       </c>
       <c r="M27" t="n">
-        <v>51083.5</v>
+        <v>50297</v>
       </c>
       <c r="N27" t="n">
-        <v>52372.25</v>
+        <v>50868</v>
       </c>
       <c r="O27" t="n">
-        <v>52020</v>
+        <v>52067</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2779,10 +2773,8 @@
       <c r="Q27" s="6" t="n">
         <v/>
       </c>
-      <c r="R27" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R27" s="6" t="n">
+        <v/>
       </c>
       <c r="S27" s="10" t="inlineStr">
         <is>
@@ -2812,63 +2804,67 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>49549</v>
+        <v>49642</v>
       </c>
       <c r="C28" t="n">
-        <v>49967</v>
+        <v>49872</v>
       </c>
       <c r="D28" t="n">
-        <v>49204</v>
+        <v>48699</v>
       </c>
       <c r="E28" t="n">
-        <v>49674</v>
+        <v>49000</v>
       </c>
       <c r="F28" t="n">
-        <v>105</v>
+        <v>-674</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.0021</v>
+        <v>-0.0136</v>
       </c>
       <c r="H28" t="n">
-        <v>763</v>
+        <v>1173</v>
       </c>
       <c r="I28" t="n">
-        <v>47699</v>
+        <v>48441</v>
       </c>
       <c r="J28" t="n">
-        <v>47956</v>
+        <v>48955.25</v>
       </c>
       <c r="K28" t="n">
-        <v>48841</v>
+        <v>49292.5</v>
       </c>
       <c r="L28" t="n">
-        <v>49726</v>
+        <v>49629.75</v>
       </c>
       <c r="M28" t="n">
-        <v>50297</v>
+        <v>50055.5</v>
       </c>
       <c r="N28" t="n">
-        <v>50868</v>
+        <v>50481.25</v>
       </c>
       <c r="O28" t="n">
-        <v>52067</v>
+        <v>50730</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
       </c>
-      <c r="Q28" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R28" s="6" t="n">
-        <v/>
+      <c r="Q28" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R28" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S28" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T28" s="8" t="n">
@@ -2887,64 +2883,66 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>49642</v>
+        <v>48451</v>
       </c>
       <c r="C29" t="n">
-        <v>49872</v>
+        <v>49121</v>
       </c>
       <c r="D29" t="n">
-        <v>48699</v>
+        <v>47025</v>
       </c>
       <c r="E29" t="n">
-        <v>49000</v>
+        <v>47517</v>
       </c>
       <c r="F29" t="n">
-        <v>-674</v>
+        <v>-1483</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.0136</v>
+        <v>-0.0303</v>
       </c>
       <c r="H29" t="n">
-        <v>1173</v>
+        <v>2096</v>
       </c>
       <c r="I29" t="n">
-        <v>48441</v>
+        <v>47526</v>
       </c>
       <c r="J29" t="n">
-        <v>48955.25</v>
+        <v>47684.25</v>
       </c>
       <c r="K29" t="n">
-        <v>49292.5</v>
+        <v>48413.5</v>
       </c>
       <c r="L29" t="n">
-        <v>49629.75</v>
+        <v>49142.75</v>
       </c>
       <c r="M29" t="n">
-        <v>50055.5</v>
+        <v>49586.5</v>
       </c>
       <c r="N29" t="n">
-        <v>50481.25</v>
+        <v>50030.25</v>
       </c>
       <c r="O29" t="n">
-        <v>50730</v>
-      </c>
-      <c r="P29" s="6" t="n">
-        <v/>
+        <v>51045</v>
+      </c>
+      <c r="P29" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q29" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="R29" s="6" t="inlineStr">
@@ -2966,78 +2964,70 @@
       <c r="V29" s="8" t="n">
         <v/>
       </c>
-      <c r="W29" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X29" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W29" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>48451</v>
+        <v>47177</v>
       </c>
       <c r="C30" t="n">
-        <v>49121</v>
+        <v>48266</v>
       </c>
       <c r="D30" t="n">
-        <v>47025</v>
+        <v>46333</v>
       </c>
       <c r="E30" t="n">
-        <v>47517</v>
+        <v>46592</v>
       </c>
       <c r="F30" t="n">
-        <v>-1483</v>
+        <v>-925</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0.0303</v>
+        <v>-0.0195</v>
       </c>
       <c r="H30" t="n">
-        <v>2096</v>
+        <v>1933</v>
       </c>
       <c r="I30" t="n">
-        <v>47526</v>
+        <v>44929</v>
       </c>
       <c r="J30" t="n">
-        <v>47684.25</v>
+        <v>45143</v>
       </c>
       <c r="K30" t="n">
-        <v>48413.5</v>
+        <v>46469</v>
       </c>
       <c r="L30" t="n">
-        <v>49142.75</v>
+        <v>47795</v>
       </c>
       <c r="M30" t="n">
-        <v>49586.5</v>
+        <v>48565</v>
       </c>
       <c r="N30" t="n">
-        <v>50030.25</v>
+        <v>49335</v>
       </c>
       <c r="O30" t="n">
-        <v>51045</v>
-      </c>
-      <c r="P30" s="6" t="inlineStr">
+        <v>51217</v>
+      </c>
+      <c r="P30" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q30" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R30" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="Q30" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R30" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S30" s="10" t="inlineStr">
@@ -3064,50 +3054,50 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>47177</v>
+        <v>46392</v>
       </c>
       <c r="C31" t="n">
-        <v>48266</v>
+        <v>47457</v>
       </c>
       <c r="D31" t="n">
-        <v>46333</v>
+        <v>45713</v>
       </c>
       <c r="E31" t="n">
-        <v>46592</v>
+        <v>45897</v>
       </c>
       <c r="F31" t="n">
-        <v>-925</v>
+        <v>-695</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-0.0195</v>
+        <v>-0.0149</v>
       </c>
       <c r="H31" t="n">
-        <v>1933</v>
+        <v>1744</v>
       </c>
       <c r="I31" t="n">
-        <v>44929</v>
+        <v>44400</v>
       </c>
       <c r="J31" t="n">
-        <v>45143</v>
+        <v>44305.25</v>
       </c>
       <c r="K31" t="n">
-        <v>46469</v>
+        <v>45625.5</v>
       </c>
       <c r="L31" t="n">
-        <v>47795</v>
+        <v>46945.75</v>
       </c>
       <c r="M31" t="n">
-        <v>48565</v>
+        <v>47558.5</v>
       </c>
       <c r="N31" t="n">
-        <v>49335</v>
+        <v>48171.25</v>
       </c>
       <c r="O31" t="n">
-        <v>51217</v>
+        <v>50199</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3144,50 +3134,50 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>46392</v>
+        <v>45605</v>
       </c>
       <c r="C32" t="n">
-        <v>47457</v>
+        <v>47210</v>
       </c>
       <c r="D32" t="n">
-        <v>45713</v>
+        <v>45272</v>
       </c>
       <c r="E32" t="n">
-        <v>45897</v>
+        <v>45424</v>
       </c>
       <c r="F32" t="n">
-        <v>-695</v>
+        <v>-473</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>-0.0149</v>
+        <v>-0.0103</v>
       </c>
       <c r="H32" t="n">
-        <v>1744</v>
+        <v>1938</v>
       </c>
       <c r="I32" t="n">
-        <v>44400</v>
+        <v>43969</v>
       </c>
       <c r="J32" t="n">
-        <v>44305.25</v>
+        <v>43809</v>
       </c>
       <c r="K32" t="n">
-        <v>45625.5</v>
+        <v>45025</v>
       </c>
       <c r="L32" t="n">
-        <v>46945.75</v>
+        <v>46241</v>
       </c>
       <c r="M32" t="n">
-        <v>47558.5</v>
+        <v>46769</v>
       </c>
       <c r="N32" t="n">
-        <v>48171.25</v>
+        <v>47297</v>
       </c>
       <c r="O32" t="n">
-        <v>50199</v>
+        <v>49201</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3205,8 +3195,10 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T32" s="8" t="n">
-        <v/>
+      <c r="T32" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U32" s="8" t="n">
         <v/>
@@ -3224,50 +3216,50 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>45605</v>
+        <v>45244</v>
       </c>
       <c r="C33" t="n">
-        <v>47210</v>
+        <v>47090</v>
       </c>
       <c r="D33" t="n">
-        <v>45272</v>
+        <v>45052</v>
       </c>
       <c r="E33" t="n">
-        <v>45424</v>
+        <v>46629</v>
       </c>
       <c r="F33" t="n">
-        <v>-473</v>
+        <v>1205</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>-0.0103</v>
+        <v>0.0265</v>
       </c>
       <c r="H33" t="n">
-        <v>1938</v>
+        <v>2038</v>
       </c>
       <c r="I33" t="n">
-        <v>43969</v>
+        <v>43334</v>
       </c>
       <c r="J33" t="n">
-        <v>43809</v>
+        <v>43077.5</v>
       </c>
       <c r="K33" t="n">
-        <v>45025</v>
+        <v>44455</v>
       </c>
       <c r="L33" t="n">
-        <v>46241</v>
+        <v>45832.5</v>
       </c>
       <c r="M33" t="n">
-        <v>46769</v>
+        <v>46393</v>
       </c>
       <c r="N33" t="n">
-        <v>47297</v>
+        <v>46953.5</v>
       </c>
       <c r="O33" t="n">
-        <v>49201</v>
+        <v>49148</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3275,24 +3267,24 @@
       <c r="Q33" s="6" t="n">
         <v/>
       </c>
-      <c r="R33" s="6" t="inlineStr">
+      <c r="R33" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S33" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S33" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="inlineStr">
+      <c r="U33" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U33" s="8" t="n">
-        <v/>
-      </c>
       <c r="V33" s="8" t="n">
         <v/>
       </c>
@@ -3301,55 +3293,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr"/>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>45244</v>
+        <v>46569</v>
       </c>
       <c r="C34" t="n">
-        <v>47090</v>
+        <v>48555</v>
       </c>
       <c r="D34" t="n">
-        <v>45052</v>
+        <v>46362</v>
       </c>
       <c r="E34" t="n">
-        <v>46629</v>
+        <v>48129</v>
       </c>
       <c r="F34" t="n">
-        <v>1205</v>
+        <v>1500</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0265</v>
+        <v>0.0322</v>
       </c>
       <c r="H34" t="n">
-        <v>2038</v>
+        <v>2193</v>
       </c>
       <c r="I34" t="n">
-        <v>43334</v>
+        <v>43014</v>
       </c>
       <c r="J34" t="n">
-        <v>43077.5</v>
+        <v>44870</v>
       </c>
       <c r="K34" t="n">
-        <v>44455</v>
+        <v>45610</v>
       </c>
       <c r="L34" t="n">
-        <v>45832.5</v>
+        <v>46350</v>
       </c>
       <c r="M34" t="n">
-        <v>46393</v>
+        <v>47648</v>
       </c>
       <c r="N34" t="n">
-        <v>46953.5</v>
+        <v>48946</v>
       </c>
       <c r="O34" t="n">
-        <v>49148</v>
+        <v>49128</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3370,10 +3366,8 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U34" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U34" s="8" t="n">
+        <v/>
       </c>
       <c r="V34" s="8" t="n">
         <v/>
@@ -3385,57 +3379,57 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>46569</v>
+        <v>47674</v>
       </c>
       <c r="C35" t="n">
-        <v>48555</v>
+        <v>49924</v>
       </c>
       <c r="D35" t="n">
-        <v>46362</v>
+        <v>47534</v>
       </c>
       <c r="E35" t="n">
-        <v>48129</v>
+        <v>49641</v>
       </c>
       <c r="F35" t="n">
-        <v>1500</v>
+        <v>1512</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.0322</v>
+        <v>0.0314</v>
       </c>
       <c r="H35" t="n">
-        <v>2193</v>
+        <v>2390</v>
       </c>
       <c r="I35" t="n">
-        <v>43014</v>
+        <v>44169</v>
       </c>
       <c r="J35" t="n">
-        <v>44870</v>
+        <v>46271.25</v>
       </c>
       <c r="K35" t="n">
-        <v>45610</v>
+        <v>47032.5</v>
       </c>
       <c r="L35" t="n">
-        <v>46350</v>
+        <v>47793.75</v>
       </c>
       <c r="M35" t="n">
-        <v>47648</v>
+        <v>49225.5</v>
       </c>
       <c r="N35" t="n">
-        <v>48946</v>
+        <v>50657.25</v>
       </c>
       <c r="O35" t="n">
-        <v>49128</v>
+        <v>50748</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3476,50 +3470,50 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>47674</v>
+        <v>49324</v>
       </c>
       <c r="C36" t="n">
-        <v>49924</v>
+        <v>50043</v>
       </c>
       <c r="D36" t="n">
-        <v>47534</v>
+        <v>49036</v>
       </c>
       <c r="E36" t="n">
-        <v>49641</v>
+        <v>49392</v>
       </c>
       <c r="F36" t="n">
-        <v>1512</v>
+        <v>-249</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.0314</v>
+        <v>-0.005</v>
       </c>
       <c r="H36" t="n">
-        <v>2390</v>
+        <v>1007</v>
       </c>
       <c r="I36" t="n">
-        <v>44169</v>
+        <v>45144</v>
       </c>
       <c r="J36" t="n">
-        <v>46271.25</v>
+        <v>47707</v>
       </c>
       <c r="K36" t="n">
-        <v>47032.5</v>
+        <v>48446</v>
       </c>
       <c r="L36" t="n">
-        <v>47793.75</v>
+        <v>49185</v>
       </c>
       <c r="M36" t="n">
-        <v>49225.5</v>
+        <v>50836</v>
       </c>
       <c r="N36" t="n">
-        <v>50657.25</v>
+        <v>52487</v>
       </c>
       <c r="O36" t="n">
-        <v>50748</v>
+        <v>52314</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3532,13 +3526,11 @@
       </c>
       <c r="S36" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="n">
+        <v/>
       </c>
       <c r="U36" s="8" t="n">
         <v/>
@@ -3553,57 +3545,57 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>49324</v>
+        <v>49382</v>
       </c>
       <c r="C37" t="n">
-        <v>50043</v>
+        <v>50138</v>
       </c>
       <c r="D37" t="n">
-        <v>49036</v>
+        <v>48608</v>
       </c>
       <c r="E37" t="n">
-        <v>49392</v>
+        <v>49646</v>
       </c>
       <c r="F37" t="n">
-        <v>-249</v>
+        <v>254</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.005</v>
+        <v>0.0051</v>
       </c>
       <c r="H37" t="n">
-        <v>1007</v>
+        <v>1530</v>
       </c>
       <c r="I37" t="n">
-        <v>45144</v>
+        <v>48029</v>
       </c>
       <c r="J37" t="n">
-        <v>47707</v>
+        <v>48311.25</v>
       </c>
       <c r="K37" t="n">
-        <v>48446</v>
+        <v>48888.5</v>
       </c>
       <c r="L37" t="n">
-        <v>49185</v>
+        <v>49465.75</v>
       </c>
       <c r="M37" t="n">
-        <v>50836</v>
+        <v>49895.5</v>
       </c>
       <c r="N37" t="n">
-        <v>52487</v>
+        <v>50325.25</v>
       </c>
       <c r="O37" t="n">
-        <v>52314</v>
+        <v>51050</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3611,16 +3603,20 @@
       <c r="Q37" s="6" t="n">
         <v/>
       </c>
-      <c r="R37" s="6" t="n">
-        <v/>
+      <c r="R37" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S37" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
       </c>
-      <c r="T37" s="8" t="n">
-        <v/>
+      <c r="T37" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U37" s="8" t="n">
         <v/>
@@ -3642,50 +3638,50 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>49382</v>
+        <v>49705</v>
       </c>
       <c r="C38" t="n">
-        <v>50138</v>
+        <v>50238</v>
       </c>
       <c r="D38" t="n">
-        <v>48608</v>
+        <v>49016</v>
       </c>
       <c r="E38" t="n">
-        <v>49646</v>
+        <v>49691</v>
       </c>
       <c r="F38" t="n">
-        <v>254</v>
+        <v>45</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.0051</v>
+        <v>0.0009</v>
       </c>
       <c r="H38" t="n">
-        <v>1530</v>
+        <v>1222</v>
       </c>
       <c r="I38" t="n">
-        <v>48029</v>
+        <v>47078</v>
       </c>
       <c r="J38" t="n">
-        <v>48311.25</v>
+        <v>48252.5</v>
       </c>
       <c r="K38" t="n">
-        <v>48888.5</v>
+        <v>48881</v>
       </c>
       <c r="L38" t="n">
-        <v>49465.75</v>
+        <v>49509.5</v>
       </c>
       <c r="M38" t="n">
-        <v>49895.5</v>
+        <v>50411</v>
       </c>
       <c r="N38" t="n">
-        <v>50325.25</v>
+        <v>51312.5</v>
       </c>
       <c r="O38" t="n">
-        <v>51050</v>
+        <v>51668</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3693,20 +3689,16 @@
       <c r="Q38" s="6" t="n">
         <v/>
       </c>
-      <c r="R38" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R38" s="6" t="n">
+        <v/>
       </c>
       <c r="S38" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
       </c>
-      <c r="T38" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T38" s="8" t="n">
+        <v/>
       </c>
       <c r="U38" s="8" t="n">
         <v/>
@@ -3721,57 +3713,57 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>49705</v>
+        <v>49640</v>
       </c>
       <c r="C39" t="n">
-        <v>50238</v>
+        <v>50292</v>
       </c>
       <c r="D39" t="n">
-        <v>49016</v>
+        <v>49397</v>
       </c>
       <c r="E39" t="n">
-        <v>49691</v>
+        <v>49617</v>
       </c>
       <c r="F39" t="n">
-        <v>45</v>
+        <v>-74</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.0009</v>
+        <v>-0.0015</v>
       </c>
       <c r="H39" t="n">
-        <v>1222</v>
+        <v>895</v>
       </c>
       <c r="I39" t="n">
-        <v>47078</v>
+        <v>47794</v>
       </c>
       <c r="J39" t="n">
-        <v>48252.5</v>
+        <v>48501</v>
       </c>
       <c r="K39" t="n">
-        <v>48881</v>
+        <v>49080</v>
       </c>
       <c r="L39" t="n">
-        <v>49509.5</v>
+        <v>49659</v>
       </c>
       <c r="M39" t="n">
-        <v>50411</v>
+        <v>50302</v>
       </c>
       <c r="N39" t="n">
-        <v>51312.5</v>
+        <v>50945</v>
       </c>
       <c r="O39" t="n">
-        <v>51668</v>
+        <v>51460</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3782,9 +3774,9 @@
       <c r="R39" s="6" t="n">
         <v/>
       </c>
-      <c r="S39" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S39" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T39" s="8" t="n">
@@ -3803,57 +3795,57 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>49640</v>
+        <v>49464</v>
       </c>
       <c r="C40" t="n">
-        <v>50292</v>
+        <v>50920</v>
       </c>
       <c r="D40" t="n">
-        <v>49397</v>
+        <v>49152</v>
       </c>
       <c r="E40" t="n">
-        <v>49617</v>
+        <v>50662</v>
       </c>
       <c r="F40" t="n">
-        <v>-74</v>
+        <v>1045</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.0015</v>
+        <v>0.0211</v>
       </c>
       <c r="H40" t="n">
-        <v>895</v>
+        <v>1768</v>
       </c>
       <c r="I40" t="n">
-        <v>47794</v>
+        <v>48502</v>
       </c>
       <c r="J40" t="n">
-        <v>48501</v>
+        <v>48608.25</v>
       </c>
       <c r="K40" t="n">
-        <v>49080</v>
+        <v>49169.5</v>
       </c>
       <c r="L40" t="n">
-        <v>49659</v>
+        <v>49730.75</v>
       </c>
       <c r="M40" t="n">
-        <v>50302</v>
+        <v>50064.5</v>
       </c>
       <c r="N40" t="n">
-        <v>50945</v>
+        <v>50398.25</v>
       </c>
       <c r="O40" t="n">
-        <v>51460</v>
+        <v>51187</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3861,81 +3853,87 @@
       <c r="Q40" s="6" t="n">
         <v/>
       </c>
-      <c r="R40" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S40" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U40" s="8" t="n">
-        <v/>
+      <c r="R40" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S40" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U40" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V40" s="8" t="n">
         <v/>
       </c>
-      <c r="W40" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W40" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>49464</v>
+        <v>50776</v>
       </c>
       <c r="C41" t="n">
-        <v>50920</v>
+        <v>51209</v>
       </c>
       <c r="D41" t="n">
-        <v>49152</v>
+        <v>50386</v>
       </c>
       <c r="E41" t="n">
-        <v>50662</v>
+        <v>51077</v>
       </c>
       <c r="F41" t="n">
-        <v>1045</v>
+        <v>415</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.0211</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="H41" t="n">
-        <v>1768</v>
+        <v>823</v>
       </c>
       <c r="I41" t="n">
-        <v>48502</v>
+        <v>47384</v>
       </c>
       <c r="J41" t="n">
-        <v>48608.25</v>
+        <v>49207</v>
       </c>
       <c r="K41" t="n">
-        <v>49169.5</v>
+        <v>49778</v>
       </c>
       <c r="L41" t="n">
-        <v>49730.75</v>
+        <v>50349</v>
       </c>
       <c r="M41" t="n">
-        <v>50064.5</v>
+        <v>51546</v>
       </c>
       <c r="N41" t="n">
-        <v>50398.25</v>
+        <v>52743</v>
       </c>
       <c r="O41" t="n">
-        <v>51187</v>
+        <v>52688</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3943,10 +3941,8 @@
       <c r="Q41" s="6" t="n">
         <v/>
       </c>
-      <c r="R41" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R41" s="6" t="n">
+        <v/>
       </c>
       <c r="S41" s="7" t="inlineStr">
         <is>
@@ -3955,14 +3951,12 @@
       </c>
       <c r="T41" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U41" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U41" s="8" t="n">
+        <v/>
+      </c>
       <c r="V41" s="8" t="n">
         <v/>
       </c>
@@ -3971,59 +3965,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>50776</v>
+        <v>51128</v>
       </c>
       <c r="C42" t="n">
-        <v>51209</v>
+        <v>51849</v>
       </c>
       <c r="D42" t="n">
-        <v>50386</v>
+        <v>50736</v>
       </c>
       <c r="E42" t="n">
-        <v>51077</v>
+        <v>50936</v>
       </c>
       <c r="F42" t="n">
-        <v>415</v>
+        <v>-141</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.008200000000000001</v>
+        <v>-0.0028</v>
       </c>
       <c r="H42" t="n">
-        <v>823</v>
+        <v>1113</v>
       </c>
       <c r="I42" t="n">
-        <v>47384</v>
+        <v>49563</v>
       </c>
       <c r="J42" t="n">
-        <v>49207</v>
+        <v>50393.75</v>
       </c>
       <c r="K42" t="n">
-        <v>49778</v>
+        <v>50665.5</v>
       </c>
       <c r="L42" t="n">
-        <v>50349</v>
+        <v>50937.25</v>
       </c>
       <c r="M42" t="n">
-        <v>51546</v>
+        <v>51488.5</v>
       </c>
       <c r="N42" t="n">
-        <v>52743</v>
+        <v>52039.75</v>
       </c>
       <c r="O42" t="n">
-        <v>52688</v>
+        <v>52032</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4034,14 +4024,14 @@
       <c r="R42" s="6" t="n">
         <v/>
       </c>
-      <c r="S42" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S42" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T42" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U42" s="8" t="n">
@@ -4055,55 +4045,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr"/>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>51128</v>
+        <v>50796</v>
       </c>
       <c r="C43" t="n">
-        <v>51849</v>
+        <v>51443</v>
       </c>
       <c r="D43" t="n">
-        <v>50736</v>
+        <v>49758</v>
       </c>
       <c r="E43" t="n">
-        <v>50936</v>
+        <v>51227</v>
       </c>
       <c r="F43" t="n">
-        <v>-141</v>
+        <v>291</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.0028</v>
+        <v>0.0057</v>
       </c>
       <c r="H43" t="n">
-        <v>1113</v>
+        <v>1685</v>
       </c>
       <c r="I43" t="n">
-        <v>49563</v>
+        <v>49623</v>
       </c>
       <c r="J43" t="n">
-        <v>50393.75</v>
+        <v>49644.75</v>
       </c>
       <c r="K43" t="n">
-        <v>50665.5</v>
+        <v>50379.5</v>
       </c>
       <c r="L43" t="n">
-        <v>50937.25</v>
+        <v>51114.25</v>
       </c>
       <c r="M43" t="n">
-        <v>51488.5</v>
+        <v>51492.5</v>
       </c>
       <c r="N43" t="n">
-        <v>52039.75</v>
+        <v>51870.75</v>
       </c>
       <c r="O43" t="n">
-        <v>52032</v>
+        <v>52962</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4111,19 +4105,19 @@
       <c r="Q43" s="6" t="n">
         <v/>
       </c>
-      <c r="R43" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S43" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="inlineStr">
+      <c r="R43" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="S43" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="n">
+        <v/>
+      </c>
       <c r="U43" s="8" t="n">
         <v/>
       </c>
@@ -4137,57 +4131,57 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>50796</v>
+        <v>51450</v>
       </c>
       <c r="C44" t="n">
-        <v>51443</v>
+        <v>52300</v>
       </c>
       <c r="D44" t="n">
-        <v>49758</v>
+        <v>51420</v>
       </c>
       <c r="E44" t="n">
-        <v>51227</v>
+        <v>51888</v>
       </c>
       <c r="F44" t="n">
-        <v>291</v>
+        <v>661</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.0057</v>
+        <v>0.0129</v>
       </c>
       <c r="H44" t="n">
-        <v>1685</v>
+        <v>880</v>
       </c>
       <c r="I44" t="n">
-        <v>49623</v>
+        <v>48073</v>
       </c>
       <c r="J44" t="n">
-        <v>49644.75</v>
+        <v>49855.25</v>
       </c>
       <c r="K44" t="n">
-        <v>50379.5</v>
+        <v>50384.5</v>
       </c>
       <c r="L44" t="n">
-        <v>51114.25</v>
+        <v>50913.75</v>
       </c>
       <c r="M44" t="n">
-        <v>51492.5</v>
+        <v>52069.5</v>
       </c>
       <c r="N44" t="n">
-        <v>51870.75</v>
+        <v>53225.25</v>
       </c>
       <c r="O44" t="n">
-        <v>52962</v>
+        <v>53128</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4195,18 +4189,18 @@
       <c r="Q44" s="6" t="n">
         <v/>
       </c>
-      <c r="R44" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R44" s="6" t="n">
+        <v/>
       </c>
       <c r="S44" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U44" s="8" t="n">
         <v/>
@@ -4219,59 +4213,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>51450</v>
+        <v>51870</v>
       </c>
       <c r="C45" t="n">
-        <v>52300</v>
+        <v>53097</v>
       </c>
       <c r="D45" t="n">
-        <v>51420</v>
+        <v>51691</v>
       </c>
       <c r="E45" t="n">
-        <v>51888</v>
+        <v>52209</v>
       </c>
       <c r="F45" t="n">
-        <v>661</v>
+        <v>321</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.0129</v>
+        <v>0.0062</v>
       </c>
       <c r="H45" t="n">
-        <v>880</v>
+        <v>1406</v>
       </c>
       <c r="I45" t="n">
-        <v>48073</v>
+        <v>50540</v>
       </c>
       <c r="J45" t="n">
-        <v>49855.25</v>
+        <v>51022</v>
       </c>
       <c r="K45" t="n">
-        <v>50384.5</v>
+        <v>51448</v>
       </c>
       <c r="L45" t="n">
-        <v>50913.75</v>
+        <v>51874</v>
       </c>
       <c r="M45" t="n">
-        <v>52069.5</v>
+        <v>52328</v>
       </c>
       <c r="N45" t="n">
-        <v>53225.25</v>
+        <v>52782</v>
       </c>
       <c r="O45" t="n">
-        <v>53128</v>
+        <v>53180</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4292,8 +4282,10 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U45" s="8" t="n">
-        <v/>
+      <c r="U45" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V45" s="8" t="n">
         <v/>
@@ -4308,50 +4300,50 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>51870</v>
+        <v>52183</v>
       </c>
       <c r="C46" t="n">
-        <v>53097</v>
+        <v>53400</v>
       </c>
       <c r="D46" t="n">
-        <v>51691</v>
+        <v>52179</v>
       </c>
       <c r="E46" t="n">
-        <v>52209</v>
+        <v>53162</v>
       </c>
       <c r="F46" t="n">
-        <v>321</v>
+        <v>953</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.0062</v>
+        <v>0.0183</v>
       </c>
       <c r="H46" t="n">
-        <v>1406</v>
+        <v>1221</v>
       </c>
       <c r="I46" t="n">
-        <v>50540</v>
+        <v>50285</v>
       </c>
       <c r="J46" t="n">
-        <v>51022</v>
+        <v>50710.5</v>
       </c>
       <c r="K46" t="n">
-        <v>51448</v>
+        <v>51506</v>
       </c>
       <c r="L46" t="n">
-        <v>51874</v>
+        <v>52301.5</v>
       </c>
       <c r="M46" t="n">
-        <v>52328</v>
+        <v>52912</v>
       </c>
       <c r="N46" t="n">
-        <v>52782</v>
+        <v>53522.5</v>
       </c>
       <c r="O46" t="n">
-        <v>53180</v>
+        <v>54503</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4372,10 +4364,8 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U46" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U46" s="8" t="n">
+        <v/>
       </c>
       <c r="V46" s="8" t="n">
         <v/>
@@ -4390,50 +4380,50 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>52183</v>
+        <v>53230</v>
       </c>
       <c r="C47" t="n">
-        <v>53400</v>
+        <v>53656</v>
       </c>
       <c r="D47" t="n">
-        <v>52179</v>
+        <v>52343</v>
       </c>
       <c r="E47" t="n">
-        <v>53162</v>
+        <v>52906</v>
       </c>
       <c r="F47" t="n">
-        <v>953</v>
+        <v>-256</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.0183</v>
+        <v>-0.0048</v>
       </c>
       <c r="H47" t="n">
-        <v>1221</v>
+        <v>1313</v>
       </c>
       <c r="I47" t="n">
-        <v>50285</v>
+        <v>50958</v>
       </c>
       <c r="J47" t="n">
-        <v>50710.5</v>
+        <v>52127.25</v>
       </c>
       <c r="K47" t="n">
-        <v>51506</v>
+        <v>52551.5</v>
       </c>
       <c r="L47" t="n">
-        <v>52301.5</v>
+        <v>52975.75</v>
       </c>
       <c r="M47" t="n">
-        <v>52912</v>
+        <v>53772.5</v>
       </c>
       <c r="N47" t="n">
-        <v>53522.5</v>
+        <v>54569.25</v>
       </c>
       <c r="O47" t="n">
-        <v>54503</v>
+        <v>54621</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4441,18 +4431,18 @@
       <c r="Q47" s="6" t="n">
         <v/>
       </c>
-      <c r="R47" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S47" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R47" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S47" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="n">
+        <v/>
       </c>
       <c r="U47" s="8" t="n">
         <v/>
@@ -4465,55 +4455,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr"/>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>53230</v>
+        <v>52844</v>
       </c>
       <c r="C48" t="n">
-        <v>53656</v>
+        <v>53113</v>
       </c>
       <c r="D48" t="n">
-        <v>52343</v>
+        <v>52174</v>
       </c>
       <c r="E48" t="n">
-        <v>52906</v>
+        <v>52375</v>
       </c>
       <c r="F48" t="n">
-        <v>-256</v>
+        <v>-531</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0.0048</v>
+        <v>-0.01</v>
       </c>
       <c r="H48" t="n">
-        <v>1313</v>
+        <v>939</v>
       </c>
       <c r="I48" t="n">
-        <v>50958</v>
+        <v>51030</v>
       </c>
       <c r="J48" t="n">
-        <v>52127.25</v>
+        <v>51546.25</v>
       </c>
       <c r="K48" t="n">
-        <v>52551.5</v>
+        <v>52249.5</v>
       </c>
       <c r="L48" t="n">
-        <v>52975.75</v>
+        <v>52952.75</v>
       </c>
       <c r="M48" t="n">
-        <v>53772.5</v>
+        <v>53562.5</v>
       </c>
       <c r="N48" t="n">
-        <v>54569.25</v>
+        <v>54172.25</v>
       </c>
       <c r="O48" t="n">
-        <v>54621</v>
+        <v>54969</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4523,12 +4517,12 @@
       </c>
       <c r="R48" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S48" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T48" s="8" t="n">
@@ -4547,57 +4541,57 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>52844</v>
+        <v>52300</v>
       </c>
       <c r="C49" t="n">
-        <v>53113</v>
+        <v>52721</v>
       </c>
       <c r="D49" t="n">
-        <v>52174</v>
+        <v>51720</v>
       </c>
       <c r="E49" t="n">
-        <v>52375</v>
+        <v>52124</v>
       </c>
       <c r="F49" t="n">
-        <v>-531</v>
+        <v>-251</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.01</v>
+        <v>-0.0048</v>
       </c>
       <c r="H49" t="n">
-        <v>939</v>
+        <v>1001</v>
       </c>
       <c r="I49" t="n">
-        <v>51030</v>
+        <v>51235</v>
       </c>
       <c r="J49" t="n">
-        <v>51546.25</v>
+        <v>51301.75</v>
       </c>
       <c r="K49" t="n">
-        <v>52249.5</v>
+        <v>51905.5</v>
       </c>
       <c r="L49" t="n">
-        <v>52952.75</v>
+        <v>52509.25</v>
       </c>
       <c r="M49" t="n">
-        <v>53562.5</v>
+        <v>52844.5</v>
       </c>
       <c r="N49" t="n">
-        <v>54172.25</v>
+        <v>53179.75</v>
       </c>
       <c r="O49" t="n">
-        <v>54969</v>
+        <v>54052</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4638,50 +4632,50 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>52300</v>
+        <v>52299</v>
       </c>
       <c r="C50" t="n">
-        <v>52721</v>
+        <v>53105</v>
       </c>
       <c r="D50" t="n">
-        <v>51720</v>
+        <v>51630</v>
       </c>
       <c r="E50" t="n">
-        <v>52124</v>
+        <v>52635</v>
       </c>
       <c r="F50" t="n">
-        <v>-251</v>
+        <v>511</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.0048</v>
+        <v>0.0098</v>
       </c>
       <c r="H50" t="n">
-        <v>1001</v>
+        <v>1475</v>
       </c>
       <c r="I50" t="n">
-        <v>51235</v>
+        <v>50719</v>
       </c>
       <c r="J50" t="n">
-        <v>51301.75</v>
+        <v>51074.75</v>
       </c>
       <c r="K50" t="n">
-        <v>51905.5</v>
+        <v>51623.5</v>
       </c>
       <c r="L50" t="n">
-        <v>52509.25</v>
+        <v>52172.25</v>
       </c>
       <c r="M50" t="n">
-        <v>52844.5</v>
+        <v>52624.5</v>
       </c>
       <c r="N50" t="n">
-        <v>53179.75</v>
+        <v>53076.75</v>
       </c>
       <c r="O50" t="n">
-        <v>54052</v>
+        <v>53722</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4689,21 +4683,23 @@
       <c r="Q50" s="6" t="n">
         <v/>
       </c>
-      <c r="R50" s="6" t="inlineStr">
+      <c r="R50" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S50" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T50" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S50" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T50" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U50" s="8" t="n">
-        <v/>
+      <c r="U50" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V50" s="8" t="n">
         <v/>
@@ -4715,57 +4711,57 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>52299</v>
+        <v>52780</v>
       </c>
       <c r="C51" t="n">
-        <v>53105</v>
+        <v>54884</v>
       </c>
       <c r="D51" t="n">
-        <v>51630</v>
+        <v>52777</v>
       </c>
       <c r="E51" t="n">
-        <v>52635</v>
+        <v>54152</v>
       </c>
       <c r="F51" t="n">
-        <v>511</v>
+        <v>1517</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.0098</v>
+        <v>0.0288</v>
       </c>
       <c r="H51" t="n">
-        <v>1475</v>
+        <v>2107</v>
       </c>
       <c r="I51" t="n">
-        <v>50719</v>
+        <v>50155</v>
       </c>
       <c r="J51" t="n">
-        <v>51074.75</v>
+        <v>51293.75</v>
       </c>
       <c r="K51" t="n">
-        <v>51623.5</v>
+        <v>51897.5</v>
       </c>
       <c r="L51" t="n">
-        <v>52172.25</v>
+        <v>52501.25</v>
       </c>
       <c r="M51" t="n">
-        <v>52624.5</v>
+        <v>53372.5</v>
       </c>
       <c r="N51" t="n">
-        <v>53076.75</v>
+        <v>54243.75</v>
       </c>
       <c r="O51" t="n">
-        <v>53722</v>
+        <v>54580</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4783,75 +4779,73 @@
       </c>
       <c r="T51" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U51" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U51" s="8" t="inlineStr">
+      <c r="V51" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="V51" s="8" t="n">
-        <v/>
-      </c>
       <c r="W51" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>52780</v>
+        <v>54133</v>
       </c>
       <c r="C52" t="n">
-        <v>54884</v>
+        <v>54336</v>
       </c>
       <c r="D52" t="n">
-        <v>52777</v>
+        <v>53715</v>
       </c>
       <c r="E52" t="n">
-        <v>54152</v>
+        <v>53807</v>
       </c>
       <c r="F52" t="n">
-        <v>1517</v>
+        <v>-345</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.0288</v>
+        <v>-0.0064</v>
       </c>
       <c r="H52" t="n">
-        <v>2107</v>
+        <v>621</v>
       </c>
       <c r="I52" t="n">
-        <v>50155</v>
+        <v>50670</v>
       </c>
       <c r="J52" t="n">
-        <v>51293.75</v>
+        <v>52205.75</v>
       </c>
       <c r="K52" t="n">
-        <v>51897.5</v>
+        <v>53098.5</v>
       </c>
       <c r="L52" t="n">
-        <v>52501.25</v>
+        <v>53991.25</v>
       </c>
       <c r="M52" t="n">
-        <v>53372.5</v>
+        <v>55205.5</v>
       </c>
       <c r="N52" t="n">
-        <v>54243.75</v>
+        <v>56419.75</v>
       </c>
       <c r="O52" t="n">
-        <v>54580</v>
+        <v>56991</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4862,93 +4856,97 @@
       <c r="R52" s="6" t="n">
         <v/>
       </c>
-      <c r="S52" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T52" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U52" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V52" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S52" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T52" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U52" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V52" s="8" t="n">
+        <v/>
       </c>
       <c r="W52" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr"/>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>54133</v>
+        <v>53790</v>
       </c>
       <c r="C53" t="n">
-        <v>54336</v>
+        <v>53840</v>
       </c>
       <c r="D53" t="n">
-        <v>53715</v>
+        <v>52812</v>
       </c>
       <c r="E53" t="n">
-        <v>53807</v>
+        <v>53353</v>
       </c>
       <c r="F53" t="n">
-        <v>-345</v>
+        <v>-454</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.0064</v>
+        <v>-0.008399999999999999</v>
       </c>
       <c r="H53" t="n">
-        <v>621</v>
+        <v>1028</v>
       </c>
       <c r="I53" t="n">
-        <v>50670</v>
+        <v>53094</v>
       </c>
       <c r="J53" t="n">
-        <v>52205.75</v>
+        <v>53076.75</v>
       </c>
       <c r="K53" t="n">
-        <v>53098.5</v>
+        <v>53496.5</v>
       </c>
       <c r="L53" t="n">
-        <v>53991.25</v>
+        <v>53916.25</v>
       </c>
       <c r="M53" t="n">
-        <v>55205.5</v>
+        <v>54117.5</v>
       </c>
       <c r="N53" t="n">
-        <v>56419.75</v>
+        <v>54318.75</v>
       </c>
       <c r="O53" t="n">
-        <v>56991</v>
-      </c>
-      <c r="P53" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q53" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R53" s="6" t="n">
-        <v/>
+        <v>54957</v>
+      </c>
+      <c r="P53" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q53" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R53" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S53" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T53" s="8" t="n">
@@ -4967,76 +4965,70 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>53790</v>
+        <v>53367</v>
       </c>
       <c r="C54" t="n">
-        <v>53840</v>
+        <v>53862</v>
       </c>
       <c r="D54" t="n">
-        <v>52812</v>
+        <v>53210</v>
       </c>
       <c r="E54" t="n">
-        <v>53353</v>
+        <v>53584</v>
       </c>
       <c r="F54" t="n">
-        <v>-454</v>
+        <v>231</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.008399999999999999</v>
+        <v>0.0043</v>
       </c>
       <c r="H54" t="n">
-        <v>1028</v>
+        <v>652</v>
       </c>
       <c r="I54" t="n">
-        <v>53094</v>
+        <v>51784</v>
       </c>
       <c r="J54" t="n">
-        <v>53076.75</v>
+        <v>52338.5</v>
       </c>
       <c r="K54" t="n">
-        <v>53496.5</v>
+        <v>52839</v>
       </c>
       <c r="L54" t="n">
-        <v>53916.25</v>
+        <v>53339.5</v>
       </c>
       <c r="M54" t="n">
-        <v>54117.5</v>
+        <v>53867</v>
       </c>
       <c r="N54" t="n">
-        <v>54318.75</v>
+        <v>54394.5</v>
       </c>
       <c r="O54" t="n">
-        <v>54957</v>
-      </c>
-      <c r="P54" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q54" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R54" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S54" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>54868</v>
+      </c>
+      <c r="P54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S54" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T54" s="8" t="n">
@@ -5053,72 +5045,72 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>53367</v>
+        <v>53664</v>
       </c>
       <c r="C55" t="n">
-        <v>53862</v>
+        <v>53827</v>
       </c>
       <c r="D55" t="n">
-        <v>53210</v>
+        <v>52720</v>
       </c>
       <c r="E55" t="n">
-        <v>53584</v>
+        <v>53440</v>
       </c>
       <c r="F55" t="n">
-        <v>231</v>
+        <v>-144</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.0043</v>
+        <v>-0.0027</v>
       </c>
       <c r="H55" t="n">
-        <v>652</v>
+        <v>1107</v>
       </c>
       <c r="I55" t="n">
-        <v>51784</v>
+        <v>52558</v>
       </c>
       <c r="J55" t="n">
-        <v>52338.5</v>
+        <v>52956</v>
       </c>
       <c r="K55" t="n">
-        <v>52839</v>
+        <v>53258</v>
       </c>
       <c r="L55" t="n">
-        <v>53339.5</v>
+        <v>53560</v>
       </c>
       <c r="M55" t="n">
-        <v>53867</v>
+        <v>53910</v>
       </c>
       <c r="N55" t="n">
-        <v>54394.5</v>
+        <v>54260</v>
       </c>
       <c r="O55" t="n">
-        <v>54868</v>
+        <v>54514</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
       </c>
-      <c r="Q55" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R55" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S55" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="Q55" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R55" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S55" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T55" s="8" t="n">
@@ -5135,72 +5127,76 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr"/>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>53664</v>
+        <v>53261</v>
       </c>
       <c r="C56" t="n">
-        <v>53827</v>
+        <v>53336</v>
       </c>
       <c r="D56" t="n">
-        <v>52720</v>
+        <v>51992</v>
       </c>
       <c r="E56" t="n">
-        <v>53440</v>
+        <v>52585</v>
       </c>
       <c r="F56" t="n">
-        <v>-144</v>
+        <v>-855</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.0027</v>
+        <v>-0.016</v>
       </c>
       <c r="H56" t="n">
-        <v>1107</v>
+        <v>1344</v>
       </c>
       <c r="I56" t="n">
-        <v>52558</v>
+        <v>51613</v>
       </c>
       <c r="J56" t="n">
-        <v>52956</v>
+        <v>52416.25</v>
       </c>
       <c r="K56" t="n">
-        <v>53258</v>
+        <v>52886.5</v>
       </c>
       <c r="L56" t="n">
-        <v>53560</v>
+        <v>53356.75</v>
       </c>
       <c r="M56" t="n">
-        <v>53910</v>
+        <v>53993.5</v>
       </c>
       <c r="N56" t="n">
-        <v>54260</v>
+        <v>54630.25</v>
       </c>
       <c r="O56" t="n">
-        <v>54514</v>
+        <v>54934</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
       </c>
       <c r="Q56" s="6" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R56" s="6" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R56" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S56" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T56" s="8" t="n">
@@ -5226,64 +5222,62 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>53261</v>
+        <v>52376</v>
       </c>
       <c r="C57" t="n">
-        <v>53336</v>
+        <v>52672</v>
       </c>
       <c r="D57" t="n">
-        <v>51992</v>
+        <v>51209</v>
       </c>
       <c r="E57" t="n">
-        <v>52585</v>
+        <v>52079</v>
       </c>
       <c r="F57" t="n">
-        <v>-855</v>
+        <v>-506</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.016</v>
+        <v>-0.009599999999999999</v>
       </c>
       <c r="H57" t="n">
-        <v>1344</v>
+        <v>1463</v>
       </c>
       <c r="I57" t="n">
-        <v>51613</v>
+        <v>50648</v>
       </c>
       <c r="J57" t="n">
-        <v>52416.25</v>
+        <v>51201.5</v>
       </c>
       <c r="K57" t="n">
-        <v>52886.5</v>
+        <v>51913</v>
       </c>
       <c r="L57" t="n">
-        <v>53356.75</v>
+        <v>52624.5</v>
       </c>
       <c r="M57" t="n">
-        <v>53993.5</v>
+        <v>53257</v>
       </c>
       <c r="N57" t="n">
-        <v>54630.25</v>
+        <v>53889.5</v>
       </c>
       <c r="O57" t="n">
-        <v>54934</v>
+        <v>54680</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
       </c>
-      <c r="Q57" s="6" t="inlineStr">
+      <c r="Q57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R57" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R57" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S57" s="10" t="inlineStr">
         <is>
           <t>↓</t>
@@ -5304,90 +5298,6 @@
         </is>
       </c>
       <c r="X57" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="B58" t="n">
-        <v>52376</v>
-      </c>
-      <c r="C58" t="n">
-        <v>52672</v>
-      </c>
-      <c r="D58" t="n">
-        <v>51209</v>
-      </c>
-      <c r="E58" t="n">
-        <v>52205</v>
-      </c>
-      <c r="F58" t="n">
-        <v>-380</v>
-      </c>
-      <c r="G58" s="5" t="n">
-        <v>-0.0072</v>
-      </c>
-      <c r="H58" t="n">
-        <v>1463</v>
-      </c>
-      <c r="I58" t="n">
-        <v>50648</v>
-      </c>
-      <c r="J58" t="n">
-        <v>51201.5</v>
-      </c>
-      <c r="K58" t="n">
-        <v>51913</v>
-      </c>
-      <c r="L58" t="n">
-        <v>52624.5</v>
-      </c>
-      <c r="M58" t="n">
-        <v>53257</v>
-      </c>
-      <c r="N58" t="n">
-        <v>53889.5</v>
-      </c>
-      <c r="O58" t="n">
-        <v>54680</v>
-      </c>
-      <c r="P58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R58" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S58" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W58" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X58" t="inlineStr">
         <is>
           <t>強警訊</t>
         </is>

--- a/three_gate/analysis/YM_weekly.xlsx
+++ b/three_gate/analysis/YM_weekly.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X57"/>
+  <dimension ref="A1:X58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5235,13 +5235,13 @@
         <v>51209</v>
       </c>
       <c r="E57" t="n">
-        <v>52079</v>
+        <v>51761</v>
       </c>
       <c r="F57" t="n">
-        <v>-506</v>
+        <v>-824</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.009599999999999999</v>
+        <v>-0.0157</v>
       </c>
       <c r="H57" t="n">
         <v>1463</v>
@@ -5300,6 +5300,90 @@
       <c r="X57" t="inlineStr">
         <is>
           <t>強警訊</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>52470</v>
+      </c>
+      <c r="C58" t="n">
+        <v>52473</v>
+      </c>
+      <c r="D58" t="n">
+        <v>52452</v>
+      </c>
+      <c r="E58" t="n">
+        <v>52468</v>
+      </c>
+      <c r="F58" t="n">
+        <v>707</v>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v>0.0137</v>
+      </c>
+      <c r="H58" t="n">
+        <v>21</v>
+      </c>
+      <c r="I58" t="n">
+        <v>49746</v>
+      </c>
+      <c r="J58" t="n">
+        <v>50208.25</v>
+      </c>
+      <c r="K58" t="n">
+        <v>51029.5</v>
+      </c>
+      <c r="L58" t="n">
+        <v>51850.75</v>
+      </c>
+      <c r="M58" t="n">
+        <v>52492.5</v>
+      </c>
+      <c r="N58" t="n">
+        <v>53134.25</v>
+      </c>
+      <c r="O58" t="n">
+        <v>54135</v>
+      </c>
+      <c r="P58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S58" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W58" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/YM_weekly.xlsx
+++ b/three_gate/analysis/YM_weekly.xlsx
@@ -5310,25 +5310,25 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>52470</v>
+        <v>52085</v>
       </c>
       <c r="C58" t="n">
-        <v>52473</v>
+        <v>52844</v>
       </c>
       <c r="D58" t="n">
-        <v>52452</v>
+        <v>52080</v>
       </c>
       <c r="E58" t="n">
-        <v>52468</v>
+        <v>52423</v>
       </c>
       <c r="F58" t="n">
-        <v>707</v>
+        <v>662</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0137</v>
+        <v>0.0128</v>
       </c>
       <c r="H58" t="n">
-        <v>21</v>
+        <v>764</v>
       </c>
       <c r="I58" t="n">
         <v>49746</v>
@@ -5381,11 +5381,7 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X58" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/YM_weekly.xlsx
+++ b/three_gate/analysis/YM_weekly.xlsx
@@ -5319,13 +5319,13 @@
         <v>52080</v>
       </c>
       <c r="E58" t="n">
-        <v>52423</v>
+        <v>52228</v>
       </c>
       <c r="F58" t="n">
-        <v>662</v>
+        <v>467</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0128</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="H58" t="n">
         <v>764</v>

--- a/three_gate/analysis/YM_weekly.xlsx
+++ b/three_gate/analysis/YM_weekly.xlsx
@@ -5313,22 +5313,22 @@
         <v>52085</v>
       </c>
       <c r="C58" t="n">
-        <v>52844</v>
+        <v>52557</v>
       </c>
       <c r="D58" t="n">
         <v>52080</v>
       </c>
       <c r="E58" t="n">
-        <v>52228</v>
+        <v>52275</v>
       </c>
       <c r="F58" t="n">
-        <v>467</v>
+        <v>514</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.009900000000000001</v>
       </c>
       <c r="H58" t="n">
-        <v>764</v>
+        <v>477</v>
       </c>
       <c r="I58" t="n">
         <v>49746</v>
@@ -5381,7 +5381,11 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr"/>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/YM_weekly.xlsx
+++ b/three_gate/analysis/YM_weekly.xlsx
@@ -5319,13 +5319,13 @@
         <v>52080</v>
       </c>
       <c r="E58" t="n">
-        <v>52275</v>
+        <v>52269</v>
       </c>
       <c r="F58" t="n">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.009900000000000001</v>
+        <v>0.0098</v>
       </c>
       <c r="H58" t="n">
         <v>477</v>

--- a/three_gate/analysis/YM_weekly.xlsx
+++ b/three_gate/analysis/YM_weekly.xlsx
@@ -5319,13 +5319,13 @@
         <v>52080</v>
       </c>
       <c r="E58" t="n">
-        <v>52269</v>
+        <v>52288</v>
       </c>
       <c r="F58" t="n">
-        <v>508</v>
+        <v>527</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0098</v>
+        <v>0.0102</v>
       </c>
       <c r="H58" t="n">
         <v>477</v>

--- a/three_gate/analysis/YM_weekly.xlsx
+++ b/three_gate/analysis/YM_weekly.xlsx
@@ -5319,13 +5319,13 @@
         <v>52080</v>
       </c>
       <c r="E58" t="n">
-        <v>52288</v>
+        <v>52302</v>
       </c>
       <c r="F58" t="n">
-        <v>527</v>
+        <v>541</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0102</v>
+        <v>0.0105</v>
       </c>
       <c r="H58" t="n">
         <v>477</v>

--- a/three_gate/analysis/YM_weekly.xlsx
+++ b/three_gate/analysis/YM_weekly.xlsx
@@ -5319,13 +5319,13 @@
         <v>52080</v>
       </c>
       <c r="E58" t="n">
-        <v>52302</v>
+        <v>52331</v>
       </c>
       <c r="F58" t="n">
-        <v>541</v>
+        <v>570</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0105</v>
+        <v>0.011</v>
       </c>
       <c r="H58" t="n">
         <v>477</v>

--- a/three_gate/analysis/YM_weekly.xlsx
+++ b/three_gate/analysis/YM_weekly.xlsx
@@ -5313,22 +5313,22 @@
         <v>52085</v>
       </c>
       <c r="C58" t="n">
-        <v>52557</v>
+        <v>52844</v>
       </c>
       <c r="D58" t="n">
-        <v>52080</v>
+        <v>52076</v>
       </c>
       <c r="E58" t="n">
-        <v>52331</v>
+        <v>52081</v>
       </c>
       <c r="F58" t="n">
-        <v>570</v>
+        <v>320</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.011</v>
+        <v>0.0062</v>
       </c>
       <c r="H58" t="n">
-        <v>477</v>
+        <v>768</v>
       </c>
       <c r="I58" t="n">
         <v>49746</v>
@@ -5362,12 +5362,12 @@
       </c>
       <c r="S58" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T58" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U58" s="8" t="n">
@@ -5381,11 +5381,7 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X58" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/YM_weekly.xlsx
+++ b/three_gate/analysis/YM_weekly.xlsx
@@ -5316,19 +5316,19 @@
         <v>52844</v>
       </c>
       <c r="D58" t="n">
-        <v>52076</v>
+        <v>51878</v>
       </c>
       <c r="E58" t="n">
-        <v>52081</v>
+        <v>51889</v>
       </c>
       <c r="F58" t="n">
-        <v>320</v>
+        <v>128</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0062</v>
+        <v>0.0025</v>
       </c>
       <c r="H58" t="n">
-        <v>768</v>
+        <v>966</v>
       </c>
       <c r="I58" t="n">
         <v>49746</v>

--- a/three_gate/analysis/YM_weekly.xlsx
+++ b/three_gate/analysis/YM_weekly.xlsx
@@ -5316,19 +5316,19 @@
         <v>52844</v>
       </c>
       <c r="D58" t="n">
-        <v>51878</v>
+        <v>51654</v>
       </c>
       <c r="E58" t="n">
-        <v>51889</v>
+        <v>51669</v>
       </c>
       <c r="F58" t="n">
-        <v>128</v>
+        <v>-92</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0025</v>
+        <v>-0.0018</v>
       </c>
       <c r="H58" t="n">
-        <v>966</v>
+        <v>1190</v>
       </c>
       <c r="I58" t="n">
         <v>49746</v>
@@ -5360,9 +5360,9 @@
       <c r="R58" s="6" t="n">
         <v/>
       </c>
-      <c r="S58" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S58" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T58" s="8" t="inlineStr">
@@ -5381,7 +5381,11 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr"/>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/YM_weekly.xlsx
+++ b/three_gate/analysis/YM_weekly.xlsx
@@ -104,14 +104,14 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X58"/>
+  <dimension ref="A1:X57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,63 +634,67 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>45721</v>
+        <v>45685</v>
       </c>
       <c r="C2" t="n">
-        <v>45801</v>
+        <v>45832</v>
       </c>
       <c r="D2" t="n">
-        <v>45183</v>
+        <v>45000</v>
       </c>
       <c r="E2" t="n">
-        <v>45601</v>
+        <v>45459</v>
       </c>
       <c r="F2" t="n">
-        <v>-114</v>
+        <v>-142</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>-0.0025</v>
+        <v>-0.0031</v>
       </c>
       <c r="H2" t="n">
-        <v>618</v>
+        <v>832</v>
       </c>
       <c r="I2" t="n">
-        <v>43443</v>
+        <v>44565</v>
       </c>
       <c r="J2" t="n">
-        <v>44752.75</v>
+        <v>45037.5</v>
       </c>
       <c r="K2" t="n">
-        <v>45115.5</v>
+        <v>45292</v>
       </c>
       <c r="L2" t="n">
-        <v>45478.25</v>
+        <v>45546.5</v>
       </c>
       <c r="M2" t="n">
-        <v>46314.5</v>
+        <v>45910</v>
       </c>
       <c r="N2" t="n">
-        <v>47150.75</v>
+        <v>46273.5</v>
       </c>
       <c r="O2" t="n">
-        <v>47040</v>
+        <v>46419</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
       </c>
-      <c r="Q2" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R2" s="6" t="n">
-        <v/>
+      <c r="Q2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T2" s="8" t="n">
@@ -716,71 +720,69 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>45685</v>
+        <v>45475</v>
       </c>
       <c r="C3" t="n">
-        <v>45832</v>
+        <v>46176</v>
       </c>
       <c r="D3" t="n">
-        <v>45000</v>
+        <v>45321</v>
       </c>
       <c r="E3" t="n">
-        <v>45459</v>
+        <v>45854</v>
       </c>
       <c r="F3" t="n">
-        <v>-142</v>
+        <v>395</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.0031</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="H3" t="n">
-        <v>832</v>
+        <v>855</v>
       </c>
       <c r="I3" t="n">
-        <v>44565</v>
+        <v>44168</v>
       </c>
       <c r="J3" t="n">
-        <v>45037.5</v>
+        <v>44648.5</v>
       </c>
       <c r="K3" t="n">
-        <v>45292</v>
+        <v>45043</v>
       </c>
       <c r="L3" t="n">
-        <v>45546.5</v>
+        <v>45437.5</v>
       </c>
       <c r="M3" t="n">
-        <v>45910</v>
+        <v>45875</v>
       </c>
       <c r="N3" t="n">
-        <v>46273.5</v>
+        <v>46312.5</v>
       </c>
       <c r="O3" t="n">
-        <v>46419</v>
+        <v>46664</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
       </c>
-      <c r="Q3" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R3" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q3" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R3" s="6" t="n">
+        <v/>
       </c>
       <c r="S3" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U3" s="8" t="n">
         <v/>
@@ -793,59 +795,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>45475</v>
+        <v>45860</v>
       </c>
       <c r="C4" t="n">
-        <v>46176</v>
+        <v>46379</v>
       </c>
       <c r="D4" t="n">
-        <v>45321</v>
+        <v>45680</v>
       </c>
       <c r="E4" t="n">
-        <v>45854</v>
+        <v>46328</v>
       </c>
       <c r="F4" t="n">
-        <v>395</v>
+        <v>474</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.008699999999999999</v>
+        <v>0.0103</v>
       </c>
       <c r="H4" t="n">
-        <v>855</v>
+        <v>699</v>
       </c>
       <c r="I4" t="n">
-        <v>44168</v>
+        <v>44466</v>
       </c>
       <c r="J4" t="n">
-        <v>44648.5</v>
+        <v>45051.75</v>
       </c>
       <c r="K4" t="n">
-        <v>45043</v>
+        <v>45426.5</v>
       </c>
       <c r="L4" t="n">
-        <v>45437.5</v>
+        <v>45801.25</v>
       </c>
       <c r="M4" t="n">
-        <v>45875</v>
+        <v>46281.5</v>
       </c>
       <c r="N4" t="n">
-        <v>46312.5</v>
+        <v>46761.75</v>
       </c>
       <c r="O4" t="n">
-        <v>46664</v>
+        <v>47031</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -856,7 +854,7 @@
       <c r="R4" s="6" t="n">
         <v/>
       </c>
-      <c r="S4" s="7" t="inlineStr">
+      <c r="S4" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -882,50 +880,50 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>45860</v>
+        <v>46605</v>
       </c>
       <c r="C5" t="n">
-        <v>46379</v>
+        <v>47055</v>
       </c>
       <c r="D5" t="n">
-        <v>45680</v>
+        <v>46098</v>
       </c>
       <c r="E5" t="n">
-        <v>46328</v>
+        <v>46556</v>
       </c>
       <c r="F5" t="n">
-        <v>474</v>
+        <v>228</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.0103</v>
+        <v>0.0049</v>
       </c>
       <c r="H5" t="n">
-        <v>699</v>
+        <v>957</v>
       </c>
       <c r="I5" t="n">
-        <v>44466</v>
+        <v>44981</v>
       </c>
       <c r="J5" t="n">
-        <v>45051.75</v>
+        <v>45778.25</v>
       </c>
       <c r="K5" t="n">
-        <v>45426.5</v>
+        <v>45978.5</v>
       </c>
       <c r="L5" t="n">
-        <v>45801.25</v>
+        <v>46178.75</v>
       </c>
       <c r="M5" t="n">
-        <v>46281.5</v>
+        <v>46677.5</v>
       </c>
       <c r="N5" t="n">
-        <v>46761.75</v>
+        <v>47176.25</v>
       </c>
       <c r="O5" t="n">
-        <v>47031</v>
+        <v>47078</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -936,7 +934,7 @@
       <c r="R5" s="6" t="n">
         <v/>
       </c>
-      <c r="S5" s="7" t="inlineStr">
+      <c r="S5" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -962,50 +960,50 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>46605</v>
+        <v>46565</v>
       </c>
       <c r="C6" t="n">
-        <v>47055</v>
+        <v>47323</v>
       </c>
       <c r="D6" t="n">
-        <v>46098</v>
+        <v>46335</v>
       </c>
       <c r="E6" t="n">
-        <v>46556</v>
+        <v>47031</v>
       </c>
       <c r="F6" t="n">
-        <v>228</v>
+        <v>475</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.0049</v>
+        <v>0.0102</v>
       </c>
       <c r="H6" t="n">
-        <v>957</v>
+        <v>988</v>
       </c>
       <c r="I6" t="n">
-        <v>44981</v>
+        <v>45141</v>
       </c>
       <c r="J6" t="n">
-        <v>45778.25</v>
+        <v>45588.75</v>
       </c>
       <c r="K6" t="n">
-        <v>45978.5</v>
+        <v>46077.5</v>
       </c>
       <c r="L6" t="n">
-        <v>46178.75</v>
+        <v>46566.25</v>
       </c>
       <c r="M6" t="n">
-        <v>46677.5</v>
+        <v>47034.5</v>
       </c>
       <c r="N6" t="n">
-        <v>47176.25</v>
+        <v>47502.75</v>
       </c>
       <c r="O6" t="n">
-        <v>47078</v>
+        <v>48012</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1016,7 +1014,7 @@
       <c r="R6" s="6" t="n">
         <v/>
       </c>
-      <c r="S6" s="7" t="inlineStr">
+      <c r="S6" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1042,69 +1040,73 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>46565</v>
+        <v>47048</v>
       </c>
       <c r="C7" t="n">
-        <v>47323</v>
+        <v>47162</v>
       </c>
       <c r="D7" t="n">
-        <v>46335</v>
+        <v>45387</v>
       </c>
       <c r="E7" t="n">
-        <v>47031</v>
+        <v>45706</v>
       </c>
       <c r="F7" t="n">
-        <v>475</v>
+        <v>-1325</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.0102</v>
+        <v>-0.0282</v>
       </c>
       <c r="H7" t="n">
-        <v>988</v>
+        <v>1775</v>
       </c>
       <c r="I7" t="n">
-        <v>45141</v>
+        <v>45347</v>
       </c>
       <c r="J7" t="n">
-        <v>45588.75</v>
+        <v>46144</v>
       </c>
       <c r="K7" t="n">
-        <v>46077.5</v>
+        <v>46537</v>
       </c>
       <c r="L7" t="n">
-        <v>46566.25</v>
+        <v>46930</v>
       </c>
       <c r="M7" t="n">
-        <v>47034.5</v>
+        <v>47525</v>
       </c>
       <c r="N7" t="n">
-        <v>47502.75</v>
+        <v>48120</v>
       </c>
       <c r="O7" t="n">
-        <v>48012</v>
-      </c>
-      <c r="P7" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q7" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R7" s="6" t="n">
-        <v/>
+        <v>48311</v>
+      </c>
+      <c r="P7" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q7" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R7" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S7" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="n">
+        <v/>
       </c>
       <c r="U7" s="8" t="n">
         <v/>
@@ -1112,9 +1114,9 @@
       <c r="V7" s="8" t="n">
         <v/>
       </c>
-      <c r="W7" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W7" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X7" t="inlineStr"/>
@@ -1122,74 +1124,70 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>47048</v>
+        <v>45837</v>
       </c>
       <c r="C8" t="n">
-        <v>47162</v>
+        <v>46915</v>
       </c>
       <c r="D8" t="n">
-        <v>45387</v>
+        <v>45605</v>
       </c>
       <c r="E8" t="n">
-        <v>45706</v>
+        <v>46381</v>
       </c>
       <c r="F8" t="n">
-        <v>-1325</v>
+        <v>675</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.0282</v>
+        <v>0.0148</v>
       </c>
       <c r="H8" t="n">
-        <v>1775</v>
+        <v>1310</v>
       </c>
       <c r="I8" t="n">
-        <v>45347</v>
+        <v>43612</v>
       </c>
       <c r="J8" t="n">
-        <v>46144</v>
+        <v>43646.75</v>
       </c>
       <c r="K8" t="n">
-        <v>46537</v>
+        <v>44818.5</v>
       </c>
       <c r="L8" t="n">
-        <v>46930</v>
+        <v>45990.25</v>
       </c>
       <c r="M8" t="n">
-        <v>47525</v>
+        <v>46593.5</v>
       </c>
       <c r="N8" t="n">
-        <v>48120</v>
+        <v>47196.75</v>
       </c>
       <c r="O8" t="n">
-        <v>48311</v>
-      </c>
-      <c r="P8" s="6" t="inlineStr">
+        <v>48937</v>
+      </c>
+      <c r="P8" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q8" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R8" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S8" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q8" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R8" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S8" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="n">
-        <v/>
-      </c>
       <c r="U8" s="8" t="n">
         <v/>
       </c>
@@ -1201,55 +1199,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr"/>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>45837</v>
+        <v>46489</v>
       </c>
       <c r="C9" t="n">
-        <v>46915</v>
+        <v>47508</v>
       </c>
       <c r="D9" t="n">
-        <v>45605</v>
+        <v>46316</v>
       </c>
       <c r="E9" t="n">
-        <v>46381</v>
+        <v>47396</v>
       </c>
       <c r="F9" t="n">
-        <v>675</v>
+        <v>1015</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.0148</v>
+        <v>0.0219</v>
       </c>
       <c r="H9" t="n">
-        <v>1310</v>
+        <v>1192</v>
       </c>
       <c r="I9" t="n">
-        <v>43612</v>
+        <v>44295</v>
       </c>
       <c r="J9" t="n">
-        <v>43646.75</v>
+        <v>45131.5</v>
       </c>
       <c r="K9" t="n">
-        <v>44818.5</v>
+        <v>45726</v>
       </c>
       <c r="L9" t="n">
-        <v>45990.25</v>
+        <v>46320.5</v>
       </c>
       <c r="M9" t="n">
-        <v>46593.5</v>
+        <v>47036</v>
       </c>
       <c r="N9" t="n">
-        <v>47196.75</v>
+        <v>47751.5</v>
       </c>
       <c r="O9" t="n">
-        <v>48937</v>
+        <v>48225</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1260,19 +1262,21 @@
       <c r="R9" s="6" t="n">
         <v/>
       </c>
-      <c r="S9" s="7" t="inlineStr">
+      <c r="S9" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T9" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U9" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U9" s="8" t="n">
-        <v/>
-      </c>
       <c r="V9" s="8" t="n">
         <v/>
       </c>
@@ -1283,57 +1287,57 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>46489</v>
+        <v>47711</v>
       </c>
       <c r="C10" t="n">
-        <v>47508</v>
+        <v>48214</v>
       </c>
       <c r="D10" t="n">
-        <v>46316</v>
+        <v>47488</v>
       </c>
       <c r="E10" t="n">
-        <v>47396</v>
+        <v>47722</v>
       </c>
       <c r="F10" t="n">
-        <v>1015</v>
+        <v>326</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.0219</v>
+        <v>0.0069</v>
       </c>
       <c r="H10" t="n">
-        <v>1192</v>
+        <v>726</v>
       </c>
       <c r="I10" t="n">
-        <v>44295</v>
+        <v>45124</v>
       </c>
       <c r="J10" t="n">
-        <v>45131.5</v>
+        <v>46446</v>
       </c>
       <c r="K10" t="n">
-        <v>45726</v>
+        <v>46800</v>
       </c>
       <c r="L10" t="n">
-        <v>46320.5</v>
+        <v>47154</v>
       </c>
       <c r="M10" t="n">
-        <v>47036</v>
+        <v>47992</v>
       </c>
       <c r="N10" t="n">
-        <v>47751.5</v>
+        <v>48830</v>
       </c>
       <c r="O10" t="n">
-        <v>48225</v>
+        <v>48700</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1344,20 +1348,18 @@
       <c r="R10" s="6" t="n">
         <v/>
       </c>
-      <c r="S10" s="7" t="inlineStr">
+      <c r="S10" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T10" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U10" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U10" s="8" t="n">
+        <v/>
       </c>
       <c r="V10" s="8" t="n">
         <v/>
@@ -1376,69 +1378,73 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>47711</v>
+        <v>47735</v>
       </c>
       <c r="C11" t="n">
-        <v>48214</v>
+        <v>47869</v>
       </c>
       <c r="D11" t="n">
-        <v>47488</v>
+        <v>46574</v>
       </c>
       <c r="E11" t="n">
-        <v>47722</v>
+        <v>47085</v>
       </c>
       <c r="F11" t="n">
-        <v>326</v>
+        <v>-637</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0069</v>
+        <v>-0.0133</v>
       </c>
       <c r="H11" t="n">
-        <v>726</v>
+        <v>1295</v>
       </c>
       <c r="I11" t="n">
-        <v>45124</v>
+        <v>46762</v>
       </c>
       <c r="J11" t="n">
-        <v>46446</v>
+        <v>46931.5</v>
       </c>
       <c r="K11" t="n">
-        <v>46800</v>
+        <v>47359</v>
       </c>
       <c r="L11" t="n">
-        <v>47154</v>
+        <v>47786.5</v>
       </c>
       <c r="M11" t="n">
-        <v>47992</v>
+        <v>48085</v>
       </c>
       <c r="N11" t="n">
-        <v>48830</v>
+        <v>48383.5</v>
       </c>
       <c r="O11" t="n">
-        <v>48700</v>
-      </c>
-      <c r="P11" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q11" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R11" s="6" t="n">
-        <v/>
+        <v>48940</v>
+      </c>
+      <c r="P11" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q11" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R11" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S11" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="n">
+        <v/>
       </c>
       <c r="U11" s="8" t="n">
         <v/>
@@ -1451,86 +1457,80 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>47735</v>
+        <v>47208</v>
       </c>
       <c r="C12" t="n">
-        <v>47869</v>
+        <v>48528</v>
       </c>
       <c r="D12" t="n">
-        <v>46574</v>
+        <v>46939</v>
       </c>
       <c r="E12" t="n">
-        <v>47085</v>
+        <v>47229</v>
       </c>
       <c r="F12" t="n">
-        <v>-637</v>
+        <v>144</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.0133</v>
+        <v>0.0031</v>
       </c>
       <c r="H12" t="n">
-        <v>1295</v>
+        <v>1589</v>
       </c>
       <c r="I12" t="n">
-        <v>46762</v>
+        <v>45279</v>
       </c>
       <c r="J12" t="n">
-        <v>46931.5</v>
+        <v>45721.75</v>
       </c>
       <c r="K12" t="n">
-        <v>47359</v>
+        <v>46437.5</v>
       </c>
       <c r="L12" t="n">
-        <v>47786.5</v>
+        <v>47153.25</v>
       </c>
       <c r="M12" t="n">
-        <v>48085</v>
+        <v>47732.5</v>
       </c>
       <c r="N12" t="n">
-        <v>48383.5</v>
+        <v>48311.75</v>
       </c>
       <c r="O12" t="n">
-        <v>48940</v>
-      </c>
-      <c r="P12" s="6" t="inlineStr">
+        <v>49164</v>
+      </c>
+      <c r="P12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S12" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q12" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R12" s="6" t="inlineStr">
+      <c r="U12" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S12" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U12" s="8" t="n">
-        <v/>
-      </c>
       <c r="V12" s="8" t="n">
         <v/>
       </c>
@@ -1539,55 +1539,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr"/>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>47208</v>
+        <v>47237</v>
       </c>
       <c r="C13" t="n">
-        <v>48528</v>
+        <v>47368</v>
       </c>
       <c r="D13" t="n">
-        <v>46939</v>
+        <v>45779</v>
       </c>
       <c r="E13" t="n">
-        <v>47229</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="n">
-        <v>144</v>
+        <v>-908</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.0031</v>
+        <v>-0.0192</v>
       </c>
       <c r="H13" t="n">
         <v>1589</v>
       </c>
       <c r="I13" t="n">
-        <v>45279</v>
+        <v>45350</v>
       </c>
       <c r="J13" t="n">
-        <v>45721.75</v>
+        <v>45387.75</v>
       </c>
       <c r="K13" t="n">
-        <v>46437.5</v>
+        <v>46434.5</v>
       </c>
       <c r="L13" t="n">
-        <v>47153.25</v>
+        <v>47481.25</v>
       </c>
       <c r="M13" t="n">
-        <v>47732.5</v>
+        <v>48023.5</v>
       </c>
       <c r="N13" t="n">
-        <v>48311.75</v>
+        <v>48565.75</v>
       </c>
       <c r="O13" t="n">
-        <v>49164</v>
+        <v>50117</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1595,23 +1599,21 @@
       <c r="Q13" s="6" t="n">
         <v/>
       </c>
-      <c r="R13" s="6" t="n">
-        <v/>
+      <c r="R13" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S13" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U13" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U13" s="8" t="n">
+        <v/>
       </c>
       <c r="V13" s="8" t="n">
         <v/>
@@ -1621,59 +1623,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>47237</v>
+        <v>46504</v>
       </c>
       <c r="C14" t="n">
-        <v>47368</v>
+        <v>47796</v>
       </c>
       <c r="D14" t="n">
-        <v>45779</v>
+        <v>46165</v>
       </c>
       <c r="E14" t="n">
-        <v>46321</v>
+        <v>47743</v>
       </c>
       <c r="F14" t="n">
-        <v>-908</v>
+        <v>1422</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.0192</v>
+        <v>0.0307</v>
       </c>
       <c r="H14" t="n">
-        <v>1589</v>
+        <v>1631</v>
       </c>
       <c r="I14" t="n">
-        <v>45350</v>
+        <v>44190</v>
       </c>
       <c r="J14" t="n">
-        <v>45387.75</v>
+        <v>44605.75</v>
       </c>
       <c r="K14" t="n">
-        <v>46434.5</v>
+        <v>45526.5</v>
       </c>
       <c r="L14" t="n">
-        <v>47481.25</v>
+        <v>46447.25</v>
       </c>
       <c r="M14" t="n">
-        <v>48023.5</v>
+        <v>47115.5</v>
       </c>
       <c r="N14" t="n">
-        <v>48565.75</v>
+        <v>47783.75</v>
       </c>
       <c r="O14" t="n">
-        <v>50117</v>
+        <v>48957</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1681,22 +1679,24 @@
       <c r="Q14" s="6" t="n">
         <v/>
       </c>
-      <c r="R14" s="6" t="inlineStr">
+      <c r="R14" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S14" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U14" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S14" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U14" s="8" t="n">
-        <v/>
-      </c>
       <c r="V14" s="8" t="n">
         <v/>
       </c>
@@ -1705,55 +1705,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr"/>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>46504</v>
+        <v>47741</v>
       </c>
       <c r="C15" t="n">
-        <v>47796</v>
+        <v>48184</v>
       </c>
       <c r="D15" t="n">
-        <v>46165</v>
+        <v>47269</v>
       </c>
       <c r="E15" t="n">
-        <v>47743</v>
+        <v>48001</v>
       </c>
       <c r="F15" t="n">
-        <v>1422</v>
+        <v>258</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.0307</v>
+        <v>0.0054</v>
       </c>
       <c r="H15" t="n">
-        <v>1631</v>
+        <v>915</v>
       </c>
       <c r="I15" t="n">
-        <v>44190</v>
+        <v>44534</v>
       </c>
       <c r="J15" t="n">
-        <v>44605.75</v>
+        <v>46493.25</v>
       </c>
       <c r="K15" t="n">
-        <v>45526.5</v>
+        <v>46927.5</v>
       </c>
       <c r="L15" t="n">
-        <v>46447.25</v>
+        <v>47361.75</v>
       </c>
       <c r="M15" t="n">
-        <v>47115.5</v>
+        <v>48558.5</v>
       </c>
       <c r="N15" t="n">
-        <v>47783.75</v>
+        <v>49755.25</v>
       </c>
       <c r="O15" t="n">
-        <v>48957</v>
+        <v>49427</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1764,20 +1768,18 @@
       <c r="R15" s="6" t="n">
         <v/>
       </c>
-      <c r="S15" s="7" t="inlineStr">
+      <c r="S15" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T15" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U15" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U15" s="8" t="n">
+        <v/>
       </c>
       <c r="V15" s="8" t="n">
         <v/>
@@ -1796,50 +1798,50 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>47741</v>
+        <v>48015</v>
       </c>
       <c r="C16" t="n">
-        <v>48184</v>
+        <v>48917</v>
       </c>
       <c r="D16" t="n">
-        <v>47269</v>
+        <v>47504</v>
       </c>
       <c r="E16" t="n">
-        <v>48001</v>
+        <v>48474</v>
       </c>
       <c r="F16" t="n">
-        <v>258</v>
+        <v>473</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0054</v>
+        <v>0.009900000000000001</v>
       </c>
       <c r="H16" t="n">
-        <v>915</v>
+        <v>1413</v>
       </c>
       <c r="I16" t="n">
-        <v>44534</v>
+        <v>46354</v>
       </c>
       <c r="J16" t="n">
-        <v>46493.25</v>
+        <v>47223.25</v>
       </c>
       <c r="K16" t="n">
-        <v>46927.5</v>
+        <v>47543.5</v>
       </c>
       <c r="L16" t="n">
-        <v>47361.75</v>
+        <v>47863.75</v>
       </c>
       <c r="M16" t="n">
-        <v>48558.5</v>
+        <v>48458.5</v>
       </c>
       <c r="N16" t="n">
-        <v>49755.25</v>
+        <v>49053.25</v>
       </c>
       <c r="O16" t="n">
-        <v>49427</v>
+        <v>49099</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1847,10 +1849,12 @@
       <c r="Q16" s="6" t="n">
         <v/>
       </c>
-      <c r="R16" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S16" s="7" t="inlineStr">
+      <c r="R16" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S16" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1880,50 +1884,50 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>48015</v>
+        <v>48517</v>
       </c>
       <c r="C17" t="n">
-        <v>48917</v>
+        <v>48745</v>
       </c>
       <c r="D17" t="n">
-        <v>47504</v>
+        <v>47809</v>
       </c>
       <c r="E17" t="n">
-        <v>48474</v>
+        <v>48090</v>
       </c>
       <c r="F17" t="n">
-        <v>473</v>
+        <v>-384</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.009900000000000001</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="H17" t="n">
-        <v>1413</v>
+        <v>936</v>
       </c>
       <c r="I17" t="n">
-        <v>46354</v>
+        <v>46091</v>
       </c>
       <c r="J17" t="n">
-        <v>47223.25</v>
+        <v>47192.75</v>
       </c>
       <c r="K17" t="n">
-        <v>47543.5</v>
+        <v>47767.5</v>
       </c>
       <c r="L17" t="n">
-        <v>47863.75</v>
+        <v>48342.25</v>
       </c>
       <c r="M17" t="n">
-        <v>48458.5</v>
+        <v>49180.5</v>
       </c>
       <c r="N17" t="n">
-        <v>49053.25</v>
+        <v>50018.75</v>
       </c>
       <c r="O17" t="n">
-        <v>49099</v>
+        <v>50330</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1931,20 +1935,16 @@
       <c r="Q17" s="6" t="n">
         <v/>
       </c>
-      <c r="R17" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R17" s="6" t="n">
+        <v/>
       </c>
       <c r="S17" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="n">
+        <v/>
       </c>
       <c r="U17" s="8" t="n">
         <v/>
@@ -1959,57 +1959,57 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>48517</v>
+        <v>48600</v>
       </c>
       <c r="C18" t="n">
-        <v>48745</v>
+        <v>49086</v>
       </c>
       <c r="D18" t="n">
-        <v>47809</v>
+        <v>48458</v>
       </c>
       <c r="E18" t="n">
-        <v>48090</v>
+        <v>48998</v>
       </c>
       <c r="F18" t="n">
-        <v>-384</v>
+        <v>908</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-0.007900000000000001</v>
+        <v>0.0189</v>
       </c>
       <c r="H18" t="n">
-        <v>936</v>
+        <v>628</v>
       </c>
       <c r="I18" t="n">
-        <v>46091</v>
+        <v>46873</v>
       </c>
       <c r="J18" t="n">
-        <v>47192.75</v>
+        <v>47060.5</v>
       </c>
       <c r="K18" t="n">
-        <v>47767.5</v>
+        <v>47622</v>
       </c>
       <c r="L18" t="n">
-        <v>48342.25</v>
+        <v>48183.5</v>
       </c>
       <c r="M18" t="n">
-        <v>49180.5</v>
+        <v>48558</v>
       </c>
       <c r="N18" t="n">
-        <v>50018.75</v>
+        <v>48932.5</v>
       </c>
       <c r="O18" t="n">
-        <v>50330</v>
+        <v>49681</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2022,100 +2022,100 @@
       </c>
       <c r="S18" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U18" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U18" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V18" s="8" t="n">
         <v/>
       </c>
-      <c r="W18" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W18" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>48600</v>
+        <v>48998</v>
       </c>
       <c r="C19" t="n">
-        <v>49086</v>
+        <v>49052</v>
       </c>
       <c r="D19" t="n">
-        <v>48458</v>
+        <v>48092</v>
       </c>
       <c r="E19" t="n">
-        <v>48998</v>
+        <v>48616</v>
       </c>
       <c r="F19" t="n">
-        <v>908</v>
+        <v>-382</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.0189</v>
+        <v>-0.0078</v>
       </c>
       <c r="H19" t="n">
-        <v>628</v>
+        <v>960</v>
       </c>
       <c r="I19" t="n">
-        <v>46873</v>
+        <v>47830</v>
       </c>
       <c r="J19" t="n">
-        <v>47060.5</v>
+        <v>48483</v>
       </c>
       <c r="K19" t="n">
-        <v>47622</v>
+        <v>48684</v>
       </c>
       <c r="L19" t="n">
-        <v>48183.5</v>
+        <v>48885</v>
       </c>
       <c r="M19" t="n">
-        <v>48558</v>
+        <v>49312</v>
       </c>
       <c r="N19" t="n">
-        <v>48932.5</v>
+        <v>49739</v>
       </c>
       <c r="O19" t="n">
-        <v>49681</v>
+        <v>49714</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
       </c>
-      <c r="Q19" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R19" s="6" t="n">
-        <v/>
+      <c r="Q19" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R19" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S19" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U19" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U19" s="8" t="n">
+        <v/>
       </c>
       <c r="V19" s="8" t="n">
         <v/>
@@ -2125,80 +2125,84 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr"/>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>48998</v>
+        <v>48653</v>
       </c>
       <c r="C20" t="n">
-        <v>49052</v>
+        <v>49876</v>
       </c>
       <c r="D20" t="n">
-        <v>48092</v>
+        <v>48556</v>
       </c>
       <c r="E20" t="n">
-        <v>48616</v>
+        <v>49726</v>
       </c>
       <c r="F20" t="n">
-        <v>-382</v>
+        <v>1110</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-0.0078</v>
+        <v>0.0228</v>
       </c>
       <c r="H20" t="n">
-        <v>960</v>
+        <v>1320</v>
       </c>
       <c r="I20" t="n">
-        <v>47830</v>
+        <v>47132</v>
       </c>
       <c r="J20" t="n">
-        <v>48483</v>
+        <v>47678</v>
       </c>
       <c r="K20" t="n">
-        <v>48684</v>
+        <v>48136</v>
       </c>
       <c r="L20" t="n">
-        <v>48885</v>
+        <v>48594</v>
       </c>
       <c r="M20" t="n">
-        <v>49312</v>
+        <v>49096</v>
       </c>
       <c r="N20" t="n">
-        <v>49739</v>
+        <v>49598</v>
       </c>
       <c r="O20" t="n">
-        <v>49714</v>
+        <v>50012</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
       </c>
-      <c r="Q20" s="6" t="inlineStr">
+      <c r="Q20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S20" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R20" s="6" t="inlineStr">
+      <c r="U20" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S20" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U20" s="8" t="n">
-        <v/>
-      </c>
       <c r="V20" s="8" t="n">
         <v/>
       </c>
@@ -2207,59 +2211,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>48653</v>
+        <v>49720</v>
       </c>
       <c r="C21" t="n">
-        <v>49876</v>
+        <v>49901</v>
       </c>
       <c r="D21" t="n">
-        <v>48556</v>
+        <v>49057</v>
       </c>
       <c r="E21" t="n">
-        <v>49726</v>
+        <v>49547</v>
       </c>
       <c r="F21" t="n">
-        <v>1110</v>
+        <v>-179</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.0228</v>
+        <v>-0.0036</v>
       </c>
       <c r="H21" t="n">
-        <v>1320</v>
+        <v>844</v>
       </c>
       <c r="I21" t="n">
-        <v>47132</v>
+        <v>47236</v>
       </c>
       <c r="J21" t="n">
-        <v>47678</v>
+        <v>48661</v>
       </c>
       <c r="K21" t="n">
-        <v>48136</v>
+        <v>49066</v>
       </c>
       <c r="L21" t="n">
-        <v>48594</v>
+        <v>49471</v>
       </c>
       <c r="M21" t="n">
-        <v>49096</v>
+        <v>50386</v>
       </c>
       <c r="N21" t="n">
-        <v>49598</v>
+        <v>51301</v>
       </c>
       <c r="O21" t="n">
-        <v>50012</v>
+        <v>51196</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2267,23 +2267,21 @@
       <c r="Q21" s="6" t="n">
         <v/>
       </c>
-      <c r="R21" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S21" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="inlineStr">
+      <c r="R21" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U21" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S21" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U21" s="8" t="n">
+        <v/>
       </c>
       <c r="V21" s="8" t="n">
         <v/>
@@ -2293,70 +2291,76 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr"/>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>49720</v>
+        <v>49310</v>
       </c>
       <c r="C22" t="n">
-        <v>49901</v>
+        <v>49795</v>
       </c>
       <c r="D22" t="n">
-        <v>49057</v>
+        <v>48488</v>
       </c>
       <c r="E22" t="n">
-        <v>49547</v>
+        <v>49263</v>
       </c>
       <c r="F22" t="n">
-        <v>-179</v>
+        <v>-284</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.0036</v>
+        <v>-0.0057</v>
       </c>
       <c r="H22" t="n">
-        <v>844</v>
+        <v>1307</v>
       </c>
       <c r="I22" t="n">
-        <v>47236</v>
+        <v>48213</v>
       </c>
       <c r="J22" t="n">
-        <v>48661</v>
+        <v>48737</v>
       </c>
       <c r="K22" t="n">
-        <v>49066</v>
+        <v>49125</v>
       </c>
       <c r="L22" t="n">
-        <v>49471</v>
+        <v>49513</v>
       </c>
       <c r="M22" t="n">
-        <v>50386</v>
+        <v>49969</v>
       </c>
       <c r="N22" t="n">
-        <v>51301</v>
+        <v>50425</v>
       </c>
       <c r="O22" t="n">
-        <v>51196</v>
+        <v>50745</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
       </c>
-      <c r="Q22" s="6" t="n">
-        <v/>
+      <c r="Q22" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R22" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S22" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T22" s="8" t="n">
@@ -2375,74 +2379,72 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>49310</v>
+        <v>49036</v>
       </c>
       <c r="C23" t="n">
-        <v>49795</v>
+        <v>49644</v>
       </c>
       <c r="D23" t="n">
-        <v>48488</v>
+        <v>48571</v>
       </c>
       <c r="E23" t="n">
-        <v>49263</v>
+        <v>49008</v>
       </c>
       <c r="F23" t="n">
-        <v>-284</v>
+        <v>-255</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-0.0057</v>
+        <v>-0.0052</v>
       </c>
       <c r="H23" t="n">
-        <v>1307</v>
+        <v>1073</v>
       </c>
       <c r="I23" t="n">
-        <v>48213</v>
+        <v>47181</v>
       </c>
       <c r="J23" t="n">
-        <v>48737</v>
+        <v>48016.75</v>
       </c>
       <c r="K23" t="n">
-        <v>49125</v>
+        <v>48609.5</v>
       </c>
       <c r="L23" t="n">
-        <v>49513</v>
+        <v>49202.25</v>
       </c>
       <c r="M23" t="n">
-        <v>49969</v>
+        <v>49916.5</v>
       </c>
       <c r="N23" t="n">
-        <v>50425</v>
+        <v>50630.75</v>
       </c>
       <c r="O23" t="n">
-        <v>50745</v>
+        <v>51102</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
       </c>
-      <c r="Q23" s="6" t="inlineStr">
+      <c r="Q23" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R23" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R23" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S23" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="S23" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T23" s="8" t="n">
@@ -2461,57 +2463,57 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>49036</v>
+        <v>48864</v>
       </c>
       <c r="C24" t="n">
-        <v>49644</v>
+        <v>50263</v>
       </c>
       <c r="D24" t="n">
-        <v>48571</v>
+        <v>48506</v>
       </c>
       <c r="E24" t="n">
-        <v>49008</v>
+        <v>50205</v>
       </c>
       <c r="F24" t="n">
-        <v>-255</v>
+        <v>1197</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-0.0052</v>
+        <v>0.0244</v>
       </c>
       <c r="H24" t="n">
-        <v>1073</v>
+        <v>1757</v>
       </c>
       <c r="I24" t="n">
-        <v>47181</v>
+        <v>47498</v>
       </c>
       <c r="J24" t="n">
-        <v>48016.75</v>
+        <v>47885.25</v>
       </c>
       <c r="K24" t="n">
-        <v>48609.5</v>
+        <v>48471.5</v>
       </c>
       <c r="L24" t="n">
-        <v>49202.25</v>
+        <v>49057.75</v>
       </c>
       <c r="M24" t="n">
-        <v>49916.5</v>
+        <v>49544.5</v>
       </c>
       <c r="N24" t="n">
-        <v>50630.75</v>
+        <v>50031.25</v>
       </c>
       <c r="O24" t="n">
-        <v>51102</v>
+        <v>50717</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2519,21 +2521,23 @@
       <c r="Q24" s="6" t="n">
         <v/>
       </c>
-      <c r="R24" s="6" t="inlineStr">
+      <c r="R24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S24" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S24" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U24" s="8" t="n">
-        <v/>
+      <c r="U24" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V24" s="8" t="n">
         <v/>
@@ -2545,57 +2549,57 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>48864</v>
+        <v>50240</v>
       </c>
       <c r="C25" t="n">
-        <v>50263</v>
+        <v>50611</v>
       </c>
       <c r="D25" t="n">
-        <v>48506</v>
+        <v>49155</v>
       </c>
       <c r="E25" t="n">
-        <v>50205</v>
+        <v>49569</v>
       </c>
       <c r="F25" t="n">
-        <v>1197</v>
+        <v>-636</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.0244</v>
+        <v>-0.0127</v>
       </c>
       <c r="H25" t="n">
-        <v>1757</v>
+        <v>1456</v>
       </c>
       <c r="I25" t="n">
-        <v>47498</v>
+        <v>46749</v>
       </c>
       <c r="J25" t="n">
-        <v>47885.25</v>
+        <v>48858.25</v>
       </c>
       <c r="K25" t="n">
-        <v>48471.5</v>
+        <v>49326.5</v>
       </c>
       <c r="L25" t="n">
-        <v>49057.75</v>
+        <v>49794.75</v>
       </c>
       <c r="M25" t="n">
-        <v>49544.5</v>
+        <v>51083.5</v>
       </c>
       <c r="N25" t="n">
-        <v>50031.25</v>
+        <v>52372.25</v>
       </c>
       <c r="O25" t="n">
-        <v>50717</v>
+        <v>52020</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2603,23 +2607,21 @@
       <c r="Q25" s="6" t="n">
         <v/>
       </c>
-      <c r="R25" s="6" t="n">
-        <v/>
+      <c r="R25" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S25" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U25" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U25" s="8" t="n">
+        <v/>
       </c>
       <c r="V25" s="8" t="n">
         <v/>
@@ -2638,50 +2640,50 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>50240</v>
+        <v>49549</v>
       </c>
       <c r="C26" t="n">
-        <v>50611</v>
+        <v>49967</v>
       </c>
       <c r="D26" t="n">
-        <v>49155</v>
+        <v>49204</v>
       </c>
       <c r="E26" t="n">
-        <v>49569</v>
+        <v>49674</v>
       </c>
       <c r="F26" t="n">
-        <v>-636</v>
+        <v>105</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.0127</v>
+        <v>0.0021</v>
       </c>
       <c r="H26" t="n">
-        <v>1456</v>
+        <v>763</v>
       </c>
       <c r="I26" t="n">
-        <v>46749</v>
+        <v>47699</v>
       </c>
       <c r="J26" t="n">
-        <v>48858.25</v>
+        <v>47956</v>
       </c>
       <c r="K26" t="n">
-        <v>49326.5</v>
+        <v>48841</v>
       </c>
       <c r="L26" t="n">
-        <v>49794.75</v>
+        <v>49726</v>
       </c>
       <c r="M26" t="n">
-        <v>51083.5</v>
+        <v>50297</v>
       </c>
       <c r="N26" t="n">
-        <v>52372.25</v>
+        <v>50868</v>
       </c>
       <c r="O26" t="n">
-        <v>52020</v>
+        <v>52067</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2689,12 +2691,10 @@
       <c r="Q26" s="6" t="n">
         <v/>
       </c>
-      <c r="R26" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S26" s="10" t="inlineStr">
+      <c r="R26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S26" s="7" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -2722,63 +2722,67 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>49549</v>
+        <v>49642</v>
       </c>
       <c r="C27" t="n">
-        <v>49967</v>
+        <v>49872</v>
       </c>
       <c r="D27" t="n">
-        <v>49204</v>
+        <v>48699</v>
       </c>
       <c r="E27" t="n">
-        <v>49674</v>
+        <v>49000</v>
       </c>
       <c r="F27" t="n">
-        <v>105</v>
+        <v>-674</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.0021</v>
+        <v>-0.0136</v>
       </c>
       <c r="H27" t="n">
-        <v>763</v>
+        <v>1173</v>
       </c>
       <c r="I27" t="n">
-        <v>47699</v>
+        <v>48441</v>
       </c>
       <c r="J27" t="n">
-        <v>47956</v>
+        <v>48955.25</v>
       </c>
       <c r="K27" t="n">
-        <v>48841</v>
+        <v>49292.5</v>
       </c>
       <c r="L27" t="n">
-        <v>49726</v>
+        <v>49629.75</v>
       </c>
       <c r="M27" t="n">
-        <v>50297</v>
+        <v>50055.5</v>
       </c>
       <c r="N27" t="n">
-        <v>50868</v>
+        <v>50481.25</v>
       </c>
       <c r="O27" t="n">
-        <v>52067</v>
+        <v>50730</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
       </c>
-      <c r="Q27" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R27" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S27" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="Q27" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R27" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S27" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T27" s="8" t="n">
@@ -2797,64 +2801,66 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>49642</v>
+        <v>48451</v>
       </c>
       <c r="C28" t="n">
-        <v>49872</v>
+        <v>49121</v>
       </c>
       <c r="D28" t="n">
-        <v>48699</v>
+        <v>47025</v>
       </c>
       <c r="E28" t="n">
-        <v>49000</v>
+        <v>47517</v>
       </c>
       <c r="F28" t="n">
-        <v>-674</v>
+        <v>-1483</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.0136</v>
+        <v>-0.0303</v>
       </c>
       <c r="H28" t="n">
-        <v>1173</v>
+        <v>2096</v>
       </c>
       <c r="I28" t="n">
-        <v>48441</v>
+        <v>47526</v>
       </c>
       <c r="J28" t="n">
-        <v>48955.25</v>
+        <v>47684.25</v>
       </c>
       <c r="K28" t="n">
-        <v>49292.5</v>
+        <v>48413.5</v>
       </c>
       <c r="L28" t="n">
-        <v>49629.75</v>
+        <v>49142.75</v>
       </c>
       <c r="M28" t="n">
-        <v>50055.5</v>
+        <v>49586.5</v>
       </c>
       <c r="N28" t="n">
-        <v>50481.25</v>
+        <v>50030.25</v>
       </c>
       <c r="O28" t="n">
-        <v>50730</v>
-      </c>
-      <c r="P28" s="6" t="n">
-        <v/>
+        <v>51045</v>
+      </c>
+      <c r="P28" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q28" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="R28" s="6" t="inlineStr">
@@ -2862,7 +2868,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S28" s="10" t="inlineStr">
+      <c r="S28" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -2876,81 +2882,73 @@
       <c r="V28" s="8" t="n">
         <v/>
       </c>
-      <c r="W28" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W28" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>48451</v>
+        <v>47177</v>
       </c>
       <c r="C29" t="n">
-        <v>49121</v>
+        <v>48266</v>
       </c>
       <c r="D29" t="n">
-        <v>47025</v>
+        <v>46333</v>
       </c>
       <c r="E29" t="n">
-        <v>47517</v>
+        <v>46592</v>
       </c>
       <c r="F29" t="n">
-        <v>-1483</v>
+        <v>-925</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.0303</v>
+        <v>-0.0195</v>
       </c>
       <c r="H29" t="n">
-        <v>2096</v>
+        <v>1933</v>
       </c>
       <c r="I29" t="n">
-        <v>47526</v>
+        <v>44929</v>
       </c>
       <c r="J29" t="n">
-        <v>47684.25</v>
+        <v>45143</v>
       </c>
       <c r="K29" t="n">
-        <v>48413.5</v>
+        <v>46469</v>
       </c>
       <c r="L29" t="n">
-        <v>49142.75</v>
+        <v>47795</v>
       </c>
       <c r="M29" t="n">
-        <v>49586.5</v>
+        <v>48565</v>
       </c>
       <c r="N29" t="n">
-        <v>50030.25</v>
+        <v>49335</v>
       </c>
       <c r="O29" t="n">
-        <v>51045</v>
-      </c>
-      <c r="P29" s="6" t="inlineStr">
+        <v>51217</v>
+      </c>
+      <c r="P29" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q29" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R29" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q29" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R29" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S29" s="10" t="inlineStr">
+      <c r="S29" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -2974,50 +2972,50 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>47177</v>
+        <v>46392</v>
       </c>
       <c r="C30" t="n">
-        <v>48266</v>
+        <v>47457</v>
       </c>
       <c r="D30" t="n">
-        <v>46333</v>
+        <v>45713</v>
       </c>
       <c r="E30" t="n">
-        <v>46592</v>
+        <v>45897</v>
       </c>
       <c r="F30" t="n">
-        <v>-925</v>
+        <v>-695</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0.0195</v>
+        <v>-0.0149</v>
       </c>
       <c r="H30" t="n">
-        <v>1933</v>
+        <v>1744</v>
       </c>
       <c r="I30" t="n">
-        <v>44929</v>
+        <v>44400</v>
       </c>
       <c r="J30" t="n">
-        <v>45143</v>
+        <v>44305.25</v>
       </c>
       <c r="K30" t="n">
-        <v>46469</v>
+        <v>45625.5</v>
       </c>
       <c r="L30" t="n">
-        <v>47795</v>
+        <v>46945.75</v>
       </c>
       <c r="M30" t="n">
-        <v>48565</v>
+        <v>47558.5</v>
       </c>
       <c r="N30" t="n">
-        <v>49335</v>
+        <v>48171.25</v>
       </c>
       <c r="O30" t="n">
-        <v>51217</v>
+        <v>50199</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3030,7 +3028,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S30" s="10" t="inlineStr">
+      <c r="S30" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -3054,50 +3052,50 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>46392</v>
+        <v>45605</v>
       </c>
       <c r="C31" t="n">
-        <v>47457</v>
+        <v>47210</v>
       </c>
       <c r="D31" t="n">
-        <v>45713</v>
+        <v>45272</v>
       </c>
       <c r="E31" t="n">
-        <v>45897</v>
+        <v>45424</v>
       </c>
       <c r="F31" t="n">
-        <v>-695</v>
+        <v>-473</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-0.0149</v>
+        <v>-0.0103</v>
       </c>
       <c r="H31" t="n">
-        <v>1744</v>
+        <v>1938</v>
       </c>
       <c r="I31" t="n">
-        <v>44400</v>
+        <v>43969</v>
       </c>
       <c r="J31" t="n">
-        <v>44305.25</v>
+        <v>43809</v>
       </c>
       <c r="K31" t="n">
-        <v>45625.5</v>
+        <v>45025</v>
       </c>
       <c r="L31" t="n">
-        <v>46945.75</v>
+        <v>46241</v>
       </c>
       <c r="M31" t="n">
-        <v>47558.5</v>
+        <v>46769</v>
       </c>
       <c r="N31" t="n">
-        <v>48171.25</v>
+        <v>47297</v>
       </c>
       <c r="O31" t="n">
-        <v>50199</v>
+        <v>49201</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3110,13 +3108,15 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S31" s="10" t="inlineStr">
+      <c r="S31" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T31" s="8" t="n">
-        <v/>
+      <c r="T31" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U31" s="8" t="n">
         <v/>
@@ -3134,50 +3134,50 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>45605</v>
+        <v>45244</v>
       </c>
       <c r="C32" t="n">
-        <v>47210</v>
+        <v>47090</v>
       </c>
       <c r="D32" t="n">
-        <v>45272</v>
+        <v>45052</v>
       </c>
       <c r="E32" t="n">
-        <v>45424</v>
+        <v>46629</v>
       </c>
       <c r="F32" t="n">
-        <v>-473</v>
+        <v>1205</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>-0.0103</v>
+        <v>0.0265</v>
       </c>
       <c r="H32" t="n">
-        <v>1938</v>
+        <v>2038</v>
       </c>
       <c r="I32" t="n">
-        <v>43969</v>
+        <v>43334</v>
       </c>
       <c r="J32" t="n">
-        <v>43809</v>
+        <v>43077.5</v>
       </c>
       <c r="K32" t="n">
-        <v>45025</v>
+        <v>44455</v>
       </c>
       <c r="L32" t="n">
-        <v>46241</v>
+        <v>45832.5</v>
       </c>
       <c r="M32" t="n">
-        <v>46769</v>
+        <v>46393</v>
       </c>
       <c r="N32" t="n">
-        <v>47297</v>
+        <v>46953.5</v>
       </c>
       <c r="O32" t="n">
-        <v>49201</v>
+        <v>49148</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3185,24 +3185,24 @@
       <c r="Q32" s="6" t="n">
         <v/>
       </c>
-      <c r="R32" s="6" t="inlineStr">
+      <c r="R32" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S32" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S32" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="inlineStr">
+      <c r="U32" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U32" s="8" t="n">
-        <v/>
-      </c>
       <c r="V32" s="8" t="n">
         <v/>
       </c>
@@ -3211,55 +3211,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr"/>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>45244</v>
+        <v>46569</v>
       </c>
       <c r="C33" t="n">
-        <v>47090</v>
+        <v>48555</v>
       </c>
       <c r="D33" t="n">
-        <v>45052</v>
+        <v>46362</v>
       </c>
       <c r="E33" t="n">
-        <v>46629</v>
+        <v>48129</v>
       </c>
       <c r="F33" t="n">
-        <v>1205</v>
+        <v>1500</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0265</v>
+        <v>0.0322</v>
       </c>
       <c r="H33" t="n">
-        <v>2038</v>
+        <v>2193</v>
       </c>
       <c r="I33" t="n">
-        <v>43334</v>
+        <v>43014</v>
       </c>
       <c r="J33" t="n">
-        <v>43077.5</v>
+        <v>44870</v>
       </c>
       <c r="K33" t="n">
-        <v>44455</v>
+        <v>45610</v>
       </c>
       <c r="L33" t="n">
-        <v>45832.5</v>
+        <v>46350</v>
       </c>
       <c r="M33" t="n">
-        <v>46393</v>
+        <v>47648</v>
       </c>
       <c r="N33" t="n">
-        <v>46953.5</v>
+        <v>48946</v>
       </c>
       <c r="O33" t="n">
-        <v>49148</v>
+        <v>49128</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3270,7 +3274,7 @@
       <c r="R33" s="6" t="n">
         <v/>
       </c>
-      <c r="S33" s="7" t="inlineStr">
+      <c r="S33" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3280,10 +3284,8 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U33" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U33" s="8" t="n">
+        <v/>
       </c>
       <c r="V33" s="8" t="n">
         <v/>
@@ -3295,57 +3297,57 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>46569</v>
+        <v>47674</v>
       </c>
       <c r="C34" t="n">
-        <v>48555</v>
+        <v>49924</v>
       </c>
       <c r="D34" t="n">
-        <v>46362</v>
+        <v>47534</v>
       </c>
       <c r="E34" t="n">
-        <v>48129</v>
+        <v>49641</v>
       </c>
       <c r="F34" t="n">
-        <v>1500</v>
+        <v>1512</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0322</v>
+        <v>0.0314</v>
       </c>
       <c r="H34" t="n">
-        <v>2193</v>
+        <v>2390</v>
       </c>
       <c r="I34" t="n">
-        <v>43014</v>
+        <v>44169</v>
       </c>
       <c r="J34" t="n">
-        <v>44870</v>
+        <v>46271.25</v>
       </c>
       <c r="K34" t="n">
-        <v>45610</v>
+        <v>47032.5</v>
       </c>
       <c r="L34" t="n">
-        <v>46350</v>
+        <v>47793.75</v>
       </c>
       <c r="M34" t="n">
-        <v>47648</v>
+        <v>49225.5</v>
       </c>
       <c r="N34" t="n">
-        <v>48946</v>
+        <v>50657.25</v>
       </c>
       <c r="O34" t="n">
-        <v>49128</v>
+        <v>50748</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3356,7 +3358,7 @@
       <c r="R34" s="6" t="n">
         <v/>
       </c>
-      <c r="S34" s="7" t="inlineStr">
+      <c r="S34" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3386,50 +3388,50 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>47674</v>
+        <v>49324</v>
       </c>
       <c r="C35" t="n">
-        <v>49924</v>
+        <v>50043</v>
       </c>
       <c r="D35" t="n">
-        <v>47534</v>
+        <v>49036</v>
       </c>
       <c r="E35" t="n">
-        <v>49641</v>
+        <v>49392</v>
       </c>
       <c r="F35" t="n">
-        <v>1512</v>
+        <v>-249</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.0314</v>
+        <v>-0.005</v>
       </c>
       <c r="H35" t="n">
-        <v>2390</v>
+        <v>1007</v>
       </c>
       <c r="I35" t="n">
-        <v>44169</v>
+        <v>45144</v>
       </c>
       <c r="J35" t="n">
-        <v>46271.25</v>
+        <v>47707</v>
       </c>
       <c r="K35" t="n">
-        <v>47032.5</v>
+        <v>48446</v>
       </c>
       <c r="L35" t="n">
-        <v>47793.75</v>
+        <v>49185</v>
       </c>
       <c r="M35" t="n">
-        <v>49225.5</v>
+        <v>50836</v>
       </c>
       <c r="N35" t="n">
-        <v>50657.25</v>
+        <v>52487</v>
       </c>
       <c r="O35" t="n">
-        <v>50748</v>
+        <v>52314</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3440,15 +3442,13 @@
       <c r="R35" s="6" t="n">
         <v/>
       </c>
-      <c r="S35" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S35" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="n">
+        <v/>
       </c>
       <c r="U35" s="8" t="n">
         <v/>
@@ -3463,57 +3463,57 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>49324</v>
+        <v>49382</v>
       </c>
       <c r="C36" t="n">
-        <v>50043</v>
+        <v>50138</v>
       </c>
       <c r="D36" t="n">
-        <v>49036</v>
+        <v>48608</v>
       </c>
       <c r="E36" t="n">
-        <v>49392</v>
+        <v>49646</v>
       </c>
       <c r="F36" t="n">
-        <v>-249</v>
+        <v>254</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>-0.005</v>
+        <v>0.0051</v>
       </c>
       <c r="H36" t="n">
-        <v>1007</v>
+        <v>1530</v>
       </c>
       <c r="I36" t="n">
-        <v>45144</v>
+        <v>48029</v>
       </c>
       <c r="J36" t="n">
-        <v>47707</v>
+        <v>48311.25</v>
       </c>
       <c r="K36" t="n">
-        <v>48446</v>
+        <v>48888.5</v>
       </c>
       <c r="L36" t="n">
-        <v>49185</v>
+        <v>49465.75</v>
       </c>
       <c r="M36" t="n">
-        <v>50836</v>
+        <v>49895.5</v>
       </c>
       <c r="N36" t="n">
-        <v>52487</v>
+        <v>50325.25</v>
       </c>
       <c r="O36" t="n">
-        <v>52314</v>
+        <v>51050</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3521,16 +3521,20 @@
       <c r="Q36" s="6" t="n">
         <v/>
       </c>
-      <c r="R36" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S36" s="7" t="inlineStr">
+      <c r="R36" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S36" s="10" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
       </c>
-      <c r="T36" s="8" t="n">
-        <v/>
+      <c r="T36" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U36" s="8" t="n">
         <v/>
@@ -3552,50 +3556,50 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>49382</v>
+        <v>49705</v>
       </c>
       <c r="C37" t="n">
-        <v>50138</v>
+        <v>50238</v>
       </c>
       <c r="D37" t="n">
-        <v>48608</v>
+        <v>49016</v>
       </c>
       <c r="E37" t="n">
-        <v>49646</v>
+        <v>49691</v>
       </c>
       <c r="F37" t="n">
-        <v>254</v>
+        <v>45</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.0051</v>
+        <v>0.0009</v>
       </c>
       <c r="H37" t="n">
-        <v>1530</v>
+        <v>1222</v>
       </c>
       <c r="I37" t="n">
-        <v>48029</v>
+        <v>47078</v>
       </c>
       <c r="J37" t="n">
-        <v>48311.25</v>
+        <v>48252.5</v>
       </c>
       <c r="K37" t="n">
-        <v>48888.5</v>
+        <v>48881</v>
       </c>
       <c r="L37" t="n">
-        <v>49465.75</v>
+        <v>49509.5</v>
       </c>
       <c r="M37" t="n">
-        <v>49895.5</v>
+        <v>50411</v>
       </c>
       <c r="N37" t="n">
-        <v>50325.25</v>
+        <v>51312.5</v>
       </c>
       <c r="O37" t="n">
-        <v>51050</v>
+        <v>51668</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3603,20 +3607,16 @@
       <c r="Q37" s="6" t="n">
         <v/>
       </c>
-      <c r="R37" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S37" s="7" t="inlineStr">
+      <c r="R37" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S37" s="10" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
       </c>
-      <c r="T37" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T37" s="8" t="n">
+        <v/>
       </c>
       <c r="U37" s="8" t="n">
         <v/>
@@ -3631,57 +3631,57 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>49705</v>
+        <v>49640</v>
       </c>
       <c r="C38" t="n">
-        <v>50238</v>
+        <v>50292</v>
       </c>
       <c r="D38" t="n">
-        <v>49016</v>
+        <v>49397</v>
       </c>
       <c r="E38" t="n">
-        <v>49691</v>
+        <v>49617</v>
       </c>
       <c r="F38" t="n">
-        <v>45</v>
+        <v>-74</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.0009</v>
+        <v>-0.0015</v>
       </c>
       <c r="H38" t="n">
-        <v>1222</v>
+        <v>895</v>
       </c>
       <c r="I38" t="n">
-        <v>47078</v>
+        <v>47794</v>
       </c>
       <c r="J38" t="n">
-        <v>48252.5</v>
+        <v>48501</v>
       </c>
       <c r="K38" t="n">
-        <v>48881</v>
+        <v>49080</v>
       </c>
       <c r="L38" t="n">
-        <v>49509.5</v>
+        <v>49659</v>
       </c>
       <c r="M38" t="n">
-        <v>50411</v>
+        <v>50302</v>
       </c>
       <c r="N38" t="n">
-        <v>51312.5</v>
+        <v>50945</v>
       </c>
       <c r="O38" t="n">
-        <v>51668</v>
+        <v>51460</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3694,7 +3694,7 @@
       </c>
       <c r="S38" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T38" s="8" t="n">
@@ -3713,57 +3713,57 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>49640</v>
+        <v>49464</v>
       </c>
       <c r="C39" t="n">
-        <v>50292</v>
+        <v>50920</v>
       </c>
       <c r="D39" t="n">
-        <v>49397</v>
+        <v>49152</v>
       </c>
       <c r="E39" t="n">
-        <v>49617</v>
+        <v>50662</v>
       </c>
       <c r="F39" t="n">
-        <v>-74</v>
+        <v>1045</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.0015</v>
+        <v>0.0211</v>
       </c>
       <c r="H39" t="n">
-        <v>895</v>
+        <v>1768</v>
       </c>
       <c r="I39" t="n">
-        <v>47794</v>
+        <v>48502</v>
       </c>
       <c r="J39" t="n">
-        <v>48501</v>
+        <v>48608.25</v>
       </c>
       <c r="K39" t="n">
-        <v>49080</v>
+        <v>49169.5</v>
       </c>
       <c r="L39" t="n">
-        <v>49659</v>
+        <v>49730.75</v>
       </c>
       <c r="M39" t="n">
-        <v>50302</v>
+        <v>50064.5</v>
       </c>
       <c r="N39" t="n">
-        <v>50945</v>
+        <v>50398.25</v>
       </c>
       <c r="O39" t="n">
-        <v>51460</v>
+        <v>51187</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3771,81 +3771,87 @@
       <c r="Q39" s="6" t="n">
         <v/>
       </c>
-      <c r="R39" s="6" t="n">
-        <v/>
+      <c r="R39" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S39" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U39" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U39" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V39" s="8" t="n">
         <v/>
       </c>
-      <c r="W39" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W39" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>49464</v>
+        <v>50776</v>
       </c>
       <c r="C40" t="n">
-        <v>50920</v>
+        <v>51209</v>
       </c>
       <c r="D40" t="n">
-        <v>49152</v>
+        <v>50386</v>
       </c>
       <c r="E40" t="n">
-        <v>50662</v>
+        <v>51077</v>
       </c>
       <c r="F40" t="n">
-        <v>1045</v>
+        <v>415</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.0211</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="H40" t="n">
-        <v>1768</v>
+        <v>823</v>
       </c>
       <c r="I40" t="n">
-        <v>48502</v>
+        <v>47384</v>
       </c>
       <c r="J40" t="n">
-        <v>48608.25</v>
+        <v>49207</v>
       </c>
       <c r="K40" t="n">
-        <v>49169.5</v>
+        <v>49778</v>
       </c>
       <c r="L40" t="n">
-        <v>49730.75</v>
+        <v>50349</v>
       </c>
       <c r="M40" t="n">
-        <v>50064.5</v>
+        <v>51546</v>
       </c>
       <c r="N40" t="n">
-        <v>50398.25</v>
+        <v>52743</v>
       </c>
       <c r="O40" t="n">
-        <v>51187</v>
+        <v>52688</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3853,26 +3859,22 @@
       <c r="Q40" s="6" t="n">
         <v/>
       </c>
-      <c r="R40" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S40" s="7" t="inlineStr">
+      <c r="R40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S40" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T40" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U40" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U40" s="8" t="n">
+        <v/>
+      </c>
       <c r="V40" s="8" t="n">
         <v/>
       </c>
@@ -3881,59 +3883,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>50776</v>
+        <v>51128</v>
       </c>
       <c r="C41" t="n">
-        <v>51209</v>
+        <v>51849</v>
       </c>
       <c r="D41" t="n">
-        <v>50386</v>
+        <v>50736</v>
       </c>
       <c r="E41" t="n">
-        <v>51077</v>
+        <v>50936</v>
       </c>
       <c r="F41" t="n">
-        <v>415</v>
+        <v>-141</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.008200000000000001</v>
+        <v>-0.0028</v>
       </c>
       <c r="H41" t="n">
-        <v>823</v>
+        <v>1113</v>
       </c>
       <c r="I41" t="n">
-        <v>47384</v>
+        <v>49563</v>
       </c>
       <c r="J41" t="n">
-        <v>49207</v>
+        <v>50393.75</v>
       </c>
       <c r="K41" t="n">
-        <v>49778</v>
+        <v>50665.5</v>
       </c>
       <c r="L41" t="n">
-        <v>50349</v>
+        <v>50937.25</v>
       </c>
       <c r="M41" t="n">
-        <v>51546</v>
+        <v>51488.5</v>
       </c>
       <c r="N41" t="n">
-        <v>52743</v>
+        <v>52039.75</v>
       </c>
       <c r="O41" t="n">
-        <v>52688</v>
+        <v>52032</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3946,12 +3944,12 @@
       </c>
       <c r="S41" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T41" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U41" s="8" t="n">
@@ -3965,55 +3963,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr"/>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>51128</v>
+        <v>50796</v>
       </c>
       <c r="C42" t="n">
-        <v>51849</v>
+        <v>51443</v>
       </c>
       <c r="D42" t="n">
-        <v>50736</v>
+        <v>49758</v>
       </c>
       <c r="E42" t="n">
-        <v>50936</v>
+        <v>51227</v>
       </c>
       <c r="F42" t="n">
-        <v>-141</v>
+        <v>291</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.0028</v>
+        <v>0.0057</v>
       </c>
       <c r="H42" t="n">
-        <v>1113</v>
+        <v>1685</v>
       </c>
       <c r="I42" t="n">
-        <v>49563</v>
+        <v>49623</v>
       </c>
       <c r="J42" t="n">
-        <v>50393.75</v>
+        <v>49644.75</v>
       </c>
       <c r="K42" t="n">
-        <v>50665.5</v>
+        <v>50379.5</v>
       </c>
       <c r="L42" t="n">
-        <v>50937.25</v>
+        <v>51114.25</v>
       </c>
       <c r="M42" t="n">
-        <v>51488.5</v>
+        <v>51492.5</v>
       </c>
       <c r="N42" t="n">
-        <v>52039.75</v>
+        <v>51870.75</v>
       </c>
       <c r="O42" t="n">
-        <v>52032</v>
+        <v>52962</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4021,18 +4023,18 @@
       <c r="Q42" s="6" t="n">
         <v/>
       </c>
-      <c r="R42" s="6" t="n">
-        <v/>
+      <c r="R42" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S42" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="n">
+        <v/>
       </c>
       <c r="U42" s="8" t="n">
         <v/>
@@ -4047,57 +4049,57 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>50796</v>
+        <v>51450</v>
       </c>
       <c r="C43" t="n">
-        <v>51443</v>
+        <v>52300</v>
       </c>
       <c r="D43" t="n">
-        <v>49758</v>
+        <v>51420</v>
       </c>
       <c r="E43" t="n">
-        <v>51227</v>
+        <v>51888</v>
       </c>
       <c r="F43" t="n">
-        <v>291</v>
+        <v>661</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.0057</v>
+        <v>0.0129</v>
       </c>
       <c r="H43" t="n">
-        <v>1685</v>
+        <v>880</v>
       </c>
       <c r="I43" t="n">
-        <v>49623</v>
+        <v>48073</v>
       </c>
       <c r="J43" t="n">
-        <v>49644.75</v>
+        <v>49855.25</v>
       </c>
       <c r="K43" t="n">
-        <v>50379.5</v>
+        <v>50384.5</v>
       </c>
       <c r="L43" t="n">
-        <v>51114.25</v>
+        <v>50913.75</v>
       </c>
       <c r="M43" t="n">
-        <v>51492.5</v>
+        <v>52069.5</v>
       </c>
       <c r="N43" t="n">
-        <v>51870.75</v>
+        <v>53225.25</v>
       </c>
       <c r="O43" t="n">
-        <v>52962</v>
+        <v>53128</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4105,18 +4107,18 @@
       <c r="Q43" s="6" t="n">
         <v/>
       </c>
-      <c r="R43" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S43" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="n">
-        <v/>
+      <c r="R43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S43" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U43" s="8" t="n">
         <v/>
@@ -4129,59 +4131,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>51450</v>
+        <v>51870</v>
       </c>
       <c r="C44" t="n">
-        <v>52300</v>
+        <v>53097</v>
       </c>
       <c r="D44" t="n">
-        <v>51420</v>
+        <v>51691</v>
       </c>
       <c r="E44" t="n">
-        <v>51888</v>
+        <v>52209</v>
       </c>
       <c r="F44" t="n">
-        <v>661</v>
+        <v>321</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.0129</v>
+        <v>0.0062</v>
       </c>
       <c r="H44" t="n">
-        <v>880</v>
+        <v>1406</v>
       </c>
       <c r="I44" t="n">
-        <v>48073</v>
+        <v>50540</v>
       </c>
       <c r="J44" t="n">
-        <v>49855.25</v>
+        <v>51022</v>
       </c>
       <c r="K44" t="n">
-        <v>50384.5</v>
+        <v>51448</v>
       </c>
       <c r="L44" t="n">
-        <v>50913.75</v>
+        <v>51874</v>
       </c>
       <c r="M44" t="n">
-        <v>52069.5</v>
+        <v>52328</v>
       </c>
       <c r="N44" t="n">
-        <v>53225.25</v>
+        <v>52782</v>
       </c>
       <c r="O44" t="n">
-        <v>53128</v>
+        <v>53180</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4192,7 +4190,7 @@
       <c r="R44" s="6" t="n">
         <v/>
       </c>
-      <c r="S44" s="7" t="inlineStr">
+      <c r="S44" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -4202,8 +4200,10 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U44" s="8" t="n">
-        <v/>
+      <c r="U44" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V44" s="8" t="n">
         <v/>
@@ -4218,50 +4218,50 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>51870</v>
+        <v>52183</v>
       </c>
       <c r="C45" t="n">
-        <v>53097</v>
+        <v>53400</v>
       </c>
       <c r="D45" t="n">
-        <v>51691</v>
+        <v>52179</v>
       </c>
       <c r="E45" t="n">
-        <v>52209</v>
+        <v>53162</v>
       </c>
       <c r="F45" t="n">
-        <v>321</v>
+        <v>953</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.0062</v>
+        <v>0.0183</v>
       </c>
       <c r="H45" t="n">
-        <v>1406</v>
+        <v>1221</v>
       </c>
       <c r="I45" t="n">
-        <v>50540</v>
+        <v>50285</v>
       </c>
       <c r="J45" t="n">
-        <v>51022</v>
+        <v>50710.5</v>
       </c>
       <c r="K45" t="n">
-        <v>51448</v>
+        <v>51506</v>
       </c>
       <c r="L45" t="n">
-        <v>51874</v>
+        <v>52301.5</v>
       </c>
       <c r="M45" t="n">
-        <v>52328</v>
+        <v>52912</v>
       </c>
       <c r="N45" t="n">
-        <v>52782</v>
+        <v>53522.5</v>
       </c>
       <c r="O45" t="n">
-        <v>53180</v>
+        <v>54503</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4272,7 +4272,7 @@
       <c r="R45" s="6" t="n">
         <v/>
       </c>
-      <c r="S45" s="7" t="inlineStr">
+      <c r="S45" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -4282,10 +4282,8 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U45" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U45" s="8" t="n">
+        <v/>
       </c>
       <c r="V45" s="8" t="n">
         <v/>
@@ -4300,50 +4298,50 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>52183</v>
+        <v>53230</v>
       </c>
       <c r="C46" t="n">
-        <v>53400</v>
+        <v>53656</v>
       </c>
       <c r="D46" t="n">
-        <v>52179</v>
+        <v>52343</v>
       </c>
       <c r="E46" t="n">
-        <v>53162</v>
+        <v>52906</v>
       </c>
       <c r="F46" t="n">
-        <v>953</v>
+        <v>-256</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.0183</v>
+        <v>-0.0048</v>
       </c>
       <c r="H46" t="n">
-        <v>1221</v>
+        <v>1313</v>
       </c>
       <c r="I46" t="n">
-        <v>50285</v>
+        <v>50958</v>
       </c>
       <c r="J46" t="n">
-        <v>50710.5</v>
+        <v>52127.25</v>
       </c>
       <c r="K46" t="n">
-        <v>51506</v>
+        <v>52551.5</v>
       </c>
       <c r="L46" t="n">
-        <v>52301.5</v>
+        <v>52975.75</v>
       </c>
       <c r="M46" t="n">
-        <v>52912</v>
+        <v>53772.5</v>
       </c>
       <c r="N46" t="n">
-        <v>53522.5</v>
+        <v>54569.25</v>
       </c>
       <c r="O46" t="n">
-        <v>54503</v>
+        <v>54621</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4351,18 +4349,18 @@
       <c r="Q46" s="6" t="n">
         <v/>
       </c>
-      <c r="R46" s="6" t="n">
-        <v/>
+      <c r="R46" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S46" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="n">
+        <v/>
       </c>
       <c r="U46" s="8" t="n">
         <v/>
@@ -4375,55 +4373,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr"/>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>53230</v>
+        <v>52844</v>
       </c>
       <c r="C47" t="n">
-        <v>53656</v>
+        <v>53113</v>
       </c>
       <c r="D47" t="n">
-        <v>52343</v>
+        <v>52174</v>
       </c>
       <c r="E47" t="n">
-        <v>52906</v>
+        <v>52375</v>
       </c>
       <c r="F47" t="n">
-        <v>-256</v>
+        <v>-531</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>-0.0048</v>
+        <v>-0.01</v>
       </c>
       <c r="H47" t="n">
-        <v>1313</v>
+        <v>939</v>
       </c>
       <c r="I47" t="n">
-        <v>50958</v>
+        <v>51030</v>
       </c>
       <c r="J47" t="n">
-        <v>52127.25</v>
+        <v>51546.25</v>
       </c>
       <c r="K47" t="n">
-        <v>52551.5</v>
+        <v>52249.5</v>
       </c>
       <c r="L47" t="n">
-        <v>52975.75</v>
+        <v>52952.75</v>
       </c>
       <c r="M47" t="n">
-        <v>53772.5</v>
+        <v>53562.5</v>
       </c>
       <c r="N47" t="n">
-        <v>54569.25</v>
+        <v>54172.25</v>
       </c>
       <c r="O47" t="n">
-        <v>54621</v>
+        <v>54969</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4433,12 +4435,12 @@
       </c>
       <c r="R47" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S47" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S47" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T47" s="8" t="n">
@@ -4457,57 +4459,57 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>52844</v>
+        <v>52300</v>
       </c>
       <c r="C48" t="n">
-        <v>53113</v>
+        <v>52721</v>
       </c>
       <c r="D48" t="n">
-        <v>52174</v>
+        <v>51720</v>
       </c>
       <c r="E48" t="n">
-        <v>52375</v>
+        <v>52124</v>
       </c>
       <c r="F48" t="n">
-        <v>-531</v>
+        <v>-251</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0.01</v>
+        <v>-0.0048</v>
       </c>
       <c r="H48" t="n">
-        <v>939</v>
+        <v>1001</v>
       </c>
       <c r="I48" t="n">
-        <v>51030</v>
+        <v>51235</v>
       </c>
       <c r="J48" t="n">
-        <v>51546.25</v>
+        <v>51301.75</v>
       </c>
       <c r="K48" t="n">
-        <v>52249.5</v>
+        <v>51905.5</v>
       </c>
       <c r="L48" t="n">
-        <v>52952.75</v>
+        <v>52509.25</v>
       </c>
       <c r="M48" t="n">
-        <v>53562.5</v>
+        <v>52844.5</v>
       </c>
       <c r="N48" t="n">
-        <v>54172.25</v>
+        <v>53179.75</v>
       </c>
       <c r="O48" t="n">
-        <v>54969</v>
+        <v>54052</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4520,7 +4522,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S48" s="10" t="inlineStr">
+      <c r="S48" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4548,50 +4550,50 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>52300</v>
+        <v>52299</v>
       </c>
       <c r="C49" t="n">
-        <v>52721</v>
+        <v>53105</v>
       </c>
       <c r="D49" t="n">
-        <v>51720</v>
+        <v>51630</v>
       </c>
       <c r="E49" t="n">
-        <v>52124</v>
+        <v>52635</v>
       </c>
       <c r="F49" t="n">
-        <v>-251</v>
+        <v>511</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.0048</v>
+        <v>0.0098</v>
       </c>
       <c r="H49" t="n">
-        <v>1001</v>
+        <v>1475</v>
       </c>
       <c r="I49" t="n">
-        <v>51235</v>
+        <v>50719</v>
       </c>
       <c r="J49" t="n">
-        <v>51301.75</v>
+        <v>51074.75</v>
       </c>
       <c r="K49" t="n">
-        <v>51905.5</v>
+        <v>51623.5</v>
       </c>
       <c r="L49" t="n">
-        <v>52509.25</v>
+        <v>52172.25</v>
       </c>
       <c r="M49" t="n">
-        <v>52844.5</v>
+        <v>52624.5</v>
       </c>
       <c r="N49" t="n">
-        <v>53179.75</v>
+        <v>53076.75</v>
       </c>
       <c r="O49" t="n">
-        <v>54052</v>
+        <v>53722</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4599,21 +4601,23 @@
       <c r="Q49" s="6" t="n">
         <v/>
       </c>
-      <c r="R49" s="6" t="inlineStr">
+      <c r="R49" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S49" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S49" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T49" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U49" s="8" t="n">
-        <v/>
+      <c r="U49" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V49" s="8" t="n">
         <v/>
@@ -4625,57 +4629,57 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>52299</v>
+        <v>52780</v>
       </c>
       <c r="C50" t="n">
-        <v>53105</v>
+        <v>54884</v>
       </c>
       <c r="D50" t="n">
-        <v>51630</v>
+        <v>52777</v>
       </c>
       <c r="E50" t="n">
-        <v>52635</v>
+        <v>54152</v>
       </c>
       <c r="F50" t="n">
-        <v>511</v>
+        <v>1517</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.0098</v>
+        <v>0.0288</v>
       </c>
       <c r="H50" t="n">
-        <v>1475</v>
+        <v>2107</v>
       </c>
       <c r="I50" t="n">
-        <v>50719</v>
+        <v>50155</v>
       </c>
       <c r="J50" t="n">
-        <v>51074.75</v>
+        <v>51293.75</v>
       </c>
       <c r="K50" t="n">
-        <v>51623.5</v>
+        <v>51897.5</v>
       </c>
       <c r="L50" t="n">
-        <v>52172.25</v>
+        <v>52501.25</v>
       </c>
       <c r="M50" t="n">
-        <v>52624.5</v>
+        <v>53372.5</v>
       </c>
       <c r="N50" t="n">
-        <v>53076.75</v>
+        <v>54243.75</v>
       </c>
       <c r="O50" t="n">
-        <v>53722</v>
+        <v>54580</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4686,82 +4690,80 @@
       <c r="R50" s="6" t="n">
         <v/>
       </c>
-      <c r="S50" s="7" t="inlineStr">
+      <c r="S50" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T50" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U50" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U50" s="8" t="inlineStr">
+      <c r="V50" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="V50" s="8" t="n">
-        <v/>
-      </c>
       <c r="W50" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>52780</v>
+        <v>54133</v>
       </c>
       <c r="C51" t="n">
-        <v>54884</v>
+        <v>54336</v>
       </c>
       <c r="D51" t="n">
-        <v>52777</v>
+        <v>53715</v>
       </c>
       <c r="E51" t="n">
-        <v>54152</v>
+        <v>53807</v>
       </c>
       <c r="F51" t="n">
-        <v>1517</v>
+        <v>-345</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.0288</v>
+        <v>-0.0064</v>
       </c>
       <c r="H51" t="n">
-        <v>2107</v>
+        <v>621</v>
       </c>
       <c r="I51" t="n">
-        <v>50155</v>
+        <v>50670</v>
       </c>
       <c r="J51" t="n">
-        <v>51293.75</v>
+        <v>52205.75</v>
       </c>
       <c r="K51" t="n">
-        <v>51897.5</v>
+        <v>53098.5</v>
       </c>
       <c r="L51" t="n">
-        <v>52501.25</v>
+        <v>53991.25</v>
       </c>
       <c r="M51" t="n">
-        <v>53372.5</v>
+        <v>55205.5</v>
       </c>
       <c r="N51" t="n">
-        <v>54243.75</v>
+        <v>56419.75</v>
       </c>
       <c r="O51" t="n">
-        <v>54580</v>
+        <v>56991</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4774,91 +4776,95 @@
       </c>
       <c r="S51" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T51" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U51" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V51" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T51" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U51" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V51" s="8" t="n">
+        <v/>
       </c>
       <c r="W51" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr"/>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>54133</v>
+        <v>53790</v>
       </c>
       <c r="C52" t="n">
-        <v>54336</v>
+        <v>53840</v>
       </c>
       <c r="D52" t="n">
-        <v>53715</v>
+        <v>52812</v>
       </c>
       <c r="E52" t="n">
-        <v>53807</v>
+        <v>53353</v>
       </c>
       <c r="F52" t="n">
-        <v>-345</v>
+        <v>-454</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.0064</v>
+        <v>-0.008399999999999999</v>
       </c>
       <c r="H52" t="n">
-        <v>621</v>
+        <v>1028</v>
       </c>
       <c r="I52" t="n">
-        <v>50670</v>
+        <v>53094</v>
       </c>
       <c r="J52" t="n">
-        <v>52205.75</v>
+        <v>53076.75</v>
       </c>
       <c r="K52" t="n">
-        <v>53098.5</v>
+        <v>53496.5</v>
       </c>
       <c r="L52" t="n">
-        <v>53991.25</v>
+        <v>53916.25</v>
       </c>
       <c r="M52" t="n">
-        <v>55205.5</v>
+        <v>54117.5</v>
       </c>
       <c r="N52" t="n">
-        <v>56419.75</v>
+        <v>54318.75</v>
       </c>
       <c r="O52" t="n">
-        <v>56991</v>
-      </c>
-      <c r="P52" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q52" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R52" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S52" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+        <v>54957</v>
+      </c>
+      <c r="P52" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q52" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R52" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S52" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T52" s="8" t="n">
@@ -4877,76 +4883,70 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>53790</v>
+        <v>53367</v>
       </c>
       <c r="C53" t="n">
-        <v>53840</v>
+        <v>53862</v>
       </c>
       <c r="D53" t="n">
-        <v>52812</v>
+        <v>53210</v>
       </c>
       <c r="E53" t="n">
-        <v>53353</v>
+        <v>53584</v>
       </c>
       <c r="F53" t="n">
-        <v>-454</v>
+        <v>231</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.008399999999999999</v>
+        <v>0.0043</v>
       </c>
       <c r="H53" t="n">
-        <v>1028</v>
+        <v>652</v>
       </c>
       <c r="I53" t="n">
-        <v>53094</v>
+        <v>51784</v>
       </c>
       <c r="J53" t="n">
-        <v>53076.75</v>
+        <v>52338.5</v>
       </c>
       <c r="K53" t="n">
-        <v>53496.5</v>
+        <v>52839</v>
       </c>
       <c r="L53" t="n">
-        <v>53916.25</v>
+        <v>53339.5</v>
       </c>
       <c r="M53" t="n">
-        <v>54117.5</v>
+        <v>53867</v>
       </c>
       <c r="N53" t="n">
-        <v>54318.75</v>
+        <v>54394.5</v>
       </c>
       <c r="O53" t="n">
-        <v>54957</v>
-      </c>
-      <c r="P53" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q53" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R53" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+        <v>54868</v>
+      </c>
+      <c r="P53" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q53" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R53" s="6" t="n">
+        <v/>
       </c>
       <c r="S53" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T53" s="8" t="n">
@@ -4963,72 +4963,72 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>53367</v>
+        <v>53664</v>
       </c>
       <c r="C54" t="n">
-        <v>53862</v>
+        <v>53827</v>
       </c>
       <c r="D54" t="n">
-        <v>53210</v>
+        <v>52720</v>
       </c>
       <c r="E54" t="n">
-        <v>53584</v>
+        <v>53440</v>
       </c>
       <c r="F54" t="n">
-        <v>231</v>
+        <v>-144</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.0043</v>
+        <v>-0.0027</v>
       </c>
       <c r="H54" t="n">
-        <v>652</v>
+        <v>1107</v>
       </c>
       <c r="I54" t="n">
-        <v>51784</v>
+        <v>52558</v>
       </c>
       <c r="J54" t="n">
-        <v>52338.5</v>
+        <v>52956</v>
       </c>
       <c r="K54" t="n">
-        <v>52839</v>
+        <v>53258</v>
       </c>
       <c r="L54" t="n">
-        <v>53339.5</v>
+        <v>53560</v>
       </c>
       <c r="M54" t="n">
-        <v>53867</v>
+        <v>53910</v>
       </c>
       <c r="N54" t="n">
-        <v>54394.5</v>
+        <v>54260</v>
       </c>
       <c r="O54" t="n">
-        <v>54868</v>
+        <v>54514</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
       </c>
-      <c r="Q54" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R54" s="6" t="n">
-        <v/>
+      <c r="Q54" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R54" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S54" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T54" s="8" t="n">
@@ -5045,72 +5045,76 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr"/>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>53664</v>
+        <v>53261</v>
       </c>
       <c r="C55" t="n">
-        <v>53827</v>
+        <v>53336</v>
       </c>
       <c r="D55" t="n">
-        <v>52720</v>
+        <v>51992</v>
       </c>
       <c r="E55" t="n">
-        <v>53440</v>
+        <v>52585</v>
       </c>
       <c r="F55" t="n">
-        <v>-144</v>
+        <v>-855</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.0027</v>
+        <v>-0.016</v>
       </c>
       <c r="H55" t="n">
-        <v>1107</v>
+        <v>1344</v>
       </c>
       <c r="I55" t="n">
-        <v>52558</v>
+        <v>51613</v>
       </c>
       <c r="J55" t="n">
-        <v>52956</v>
+        <v>52416.25</v>
       </c>
       <c r="K55" t="n">
-        <v>53258</v>
+        <v>52886.5</v>
       </c>
       <c r="L55" t="n">
-        <v>53560</v>
+        <v>53356.75</v>
       </c>
       <c r="M55" t="n">
-        <v>53910</v>
+        <v>53993.5</v>
       </c>
       <c r="N55" t="n">
-        <v>54260</v>
+        <v>54630.25</v>
       </c>
       <c r="O55" t="n">
-        <v>54514</v>
+        <v>54934</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
       </c>
       <c r="Q55" s="6" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R55" s="6" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R55" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S55" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S55" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T55" s="8" t="n">
@@ -5136,65 +5140,63 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>53261</v>
+        <v>52376</v>
       </c>
       <c r="C56" t="n">
-        <v>53336</v>
+        <v>52672</v>
       </c>
       <c r="D56" t="n">
-        <v>51992</v>
+        <v>51209</v>
       </c>
       <c r="E56" t="n">
-        <v>52585</v>
+        <v>51761</v>
       </c>
       <c r="F56" t="n">
-        <v>-855</v>
+        <v>-824</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.016</v>
+        <v>-0.0157</v>
       </c>
       <c r="H56" t="n">
-        <v>1344</v>
+        <v>1463</v>
       </c>
       <c r="I56" t="n">
-        <v>51613</v>
+        <v>50648</v>
       </c>
       <c r="J56" t="n">
-        <v>52416.25</v>
+        <v>51201.5</v>
       </c>
       <c r="K56" t="n">
-        <v>52886.5</v>
+        <v>51913</v>
       </c>
       <c r="L56" t="n">
-        <v>53356.75</v>
+        <v>52624.5</v>
       </c>
       <c r="M56" t="n">
-        <v>53993.5</v>
+        <v>53257</v>
       </c>
       <c r="N56" t="n">
-        <v>54630.25</v>
+        <v>53889.5</v>
       </c>
       <c r="O56" t="n">
-        <v>54934</v>
+        <v>54680</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
       </c>
-      <c r="Q56" s="6" t="inlineStr">
+      <c r="Q56" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R56" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R56" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S56" s="10" t="inlineStr">
+      <c r="S56" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -5222,50 +5224,50 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>52376</v>
+        <v>52085</v>
       </c>
       <c r="C57" t="n">
-        <v>52672</v>
+        <v>52844</v>
       </c>
       <c r="D57" t="n">
-        <v>51209</v>
+        <v>51479</v>
       </c>
       <c r="E57" t="n">
-        <v>51761</v>
+        <v>52163</v>
       </c>
       <c r="F57" t="n">
-        <v>-824</v>
+        <v>402</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0157</v>
+        <v>0.0078</v>
       </c>
       <c r="H57" t="n">
-        <v>1463</v>
+        <v>1365</v>
       </c>
       <c r="I57" t="n">
-        <v>50648</v>
+        <v>49746</v>
       </c>
       <c r="J57" t="n">
-        <v>51201.5</v>
+        <v>50208.25</v>
       </c>
       <c r="K57" t="n">
-        <v>51913</v>
+        <v>51029.5</v>
       </c>
       <c r="L57" t="n">
-        <v>52624.5</v>
+        <v>51850.75</v>
       </c>
       <c r="M57" t="n">
-        <v>53257</v>
+        <v>52492.5</v>
       </c>
       <c r="N57" t="n">
-        <v>53889.5</v>
+        <v>53134.25</v>
       </c>
       <c r="O57" t="n">
-        <v>54680</v>
+        <v>54135</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5273,18 +5275,18 @@
       <c r="Q57" s="6" t="n">
         <v/>
       </c>
-      <c r="R57" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R57" s="6" t="n">
+        <v/>
       </c>
       <c r="S57" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T57" s="8" t="n">
-        <v/>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U57" s="8" t="n">
         <v/>
@@ -5297,95 +5299,7 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="B58" t="n">
-        <v>52085</v>
-      </c>
-      <c r="C58" t="n">
-        <v>52844</v>
-      </c>
-      <c r="D58" t="n">
-        <v>51654</v>
-      </c>
-      <c r="E58" t="n">
-        <v>51669</v>
-      </c>
-      <c r="F58" t="n">
-        <v>-92</v>
-      </c>
-      <c r="G58" s="5" t="n">
-        <v>-0.0018</v>
-      </c>
-      <c r="H58" t="n">
-        <v>1190</v>
-      </c>
-      <c r="I58" t="n">
-        <v>49746</v>
-      </c>
-      <c r="J58" t="n">
-        <v>50208.25</v>
-      </c>
-      <c r="K58" t="n">
-        <v>51029.5</v>
-      </c>
-      <c r="L58" t="n">
-        <v>51850.75</v>
-      </c>
-      <c r="M58" t="n">
-        <v>52492.5</v>
-      </c>
-      <c r="N58" t="n">
-        <v>53134.25</v>
-      </c>
-      <c r="O58" t="n">
-        <v>54135</v>
-      </c>
-      <c r="P58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S58" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W58" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X57" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/YM_weekly.xlsx
+++ b/three_gate/analysis/YM_weekly.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X57"/>
+  <dimension ref="A1:X58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5301,6 +5301,90 @@
       </c>
       <c r="X57" t="inlineStr"/>
     </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>51845</v>
+      </c>
+      <c r="C58" t="n">
+        <v>51848</v>
+      </c>
+      <c r="D58" t="n">
+        <v>51815</v>
+      </c>
+      <c r="E58" t="n">
+        <v>51820</v>
+      </c>
+      <c r="F58" t="n">
+        <v>-343</v>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v>-0.0066</v>
+      </c>
+      <c r="H58" t="n">
+        <v>33</v>
+      </c>
+      <c r="I58" t="n">
+        <v>50114</v>
+      </c>
+      <c r="J58" t="n">
+        <v>50798.75</v>
+      </c>
+      <c r="K58" t="n">
+        <v>51480.5</v>
+      </c>
+      <c r="L58" t="n">
+        <v>52162.25</v>
+      </c>
+      <c r="M58" t="n">
+        <v>52845.5</v>
+      </c>
+      <c r="N58" t="n">
+        <v>53528.75</v>
+      </c>
+      <c r="O58" t="n">
+        <v>54209</v>
+      </c>
+      <c r="P58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R58" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S58" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W58" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/three_gate/analysis/YM_weekly.xlsx
+++ b/three_gate/analysis/YM_weekly.xlsx
@@ -5308,25 +5308,25 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>51845</v>
+        <v>52140</v>
       </c>
       <c r="C58" t="n">
-        <v>51848</v>
+        <v>52153</v>
       </c>
       <c r="D58" t="n">
-        <v>51815</v>
+        <v>51744</v>
       </c>
       <c r="E58" t="n">
-        <v>51820</v>
+        <v>51782</v>
       </c>
       <c r="F58" t="n">
-        <v>-343</v>
+        <v>-381</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0066</v>
+        <v>-0.0073</v>
       </c>
       <c r="H58" t="n">
-        <v>33</v>
+        <v>409</v>
       </c>
       <c r="I58" t="n">
         <v>50114</v>

--- a/three_gate/analysis/YM_weekly.xlsx
+++ b/three_gate/analysis/YM_weekly.xlsx
@@ -659,28 +659,30 @@
         <v>832</v>
       </c>
       <c r="I2" t="n">
-        <v>44565</v>
+        <v>45047</v>
       </c>
       <c r="J2" t="n">
-        <v>45037.5</v>
+        <v>45218.25</v>
       </c>
       <c r="K2" t="n">
-        <v>45292</v>
+        <v>45412.5</v>
       </c>
       <c r="L2" t="n">
-        <v>45546.5</v>
+        <v>45606.75</v>
       </c>
       <c r="M2" t="n">
-        <v>45910</v>
+        <v>45789.5</v>
       </c>
       <c r="N2" t="n">
-        <v>46273.5</v>
+        <v>45972.25</v>
       </c>
       <c r="O2" t="n">
-        <v>46419</v>
-      </c>
-      <c r="P2" s="6" t="n">
-        <v/>
+        <v>46178</v>
+      </c>
+      <c r="P2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="Q2" s="6" t="inlineStr">
         <is>
@@ -689,16 +691,18 @@
       </c>
       <c r="R2" s="6" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S2" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
-      </c>
-      <c r="S2" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="n">
-        <v/>
       </c>
       <c r="U2" s="8" t="n">
         <v/>
@@ -5314,19 +5318,19 @@
         <v>52153</v>
       </c>
       <c r="D58" t="n">
-        <v>51744</v>
+        <v>51307</v>
       </c>
       <c r="E58" t="n">
-        <v>51782</v>
+        <v>51335</v>
       </c>
       <c r="F58" t="n">
-        <v>-381</v>
+        <v>-828</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0073</v>
+        <v>-0.0159</v>
       </c>
       <c r="H58" t="n">
-        <v>409</v>
+        <v>846</v>
       </c>
       <c r="I58" t="n">
         <v>50114</v>
@@ -5381,7 +5385,7 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/YM_weekly.xlsx
+++ b/three_gate/analysis/YM_weekly.xlsx
@@ -5318,19 +5318,19 @@
         <v>52153</v>
       </c>
       <c r="D58" t="n">
-        <v>51307</v>
+        <v>51218</v>
       </c>
       <c r="E58" t="n">
-        <v>51335</v>
+        <v>51243</v>
       </c>
       <c r="F58" t="n">
-        <v>-828</v>
+        <v>-920</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0159</v>
+        <v>-0.0176</v>
       </c>
       <c r="H58" t="n">
-        <v>846</v>
+        <v>935</v>
       </c>
       <c r="I58" t="n">
         <v>50114</v>

--- a/three_gate/analysis/YM_weekly.xlsx
+++ b/three_gate/analysis/YM_weekly.xlsx
@@ -104,14 +104,14 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X58"/>
+  <dimension ref="A1:X57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,76 +634,70 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>45685</v>
+        <v>45475</v>
       </c>
       <c r="C2" t="n">
-        <v>45832</v>
+        <v>46176</v>
       </c>
       <c r="D2" t="n">
-        <v>45000</v>
+        <v>45321</v>
       </c>
       <c r="E2" t="n">
-        <v>45459</v>
+        <v>45854</v>
       </c>
       <c r="F2" t="n">
-        <v>-142</v>
+        <v>395</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>-0.0031</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="H2" t="n">
-        <v>832</v>
+        <v>855</v>
       </c>
       <c r="I2" t="n">
-        <v>45047</v>
+        <v>44168</v>
       </c>
       <c r="J2" t="n">
-        <v>45218.25</v>
+        <v>44648.5</v>
       </c>
       <c r="K2" t="n">
-        <v>45412.5</v>
+        <v>45043</v>
       </c>
       <c r="L2" t="n">
-        <v>45606.75</v>
+        <v>45437.5</v>
       </c>
       <c r="M2" t="n">
-        <v>45789.5</v>
+        <v>45875</v>
       </c>
       <c r="N2" t="n">
-        <v>45972.25</v>
+        <v>46312.5</v>
       </c>
       <c r="O2" t="n">
-        <v>46178</v>
-      </c>
-      <c r="P2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R2" s="6" t="inlineStr">
+        <v>46664</v>
+      </c>
+      <c r="P2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S2" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S2" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="U2" s="8" t="n">
         <v/>
       </c>
@@ -715,59 +709,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>45475</v>
+        <v>45860</v>
       </c>
       <c r="C3" t="n">
-        <v>46176</v>
+        <v>46379</v>
       </c>
       <c r="D3" t="n">
-        <v>45321</v>
+        <v>45680</v>
       </c>
       <c r="E3" t="n">
-        <v>45854</v>
+        <v>46328</v>
       </c>
       <c r="F3" t="n">
-        <v>395</v>
+        <v>474</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.008699999999999999</v>
+        <v>0.0103</v>
       </c>
       <c r="H3" t="n">
-        <v>855</v>
+        <v>699</v>
       </c>
       <c r="I3" t="n">
-        <v>44168</v>
+        <v>44466</v>
       </c>
       <c r="J3" t="n">
-        <v>44648.5</v>
+        <v>45051.75</v>
       </c>
       <c r="K3" t="n">
-        <v>45043</v>
+        <v>45426.5</v>
       </c>
       <c r="L3" t="n">
-        <v>45437.5</v>
+        <v>45801.25</v>
       </c>
       <c r="M3" t="n">
-        <v>45875</v>
+        <v>46281.5</v>
       </c>
       <c r="N3" t="n">
-        <v>46312.5</v>
+        <v>46761.75</v>
       </c>
       <c r="O3" t="n">
-        <v>46664</v>
+        <v>47031</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -778,7 +768,7 @@
       <c r="R3" s="6" t="n">
         <v/>
       </c>
-      <c r="S3" s="10" t="inlineStr">
+      <c r="S3" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -804,50 +794,50 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>45860</v>
+        <v>46605</v>
       </c>
       <c r="C4" t="n">
-        <v>46379</v>
+        <v>47055</v>
       </c>
       <c r="D4" t="n">
-        <v>45680</v>
+        <v>46098</v>
       </c>
       <c r="E4" t="n">
-        <v>46328</v>
+        <v>46556</v>
       </c>
       <c r="F4" t="n">
-        <v>474</v>
+        <v>228</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.0103</v>
+        <v>0.0049</v>
       </c>
       <c r="H4" t="n">
-        <v>699</v>
+        <v>957</v>
       </c>
       <c r="I4" t="n">
-        <v>44466</v>
+        <v>44981</v>
       </c>
       <c r="J4" t="n">
-        <v>45051.75</v>
+        <v>45778.25</v>
       </c>
       <c r="K4" t="n">
-        <v>45426.5</v>
+        <v>45978.5</v>
       </c>
       <c r="L4" t="n">
-        <v>45801.25</v>
+        <v>46178.75</v>
       </c>
       <c r="M4" t="n">
-        <v>46281.5</v>
+        <v>46677.5</v>
       </c>
       <c r="N4" t="n">
-        <v>46761.75</v>
+        <v>47176.25</v>
       </c>
       <c r="O4" t="n">
-        <v>47031</v>
+        <v>47078</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -858,7 +848,7 @@
       <c r="R4" s="6" t="n">
         <v/>
       </c>
-      <c r="S4" s="10" t="inlineStr">
+      <c r="S4" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -884,50 +874,50 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>46605</v>
+        <v>46565</v>
       </c>
       <c r="C5" t="n">
-        <v>47055</v>
+        <v>47323</v>
       </c>
       <c r="D5" t="n">
-        <v>46098</v>
+        <v>46335</v>
       </c>
       <c r="E5" t="n">
-        <v>46556</v>
+        <v>47031</v>
       </c>
       <c r="F5" t="n">
-        <v>228</v>
+        <v>475</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.0049</v>
+        <v>0.0102</v>
       </c>
       <c r="H5" t="n">
-        <v>957</v>
+        <v>988</v>
       </c>
       <c r="I5" t="n">
-        <v>44981</v>
+        <v>45141</v>
       </c>
       <c r="J5" t="n">
-        <v>45778.25</v>
+        <v>45588.75</v>
       </c>
       <c r="K5" t="n">
-        <v>45978.5</v>
+        <v>46077.5</v>
       </c>
       <c r="L5" t="n">
-        <v>46178.75</v>
+        <v>46566.25</v>
       </c>
       <c r="M5" t="n">
-        <v>46677.5</v>
+        <v>47034.5</v>
       </c>
       <c r="N5" t="n">
-        <v>47176.25</v>
+        <v>47502.75</v>
       </c>
       <c r="O5" t="n">
-        <v>47078</v>
+        <v>48012</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -938,7 +928,7 @@
       <c r="R5" s="6" t="n">
         <v/>
       </c>
-      <c r="S5" s="10" t="inlineStr">
+      <c r="S5" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -964,69 +954,73 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>46565</v>
+        <v>47048</v>
       </c>
       <c r="C6" t="n">
-        <v>47323</v>
+        <v>47162</v>
       </c>
       <c r="D6" t="n">
-        <v>46335</v>
+        <v>45387</v>
       </c>
       <c r="E6" t="n">
-        <v>47031</v>
+        <v>45706</v>
       </c>
       <c r="F6" t="n">
-        <v>475</v>
+        <v>-1325</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.0102</v>
+        <v>-0.0282</v>
       </c>
       <c r="H6" t="n">
-        <v>988</v>
+        <v>1775</v>
       </c>
       <c r="I6" t="n">
-        <v>45141</v>
+        <v>45347</v>
       </c>
       <c r="J6" t="n">
-        <v>45588.75</v>
+        <v>46144</v>
       </c>
       <c r="K6" t="n">
-        <v>46077.5</v>
+        <v>46537</v>
       </c>
       <c r="L6" t="n">
-        <v>46566.25</v>
+        <v>46930</v>
       </c>
       <c r="M6" t="n">
-        <v>47034.5</v>
+        <v>47525</v>
       </c>
       <c r="N6" t="n">
-        <v>47502.75</v>
+        <v>48120</v>
       </c>
       <c r="O6" t="n">
-        <v>48012</v>
-      </c>
-      <c r="P6" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q6" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R6" s="6" t="n">
-        <v/>
+        <v>48311</v>
+      </c>
+      <c r="P6" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q6" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R6" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S6" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="n">
+        <v/>
       </c>
       <c r="U6" s="8" t="n">
         <v/>
@@ -1034,9 +1028,9 @@
       <c r="V6" s="8" t="n">
         <v/>
       </c>
-      <c r="W6" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W6" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X6" t="inlineStr"/>
@@ -1044,74 +1038,70 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>47048</v>
+        <v>45837</v>
       </c>
       <c r="C7" t="n">
-        <v>47162</v>
+        <v>46915</v>
       </c>
       <c r="D7" t="n">
-        <v>45387</v>
+        <v>45605</v>
       </c>
       <c r="E7" t="n">
-        <v>45706</v>
+        <v>46381</v>
       </c>
       <c r="F7" t="n">
-        <v>-1325</v>
+        <v>675</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-0.0282</v>
+        <v>0.0148</v>
       </c>
       <c r="H7" t="n">
-        <v>1775</v>
+        <v>1310</v>
       </c>
       <c r="I7" t="n">
-        <v>45347</v>
+        <v>43612</v>
       </c>
       <c r="J7" t="n">
-        <v>46144</v>
+        <v>43646.75</v>
       </c>
       <c r="K7" t="n">
-        <v>46537</v>
+        <v>44818.5</v>
       </c>
       <c r="L7" t="n">
-        <v>46930</v>
+        <v>45990.25</v>
       </c>
       <c r="M7" t="n">
-        <v>47525</v>
+        <v>46593.5</v>
       </c>
       <c r="N7" t="n">
-        <v>48120</v>
+        <v>47196.75</v>
       </c>
       <c r="O7" t="n">
-        <v>48311</v>
-      </c>
-      <c r="P7" s="6" t="inlineStr">
+        <v>48937</v>
+      </c>
+      <c r="P7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S7" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q7" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R7" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S7" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="n">
-        <v/>
-      </c>
       <c r="U7" s="8" t="n">
         <v/>
       </c>
@@ -1123,55 +1113,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr"/>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>45837</v>
+        <v>46489</v>
       </c>
       <c r="C8" t="n">
-        <v>46915</v>
+        <v>47508</v>
       </c>
       <c r="D8" t="n">
-        <v>45605</v>
+        <v>46316</v>
       </c>
       <c r="E8" t="n">
-        <v>46381</v>
+        <v>47396</v>
       </c>
       <c r="F8" t="n">
-        <v>675</v>
+        <v>1015</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.0148</v>
+        <v>0.0219</v>
       </c>
       <c r="H8" t="n">
-        <v>1310</v>
+        <v>1192</v>
       </c>
       <c r="I8" t="n">
-        <v>43612</v>
+        <v>44295</v>
       </c>
       <c r="J8" t="n">
-        <v>43646.75</v>
+        <v>45131.5</v>
       </c>
       <c r="K8" t="n">
-        <v>44818.5</v>
+        <v>45726</v>
       </c>
       <c r="L8" t="n">
-        <v>45990.25</v>
+        <v>46320.5</v>
       </c>
       <c r="M8" t="n">
-        <v>46593.5</v>
+        <v>47036</v>
       </c>
       <c r="N8" t="n">
-        <v>47196.75</v>
+        <v>47751.5</v>
       </c>
       <c r="O8" t="n">
-        <v>48937</v>
+        <v>48225</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1182,19 +1176,21 @@
       <c r="R8" s="6" t="n">
         <v/>
       </c>
-      <c r="S8" s="10" t="inlineStr">
+      <c r="S8" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T8" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U8" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U8" s="8" t="n">
-        <v/>
-      </c>
       <c r="V8" s="8" t="n">
         <v/>
       </c>
@@ -1205,57 +1201,57 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>46489</v>
+        <v>47711</v>
       </c>
       <c r="C9" t="n">
-        <v>47508</v>
+        <v>48214</v>
       </c>
       <c r="D9" t="n">
-        <v>46316</v>
+        <v>47488</v>
       </c>
       <c r="E9" t="n">
-        <v>47396</v>
+        <v>47722</v>
       </c>
       <c r="F9" t="n">
-        <v>1015</v>
+        <v>326</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.0219</v>
+        <v>0.0069</v>
       </c>
       <c r="H9" t="n">
-        <v>1192</v>
+        <v>726</v>
       </c>
       <c r="I9" t="n">
-        <v>44295</v>
+        <v>45124</v>
       </c>
       <c r="J9" t="n">
-        <v>45131.5</v>
+        <v>46446</v>
       </c>
       <c r="K9" t="n">
-        <v>45726</v>
+        <v>46800</v>
       </c>
       <c r="L9" t="n">
-        <v>46320.5</v>
+        <v>47154</v>
       </c>
       <c r="M9" t="n">
-        <v>47036</v>
+        <v>47992</v>
       </c>
       <c r="N9" t="n">
-        <v>47751.5</v>
+        <v>48830</v>
       </c>
       <c r="O9" t="n">
-        <v>48225</v>
+        <v>48700</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1266,20 +1262,18 @@
       <c r="R9" s="6" t="n">
         <v/>
       </c>
-      <c r="S9" s="10" t="inlineStr">
+      <c r="S9" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T9" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U9" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U9" s="8" t="n">
+        <v/>
       </c>
       <c r="V9" s="8" t="n">
         <v/>
@@ -1298,69 +1292,73 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>47711</v>
+        <v>47735</v>
       </c>
       <c r="C10" t="n">
-        <v>48214</v>
+        <v>47869</v>
       </c>
       <c r="D10" t="n">
-        <v>47488</v>
+        <v>46574</v>
       </c>
       <c r="E10" t="n">
-        <v>47722</v>
+        <v>47085</v>
       </c>
       <c r="F10" t="n">
-        <v>326</v>
+        <v>-637</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.0069</v>
+        <v>-0.0133</v>
       </c>
       <c r="H10" t="n">
-        <v>726</v>
+        <v>1295</v>
       </c>
       <c r="I10" t="n">
-        <v>45124</v>
+        <v>46762</v>
       </c>
       <c r="J10" t="n">
-        <v>46446</v>
+        <v>46931.5</v>
       </c>
       <c r="K10" t="n">
-        <v>46800</v>
+        <v>47359</v>
       </c>
       <c r="L10" t="n">
-        <v>47154</v>
+        <v>47786.5</v>
       </c>
       <c r="M10" t="n">
-        <v>47992</v>
+        <v>48085</v>
       </c>
       <c r="N10" t="n">
-        <v>48830</v>
+        <v>48383.5</v>
       </c>
       <c r="O10" t="n">
-        <v>48700</v>
-      </c>
-      <c r="P10" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q10" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R10" s="6" t="n">
-        <v/>
+        <v>48940</v>
+      </c>
+      <c r="P10" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q10" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R10" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S10" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="n">
+        <v/>
       </c>
       <c r="U10" s="8" t="n">
         <v/>
@@ -1373,86 +1371,80 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>47735</v>
+        <v>47208</v>
       </c>
       <c r="C11" t="n">
-        <v>47869</v>
+        <v>48528</v>
       </c>
       <c r="D11" t="n">
-        <v>46574</v>
+        <v>46939</v>
       </c>
       <c r="E11" t="n">
-        <v>47085</v>
+        <v>47229</v>
       </c>
       <c r="F11" t="n">
-        <v>-637</v>
+        <v>144</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0.0133</v>
+        <v>0.0031</v>
       </c>
       <c r="H11" t="n">
-        <v>1295</v>
+        <v>1589</v>
       </c>
       <c r="I11" t="n">
-        <v>46762</v>
+        <v>45279</v>
       </c>
       <c r="J11" t="n">
-        <v>46931.5</v>
+        <v>45721.75</v>
       </c>
       <c r="K11" t="n">
-        <v>47359</v>
+        <v>46437.5</v>
       </c>
       <c r="L11" t="n">
-        <v>47786.5</v>
+        <v>47153.25</v>
       </c>
       <c r="M11" t="n">
-        <v>48085</v>
+        <v>47732.5</v>
       </c>
       <c r="N11" t="n">
-        <v>48383.5</v>
+        <v>48311.75</v>
       </c>
       <c r="O11" t="n">
-        <v>48940</v>
-      </c>
-      <c r="P11" s="6" t="inlineStr">
+        <v>49164</v>
+      </c>
+      <c r="P11" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q11" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R11" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S11" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q11" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R11" s="6" t="inlineStr">
+      <c r="U11" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S11" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U11" s="8" t="n">
-        <v/>
-      </c>
       <c r="V11" s="8" t="n">
         <v/>
       </c>
@@ -1461,55 +1453,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr"/>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>47208</v>
+        <v>47237</v>
       </c>
       <c r="C12" t="n">
-        <v>48528</v>
+        <v>47368</v>
       </c>
       <c r="D12" t="n">
-        <v>46939</v>
+        <v>45779</v>
       </c>
       <c r="E12" t="n">
-        <v>47229</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="n">
-        <v>144</v>
+        <v>-908</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.0031</v>
+        <v>-0.0192</v>
       </c>
       <c r="H12" t="n">
         <v>1589</v>
       </c>
       <c r="I12" t="n">
-        <v>45279</v>
+        <v>45350</v>
       </c>
       <c r="J12" t="n">
-        <v>45721.75</v>
+        <v>45387.75</v>
       </c>
       <c r="K12" t="n">
-        <v>46437.5</v>
+        <v>46434.5</v>
       </c>
       <c r="L12" t="n">
-        <v>47153.25</v>
+        <v>47481.25</v>
       </c>
       <c r="M12" t="n">
-        <v>47732.5</v>
+        <v>48023.5</v>
       </c>
       <c r="N12" t="n">
-        <v>48311.75</v>
+        <v>48565.75</v>
       </c>
       <c r="O12" t="n">
-        <v>49164</v>
+        <v>50117</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1517,23 +1513,21 @@
       <c r="Q12" s="6" t="n">
         <v/>
       </c>
-      <c r="R12" s="6" t="n">
-        <v/>
+      <c r="R12" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S12" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U12" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U12" s="8" t="n">
+        <v/>
       </c>
       <c r="V12" s="8" t="n">
         <v/>
@@ -1543,59 +1537,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>47237</v>
+        <v>46504</v>
       </c>
       <c r="C13" t="n">
-        <v>47368</v>
+        <v>47796</v>
       </c>
       <c r="D13" t="n">
-        <v>45779</v>
+        <v>46165</v>
       </c>
       <c r="E13" t="n">
-        <v>46321</v>
+        <v>47743</v>
       </c>
       <c r="F13" t="n">
-        <v>-908</v>
+        <v>1422</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.0192</v>
+        <v>0.0307</v>
       </c>
       <c r="H13" t="n">
-        <v>1589</v>
+        <v>1631</v>
       </c>
       <c r="I13" t="n">
-        <v>45350</v>
+        <v>44190</v>
       </c>
       <c r="J13" t="n">
-        <v>45387.75</v>
+        <v>44605.75</v>
       </c>
       <c r="K13" t="n">
-        <v>46434.5</v>
+        <v>45526.5</v>
       </c>
       <c r="L13" t="n">
-        <v>47481.25</v>
+        <v>46447.25</v>
       </c>
       <c r="M13" t="n">
-        <v>48023.5</v>
+        <v>47115.5</v>
       </c>
       <c r="N13" t="n">
-        <v>48565.75</v>
+        <v>47783.75</v>
       </c>
       <c r="O13" t="n">
-        <v>50117</v>
+        <v>48957</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1603,22 +1593,24 @@
       <c r="Q13" s="6" t="n">
         <v/>
       </c>
-      <c r="R13" s="6" t="inlineStr">
+      <c r="R13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S13" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U13" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S13" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U13" s="8" t="n">
-        <v/>
-      </c>
       <c r="V13" s="8" t="n">
         <v/>
       </c>
@@ -1627,55 +1619,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr"/>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>46504</v>
+        <v>47741</v>
       </c>
       <c r="C14" t="n">
-        <v>47796</v>
+        <v>48184</v>
       </c>
       <c r="D14" t="n">
-        <v>46165</v>
+        <v>47269</v>
       </c>
       <c r="E14" t="n">
-        <v>47743</v>
+        <v>48001</v>
       </c>
       <c r="F14" t="n">
-        <v>1422</v>
+        <v>258</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0307</v>
+        <v>0.0054</v>
       </c>
       <c r="H14" t="n">
-        <v>1631</v>
+        <v>915</v>
       </c>
       <c r="I14" t="n">
-        <v>44190</v>
+        <v>44534</v>
       </c>
       <c r="J14" t="n">
-        <v>44605.75</v>
+        <v>46493.25</v>
       </c>
       <c r="K14" t="n">
-        <v>45526.5</v>
+        <v>46927.5</v>
       </c>
       <c r="L14" t="n">
-        <v>46447.25</v>
+        <v>47361.75</v>
       </c>
       <c r="M14" t="n">
-        <v>47115.5</v>
+        <v>48558.5</v>
       </c>
       <c r="N14" t="n">
-        <v>47783.75</v>
+        <v>49755.25</v>
       </c>
       <c r="O14" t="n">
-        <v>48957</v>
+        <v>49427</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1686,20 +1682,18 @@
       <c r="R14" s="6" t="n">
         <v/>
       </c>
-      <c r="S14" s="10" t="inlineStr">
+      <c r="S14" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T14" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U14" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U14" s="8" t="n">
+        <v/>
       </c>
       <c r="V14" s="8" t="n">
         <v/>
@@ -1718,50 +1712,50 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>47741</v>
+        <v>48015</v>
       </c>
       <c r="C15" t="n">
-        <v>48184</v>
+        <v>48917</v>
       </c>
       <c r="D15" t="n">
-        <v>47269</v>
+        <v>47504</v>
       </c>
       <c r="E15" t="n">
-        <v>48001</v>
+        <v>48474</v>
       </c>
       <c r="F15" t="n">
-        <v>258</v>
+        <v>473</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.0054</v>
+        <v>0.009900000000000001</v>
       </c>
       <c r="H15" t="n">
-        <v>915</v>
+        <v>1413</v>
       </c>
       <c r="I15" t="n">
-        <v>44534</v>
+        <v>46354</v>
       </c>
       <c r="J15" t="n">
-        <v>46493.25</v>
+        <v>47223.25</v>
       </c>
       <c r="K15" t="n">
-        <v>46927.5</v>
+        <v>47543.5</v>
       </c>
       <c r="L15" t="n">
-        <v>47361.75</v>
+        <v>47863.75</v>
       </c>
       <c r="M15" t="n">
-        <v>48558.5</v>
+        <v>48458.5</v>
       </c>
       <c r="N15" t="n">
-        <v>49755.25</v>
+        <v>49053.25</v>
       </c>
       <c r="O15" t="n">
-        <v>49427</v>
+        <v>49099</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1769,10 +1763,12 @@
       <c r="Q15" s="6" t="n">
         <v/>
       </c>
-      <c r="R15" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S15" s="10" t="inlineStr">
+      <c r="R15" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S15" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1802,50 +1798,50 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>48015</v>
+        <v>48517</v>
       </c>
       <c r="C16" t="n">
-        <v>48917</v>
+        <v>48745</v>
       </c>
       <c r="D16" t="n">
-        <v>47504</v>
+        <v>47809</v>
       </c>
       <c r="E16" t="n">
-        <v>48474</v>
+        <v>48090</v>
       </c>
       <c r="F16" t="n">
-        <v>473</v>
+        <v>-384</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.009900000000000001</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="H16" t="n">
-        <v>1413</v>
+        <v>936</v>
       </c>
       <c r="I16" t="n">
-        <v>46354</v>
+        <v>46091</v>
       </c>
       <c r="J16" t="n">
-        <v>47223.25</v>
+        <v>47192.75</v>
       </c>
       <c r="K16" t="n">
-        <v>47543.5</v>
+        <v>47767.5</v>
       </c>
       <c r="L16" t="n">
-        <v>47863.75</v>
+        <v>48342.25</v>
       </c>
       <c r="M16" t="n">
-        <v>48458.5</v>
+        <v>49180.5</v>
       </c>
       <c r="N16" t="n">
-        <v>49053.25</v>
+        <v>50018.75</v>
       </c>
       <c r="O16" t="n">
-        <v>49099</v>
+        <v>50330</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1853,20 +1849,16 @@
       <c r="Q16" s="6" t="n">
         <v/>
       </c>
-      <c r="R16" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R16" s="6" t="n">
+        <v/>
       </c>
       <c r="S16" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="n">
+        <v/>
       </c>
       <c r="U16" s="8" t="n">
         <v/>
@@ -1881,57 +1873,57 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>48517</v>
+        <v>48600</v>
       </c>
       <c r="C17" t="n">
-        <v>48745</v>
+        <v>49086</v>
       </c>
       <c r="D17" t="n">
-        <v>47809</v>
+        <v>48458</v>
       </c>
       <c r="E17" t="n">
-        <v>48090</v>
+        <v>48998</v>
       </c>
       <c r="F17" t="n">
-        <v>-384</v>
+        <v>908</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-0.007900000000000001</v>
+        <v>0.0189</v>
       </c>
       <c r="H17" t="n">
-        <v>936</v>
+        <v>628</v>
       </c>
       <c r="I17" t="n">
-        <v>46091</v>
+        <v>46873</v>
       </c>
       <c r="J17" t="n">
-        <v>47192.75</v>
+        <v>47060.5</v>
       </c>
       <c r="K17" t="n">
-        <v>47767.5</v>
+        <v>47622</v>
       </c>
       <c r="L17" t="n">
-        <v>48342.25</v>
+        <v>48183.5</v>
       </c>
       <c r="M17" t="n">
-        <v>49180.5</v>
+        <v>48558</v>
       </c>
       <c r="N17" t="n">
-        <v>50018.75</v>
+        <v>48932.5</v>
       </c>
       <c r="O17" t="n">
-        <v>50330</v>
+        <v>49681</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1944,100 +1936,100 @@
       </c>
       <c r="S17" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U17" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U17" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V17" s="8" t="n">
         <v/>
       </c>
-      <c r="W17" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W17" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>48600</v>
+        <v>48998</v>
       </c>
       <c r="C18" t="n">
-        <v>49086</v>
+        <v>49052</v>
       </c>
       <c r="D18" t="n">
-        <v>48458</v>
+        <v>48092</v>
       </c>
       <c r="E18" t="n">
-        <v>48998</v>
+        <v>48616</v>
       </c>
       <c r="F18" t="n">
-        <v>908</v>
+        <v>-382</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0189</v>
+        <v>-0.0078</v>
       </c>
       <c r="H18" t="n">
-        <v>628</v>
+        <v>960</v>
       </c>
       <c r="I18" t="n">
-        <v>46873</v>
+        <v>47830</v>
       </c>
       <c r="J18" t="n">
-        <v>47060.5</v>
+        <v>48483</v>
       </c>
       <c r="K18" t="n">
-        <v>47622</v>
+        <v>48684</v>
       </c>
       <c r="L18" t="n">
-        <v>48183.5</v>
+        <v>48885</v>
       </c>
       <c r="M18" t="n">
-        <v>48558</v>
+        <v>49312</v>
       </c>
       <c r="N18" t="n">
-        <v>48932.5</v>
+        <v>49739</v>
       </c>
       <c r="O18" t="n">
-        <v>49681</v>
+        <v>49714</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
       </c>
-      <c r="Q18" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R18" s="6" t="n">
-        <v/>
+      <c r="Q18" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R18" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S18" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U18" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U18" s="8" t="n">
+        <v/>
       </c>
       <c r="V18" s="8" t="n">
         <v/>
@@ -2047,80 +2039,84 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr"/>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>48998</v>
+        <v>48653</v>
       </c>
       <c r="C19" t="n">
-        <v>49052</v>
+        <v>49876</v>
       </c>
       <c r="D19" t="n">
-        <v>48092</v>
+        <v>48556</v>
       </c>
       <c r="E19" t="n">
-        <v>48616</v>
+        <v>49726</v>
       </c>
       <c r="F19" t="n">
-        <v>-382</v>
+        <v>1110</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-0.0078</v>
+        <v>0.0228</v>
       </c>
       <c r="H19" t="n">
-        <v>960</v>
+        <v>1320</v>
       </c>
       <c r="I19" t="n">
-        <v>47830</v>
+        <v>47132</v>
       </c>
       <c r="J19" t="n">
-        <v>48483</v>
+        <v>47678</v>
       </c>
       <c r="K19" t="n">
-        <v>48684</v>
+        <v>48136</v>
       </c>
       <c r="L19" t="n">
-        <v>48885</v>
+        <v>48594</v>
       </c>
       <c r="M19" t="n">
-        <v>49312</v>
+        <v>49096</v>
       </c>
       <c r="N19" t="n">
-        <v>49739</v>
+        <v>49598</v>
       </c>
       <c r="O19" t="n">
-        <v>49714</v>
+        <v>50012</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
       </c>
-      <c r="Q19" s="6" t="inlineStr">
+      <c r="Q19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S19" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R19" s="6" t="inlineStr">
+      <c r="U19" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S19" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U19" s="8" t="n">
-        <v/>
-      </c>
       <c r="V19" s="8" t="n">
         <v/>
       </c>
@@ -2129,59 +2125,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>48653</v>
+        <v>49720</v>
       </c>
       <c r="C20" t="n">
-        <v>49876</v>
+        <v>49901</v>
       </c>
       <c r="D20" t="n">
-        <v>48556</v>
+        <v>49057</v>
       </c>
       <c r="E20" t="n">
-        <v>49726</v>
+        <v>49547</v>
       </c>
       <c r="F20" t="n">
-        <v>1110</v>
+        <v>-179</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.0228</v>
+        <v>-0.0036</v>
       </c>
       <c r="H20" t="n">
-        <v>1320</v>
+        <v>844</v>
       </c>
       <c r="I20" t="n">
-        <v>47132</v>
+        <v>47236</v>
       </c>
       <c r="J20" t="n">
-        <v>47678</v>
+        <v>48661</v>
       </c>
       <c r="K20" t="n">
-        <v>48136</v>
+        <v>49066</v>
       </c>
       <c r="L20" t="n">
-        <v>48594</v>
+        <v>49471</v>
       </c>
       <c r="M20" t="n">
-        <v>49096</v>
+        <v>50386</v>
       </c>
       <c r="N20" t="n">
-        <v>49598</v>
+        <v>51301</v>
       </c>
       <c r="O20" t="n">
-        <v>50012</v>
+        <v>51196</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2189,23 +2181,21 @@
       <c r="Q20" s="6" t="n">
         <v/>
       </c>
-      <c r="R20" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S20" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="inlineStr">
+      <c r="R20" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U20" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S20" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U20" s="8" t="n">
+        <v/>
       </c>
       <c r="V20" s="8" t="n">
         <v/>
@@ -2215,70 +2205,76 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr"/>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>49720</v>
+        <v>49310</v>
       </c>
       <c r="C21" t="n">
-        <v>49901</v>
+        <v>49795</v>
       </c>
       <c r="D21" t="n">
-        <v>49057</v>
+        <v>48488</v>
       </c>
       <c r="E21" t="n">
-        <v>49547</v>
+        <v>49263</v>
       </c>
       <c r="F21" t="n">
-        <v>-179</v>
+        <v>-284</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.0036</v>
+        <v>-0.0057</v>
       </c>
       <c r="H21" t="n">
-        <v>844</v>
+        <v>1307</v>
       </c>
       <c r="I21" t="n">
-        <v>47236</v>
+        <v>48213</v>
       </c>
       <c r="J21" t="n">
-        <v>48661</v>
+        <v>48737</v>
       </c>
       <c r="K21" t="n">
-        <v>49066</v>
+        <v>49125</v>
       </c>
       <c r="L21" t="n">
-        <v>49471</v>
+        <v>49513</v>
       </c>
       <c r="M21" t="n">
-        <v>50386</v>
+        <v>49969</v>
       </c>
       <c r="N21" t="n">
-        <v>51301</v>
+        <v>50425</v>
       </c>
       <c r="O21" t="n">
-        <v>51196</v>
+        <v>50745</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
       </c>
-      <c r="Q21" s="6" t="n">
-        <v/>
+      <c r="Q21" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R21" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S21" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T21" s="8" t="n">
@@ -2297,74 +2293,72 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>49310</v>
+        <v>49036</v>
       </c>
       <c r="C22" t="n">
-        <v>49795</v>
+        <v>49644</v>
       </c>
       <c r="D22" t="n">
-        <v>48488</v>
+        <v>48571</v>
       </c>
       <c r="E22" t="n">
-        <v>49263</v>
+        <v>49008</v>
       </c>
       <c r="F22" t="n">
-        <v>-284</v>
+        <v>-255</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.0057</v>
+        <v>-0.0052</v>
       </c>
       <c r="H22" t="n">
-        <v>1307</v>
+        <v>1073</v>
       </c>
       <c r="I22" t="n">
-        <v>48213</v>
+        <v>47181</v>
       </c>
       <c r="J22" t="n">
-        <v>48737</v>
+        <v>48016.75</v>
       </c>
       <c r="K22" t="n">
-        <v>49125</v>
+        <v>48609.5</v>
       </c>
       <c r="L22" t="n">
-        <v>49513</v>
+        <v>49202.25</v>
       </c>
       <c r="M22" t="n">
-        <v>49969</v>
+        <v>49916.5</v>
       </c>
       <c r="N22" t="n">
-        <v>50425</v>
+        <v>50630.75</v>
       </c>
       <c r="O22" t="n">
-        <v>50745</v>
+        <v>51102</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
       </c>
-      <c r="Q22" s="6" t="inlineStr">
+      <c r="Q22" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R22" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R22" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S22" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="S22" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T22" s="8" t="n">
@@ -2383,57 +2377,57 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>49036</v>
+        <v>48864</v>
       </c>
       <c r="C23" t="n">
-        <v>49644</v>
+        <v>50263</v>
       </c>
       <c r="D23" t="n">
-        <v>48571</v>
+        <v>48506</v>
       </c>
       <c r="E23" t="n">
-        <v>49008</v>
+        <v>50205</v>
       </c>
       <c r="F23" t="n">
-        <v>-255</v>
+        <v>1197</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-0.0052</v>
+        <v>0.0244</v>
       </c>
       <c r="H23" t="n">
-        <v>1073</v>
+        <v>1757</v>
       </c>
       <c r="I23" t="n">
-        <v>47181</v>
+        <v>47498</v>
       </c>
       <c r="J23" t="n">
-        <v>48016.75</v>
+        <v>47885.25</v>
       </c>
       <c r="K23" t="n">
-        <v>48609.5</v>
+        <v>48471.5</v>
       </c>
       <c r="L23" t="n">
-        <v>49202.25</v>
+        <v>49057.75</v>
       </c>
       <c r="M23" t="n">
-        <v>49916.5</v>
+        <v>49544.5</v>
       </c>
       <c r="N23" t="n">
-        <v>50630.75</v>
+        <v>50031.25</v>
       </c>
       <c r="O23" t="n">
-        <v>51102</v>
+        <v>50717</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2441,21 +2435,23 @@
       <c r="Q23" s="6" t="n">
         <v/>
       </c>
-      <c r="R23" s="6" t="inlineStr">
+      <c r="R23" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S23" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S23" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U23" s="8" t="n">
-        <v/>
+      <c r="U23" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V23" s="8" t="n">
         <v/>
@@ -2467,57 +2463,57 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>48864</v>
+        <v>50240</v>
       </c>
       <c r="C24" t="n">
-        <v>50263</v>
+        <v>50611</v>
       </c>
       <c r="D24" t="n">
-        <v>48506</v>
+        <v>49155</v>
       </c>
       <c r="E24" t="n">
-        <v>50205</v>
+        <v>49569</v>
       </c>
       <c r="F24" t="n">
-        <v>1197</v>
+        <v>-636</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.0244</v>
+        <v>-0.0127</v>
       </c>
       <c r="H24" t="n">
-        <v>1757</v>
+        <v>1456</v>
       </c>
       <c r="I24" t="n">
-        <v>47498</v>
+        <v>46749</v>
       </c>
       <c r="J24" t="n">
-        <v>47885.25</v>
+        <v>48858.25</v>
       </c>
       <c r="K24" t="n">
-        <v>48471.5</v>
+        <v>49326.5</v>
       </c>
       <c r="L24" t="n">
-        <v>49057.75</v>
+        <v>49794.75</v>
       </c>
       <c r="M24" t="n">
-        <v>49544.5</v>
+        <v>51083.5</v>
       </c>
       <c r="N24" t="n">
-        <v>50031.25</v>
+        <v>52372.25</v>
       </c>
       <c r="O24" t="n">
-        <v>50717</v>
+        <v>52020</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2525,23 +2521,21 @@
       <c r="Q24" s="6" t="n">
         <v/>
       </c>
-      <c r="R24" s="6" t="n">
-        <v/>
+      <c r="R24" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S24" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U24" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U24" s="8" t="n">
+        <v/>
       </c>
       <c r="V24" s="8" t="n">
         <v/>
@@ -2560,50 +2554,50 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>50240</v>
+        <v>49549</v>
       </c>
       <c r="C25" t="n">
-        <v>50611</v>
+        <v>49967</v>
       </c>
       <c r="D25" t="n">
-        <v>49155</v>
+        <v>49204</v>
       </c>
       <c r="E25" t="n">
-        <v>49569</v>
+        <v>49674</v>
       </c>
       <c r="F25" t="n">
-        <v>-636</v>
+        <v>105</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.0127</v>
+        <v>0.0021</v>
       </c>
       <c r="H25" t="n">
-        <v>1456</v>
+        <v>763</v>
       </c>
       <c r="I25" t="n">
-        <v>46749</v>
+        <v>47699</v>
       </c>
       <c r="J25" t="n">
-        <v>48858.25</v>
+        <v>47956</v>
       </c>
       <c r="K25" t="n">
-        <v>49326.5</v>
+        <v>48841</v>
       </c>
       <c r="L25" t="n">
-        <v>49794.75</v>
+        <v>49726</v>
       </c>
       <c r="M25" t="n">
-        <v>51083.5</v>
+        <v>50297</v>
       </c>
       <c r="N25" t="n">
-        <v>52372.25</v>
+        <v>50868</v>
       </c>
       <c r="O25" t="n">
-        <v>52020</v>
+        <v>52067</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2611,12 +2605,10 @@
       <c r="Q25" s="6" t="n">
         <v/>
       </c>
-      <c r="R25" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S25" s="7" t="inlineStr">
+      <c r="R25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S25" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -2644,63 +2636,67 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>49549</v>
+        <v>49642</v>
       </c>
       <c r="C26" t="n">
-        <v>49967</v>
+        <v>49872</v>
       </c>
       <c r="D26" t="n">
-        <v>49204</v>
+        <v>48699</v>
       </c>
       <c r="E26" t="n">
-        <v>49674</v>
+        <v>49000</v>
       </c>
       <c r="F26" t="n">
-        <v>105</v>
+        <v>-674</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.0021</v>
+        <v>-0.0136</v>
       </c>
       <c r="H26" t="n">
-        <v>763</v>
+        <v>1173</v>
       </c>
       <c r="I26" t="n">
-        <v>47699</v>
+        <v>48441</v>
       </c>
       <c r="J26" t="n">
-        <v>47956</v>
+        <v>48955.25</v>
       </c>
       <c r="K26" t="n">
-        <v>48841</v>
+        <v>49292.5</v>
       </c>
       <c r="L26" t="n">
-        <v>49726</v>
+        <v>49629.75</v>
       </c>
       <c r="M26" t="n">
-        <v>50297</v>
+        <v>50055.5</v>
       </c>
       <c r="N26" t="n">
-        <v>50868</v>
+        <v>50481.25</v>
       </c>
       <c r="O26" t="n">
-        <v>52067</v>
+        <v>50730</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
       </c>
-      <c r="Q26" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R26" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S26" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="Q26" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R26" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S26" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T26" s="8" t="n">
@@ -2719,64 +2715,66 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>49642</v>
+        <v>48451</v>
       </c>
       <c r="C27" t="n">
-        <v>49872</v>
+        <v>49121</v>
       </c>
       <c r="D27" t="n">
-        <v>48699</v>
+        <v>47025</v>
       </c>
       <c r="E27" t="n">
-        <v>49000</v>
+        <v>47517</v>
       </c>
       <c r="F27" t="n">
-        <v>-674</v>
+        <v>-1483</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.0136</v>
+        <v>-0.0303</v>
       </c>
       <c r="H27" t="n">
-        <v>1173</v>
+        <v>2096</v>
       </c>
       <c r="I27" t="n">
-        <v>48441</v>
+        <v>47526</v>
       </c>
       <c r="J27" t="n">
-        <v>48955.25</v>
+        <v>47684.25</v>
       </c>
       <c r="K27" t="n">
-        <v>49292.5</v>
+        <v>48413.5</v>
       </c>
       <c r="L27" t="n">
-        <v>49629.75</v>
+        <v>49142.75</v>
       </c>
       <c r="M27" t="n">
-        <v>50055.5</v>
+        <v>49586.5</v>
       </c>
       <c r="N27" t="n">
-        <v>50481.25</v>
+        <v>50030.25</v>
       </c>
       <c r="O27" t="n">
-        <v>50730</v>
-      </c>
-      <c r="P27" s="6" t="n">
-        <v/>
+        <v>51045</v>
+      </c>
+      <c r="P27" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q27" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="R27" s="6" t="inlineStr">
@@ -2784,7 +2782,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S27" s="7" t="inlineStr">
+      <c r="S27" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -2798,81 +2796,73 @@
       <c r="V27" s="8" t="n">
         <v/>
       </c>
-      <c r="W27" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W27" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>48451</v>
+        <v>47177</v>
       </c>
       <c r="C28" t="n">
-        <v>49121</v>
+        <v>48266</v>
       </c>
       <c r="D28" t="n">
-        <v>47025</v>
+        <v>46333</v>
       </c>
       <c r="E28" t="n">
-        <v>47517</v>
+        <v>46592</v>
       </c>
       <c r="F28" t="n">
-        <v>-1483</v>
+        <v>-925</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.0303</v>
+        <v>-0.0195</v>
       </c>
       <c r="H28" t="n">
-        <v>2096</v>
+        <v>1933</v>
       </c>
       <c r="I28" t="n">
-        <v>47526</v>
+        <v>44929</v>
       </c>
       <c r="J28" t="n">
-        <v>47684.25</v>
+        <v>45143</v>
       </c>
       <c r="K28" t="n">
-        <v>48413.5</v>
+        <v>46469</v>
       </c>
       <c r="L28" t="n">
-        <v>49142.75</v>
+        <v>47795</v>
       </c>
       <c r="M28" t="n">
-        <v>49586.5</v>
+        <v>48565</v>
       </c>
       <c r="N28" t="n">
-        <v>50030.25</v>
+        <v>49335</v>
       </c>
       <c r="O28" t="n">
-        <v>51045</v>
-      </c>
-      <c r="P28" s="6" t="inlineStr">
+        <v>51217</v>
+      </c>
+      <c r="P28" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q28" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R28" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q28" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R28" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S28" s="7" t="inlineStr">
+      <c r="S28" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -2896,50 +2886,50 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>47177</v>
+        <v>46392</v>
       </c>
       <c r="C29" t="n">
-        <v>48266</v>
+        <v>47457</v>
       </c>
       <c r="D29" t="n">
-        <v>46333</v>
+        <v>45713</v>
       </c>
       <c r="E29" t="n">
-        <v>46592</v>
+        <v>45897</v>
       </c>
       <c r="F29" t="n">
-        <v>-925</v>
+        <v>-695</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.0195</v>
+        <v>-0.0149</v>
       </c>
       <c r="H29" t="n">
-        <v>1933</v>
+        <v>1744</v>
       </c>
       <c r="I29" t="n">
-        <v>44929</v>
+        <v>44400</v>
       </c>
       <c r="J29" t="n">
-        <v>45143</v>
+        <v>44305.25</v>
       </c>
       <c r="K29" t="n">
-        <v>46469</v>
+        <v>45625.5</v>
       </c>
       <c r="L29" t="n">
-        <v>47795</v>
+        <v>46945.75</v>
       </c>
       <c r="M29" t="n">
-        <v>48565</v>
+        <v>47558.5</v>
       </c>
       <c r="N29" t="n">
-        <v>49335</v>
+        <v>48171.25</v>
       </c>
       <c r="O29" t="n">
-        <v>51217</v>
+        <v>50199</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2952,7 +2942,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S29" s="7" t="inlineStr">
+      <c r="S29" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -2976,50 +2966,50 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>46392</v>
+        <v>45605</v>
       </c>
       <c r="C30" t="n">
-        <v>47457</v>
+        <v>47210</v>
       </c>
       <c r="D30" t="n">
-        <v>45713</v>
+        <v>45272</v>
       </c>
       <c r="E30" t="n">
-        <v>45897</v>
+        <v>45424</v>
       </c>
       <c r="F30" t="n">
-        <v>-695</v>
+        <v>-473</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0.0149</v>
+        <v>-0.0103</v>
       </c>
       <c r="H30" t="n">
-        <v>1744</v>
+        <v>1938</v>
       </c>
       <c r="I30" t="n">
-        <v>44400</v>
+        <v>43969</v>
       </c>
       <c r="J30" t="n">
-        <v>44305.25</v>
+        <v>43809</v>
       </c>
       <c r="K30" t="n">
-        <v>45625.5</v>
+        <v>45025</v>
       </c>
       <c r="L30" t="n">
-        <v>46945.75</v>
+        <v>46241</v>
       </c>
       <c r="M30" t="n">
-        <v>47558.5</v>
+        <v>46769</v>
       </c>
       <c r="N30" t="n">
-        <v>48171.25</v>
+        <v>47297</v>
       </c>
       <c r="O30" t="n">
-        <v>50199</v>
+        <v>49201</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3032,13 +3022,15 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S30" s="7" t="inlineStr">
+      <c r="S30" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T30" s="8" t="n">
-        <v/>
+      <c r="T30" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U30" s="8" t="n">
         <v/>
@@ -3056,50 +3048,50 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>45605</v>
+        <v>45244</v>
       </c>
       <c r="C31" t="n">
-        <v>47210</v>
+        <v>47090</v>
       </c>
       <c r="D31" t="n">
-        <v>45272</v>
+        <v>45052</v>
       </c>
       <c r="E31" t="n">
-        <v>45424</v>
+        <v>46629</v>
       </c>
       <c r="F31" t="n">
-        <v>-473</v>
+        <v>1205</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-0.0103</v>
+        <v>0.0265</v>
       </c>
       <c r="H31" t="n">
-        <v>1938</v>
+        <v>2038</v>
       </c>
       <c r="I31" t="n">
-        <v>43969</v>
+        <v>43334</v>
       </c>
       <c r="J31" t="n">
-        <v>43809</v>
+        <v>43077.5</v>
       </c>
       <c r="K31" t="n">
-        <v>45025</v>
+        <v>44455</v>
       </c>
       <c r="L31" t="n">
-        <v>46241</v>
+        <v>45832.5</v>
       </c>
       <c r="M31" t="n">
-        <v>46769</v>
+        <v>46393</v>
       </c>
       <c r="N31" t="n">
-        <v>47297</v>
+        <v>46953.5</v>
       </c>
       <c r="O31" t="n">
-        <v>49201</v>
+        <v>49148</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3107,24 +3099,24 @@
       <c r="Q31" s="6" t="n">
         <v/>
       </c>
-      <c r="R31" s="6" t="inlineStr">
+      <c r="R31" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S31" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S31" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="inlineStr">
+      <c r="U31" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U31" s="8" t="n">
-        <v/>
-      </c>
       <c r="V31" s="8" t="n">
         <v/>
       </c>
@@ -3133,55 +3125,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr"/>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>45244</v>
+        <v>46569</v>
       </c>
       <c r="C32" t="n">
-        <v>47090</v>
+        <v>48555</v>
       </c>
       <c r="D32" t="n">
-        <v>45052</v>
+        <v>46362</v>
       </c>
       <c r="E32" t="n">
-        <v>46629</v>
+        <v>48129</v>
       </c>
       <c r="F32" t="n">
-        <v>1205</v>
+        <v>1500</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.0265</v>
+        <v>0.0322</v>
       </c>
       <c r="H32" t="n">
-        <v>2038</v>
+        <v>2193</v>
       </c>
       <c r="I32" t="n">
-        <v>43334</v>
+        <v>43014</v>
       </c>
       <c r="J32" t="n">
-        <v>43077.5</v>
+        <v>44870</v>
       </c>
       <c r="K32" t="n">
-        <v>44455</v>
+        <v>45610</v>
       </c>
       <c r="L32" t="n">
-        <v>45832.5</v>
+        <v>46350</v>
       </c>
       <c r="M32" t="n">
-        <v>46393</v>
+        <v>47648</v>
       </c>
       <c r="N32" t="n">
-        <v>46953.5</v>
+        <v>48946</v>
       </c>
       <c r="O32" t="n">
-        <v>49148</v>
+        <v>49128</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3192,7 +3188,7 @@
       <c r="R32" s="6" t="n">
         <v/>
       </c>
-      <c r="S32" s="10" t="inlineStr">
+      <c r="S32" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3202,10 +3198,8 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U32" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U32" s="8" t="n">
+        <v/>
       </c>
       <c r="V32" s="8" t="n">
         <v/>
@@ -3217,57 +3211,57 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>46569</v>
+        <v>47674</v>
       </c>
       <c r="C33" t="n">
-        <v>48555</v>
+        <v>49924</v>
       </c>
       <c r="D33" t="n">
-        <v>46362</v>
+        <v>47534</v>
       </c>
       <c r="E33" t="n">
-        <v>48129</v>
+        <v>49641</v>
       </c>
       <c r="F33" t="n">
-        <v>1500</v>
+        <v>1512</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0322</v>
+        <v>0.0314</v>
       </c>
       <c r="H33" t="n">
-        <v>2193</v>
+        <v>2390</v>
       </c>
       <c r="I33" t="n">
-        <v>43014</v>
+        <v>44169</v>
       </c>
       <c r="J33" t="n">
-        <v>44870</v>
+        <v>46271.25</v>
       </c>
       <c r="K33" t="n">
-        <v>45610</v>
+        <v>47032.5</v>
       </c>
       <c r="L33" t="n">
-        <v>46350</v>
+        <v>47793.75</v>
       </c>
       <c r="M33" t="n">
-        <v>47648</v>
+        <v>49225.5</v>
       </c>
       <c r="N33" t="n">
-        <v>48946</v>
+        <v>50657.25</v>
       </c>
       <c r="O33" t="n">
-        <v>49128</v>
+        <v>50748</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3278,7 +3272,7 @@
       <c r="R33" s="6" t="n">
         <v/>
       </c>
-      <c r="S33" s="10" t="inlineStr">
+      <c r="S33" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3308,50 +3302,50 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>47674</v>
+        <v>49324</v>
       </c>
       <c r="C34" t="n">
-        <v>49924</v>
+        <v>50043</v>
       </c>
       <c r="D34" t="n">
-        <v>47534</v>
+        <v>49036</v>
       </c>
       <c r="E34" t="n">
-        <v>49641</v>
+        <v>49392</v>
       </c>
       <c r="F34" t="n">
-        <v>1512</v>
+        <v>-249</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0314</v>
+        <v>-0.005</v>
       </c>
       <c r="H34" t="n">
-        <v>2390</v>
+        <v>1007</v>
       </c>
       <c r="I34" t="n">
-        <v>44169</v>
+        <v>45144</v>
       </c>
       <c r="J34" t="n">
-        <v>46271.25</v>
+        <v>47707</v>
       </c>
       <c r="K34" t="n">
-        <v>47032.5</v>
+        <v>48446</v>
       </c>
       <c r="L34" t="n">
-        <v>47793.75</v>
+        <v>49185</v>
       </c>
       <c r="M34" t="n">
-        <v>49225.5</v>
+        <v>50836</v>
       </c>
       <c r="N34" t="n">
-        <v>50657.25</v>
+        <v>52487</v>
       </c>
       <c r="O34" t="n">
-        <v>50748</v>
+        <v>52314</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3362,15 +3356,13 @@
       <c r="R34" s="6" t="n">
         <v/>
       </c>
-      <c r="S34" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S34" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="n">
+        <v/>
       </c>
       <c r="U34" s="8" t="n">
         <v/>
@@ -3385,57 +3377,57 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>49324</v>
+        <v>49382</v>
       </c>
       <c r="C35" t="n">
-        <v>50043</v>
+        <v>50138</v>
       </c>
       <c r="D35" t="n">
-        <v>49036</v>
+        <v>48608</v>
       </c>
       <c r="E35" t="n">
-        <v>49392</v>
+        <v>49646</v>
       </c>
       <c r="F35" t="n">
-        <v>-249</v>
+        <v>254</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>-0.005</v>
+        <v>0.0051</v>
       </c>
       <c r="H35" t="n">
-        <v>1007</v>
+        <v>1530</v>
       </c>
       <c r="I35" t="n">
-        <v>45144</v>
+        <v>48029</v>
       </c>
       <c r="J35" t="n">
-        <v>47707</v>
+        <v>48311.25</v>
       </c>
       <c r="K35" t="n">
-        <v>48446</v>
+        <v>48888.5</v>
       </c>
       <c r="L35" t="n">
-        <v>49185</v>
+        <v>49465.75</v>
       </c>
       <c r="M35" t="n">
-        <v>50836</v>
+        <v>49895.5</v>
       </c>
       <c r="N35" t="n">
-        <v>52487</v>
+        <v>50325.25</v>
       </c>
       <c r="O35" t="n">
-        <v>52314</v>
+        <v>51050</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3443,16 +3435,20 @@
       <c r="Q35" s="6" t="n">
         <v/>
       </c>
-      <c r="R35" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S35" s="10" t="inlineStr">
+      <c r="R35" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S35" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
       </c>
-      <c r="T35" s="8" t="n">
-        <v/>
+      <c r="T35" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U35" s="8" t="n">
         <v/>
@@ -3474,50 +3470,50 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>49382</v>
+        <v>49705</v>
       </c>
       <c r="C36" t="n">
-        <v>50138</v>
+        <v>50238</v>
       </c>
       <c r="D36" t="n">
-        <v>48608</v>
+        <v>49016</v>
       </c>
       <c r="E36" t="n">
-        <v>49646</v>
+        <v>49691</v>
       </c>
       <c r="F36" t="n">
-        <v>254</v>
+        <v>45</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.0051</v>
+        <v>0.0009</v>
       </c>
       <c r="H36" t="n">
-        <v>1530</v>
+        <v>1222</v>
       </c>
       <c r="I36" t="n">
-        <v>48029</v>
+        <v>47078</v>
       </c>
       <c r="J36" t="n">
-        <v>48311.25</v>
+        <v>48252.5</v>
       </c>
       <c r="K36" t="n">
-        <v>48888.5</v>
+        <v>48881</v>
       </c>
       <c r="L36" t="n">
-        <v>49465.75</v>
+        <v>49509.5</v>
       </c>
       <c r="M36" t="n">
-        <v>49895.5</v>
+        <v>50411</v>
       </c>
       <c r="N36" t="n">
-        <v>50325.25</v>
+        <v>51312.5</v>
       </c>
       <c r="O36" t="n">
-        <v>51050</v>
+        <v>51668</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3525,20 +3521,16 @@
       <c r="Q36" s="6" t="n">
         <v/>
       </c>
-      <c r="R36" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S36" s="10" t="inlineStr">
+      <c r="R36" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S36" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
       </c>
-      <c r="T36" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T36" s="8" t="n">
+        <v/>
       </c>
       <c r="U36" s="8" t="n">
         <v/>
@@ -3553,57 +3545,57 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>49705</v>
+        <v>49640</v>
       </c>
       <c r="C37" t="n">
-        <v>50238</v>
+        <v>50292</v>
       </c>
       <c r="D37" t="n">
-        <v>49016</v>
+        <v>49397</v>
       </c>
       <c r="E37" t="n">
-        <v>49691</v>
+        <v>49617</v>
       </c>
       <c r="F37" t="n">
-        <v>45</v>
+        <v>-74</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.0009</v>
+        <v>-0.0015</v>
       </c>
       <c r="H37" t="n">
-        <v>1222</v>
+        <v>895</v>
       </c>
       <c r="I37" t="n">
-        <v>47078</v>
+        <v>47794</v>
       </c>
       <c r="J37" t="n">
-        <v>48252.5</v>
+        <v>48501</v>
       </c>
       <c r="K37" t="n">
-        <v>48881</v>
+        <v>49080</v>
       </c>
       <c r="L37" t="n">
-        <v>49509.5</v>
+        <v>49659</v>
       </c>
       <c r="M37" t="n">
-        <v>50411</v>
+        <v>50302</v>
       </c>
       <c r="N37" t="n">
-        <v>51312.5</v>
+        <v>50945</v>
       </c>
       <c r="O37" t="n">
-        <v>51668</v>
+        <v>51460</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3616,7 +3608,7 @@
       </c>
       <c r="S37" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T37" s="8" t="n">
@@ -3635,57 +3627,57 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>49640</v>
+        <v>49464</v>
       </c>
       <c r="C38" t="n">
-        <v>50292</v>
+        <v>50920</v>
       </c>
       <c r="D38" t="n">
-        <v>49397</v>
+        <v>49152</v>
       </c>
       <c r="E38" t="n">
-        <v>49617</v>
+        <v>50662</v>
       </c>
       <c r="F38" t="n">
-        <v>-74</v>
+        <v>1045</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.0015</v>
+        <v>0.0211</v>
       </c>
       <c r="H38" t="n">
-        <v>895</v>
+        <v>1768</v>
       </c>
       <c r="I38" t="n">
-        <v>47794</v>
+        <v>48502</v>
       </c>
       <c r="J38" t="n">
-        <v>48501</v>
+        <v>48608.25</v>
       </c>
       <c r="K38" t="n">
-        <v>49080</v>
+        <v>49169.5</v>
       </c>
       <c r="L38" t="n">
-        <v>49659</v>
+        <v>49730.75</v>
       </c>
       <c r="M38" t="n">
-        <v>50302</v>
+        <v>50064.5</v>
       </c>
       <c r="N38" t="n">
-        <v>50945</v>
+        <v>50398.25</v>
       </c>
       <c r="O38" t="n">
-        <v>51460</v>
+        <v>51187</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3693,81 +3685,87 @@
       <c r="Q38" s="6" t="n">
         <v/>
       </c>
-      <c r="R38" s="6" t="n">
-        <v/>
+      <c r="R38" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S38" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U38" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U38" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V38" s="8" t="n">
         <v/>
       </c>
-      <c r="W38" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W38" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>49464</v>
+        <v>50776</v>
       </c>
       <c r="C39" t="n">
-        <v>50920</v>
+        <v>51209</v>
       </c>
       <c r="D39" t="n">
-        <v>49152</v>
+        <v>50386</v>
       </c>
       <c r="E39" t="n">
-        <v>50662</v>
+        <v>51077</v>
       </c>
       <c r="F39" t="n">
-        <v>1045</v>
+        <v>415</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.0211</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="H39" t="n">
-        <v>1768</v>
+        <v>823</v>
       </c>
       <c r="I39" t="n">
-        <v>48502</v>
+        <v>47384</v>
       </c>
       <c r="J39" t="n">
-        <v>48608.25</v>
+        <v>49207</v>
       </c>
       <c r="K39" t="n">
-        <v>49169.5</v>
+        <v>49778</v>
       </c>
       <c r="L39" t="n">
-        <v>49730.75</v>
+        <v>50349</v>
       </c>
       <c r="M39" t="n">
-        <v>50064.5</v>
+        <v>51546</v>
       </c>
       <c r="N39" t="n">
-        <v>50398.25</v>
+        <v>52743</v>
       </c>
       <c r="O39" t="n">
-        <v>51187</v>
+        <v>52688</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3775,26 +3773,22 @@
       <c r="Q39" s="6" t="n">
         <v/>
       </c>
-      <c r="R39" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S39" s="10" t="inlineStr">
+      <c r="R39" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S39" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T39" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U39" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U39" s="8" t="n">
+        <v/>
+      </c>
       <c r="V39" s="8" t="n">
         <v/>
       </c>
@@ -3803,59 +3797,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>50776</v>
+        <v>51128</v>
       </c>
       <c r="C40" t="n">
-        <v>51209</v>
+        <v>51849</v>
       </c>
       <c r="D40" t="n">
-        <v>50386</v>
+        <v>50736</v>
       </c>
       <c r="E40" t="n">
-        <v>51077</v>
+        <v>50936</v>
       </c>
       <c r="F40" t="n">
-        <v>415</v>
+        <v>-141</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.008200000000000001</v>
+        <v>-0.0028</v>
       </c>
       <c r="H40" t="n">
-        <v>823</v>
+        <v>1113</v>
       </c>
       <c r="I40" t="n">
-        <v>47384</v>
+        <v>49563</v>
       </c>
       <c r="J40" t="n">
-        <v>49207</v>
+        <v>50393.75</v>
       </c>
       <c r="K40" t="n">
-        <v>49778</v>
+        <v>50665.5</v>
       </c>
       <c r="L40" t="n">
-        <v>50349</v>
+        <v>50937.25</v>
       </c>
       <c r="M40" t="n">
-        <v>51546</v>
+        <v>51488.5</v>
       </c>
       <c r="N40" t="n">
-        <v>52743</v>
+        <v>52039.75</v>
       </c>
       <c r="O40" t="n">
-        <v>52688</v>
+        <v>52032</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3868,12 +3858,12 @@
       </c>
       <c r="S40" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T40" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U40" s="8" t="n">
@@ -3887,55 +3877,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr"/>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>51128</v>
+        <v>50796</v>
       </c>
       <c r="C41" t="n">
-        <v>51849</v>
+        <v>51443</v>
       </c>
       <c r="D41" t="n">
-        <v>50736</v>
+        <v>49758</v>
       </c>
       <c r="E41" t="n">
-        <v>50936</v>
+        <v>51227</v>
       </c>
       <c r="F41" t="n">
-        <v>-141</v>
+        <v>291</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.0028</v>
+        <v>0.0057</v>
       </c>
       <c r="H41" t="n">
-        <v>1113</v>
+        <v>1685</v>
       </c>
       <c r="I41" t="n">
-        <v>49563</v>
+        <v>49623</v>
       </c>
       <c r="J41" t="n">
-        <v>50393.75</v>
+        <v>49644.75</v>
       </c>
       <c r="K41" t="n">
-        <v>50665.5</v>
+        <v>50379.5</v>
       </c>
       <c r="L41" t="n">
-        <v>50937.25</v>
+        <v>51114.25</v>
       </c>
       <c r="M41" t="n">
-        <v>51488.5</v>
+        <v>51492.5</v>
       </c>
       <c r="N41" t="n">
-        <v>52039.75</v>
+        <v>51870.75</v>
       </c>
       <c r="O41" t="n">
-        <v>52032</v>
+        <v>52962</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3943,18 +3937,18 @@
       <c r="Q41" s="6" t="n">
         <v/>
       </c>
-      <c r="R41" s="6" t="n">
-        <v/>
+      <c r="R41" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S41" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="n">
+        <v/>
       </c>
       <c r="U41" s="8" t="n">
         <v/>
@@ -3969,57 +3963,57 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>50796</v>
+        <v>51450</v>
       </c>
       <c r="C42" t="n">
-        <v>51443</v>
+        <v>52300</v>
       </c>
       <c r="D42" t="n">
-        <v>49758</v>
+        <v>51420</v>
       </c>
       <c r="E42" t="n">
-        <v>51227</v>
+        <v>51888</v>
       </c>
       <c r="F42" t="n">
-        <v>291</v>
+        <v>661</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.0057</v>
+        <v>0.0129</v>
       </c>
       <c r="H42" t="n">
-        <v>1685</v>
+        <v>880</v>
       </c>
       <c r="I42" t="n">
-        <v>49623</v>
+        <v>48073</v>
       </c>
       <c r="J42" t="n">
-        <v>49644.75</v>
+        <v>49855.25</v>
       </c>
       <c r="K42" t="n">
-        <v>50379.5</v>
+        <v>50384.5</v>
       </c>
       <c r="L42" t="n">
-        <v>51114.25</v>
+        <v>50913.75</v>
       </c>
       <c r="M42" t="n">
-        <v>51492.5</v>
+        <v>52069.5</v>
       </c>
       <c r="N42" t="n">
-        <v>51870.75</v>
+        <v>53225.25</v>
       </c>
       <c r="O42" t="n">
-        <v>52962</v>
+        <v>53128</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4027,18 +4021,18 @@
       <c r="Q42" s="6" t="n">
         <v/>
       </c>
-      <c r="R42" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S42" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="n">
-        <v/>
+      <c r="R42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S42" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U42" s="8" t="n">
         <v/>
@@ -4051,59 +4045,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>51450</v>
+        <v>51870</v>
       </c>
       <c r="C43" t="n">
-        <v>52300</v>
+        <v>53097</v>
       </c>
       <c r="D43" t="n">
-        <v>51420</v>
+        <v>51691</v>
       </c>
       <c r="E43" t="n">
-        <v>51888</v>
+        <v>52209</v>
       </c>
       <c r="F43" t="n">
-        <v>661</v>
+        <v>321</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.0129</v>
+        <v>0.0062</v>
       </c>
       <c r="H43" t="n">
-        <v>880</v>
+        <v>1406</v>
       </c>
       <c r="I43" t="n">
-        <v>48073</v>
+        <v>50540</v>
       </c>
       <c r="J43" t="n">
-        <v>49855.25</v>
+        <v>51022</v>
       </c>
       <c r="K43" t="n">
-        <v>50384.5</v>
+        <v>51448</v>
       </c>
       <c r="L43" t="n">
-        <v>50913.75</v>
+        <v>51874</v>
       </c>
       <c r="M43" t="n">
-        <v>52069.5</v>
+        <v>52328</v>
       </c>
       <c r="N43" t="n">
-        <v>53225.25</v>
+        <v>52782</v>
       </c>
       <c r="O43" t="n">
-        <v>53128</v>
+        <v>53180</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4114,7 +4104,7 @@
       <c r="R43" s="6" t="n">
         <v/>
       </c>
-      <c r="S43" s="10" t="inlineStr">
+      <c r="S43" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -4124,8 +4114,10 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U43" s="8" t="n">
-        <v/>
+      <c r="U43" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V43" s="8" t="n">
         <v/>
@@ -4140,50 +4132,50 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>51870</v>
+        <v>52183</v>
       </c>
       <c r="C44" t="n">
-        <v>53097</v>
+        <v>53400</v>
       </c>
       <c r="D44" t="n">
-        <v>51691</v>
+        <v>52179</v>
       </c>
       <c r="E44" t="n">
-        <v>52209</v>
+        <v>53162</v>
       </c>
       <c r="F44" t="n">
-        <v>321</v>
+        <v>953</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.0062</v>
+        <v>0.0183</v>
       </c>
       <c r="H44" t="n">
-        <v>1406</v>
+        <v>1221</v>
       </c>
       <c r="I44" t="n">
-        <v>50540</v>
+        <v>50285</v>
       </c>
       <c r="J44" t="n">
-        <v>51022</v>
+        <v>50710.5</v>
       </c>
       <c r="K44" t="n">
-        <v>51448</v>
+        <v>51506</v>
       </c>
       <c r="L44" t="n">
-        <v>51874</v>
+        <v>52301.5</v>
       </c>
       <c r="M44" t="n">
-        <v>52328</v>
+        <v>52912</v>
       </c>
       <c r="N44" t="n">
-        <v>52782</v>
+        <v>53522.5</v>
       </c>
       <c r="O44" t="n">
-        <v>53180</v>
+        <v>54503</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4194,7 +4186,7 @@
       <c r="R44" s="6" t="n">
         <v/>
       </c>
-      <c r="S44" s="10" t="inlineStr">
+      <c r="S44" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -4204,10 +4196,8 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U44" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U44" s="8" t="n">
+        <v/>
       </c>
       <c r="V44" s="8" t="n">
         <v/>
@@ -4222,50 +4212,50 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>52183</v>
+        <v>53230</v>
       </c>
       <c r="C45" t="n">
-        <v>53400</v>
+        <v>53656</v>
       </c>
       <c r="D45" t="n">
-        <v>52179</v>
+        <v>52343</v>
       </c>
       <c r="E45" t="n">
-        <v>53162</v>
+        <v>52906</v>
       </c>
       <c r="F45" t="n">
-        <v>953</v>
+        <v>-256</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.0183</v>
+        <v>-0.0048</v>
       </c>
       <c r="H45" t="n">
-        <v>1221</v>
+        <v>1313</v>
       </c>
       <c r="I45" t="n">
-        <v>50285</v>
+        <v>50958</v>
       </c>
       <c r="J45" t="n">
-        <v>50710.5</v>
+        <v>52127.25</v>
       </c>
       <c r="K45" t="n">
-        <v>51506</v>
+        <v>52551.5</v>
       </c>
       <c r="L45" t="n">
-        <v>52301.5</v>
+        <v>52975.75</v>
       </c>
       <c r="M45" t="n">
-        <v>52912</v>
+        <v>53772.5</v>
       </c>
       <c r="N45" t="n">
-        <v>53522.5</v>
+        <v>54569.25</v>
       </c>
       <c r="O45" t="n">
-        <v>54503</v>
+        <v>54621</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4273,18 +4263,18 @@
       <c r="Q45" s="6" t="n">
         <v/>
       </c>
-      <c r="R45" s="6" t="n">
-        <v/>
+      <c r="R45" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S45" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="n">
+        <v/>
       </c>
       <c r="U45" s="8" t="n">
         <v/>
@@ -4297,55 +4287,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr"/>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>53230</v>
+        <v>52844</v>
       </c>
       <c r="C46" t="n">
-        <v>53656</v>
+        <v>53113</v>
       </c>
       <c r="D46" t="n">
-        <v>52343</v>
+        <v>52174</v>
       </c>
       <c r="E46" t="n">
-        <v>52906</v>
+        <v>52375</v>
       </c>
       <c r="F46" t="n">
-        <v>-256</v>
+        <v>-531</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-0.0048</v>
+        <v>-0.01</v>
       </c>
       <c r="H46" t="n">
-        <v>1313</v>
+        <v>939</v>
       </c>
       <c r="I46" t="n">
-        <v>50958</v>
+        <v>51030</v>
       </c>
       <c r="J46" t="n">
-        <v>52127.25</v>
+        <v>51546.25</v>
       </c>
       <c r="K46" t="n">
-        <v>52551.5</v>
+        <v>52249.5</v>
       </c>
       <c r="L46" t="n">
-        <v>52975.75</v>
+        <v>52952.75</v>
       </c>
       <c r="M46" t="n">
-        <v>53772.5</v>
+        <v>53562.5</v>
       </c>
       <c r="N46" t="n">
-        <v>54569.25</v>
+        <v>54172.25</v>
       </c>
       <c r="O46" t="n">
-        <v>54621</v>
+        <v>54969</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4355,12 +4349,12 @@
       </c>
       <c r="R46" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S46" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S46" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T46" s="8" t="n">
@@ -4379,57 +4373,57 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>52844</v>
+        <v>52300</v>
       </c>
       <c r="C47" t="n">
-        <v>53113</v>
+        <v>52721</v>
       </c>
       <c r="D47" t="n">
-        <v>52174</v>
+        <v>51720</v>
       </c>
       <c r="E47" t="n">
-        <v>52375</v>
+        <v>52124</v>
       </c>
       <c r="F47" t="n">
-        <v>-531</v>
+        <v>-251</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>-0.01</v>
+        <v>-0.0048</v>
       </c>
       <c r="H47" t="n">
-        <v>939</v>
+        <v>1001</v>
       </c>
       <c r="I47" t="n">
-        <v>51030</v>
+        <v>51235</v>
       </c>
       <c r="J47" t="n">
-        <v>51546.25</v>
+        <v>51301.75</v>
       </c>
       <c r="K47" t="n">
-        <v>52249.5</v>
+        <v>51905.5</v>
       </c>
       <c r="L47" t="n">
-        <v>52952.75</v>
+        <v>52509.25</v>
       </c>
       <c r="M47" t="n">
-        <v>53562.5</v>
+        <v>52844.5</v>
       </c>
       <c r="N47" t="n">
-        <v>54172.25</v>
+        <v>53179.75</v>
       </c>
       <c r="O47" t="n">
-        <v>54969</v>
+        <v>54052</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4442,7 +4436,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S47" s="7" t="inlineStr">
+      <c r="S47" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4470,50 +4464,50 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>52300</v>
+        <v>52299</v>
       </c>
       <c r="C48" t="n">
-        <v>52721</v>
+        <v>53105</v>
       </c>
       <c r="D48" t="n">
-        <v>51720</v>
+        <v>51630</v>
       </c>
       <c r="E48" t="n">
-        <v>52124</v>
+        <v>52635</v>
       </c>
       <c r="F48" t="n">
-        <v>-251</v>
+        <v>511</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0.0048</v>
+        <v>0.0098</v>
       </c>
       <c r="H48" t="n">
-        <v>1001</v>
+        <v>1475</v>
       </c>
       <c r="I48" t="n">
-        <v>51235</v>
+        <v>50719</v>
       </c>
       <c r="J48" t="n">
-        <v>51301.75</v>
+        <v>51074.75</v>
       </c>
       <c r="K48" t="n">
-        <v>51905.5</v>
+        <v>51623.5</v>
       </c>
       <c r="L48" t="n">
-        <v>52509.25</v>
+        <v>52172.25</v>
       </c>
       <c r="M48" t="n">
-        <v>52844.5</v>
+        <v>52624.5</v>
       </c>
       <c r="N48" t="n">
-        <v>53179.75</v>
+        <v>53076.75</v>
       </c>
       <c r="O48" t="n">
-        <v>54052</v>
+        <v>53722</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4521,21 +4515,23 @@
       <c r="Q48" s="6" t="n">
         <v/>
       </c>
-      <c r="R48" s="6" t="inlineStr">
+      <c r="R48" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S48" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S48" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T48" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U48" s="8" t="n">
-        <v/>
+      <c r="U48" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V48" s="8" t="n">
         <v/>
@@ -4547,57 +4543,57 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>52299</v>
+        <v>52780</v>
       </c>
       <c r="C49" t="n">
-        <v>53105</v>
+        <v>54884</v>
       </c>
       <c r="D49" t="n">
-        <v>51630</v>
+        <v>52777</v>
       </c>
       <c r="E49" t="n">
-        <v>52635</v>
+        <v>54152</v>
       </c>
       <c r="F49" t="n">
-        <v>511</v>
+        <v>1517</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.0098</v>
+        <v>0.0288</v>
       </c>
       <c r="H49" t="n">
-        <v>1475</v>
+        <v>2107</v>
       </c>
       <c r="I49" t="n">
-        <v>50719</v>
+        <v>50155</v>
       </c>
       <c r="J49" t="n">
-        <v>51074.75</v>
+        <v>51293.75</v>
       </c>
       <c r="K49" t="n">
-        <v>51623.5</v>
+        <v>51897.5</v>
       </c>
       <c r="L49" t="n">
-        <v>52172.25</v>
+        <v>52501.25</v>
       </c>
       <c r="M49" t="n">
-        <v>52624.5</v>
+        <v>53372.5</v>
       </c>
       <c r="N49" t="n">
-        <v>53076.75</v>
+        <v>54243.75</v>
       </c>
       <c r="O49" t="n">
-        <v>53722</v>
+        <v>54580</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4608,82 +4604,80 @@
       <c r="R49" s="6" t="n">
         <v/>
       </c>
-      <c r="S49" s="10" t="inlineStr">
+      <c r="S49" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T49" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U49" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U49" s="8" t="inlineStr">
+      <c r="V49" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="V49" s="8" t="n">
-        <v/>
-      </c>
       <c r="W49" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>52780</v>
+        <v>54133</v>
       </c>
       <c r="C50" t="n">
-        <v>54884</v>
+        <v>54336</v>
       </c>
       <c r="D50" t="n">
-        <v>52777</v>
+        <v>53715</v>
       </c>
       <c r="E50" t="n">
-        <v>54152</v>
+        <v>53807</v>
       </c>
       <c r="F50" t="n">
-        <v>1517</v>
+        <v>-345</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.0288</v>
+        <v>-0.0064</v>
       </c>
       <c r="H50" t="n">
-        <v>2107</v>
+        <v>621</v>
       </c>
       <c r="I50" t="n">
-        <v>50155</v>
+        <v>50670</v>
       </c>
       <c r="J50" t="n">
-        <v>51293.75</v>
+        <v>52205.75</v>
       </c>
       <c r="K50" t="n">
-        <v>51897.5</v>
+        <v>53098.5</v>
       </c>
       <c r="L50" t="n">
-        <v>52501.25</v>
+        <v>53991.25</v>
       </c>
       <c r="M50" t="n">
-        <v>53372.5</v>
+        <v>55205.5</v>
       </c>
       <c r="N50" t="n">
-        <v>54243.75</v>
+        <v>56419.75</v>
       </c>
       <c r="O50" t="n">
-        <v>54580</v>
+        <v>56991</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4696,91 +4690,95 @@
       </c>
       <c r="S50" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T50" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U50" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V50" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T50" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U50" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V50" s="8" t="n">
+        <v/>
       </c>
       <c r="W50" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr"/>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>54133</v>
+        <v>53790</v>
       </c>
       <c r="C51" t="n">
-        <v>54336</v>
+        <v>53840</v>
       </c>
       <c r="D51" t="n">
-        <v>53715</v>
+        <v>52812</v>
       </c>
       <c r="E51" t="n">
-        <v>53807</v>
+        <v>53353</v>
       </c>
       <c r="F51" t="n">
-        <v>-345</v>
+        <v>-454</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.0064</v>
+        <v>-0.008399999999999999</v>
       </c>
       <c r="H51" t="n">
-        <v>621</v>
+        <v>1028</v>
       </c>
       <c r="I51" t="n">
-        <v>50670</v>
+        <v>53094</v>
       </c>
       <c r="J51" t="n">
-        <v>52205.75</v>
+        <v>53076.75</v>
       </c>
       <c r="K51" t="n">
-        <v>53098.5</v>
+        <v>53496.5</v>
       </c>
       <c r="L51" t="n">
-        <v>53991.25</v>
+        <v>53916.25</v>
       </c>
       <c r="M51" t="n">
-        <v>55205.5</v>
+        <v>54117.5</v>
       </c>
       <c r="N51" t="n">
-        <v>56419.75</v>
+        <v>54318.75</v>
       </c>
       <c r="O51" t="n">
-        <v>56991</v>
-      </c>
-      <c r="P51" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q51" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R51" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S51" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+        <v>54957</v>
+      </c>
+      <c r="P51" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q51" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R51" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S51" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T51" s="8" t="n">
@@ -4799,76 +4797,70 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>53790</v>
+        <v>53367</v>
       </c>
       <c r="C52" t="n">
-        <v>53840</v>
+        <v>53862</v>
       </c>
       <c r="D52" t="n">
-        <v>52812</v>
+        <v>53210</v>
       </c>
       <c r="E52" t="n">
-        <v>53353</v>
+        <v>53584</v>
       </c>
       <c r="F52" t="n">
-        <v>-454</v>
+        <v>231</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.008399999999999999</v>
+        <v>0.0043</v>
       </c>
       <c r="H52" t="n">
-        <v>1028</v>
+        <v>652</v>
       </c>
       <c r="I52" t="n">
-        <v>53094</v>
+        <v>51784</v>
       </c>
       <c r="J52" t="n">
-        <v>53076.75</v>
+        <v>52338.5</v>
       </c>
       <c r="K52" t="n">
-        <v>53496.5</v>
+        <v>52839</v>
       </c>
       <c r="L52" t="n">
-        <v>53916.25</v>
+        <v>53339.5</v>
       </c>
       <c r="M52" t="n">
-        <v>54117.5</v>
+        <v>53867</v>
       </c>
       <c r="N52" t="n">
-        <v>54318.75</v>
+        <v>54394.5</v>
       </c>
       <c r="O52" t="n">
-        <v>54957</v>
-      </c>
-      <c r="P52" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q52" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R52" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+        <v>54868</v>
+      </c>
+      <c r="P52" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q52" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R52" s="6" t="n">
+        <v/>
       </c>
       <c r="S52" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T52" s="8" t="n">
@@ -4885,72 +4877,72 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>53367</v>
+        <v>53664</v>
       </c>
       <c r="C53" t="n">
-        <v>53862</v>
+        <v>53827</v>
       </c>
       <c r="D53" t="n">
-        <v>53210</v>
+        <v>52720</v>
       </c>
       <c r="E53" t="n">
-        <v>53584</v>
+        <v>53440</v>
       </c>
       <c r="F53" t="n">
-        <v>231</v>
+        <v>-144</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.0043</v>
+        <v>-0.0027</v>
       </c>
       <c r="H53" t="n">
-        <v>652</v>
+        <v>1107</v>
       </c>
       <c r="I53" t="n">
-        <v>51784</v>
+        <v>52558</v>
       </c>
       <c r="J53" t="n">
-        <v>52338.5</v>
+        <v>52956</v>
       </c>
       <c r="K53" t="n">
-        <v>52839</v>
+        <v>53258</v>
       </c>
       <c r="L53" t="n">
-        <v>53339.5</v>
+        <v>53560</v>
       </c>
       <c r="M53" t="n">
-        <v>53867</v>
+        <v>53910</v>
       </c>
       <c r="N53" t="n">
-        <v>54394.5</v>
+        <v>54260</v>
       </c>
       <c r="O53" t="n">
-        <v>54868</v>
+        <v>54514</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
       </c>
-      <c r="Q53" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R53" s="6" t="n">
-        <v/>
+      <c r="Q53" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R53" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S53" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T53" s="8" t="n">
@@ -4967,72 +4959,76 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr"/>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>53664</v>
+        <v>53261</v>
       </c>
       <c r="C54" t="n">
-        <v>53827</v>
+        <v>53336</v>
       </c>
       <c r="D54" t="n">
-        <v>52720</v>
+        <v>51992</v>
       </c>
       <c r="E54" t="n">
-        <v>53440</v>
+        <v>52585</v>
       </c>
       <c r="F54" t="n">
-        <v>-144</v>
+        <v>-855</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.0027</v>
+        <v>-0.016</v>
       </c>
       <c r="H54" t="n">
-        <v>1107</v>
+        <v>1344</v>
       </c>
       <c r="I54" t="n">
-        <v>52558</v>
+        <v>51613</v>
       </c>
       <c r="J54" t="n">
-        <v>52956</v>
+        <v>52416.25</v>
       </c>
       <c r="K54" t="n">
-        <v>53258</v>
+        <v>52886.5</v>
       </c>
       <c r="L54" t="n">
-        <v>53560</v>
+        <v>53356.75</v>
       </c>
       <c r="M54" t="n">
-        <v>53910</v>
+        <v>53993.5</v>
       </c>
       <c r="N54" t="n">
-        <v>54260</v>
+        <v>54630.25</v>
       </c>
       <c r="O54" t="n">
-        <v>54514</v>
+        <v>54934</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
       </c>
       <c r="Q54" s="6" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R54" s="6" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R54" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S54" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S54" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T54" s="8" t="n">
@@ -5058,65 +5054,63 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>53261</v>
+        <v>52376</v>
       </c>
       <c r="C55" t="n">
-        <v>53336</v>
+        <v>52672</v>
       </c>
       <c r="D55" t="n">
-        <v>51992</v>
+        <v>51209</v>
       </c>
       <c r="E55" t="n">
-        <v>52585</v>
+        <v>51761</v>
       </c>
       <c r="F55" t="n">
-        <v>-855</v>
+        <v>-824</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.016</v>
+        <v>-0.0157</v>
       </c>
       <c r="H55" t="n">
-        <v>1344</v>
+        <v>1463</v>
       </c>
       <c r="I55" t="n">
-        <v>51613</v>
+        <v>50648</v>
       </c>
       <c r="J55" t="n">
-        <v>52416.25</v>
+        <v>51201.5</v>
       </c>
       <c r="K55" t="n">
-        <v>52886.5</v>
+        <v>51913</v>
       </c>
       <c r="L55" t="n">
-        <v>53356.75</v>
+        <v>52624.5</v>
       </c>
       <c r="M55" t="n">
-        <v>53993.5</v>
+        <v>53257</v>
       </c>
       <c r="N55" t="n">
-        <v>54630.25</v>
+        <v>53889.5</v>
       </c>
       <c r="O55" t="n">
-        <v>54934</v>
+        <v>54680</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
       </c>
-      <c r="Q55" s="6" t="inlineStr">
+      <c r="Q55" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R55" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R55" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S55" s="7" t="inlineStr">
+      <c r="S55" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -5144,50 +5138,50 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>52376</v>
+        <v>52085</v>
       </c>
       <c r="C56" t="n">
-        <v>52672</v>
+        <v>52844</v>
       </c>
       <c r="D56" t="n">
-        <v>51209</v>
+        <v>51479</v>
       </c>
       <c r="E56" t="n">
-        <v>51761</v>
+        <v>52163</v>
       </c>
       <c r="F56" t="n">
-        <v>-824</v>
+        <v>402</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.0157</v>
+        <v>0.0078</v>
       </c>
       <c r="H56" t="n">
-        <v>1463</v>
+        <v>1365</v>
       </c>
       <c r="I56" t="n">
-        <v>50648</v>
+        <v>49746</v>
       </c>
       <c r="J56" t="n">
-        <v>51201.5</v>
+        <v>50208.25</v>
       </c>
       <c r="K56" t="n">
-        <v>51913</v>
+        <v>51029.5</v>
       </c>
       <c r="L56" t="n">
-        <v>52624.5</v>
+        <v>51850.75</v>
       </c>
       <c r="M56" t="n">
-        <v>53257</v>
+        <v>52492.5</v>
       </c>
       <c r="N56" t="n">
-        <v>53889.5</v>
+        <v>53134.25</v>
       </c>
       <c r="O56" t="n">
-        <v>54680</v>
+        <v>54135</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5195,18 +5189,18 @@
       <c r="Q56" s="6" t="n">
         <v/>
       </c>
-      <c r="R56" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R56" s="6" t="n">
+        <v/>
       </c>
       <c r="S56" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T56" s="8" t="n">
-        <v/>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T56" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U56" s="8" t="n">
         <v/>
@@ -5219,59 +5213,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X56" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>52085</v>
+        <v>52140</v>
       </c>
       <c r="C57" t="n">
-        <v>52844</v>
+        <v>52153</v>
       </c>
       <c r="D57" t="n">
-        <v>51479</v>
+        <v>50859</v>
       </c>
       <c r="E57" t="n">
-        <v>52163</v>
+        <v>51477</v>
       </c>
       <c r="F57" t="n">
-        <v>402</v>
+        <v>-686</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.0078</v>
+        <v>-0.0132</v>
       </c>
       <c r="H57" t="n">
-        <v>1365</v>
+        <v>1294</v>
       </c>
       <c r="I57" t="n">
-        <v>49746</v>
+        <v>50114</v>
       </c>
       <c r="J57" t="n">
-        <v>50208.25</v>
+        <v>50798.75</v>
       </c>
       <c r="K57" t="n">
-        <v>51029.5</v>
+        <v>51480.5</v>
       </c>
       <c r="L57" t="n">
-        <v>51850.75</v>
+        <v>52162.25</v>
       </c>
       <c r="M57" t="n">
-        <v>52492.5</v>
+        <v>52845.5</v>
       </c>
       <c r="N57" t="n">
-        <v>53134.25</v>
+        <v>53528.75</v>
       </c>
       <c r="O57" t="n">
-        <v>54135</v>
+        <v>54209</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5279,18 +5269,18 @@
       <c r="Q57" s="6" t="n">
         <v/>
       </c>
-      <c r="R57" s="6" t="n">
-        <v/>
+      <c r="R57" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S57" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T57" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="n">
+        <v/>
       </c>
       <c r="U57" s="8" t="n">
         <v/>
@@ -5303,87 +5293,7 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="B58" t="n">
-        <v>52140</v>
-      </c>
-      <c r="C58" t="n">
-        <v>52153</v>
-      </c>
-      <c r="D58" t="n">
-        <v>51218</v>
-      </c>
-      <c r="E58" t="n">
-        <v>51243</v>
-      </c>
-      <c r="F58" t="n">
-        <v>-920</v>
-      </c>
-      <c r="G58" s="5" t="n">
-        <v>-0.0176</v>
-      </c>
-      <c r="H58" t="n">
-        <v>935</v>
-      </c>
-      <c r="I58" t="n">
-        <v>50114</v>
-      </c>
-      <c r="J58" t="n">
-        <v>50798.75</v>
-      </c>
-      <c r="K58" t="n">
-        <v>51480.5</v>
-      </c>
-      <c r="L58" t="n">
-        <v>52162.25</v>
-      </c>
-      <c r="M58" t="n">
-        <v>52845.5</v>
-      </c>
-      <c r="N58" t="n">
-        <v>53528.75</v>
-      </c>
-      <c r="O58" t="n">
-        <v>54209</v>
-      </c>
-      <c r="P58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R58" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S58" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W58" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X58" t="inlineStr">
+      <c r="X57" t="inlineStr">
         <is>
           <t>強警訊</t>
         </is>

--- a/three_gate/analysis/YM_weekly.xlsx
+++ b/three_gate/analysis/YM_weekly.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X57"/>
+  <dimension ref="A1:X58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5299,6 +5299,88 @@
         </is>
       </c>
     </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>51608</v>
+      </c>
+      <c r="C58" t="n">
+        <v>51625</v>
+      </c>
+      <c r="D58" t="n">
+        <v>51600</v>
+      </c>
+      <c r="E58" t="n">
+        <v>51609</v>
+      </c>
+      <c r="F58" t="n">
+        <v>132</v>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v>0.0026</v>
+      </c>
+      <c r="H58" t="n">
+        <v>25</v>
+      </c>
+      <c r="I58" t="n">
+        <v>49565</v>
+      </c>
+      <c r="J58" t="n">
+        <v>50168.5</v>
+      </c>
+      <c r="K58" t="n">
+        <v>50830</v>
+      </c>
+      <c r="L58" t="n">
+        <v>51491.5</v>
+      </c>
+      <c r="M58" t="n">
+        <v>52124</v>
+      </c>
+      <c r="N58" t="n">
+        <v>52756.5</v>
+      </c>
+      <c r="O58" t="n">
+        <v>53447</v>
+      </c>
+      <c r="P58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S58" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W58" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/three_gate/analysis/YM_weekly.xlsx
+++ b/three_gate/analysis/YM_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>855</v>
       </c>
       <c r="I2" t="n">
-        <v>44168</v>
+        <v>44238</v>
       </c>
       <c r="J2" t="n">
-        <v>44648.5</v>
+        <v>44674.75</v>
       </c>
       <c r="K2" t="n">
-        <v>45043</v>
+        <v>45060.5</v>
       </c>
       <c r="L2" t="n">
-        <v>45437.5</v>
+        <v>45446.25</v>
       </c>
       <c r="M2" t="n">
-        <v>45875</v>
+        <v>45857.5</v>
       </c>
       <c r="N2" t="n">
-        <v>46312.5</v>
+        <v>46268.75</v>
       </c>
       <c r="O2" t="n">
-        <v>46664</v>
+        <v>46629</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -5306,25 +5306,25 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>51608</v>
+        <v>51486</v>
       </c>
       <c r="C58" t="n">
-        <v>51625</v>
+        <v>51860</v>
       </c>
       <c r="D58" t="n">
-        <v>51600</v>
+        <v>51141</v>
       </c>
       <c r="E58" t="n">
-        <v>51609</v>
+        <v>51786</v>
       </c>
       <c r="F58" t="n">
-        <v>132</v>
+        <v>309</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0026</v>
+        <v>0.006</v>
       </c>
       <c r="H58" t="n">
-        <v>25</v>
+        <v>719</v>
       </c>
       <c r="I58" t="n">
         <v>49565</v>

--- a/three_gate/analysis/YM_weekly.xlsx
+++ b/three_gate/analysis/YM_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>855</v>
       </c>
       <c r="I2" t="n">
-        <v>44238</v>
+        <v>44614</v>
       </c>
       <c r="J2" t="n">
-        <v>44674.75</v>
+        <v>44815.75</v>
       </c>
       <c r="K2" t="n">
-        <v>45060.5</v>
+        <v>45154.5</v>
       </c>
       <c r="L2" t="n">
-        <v>45446.25</v>
+        <v>45493.25</v>
       </c>
       <c r="M2" t="n">
-        <v>45857.5</v>
+        <v>45763.5</v>
       </c>
       <c r="N2" t="n">
-        <v>46268.75</v>
+        <v>46033.75</v>
       </c>
       <c r="O2" t="n">
-        <v>46629</v>
+        <v>46441</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -698,8 +698,10 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U2" s="8" t="n">
-        <v/>
+      <c r="U2" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V2" s="8" t="n">
         <v/>
@@ -5309,22 +5311,22 @@
         <v>51486</v>
       </c>
       <c r="C58" t="n">
-        <v>51860</v>
+        <v>51965</v>
       </c>
       <c r="D58" t="n">
         <v>51141</v>
       </c>
       <c r="E58" t="n">
-        <v>51786</v>
+        <v>51416</v>
       </c>
       <c r="F58" t="n">
-        <v>309</v>
+        <v>-61</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.006</v>
+        <v>-0.0012</v>
       </c>
       <c r="H58" t="n">
-        <v>719</v>
+        <v>824</v>
       </c>
       <c r="I58" t="n">
         <v>49565</v>
@@ -5356,9 +5358,9 @@
       <c r="R58" s="6" t="n">
         <v/>
       </c>
-      <c r="S58" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S58" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">
@@ -5377,7 +5379,7 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/YM_weekly.xlsx
+++ b/three_gate/analysis/YM_weekly.xlsx
@@ -5317,13 +5317,13 @@
         <v>51141</v>
       </c>
       <c r="E58" t="n">
-        <v>51416</v>
+        <v>51395</v>
       </c>
       <c r="F58" t="n">
-        <v>-61</v>
+        <v>-82</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0012</v>
+        <v>-0.0016</v>
       </c>
       <c r="H58" t="n">
         <v>824</v>

--- a/three_gate/analysis/YM_weekly.xlsx
+++ b/three_gate/analysis/YM_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>855</v>
       </c>
       <c r="I2" t="n">
-        <v>44614</v>
+        <v>44684</v>
       </c>
       <c r="J2" t="n">
-        <v>44815.75</v>
+        <v>44842</v>
       </c>
       <c r="K2" t="n">
-        <v>45154.5</v>
+        <v>45172</v>
       </c>
       <c r="L2" t="n">
-        <v>45493.25</v>
+        <v>45502</v>
       </c>
       <c r="M2" t="n">
-        <v>45763.5</v>
+        <v>45746</v>
       </c>
       <c r="N2" t="n">
-        <v>46033.75</v>
+        <v>45990</v>
       </c>
       <c r="O2" t="n">
-        <v>46441</v>
+        <v>46406</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -5317,13 +5317,13 @@
         <v>51141</v>
       </c>
       <c r="E58" t="n">
-        <v>51395</v>
+        <v>51592</v>
       </c>
       <c r="F58" t="n">
-        <v>-82</v>
+        <v>115</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0016</v>
+        <v>0.0022</v>
       </c>
       <c r="H58" t="n">
         <v>824</v>
@@ -5358,9 +5358,9 @@
       <c r="R58" s="6" t="n">
         <v/>
       </c>
-      <c r="S58" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S58" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">
@@ -5379,7 +5379,7 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/YM_weekly.xlsx
+++ b/three_gate/analysis/YM_weekly.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X58"/>
+  <dimension ref="A1:X57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,50 +634,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>45475</v>
+        <v>45860</v>
       </c>
       <c r="C2" t="n">
-        <v>46176</v>
+        <v>46379</v>
       </c>
       <c r="D2" t="n">
-        <v>45321</v>
+        <v>45680</v>
       </c>
       <c r="E2" t="n">
-        <v>45854</v>
+        <v>46328</v>
       </c>
       <c r="F2" t="n">
-        <v>395</v>
+        <v>474</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.008699999999999999</v>
+        <v>0.0103</v>
       </c>
       <c r="H2" t="n">
-        <v>855</v>
+        <v>699</v>
       </c>
       <c r="I2" t="n">
-        <v>44684</v>
+        <v>44466</v>
       </c>
       <c r="J2" t="n">
-        <v>44842</v>
+        <v>45051.75</v>
       </c>
       <c r="K2" t="n">
-        <v>45172</v>
+        <v>45426.5</v>
       </c>
       <c r="L2" t="n">
-        <v>45502</v>
+        <v>45801.25</v>
       </c>
       <c r="M2" t="n">
-        <v>45746</v>
+        <v>46281.5</v>
       </c>
       <c r="N2" t="n">
-        <v>45990</v>
+        <v>46761.75</v>
       </c>
       <c r="O2" t="n">
-        <v>46406</v>
+        <v>47031</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -698,10 +698,8 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U2" s="8" t="n">
+        <v/>
       </c>
       <c r="V2" s="8" t="n">
         <v/>
@@ -716,50 +714,50 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>45860</v>
+        <v>46605</v>
       </c>
       <c r="C3" t="n">
-        <v>46379</v>
+        <v>47055</v>
       </c>
       <c r="D3" t="n">
-        <v>45680</v>
+        <v>46098</v>
       </c>
       <c r="E3" t="n">
-        <v>46328</v>
+        <v>46556</v>
       </c>
       <c r="F3" t="n">
-        <v>474</v>
+        <v>228</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.0103</v>
+        <v>0.0049</v>
       </c>
       <c r="H3" t="n">
-        <v>699</v>
+        <v>957</v>
       </c>
       <c r="I3" t="n">
-        <v>44466</v>
+        <v>44981</v>
       </c>
       <c r="J3" t="n">
-        <v>45051.75</v>
+        <v>45778.25</v>
       </c>
       <c r="K3" t="n">
-        <v>45426.5</v>
+        <v>45978.5</v>
       </c>
       <c r="L3" t="n">
-        <v>45801.25</v>
+        <v>46178.75</v>
       </c>
       <c r="M3" t="n">
-        <v>46281.5</v>
+        <v>46677.5</v>
       </c>
       <c r="N3" t="n">
-        <v>46761.75</v>
+        <v>47176.25</v>
       </c>
       <c r="O3" t="n">
-        <v>47031</v>
+        <v>47078</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -796,50 +794,50 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>46605</v>
+        <v>46565</v>
       </c>
       <c r="C4" t="n">
-        <v>47055</v>
+        <v>47323</v>
       </c>
       <c r="D4" t="n">
-        <v>46098</v>
+        <v>46335</v>
       </c>
       <c r="E4" t="n">
-        <v>46556</v>
+        <v>47031</v>
       </c>
       <c r="F4" t="n">
-        <v>228</v>
+        <v>475</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.0049</v>
+        <v>0.0102</v>
       </c>
       <c r="H4" t="n">
-        <v>957</v>
+        <v>988</v>
       </c>
       <c r="I4" t="n">
-        <v>44981</v>
+        <v>45141</v>
       </c>
       <c r="J4" t="n">
-        <v>45778.25</v>
+        <v>45588.75</v>
       </c>
       <c r="K4" t="n">
-        <v>45978.5</v>
+        <v>46077.5</v>
       </c>
       <c r="L4" t="n">
-        <v>46178.75</v>
+        <v>46566.25</v>
       </c>
       <c r="M4" t="n">
-        <v>46677.5</v>
+        <v>47034.5</v>
       </c>
       <c r="N4" t="n">
-        <v>47176.25</v>
+        <v>47502.75</v>
       </c>
       <c r="O4" t="n">
-        <v>47078</v>
+        <v>48012</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -876,79 +874,83 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>46565</v>
+        <v>47048</v>
       </c>
       <c r="C5" t="n">
-        <v>47323</v>
+        <v>47162</v>
       </c>
       <c r="D5" t="n">
-        <v>46335</v>
+        <v>45387</v>
       </c>
       <c r="E5" t="n">
-        <v>47031</v>
+        <v>45706</v>
       </c>
       <c r="F5" t="n">
-        <v>475</v>
+        <v>-1325</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.0102</v>
+        <v>-0.0282</v>
       </c>
       <c r="H5" t="n">
-        <v>988</v>
+        <v>1775</v>
       </c>
       <c r="I5" t="n">
-        <v>45141</v>
+        <v>45347</v>
       </c>
       <c r="J5" t="n">
-        <v>45588.75</v>
+        <v>46144</v>
       </c>
       <c r="K5" t="n">
-        <v>46077.5</v>
+        <v>46537</v>
       </c>
       <c r="L5" t="n">
-        <v>46566.25</v>
+        <v>46930</v>
       </c>
       <c r="M5" t="n">
-        <v>47034.5</v>
+        <v>47525</v>
       </c>
       <c r="N5" t="n">
-        <v>47502.75</v>
+        <v>48120</v>
       </c>
       <c r="O5" t="n">
-        <v>48012</v>
-      </c>
-      <c r="P5" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q5" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R5" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S5" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="inlineStr">
+        <v>48311</v>
+      </c>
+      <c r="P5" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="Q5" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R5" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S5" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="n">
+        <v/>
+      </c>
       <c r="U5" s="8" t="n">
         <v/>
       </c>
       <c r="V5" s="8" t="n">
         <v/>
       </c>
-      <c r="W5" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W5" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X5" t="inlineStr"/>
@@ -956,74 +958,70 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>47048</v>
+        <v>45837</v>
       </c>
       <c r="C6" t="n">
-        <v>47162</v>
+        <v>46915</v>
       </c>
       <c r="D6" t="n">
-        <v>45387</v>
+        <v>45605</v>
       </c>
       <c r="E6" t="n">
-        <v>45706</v>
+        <v>46381</v>
       </c>
       <c r="F6" t="n">
-        <v>-1325</v>
+        <v>675</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.0282</v>
+        <v>0.0148</v>
       </c>
       <c r="H6" t="n">
-        <v>1775</v>
+        <v>1310</v>
       </c>
       <c r="I6" t="n">
-        <v>45347</v>
+        <v>43612</v>
       </c>
       <c r="J6" t="n">
-        <v>46144</v>
+        <v>43646.75</v>
       </c>
       <c r="K6" t="n">
-        <v>46537</v>
+        <v>44818.5</v>
       </c>
       <c r="L6" t="n">
-        <v>46930</v>
+        <v>45990.25</v>
       </c>
       <c r="M6" t="n">
-        <v>47525</v>
+        <v>46593.5</v>
       </c>
       <c r="N6" t="n">
-        <v>48120</v>
+        <v>47196.75</v>
       </c>
       <c r="O6" t="n">
-        <v>48311</v>
-      </c>
-      <c r="P6" s="6" t="inlineStr">
+        <v>48937</v>
+      </c>
+      <c r="P6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S6" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q6" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R6" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S6" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="n">
-        <v/>
-      </c>
       <c r="U6" s="8" t="n">
         <v/>
       </c>
@@ -1035,55 +1033,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr"/>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>45837</v>
+        <v>46489</v>
       </c>
       <c r="C7" t="n">
-        <v>46915</v>
+        <v>47508</v>
       </c>
       <c r="D7" t="n">
-        <v>45605</v>
+        <v>46316</v>
       </c>
       <c r="E7" t="n">
-        <v>46381</v>
+        <v>47396</v>
       </c>
       <c r="F7" t="n">
-        <v>675</v>
+        <v>1015</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.0148</v>
+        <v>0.0219</v>
       </c>
       <c r="H7" t="n">
-        <v>1310</v>
+        <v>1192</v>
       </c>
       <c r="I7" t="n">
-        <v>43612</v>
+        <v>44295</v>
       </c>
       <c r="J7" t="n">
-        <v>43646.75</v>
+        <v>45131.5</v>
       </c>
       <c r="K7" t="n">
-        <v>44818.5</v>
+        <v>45726</v>
       </c>
       <c r="L7" t="n">
-        <v>45990.25</v>
+        <v>46320.5</v>
       </c>
       <c r="M7" t="n">
-        <v>46593.5</v>
+        <v>47036</v>
       </c>
       <c r="N7" t="n">
-        <v>47196.75</v>
+        <v>47751.5</v>
       </c>
       <c r="O7" t="n">
-        <v>48937</v>
+        <v>48225</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1101,12 +1103,14 @@
       </c>
       <c r="T7" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U7" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U7" s="8" t="n">
-        <v/>
-      </c>
       <c r="V7" s="8" t="n">
         <v/>
       </c>
@@ -1117,57 +1121,57 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>46489</v>
+        <v>47711</v>
       </c>
       <c r="C8" t="n">
-        <v>47508</v>
+        <v>48214</v>
       </c>
       <c r="D8" t="n">
-        <v>46316</v>
+        <v>47488</v>
       </c>
       <c r="E8" t="n">
-        <v>47396</v>
+        <v>47722</v>
       </c>
       <c r="F8" t="n">
-        <v>1015</v>
+        <v>326</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.0219</v>
+        <v>0.0069</v>
       </c>
       <c r="H8" t="n">
-        <v>1192</v>
+        <v>726</v>
       </c>
       <c r="I8" t="n">
-        <v>44295</v>
+        <v>45124</v>
       </c>
       <c r="J8" t="n">
-        <v>45131.5</v>
+        <v>46446</v>
       </c>
       <c r="K8" t="n">
-        <v>45726</v>
+        <v>46800</v>
       </c>
       <c r="L8" t="n">
-        <v>46320.5</v>
+        <v>47154</v>
       </c>
       <c r="M8" t="n">
-        <v>47036</v>
+        <v>47992</v>
       </c>
       <c r="N8" t="n">
-        <v>47751.5</v>
+        <v>48830</v>
       </c>
       <c r="O8" t="n">
-        <v>48225</v>
+        <v>48700</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1185,13 +1189,11 @@
       </c>
       <c r="T8" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U8" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U8" s="8" t="n">
+        <v/>
       </c>
       <c r="V8" s="8" t="n">
         <v/>
@@ -1210,70 +1212,74 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>47711</v>
+        <v>47735</v>
       </c>
       <c r="C9" t="n">
-        <v>48214</v>
+        <v>47869</v>
       </c>
       <c r="D9" t="n">
-        <v>47488</v>
+        <v>46574</v>
       </c>
       <c r="E9" t="n">
-        <v>47722</v>
+        <v>47085</v>
       </c>
       <c r="F9" t="n">
-        <v>326</v>
+        <v>-637</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.0069</v>
+        <v>-0.0133</v>
       </c>
       <c r="H9" t="n">
-        <v>726</v>
+        <v>1295</v>
       </c>
       <c r="I9" t="n">
-        <v>45124</v>
+        <v>46762</v>
       </c>
       <c r="J9" t="n">
-        <v>46446</v>
+        <v>46931.5</v>
       </c>
       <c r="K9" t="n">
-        <v>46800</v>
+        <v>47359</v>
       </c>
       <c r="L9" t="n">
-        <v>47154</v>
+        <v>47786.5</v>
       </c>
       <c r="M9" t="n">
-        <v>47992</v>
+        <v>48085</v>
       </c>
       <c r="N9" t="n">
-        <v>48830</v>
+        <v>48383.5</v>
       </c>
       <c r="O9" t="n">
-        <v>48700</v>
-      </c>
-      <c r="P9" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q9" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R9" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S9" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="inlineStr">
+        <v>48940</v>
+      </c>
+      <c r="P9" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q9" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R9" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S9" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="n">
+        <v/>
+      </c>
       <c r="U9" s="8" t="n">
         <v/>
       </c>
@@ -1285,86 +1291,80 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>47735</v>
+        <v>47208</v>
       </c>
       <c r="C10" t="n">
-        <v>47869</v>
+        <v>48528</v>
       </c>
       <c r="D10" t="n">
-        <v>46574</v>
+        <v>46939</v>
       </c>
       <c r="E10" t="n">
-        <v>47085</v>
+        <v>47229</v>
       </c>
       <c r="F10" t="n">
-        <v>-637</v>
+        <v>144</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.0133</v>
+        <v>0.0031</v>
       </c>
       <c r="H10" t="n">
-        <v>1295</v>
+        <v>1589</v>
       </c>
       <c r="I10" t="n">
-        <v>46762</v>
+        <v>45279</v>
       </c>
       <c r="J10" t="n">
-        <v>46931.5</v>
+        <v>45721.75</v>
       </c>
       <c r="K10" t="n">
-        <v>47359</v>
+        <v>46437.5</v>
       </c>
       <c r="L10" t="n">
-        <v>47786.5</v>
+        <v>47153.25</v>
       </c>
       <c r="M10" t="n">
-        <v>48085</v>
+        <v>47732.5</v>
       </c>
       <c r="N10" t="n">
-        <v>48383.5</v>
+        <v>48311.75</v>
       </c>
       <c r="O10" t="n">
-        <v>48940</v>
-      </c>
-      <c r="P10" s="6" t="inlineStr">
+        <v>49164</v>
+      </c>
+      <c r="P10" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q10" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R10" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S10" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q10" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R10" s="6" t="inlineStr">
+      <c r="U10" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S10" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U10" s="8" t="n">
-        <v/>
-      </c>
       <c r="V10" s="8" t="n">
         <v/>
       </c>
@@ -1373,55 +1373,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr"/>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>47208</v>
+        <v>47237</v>
       </c>
       <c r="C11" t="n">
-        <v>48528</v>
+        <v>47368</v>
       </c>
       <c r="D11" t="n">
-        <v>46939</v>
+        <v>45779</v>
       </c>
       <c r="E11" t="n">
-        <v>47229</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="n">
-        <v>144</v>
+        <v>-908</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0031</v>
+        <v>-0.0192</v>
       </c>
       <c r="H11" t="n">
         <v>1589</v>
       </c>
       <c r="I11" t="n">
-        <v>45279</v>
+        <v>45350</v>
       </c>
       <c r="J11" t="n">
-        <v>45721.75</v>
+        <v>45387.75</v>
       </c>
       <c r="K11" t="n">
-        <v>46437.5</v>
+        <v>46434.5</v>
       </c>
       <c r="L11" t="n">
-        <v>47153.25</v>
+        <v>47481.25</v>
       </c>
       <c r="M11" t="n">
-        <v>47732.5</v>
+        <v>48023.5</v>
       </c>
       <c r="N11" t="n">
-        <v>48311.75</v>
+        <v>48565.75</v>
       </c>
       <c r="O11" t="n">
-        <v>49164</v>
+        <v>50117</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1429,23 +1433,21 @@
       <c r="Q11" s="6" t="n">
         <v/>
       </c>
-      <c r="R11" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S11" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U11" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R11" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S11" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U11" s="8" t="n">
+        <v/>
       </c>
       <c r="V11" s="8" t="n">
         <v/>
@@ -1455,59 +1457,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>47237</v>
+        <v>46504</v>
       </c>
       <c r="C12" t="n">
-        <v>47368</v>
+        <v>47796</v>
       </c>
       <c r="D12" t="n">
-        <v>45779</v>
+        <v>46165</v>
       </c>
       <c r="E12" t="n">
-        <v>46321</v>
+        <v>47743</v>
       </c>
       <c r="F12" t="n">
-        <v>-908</v>
+        <v>1422</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.0192</v>
+        <v>0.0307</v>
       </c>
       <c r="H12" t="n">
-        <v>1589</v>
+        <v>1631</v>
       </c>
       <c r="I12" t="n">
-        <v>45350</v>
+        <v>44190</v>
       </c>
       <c r="J12" t="n">
-        <v>45387.75</v>
+        <v>44605.75</v>
       </c>
       <c r="K12" t="n">
-        <v>46434.5</v>
+        <v>45526.5</v>
       </c>
       <c r="L12" t="n">
-        <v>47481.25</v>
+        <v>46447.25</v>
       </c>
       <c r="M12" t="n">
-        <v>48023.5</v>
+        <v>47115.5</v>
       </c>
       <c r="N12" t="n">
-        <v>48565.75</v>
+        <v>47783.75</v>
       </c>
       <c r="O12" t="n">
-        <v>50117</v>
+        <v>48957</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1515,22 +1513,24 @@
       <c r="Q12" s="6" t="n">
         <v/>
       </c>
-      <c r="R12" s="6" t="inlineStr">
+      <c r="R12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S12" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U12" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S12" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U12" s="8" t="n">
-        <v/>
-      </c>
       <c r="V12" s="8" t="n">
         <v/>
       </c>
@@ -1539,55 +1539,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr"/>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>46504</v>
+        <v>47741</v>
       </c>
       <c r="C13" t="n">
-        <v>47796</v>
+        <v>48184</v>
       </c>
       <c r="D13" t="n">
-        <v>46165</v>
+        <v>47269</v>
       </c>
       <c r="E13" t="n">
-        <v>47743</v>
+        <v>48001</v>
       </c>
       <c r="F13" t="n">
-        <v>1422</v>
+        <v>258</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.0307</v>
+        <v>0.0054</v>
       </c>
       <c r="H13" t="n">
-        <v>1631</v>
+        <v>915</v>
       </c>
       <c r="I13" t="n">
-        <v>44190</v>
+        <v>44534</v>
       </c>
       <c r="J13" t="n">
-        <v>44605.75</v>
+        <v>46493.25</v>
       </c>
       <c r="K13" t="n">
-        <v>45526.5</v>
+        <v>46927.5</v>
       </c>
       <c r="L13" t="n">
-        <v>46447.25</v>
+        <v>47361.75</v>
       </c>
       <c r="M13" t="n">
-        <v>47115.5</v>
+        <v>48558.5</v>
       </c>
       <c r="N13" t="n">
-        <v>47783.75</v>
+        <v>49755.25</v>
       </c>
       <c r="O13" t="n">
-        <v>48957</v>
+        <v>49427</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1605,13 +1609,11 @@
       </c>
       <c r="T13" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U13" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U13" s="8" t="n">
+        <v/>
       </c>
       <c r="V13" s="8" t="n">
         <v/>
@@ -1630,50 +1632,50 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>47741</v>
+        <v>48015</v>
       </c>
       <c r="C14" t="n">
-        <v>48184</v>
+        <v>48917</v>
       </c>
       <c r="D14" t="n">
-        <v>47269</v>
+        <v>47504</v>
       </c>
       <c r="E14" t="n">
-        <v>48001</v>
+        <v>48474</v>
       </c>
       <c r="F14" t="n">
-        <v>258</v>
+        <v>473</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0054</v>
+        <v>0.009900000000000001</v>
       </c>
       <c r="H14" t="n">
-        <v>915</v>
+        <v>1413</v>
       </c>
       <c r="I14" t="n">
-        <v>44534</v>
+        <v>46354</v>
       </c>
       <c r="J14" t="n">
-        <v>46493.25</v>
+        <v>47223.25</v>
       </c>
       <c r="K14" t="n">
-        <v>46927.5</v>
+        <v>47543.5</v>
       </c>
       <c r="L14" t="n">
-        <v>47361.75</v>
+        <v>47863.75</v>
       </c>
       <c r="M14" t="n">
-        <v>48558.5</v>
+        <v>48458.5</v>
       </c>
       <c r="N14" t="n">
-        <v>49755.25</v>
+        <v>49053.25</v>
       </c>
       <c r="O14" t="n">
-        <v>49427</v>
+        <v>49099</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1681,8 +1683,10 @@
       <c r="Q14" s="6" t="n">
         <v/>
       </c>
-      <c r="R14" s="6" t="n">
-        <v/>
+      <c r="R14" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S14" s="7" t="inlineStr">
         <is>
@@ -1714,50 +1718,50 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>48015</v>
+        <v>48517</v>
       </c>
       <c r="C15" t="n">
-        <v>48917</v>
+        <v>48745</v>
       </c>
       <c r="D15" t="n">
-        <v>47504</v>
+        <v>47809</v>
       </c>
       <c r="E15" t="n">
-        <v>48474</v>
+        <v>48090</v>
       </c>
       <c r="F15" t="n">
-        <v>473</v>
+        <v>-384</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.009900000000000001</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="H15" t="n">
-        <v>1413</v>
+        <v>936</v>
       </c>
       <c r="I15" t="n">
-        <v>46354</v>
+        <v>46091</v>
       </c>
       <c r="J15" t="n">
-        <v>47223.25</v>
+        <v>47192.75</v>
       </c>
       <c r="K15" t="n">
-        <v>47543.5</v>
+        <v>47767.5</v>
       </c>
       <c r="L15" t="n">
-        <v>47863.75</v>
+        <v>48342.25</v>
       </c>
       <c r="M15" t="n">
-        <v>48458.5</v>
+        <v>49180.5</v>
       </c>
       <c r="N15" t="n">
-        <v>49053.25</v>
+        <v>50018.75</v>
       </c>
       <c r="O15" t="n">
-        <v>49099</v>
+        <v>50330</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1765,20 +1769,16 @@
       <c r="Q15" s="6" t="n">
         <v/>
       </c>
-      <c r="R15" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S15" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S15" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="n">
+        <v/>
       </c>
       <c r="U15" s="8" t="n">
         <v/>
@@ -1793,57 +1793,57 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>48517</v>
+        <v>48600</v>
       </c>
       <c r="C16" t="n">
-        <v>48745</v>
+        <v>49086</v>
       </c>
       <c r="D16" t="n">
-        <v>47809</v>
+        <v>48458</v>
       </c>
       <c r="E16" t="n">
-        <v>48090</v>
+        <v>48998</v>
       </c>
       <c r="F16" t="n">
-        <v>-384</v>
+        <v>908</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-0.007900000000000001</v>
+        <v>0.0189</v>
       </c>
       <c r="H16" t="n">
-        <v>936</v>
+        <v>628</v>
       </c>
       <c r="I16" t="n">
-        <v>46091</v>
+        <v>46873</v>
       </c>
       <c r="J16" t="n">
-        <v>47192.75</v>
+        <v>47060.5</v>
       </c>
       <c r="K16" t="n">
-        <v>47767.5</v>
+        <v>47622</v>
       </c>
       <c r="L16" t="n">
-        <v>48342.25</v>
+        <v>48183.5</v>
       </c>
       <c r="M16" t="n">
-        <v>49180.5</v>
+        <v>48558</v>
       </c>
       <c r="N16" t="n">
-        <v>50018.75</v>
+        <v>48932.5</v>
       </c>
       <c r="O16" t="n">
-        <v>50330</v>
+        <v>49681</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1854,103 +1854,103 @@
       <c r="R16" s="6" t="n">
         <v/>
       </c>
-      <c r="S16" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U16" s="8" t="n">
-        <v/>
+      <c r="S16" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U16" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V16" s="8" t="n">
         <v/>
       </c>
-      <c r="W16" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W16" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>48600</v>
+        <v>48998</v>
       </c>
       <c r="C17" t="n">
-        <v>49086</v>
+        <v>49052</v>
       </c>
       <c r="D17" t="n">
-        <v>48458</v>
+        <v>48092</v>
       </c>
       <c r="E17" t="n">
-        <v>48998</v>
+        <v>48616</v>
       </c>
       <c r="F17" t="n">
-        <v>908</v>
+        <v>-382</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0189</v>
+        <v>-0.0078</v>
       </c>
       <c r="H17" t="n">
-        <v>628</v>
+        <v>960</v>
       </c>
       <c r="I17" t="n">
-        <v>46873</v>
+        <v>47830</v>
       </c>
       <c r="J17" t="n">
-        <v>47060.5</v>
+        <v>48483</v>
       </c>
       <c r="K17" t="n">
-        <v>47622</v>
+        <v>48684</v>
       </c>
       <c r="L17" t="n">
-        <v>48183.5</v>
+        <v>48885</v>
       </c>
       <c r="M17" t="n">
-        <v>48558</v>
+        <v>49312</v>
       </c>
       <c r="N17" t="n">
-        <v>48932.5</v>
+        <v>49739</v>
       </c>
       <c r="O17" t="n">
-        <v>49681</v>
+        <v>49714</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
       </c>
-      <c r="Q17" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R17" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S17" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="inlineStr">
+      <c r="Q17" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U17" s="8" t="inlineStr">
+      <c r="R17" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S17" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U17" s="8" t="n">
+        <v/>
+      </c>
       <c r="V17" s="8" t="n">
         <v/>
       </c>
@@ -1959,80 +1959,84 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr"/>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>48998</v>
+        <v>48653</v>
       </c>
       <c r="C18" t="n">
-        <v>49052</v>
+        <v>49876</v>
       </c>
       <c r="D18" t="n">
-        <v>48092</v>
+        <v>48556</v>
       </c>
       <c r="E18" t="n">
-        <v>48616</v>
+        <v>49726</v>
       </c>
       <c r="F18" t="n">
-        <v>-382</v>
+        <v>1110</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-0.0078</v>
+        <v>0.0228</v>
       </c>
       <c r="H18" t="n">
-        <v>960</v>
+        <v>1320</v>
       </c>
       <c r="I18" t="n">
-        <v>47830</v>
+        <v>47132</v>
       </c>
       <c r="J18" t="n">
-        <v>48483</v>
+        <v>47678</v>
       </c>
       <c r="K18" t="n">
-        <v>48684</v>
+        <v>48136</v>
       </c>
       <c r="L18" t="n">
-        <v>48885</v>
+        <v>48594</v>
       </c>
       <c r="M18" t="n">
-        <v>49312</v>
+        <v>49096</v>
       </c>
       <c r="N18" t="n">
-        <v>49739</v>
+        <v>49598</v>
       </c>
       <c r="O18" t="n">
-        <v>49714</v>
+        <v>50012</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
       </c>
-      <c r="Q18" s="6" t="inlineStr">
+      <c r="Q18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S18" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R18" s="6" t="inlineStr">
+      <c r="U18" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S18" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U18" s="8" t="n">
-        <v/>
-      </c>
       <c r="V18" s="8" t="n">
         <v/>
       </c>
@@ -2041,59 +2045,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>48653</v>
+        <v>49720</v>
       </c>
       <c r="C19" t="n">
-        <v>49876</v>
+        <v>49901</v>
       </c>
       <c r="D19" t="n">
-        <v>48556</v>
+        <v>49057</v>
       </c>
       <c r="E19" t="n">
-        <v>49726</v>
+        <v>49547</v>
       </c>
       <c r="F19" t="n">
-        <v>1110</v>
+        <v>-179</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.0228</v>
+        <v>-0.0036</v>
       </c>
       <c r="H19" t="n">
-        <v>1320</v>
+        <v>844</v>
       </c>
       <c r="I19" t="n">
-        <v>47132</v>
+        <v>47236</v>
       </c>
       <c r="J19" t="n">
-        <v>47678</v>
+        <v>48661</v>
       </c>
       <c r="K19" t="n">
-        <v>48136</v>
+        <v>49066</v>
       </c>
       <c r="L19" t="n">
-        <v>48594</v>
+        <v>49471</v>
       </c>
       <c r="M19" t="n">
-        <v>49096</v>
+        <v>50386</v>
       </c>
       <c r="N19" t="n">
-        <v>49598</v>
+        <v>51301</v>
       </c>
       <c r="O19" t="n">
-        <v>50012</v>
+        <v>51196</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2101,23 +2101,21 @@
       <c r="Q19" s="6" t="n">
         <v/>
       </c>
-      <c r="R19" s="6" t="n">
-        <v/>
+      <c r="R19" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S19" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U19" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U19" s="8" t="n">
+        <v/>
       </c>
       <c r="V19" s="8" t="n">
         <v/>
@@ -2127,70 +2125,76 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr"/>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>49720</v>
+        <v>49310</v>
       </c>
       <c r="C20" t="n">
-        <v>49901</v>
+        <v>49795</v>
       </c>
       <c r="D20" t="n">
-        <v>49057</v>
+        <v>48488</v>
       </c>
       <c r="E20" t="n">
-        <v>49547</v>
+        <v>49263</v>
       </c>
       <c r="F20" t="n">
-        <v>-179</v>
+        <v>-284</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-0.0036</v>
+        <v>-0.0057</v>
       </c>
       <c r="H20" t="n">
-        <v>844</v>
+        <v>1307</v>
       </c>
       <c r="I20" t="n">
-        <v>47236</v>
+        <v>48213</v>
       </c>
       <c r="J20" t="n">
-        <v>48661</v>
+        <v>48737</v>
       </c>
       <c r="K20" t="n">
-        <v>49066</v>
+        <v>49125</v>
       </c>
       <c r="L20" t="n">
-        <v>49471</v>
+        <v>49513</v>
       </c>
       <c r="M20" t="n">
-        <v>50386</v>
+        <v>49969</v>
       </c>
       <c r="N20" t="n">
-        <v>51301</v>
+        <v>50425</v>
       </c>
       <c r="O20" t="n">
-        <v>51196</v>
+        <v>50745</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
       </c>
-      <c r="Q20" s="6" t="n">
-        <v/>
+      <c r="Q20" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R20" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S20" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S20" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T20" s="8" t="n">
@@ -2209,74 +2213,72 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>49310</v>
+        <v>49036</v>
       </c>
       <c r="C21" t="n">
-        <v>49795</v>
+        <v>49644</v>
       </c>
       <c r="D21" t="n">
-        <v>48488</v>
+        <v>48571</v>
       </c>
       <c r="E21" t="n">
-        <v>49263</v>
+        <v>49008</v>
       </c>
       <c r="F21" t="n">
-        <v>-284</v>
+        <v>-255</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.0057</v>
+        <v>-0.0052</v>
       </c>
       <c r="H21" t="n">
-        <v>1307</v>
+        <v>1073</v>
       </c>
       <c r="I21" t="n">
-        <v>48213</v>
+        <v>47181</v>
       </c>
       <c r="J21" t="n">
-        <v>48737</v>
+        <v>48016.75</v>
       </c>
       <c r="K21" t="n">
-        <v>49125</v>
+        <v>48609.5</v>
       </c>
       <c r="L21" t="n">
-        <v>49513</v>
+        <v>49202.25</v>
       </c>
       <c r="M21" t="n">
-        <v>49969</v>
+        <v>49916.5</v>
       </c>
       <c r="N21" t="n">
-        <v>50425</v>
+        <v>50630.75</v>
       </c>
       <c r="O21" t="n">
-        <v>50745</v>
+        <v>51102</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
       </c>
-      <c r="Q21" s="6" t="inlineStr">
+      <c r="Q21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R21" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R21" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
       <c r="S21" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T21" s="8" t="n">
@@ -2295,57 +2297,57 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>49036</v>
+        <v>48864</v>
       </c>
       <c r="C22" t="n">
-        <v>49644</v>
+        <v>50263</v>
       </c>
       <c r="D22" t="n">
-        <v>48571</v>
+        <v>48506</v>
       </c>
       <c r="E22" t="n">
-        <v>49008</v>
+        <v>50205</v>
       </c>
       <c r="F22" t="n">
-        <v>-255</v>
+        <v>1197</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.0052</v>
+        <v>0.0244</v>
       </c>
       <c r="H22" t="n">
-        <v>1073</v>
+        <v>1757</v>
       </c>
       <c r="I22" t="n">
-        <v>47181</v>
+        <v>47498</v>
       </c>
       <c r="J22" t="n">
-        <v>48016.75</v>
+        <v>47885.25</v>
       </c>
       <c r="K22" t="n">
-        <v>48609.5</v>
+        <v>48471.5</v>
       </c>
       <c r="L22" t="n">
-        <v>49202.25</v>
+        <v>49057.75</v>
       </c>
       <c r="M22" t="n">
-        <v>49916.5</v>
+        <v>49544.5</v>
       </c>
       <c r="N22" t="n">
-        <v>50630.75</v>
+        <v>50031.25</v>
       </c>
       <c r="O22" t="n">
-        <v>51102</v>
+        <v>50717</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2353,21 +2355,23 @@
       <c r="Q22" s="6" t="n">
         <v/>
       </c>
-      <c r="R22" s="6" t="inlineStr">
+      <c r="R22" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S22" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S22" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U22" s="8" t="n">
-        <v/>
+      <c r="U22" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V22" s="8" t="n">
         <v/>
@@ -2379,57 +2383,57 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>48864</v>
+        <v>50240</v>
       </c>
       <c r="C23" t="n">
-        <v>50263</v>
+        <v>50611</v>
       </c>
       <c r="D23" t="n">
-        <v>48506</v>
+        <v>49155</v>
       </c>
       <c r="E23" t="n">
-        <v>50205</v>
+        <v>49569</v>
       </c>
       <c r="F23" t="n">
-        <v>1197</v>
+        <v>-636</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.0244</v>
+        <v>-0.0127</v>
       </c>
       <c r="H23" t="n">
-        <v>1757</v>
+        <v>1456</v>
       </c>
       <c r="I23" t="n">
-        <v>47498</v>
+        <v>46749</v>
       </c>
       <c r="J23" t="n">
-        <v>47885.25</v>
+        <v>48858.25</v>
       </c>
       <c r="K23" t="n">
-        <v>48471.5</v>
+        <v>49326.5</v>
       </c>
       <c r="L23" t="n">
-        <v>49057.75</v>
+        <v>49794.75</v>
       </c>
       <c r="M23" t="n">
-        <v>49544.5</v>
+        <v>51083.5</v>
       </c>
       <c r="N23" t="n">
-        <v>50031.25</v>
+        <v>52372.25</v>
       </c>
       <c r="O23" t="n">
-        <v>50717</v>
+        <v>52020</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2437,23 +2441,21 @@
       <c r="Q23" s="6" t="n">
         <v/>
       </c>
-      <c r="R23" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S23" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="inlineStr">
+      <c r="R23" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U23" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S23" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U23" s="8" t="n">
+        <v/>
       </c>
       <c r="V23" s="8" t="n">
         <v/>
@@ -2472,50 +2474,50 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>50240</v>
+        <v>49549</v>
       </c>
       <c r="C24" t="n">
-        <v>50611</v>
+        <v>49967</v>
       </c>
       <c r="D24" t="n">
-        <v>49155</v>
+        <v>49204</v>
       </c>
       <c r="E24" t="n">
-        <v>49569</v>
+        <v>49674</v>
       </c>
       <c r="F24" t="n">
-        <v>-636</v>
+        <v>105</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-0.0127</v>
+        <v>0.0021</v>
       </c>
       <c r="H24" t="n">
-        <v>1456</v>
+        <v>763</v>
       </c>
       <c r="I24" t="n">
-        <v>46749</v>
+        <v>47699</v>
       </c>
       <c r="J24" t="n">
-        <v>48858.25</v>
+        <v>47956</v>
       </c>
       <c r="K24" t="n">
-        <v>49326.5</v>
+        <v>48841</v>
       </c>
       <c r="L24" t="n">
-        <v>49794.75</v>
+        <v>49726</v>
       </c>
       <c r="M24" t="n">
-        <v>51083.5</v>
+        <v>50297</v>
       </c>
       <c r="N24" t="n">
-        <v>52372.25</v>
+        <v>50868</v>
       </c>
       <c r="O24" t="n">
-        <v>52020</v>
+        <v>52067</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2523,10 +2525,8 @@
       <c r="Q24" s="6" t="n">
         <v/>
       </c>
-      <c r="R24" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R24" s="6" t="n">
+        <v/>
       </c>
       <c r="S24" s="10" t="inlineStr">
         <is>
@@ -2556,63 +2556,67 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>49549</v>
+        <v>49642</v>
       </c>
       <c r="C25" t="n">
-        <v>49967</v>
+        <v>49872</v>
       </c>
       <c r="D25" t="n">
-        <v>49204</v>
+        <v>48699</v>
       </c>
       <c r="E25" t="n">
-        <v>49674</v>
+        <v>49000</v>
       </c>
       <c r="F25" t="n">
-        <v>105</v>
+        <v>-674</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.0021</v>
+        <v>-0.0136</v>
       </c>
       <c r="H25" t="n">
-        <v>763</v>
+        <v>1173</v>
       </c>
       <c r="I25" t="n">
-        <v>47699</v>
+        <v>48441</v>
       </c>
       <c r="J25" t="n">
-        <v>47956</v>
+        <v>48955.25</v>
       </c>
       <c r="K25" t="n">
-        <v>48841</v>
+        <v>49292.5</v>
       </c>
       <c r="L25" t="n">
-        <v>49726</v>
+        <v>49629.75</v>
       </c>
       <c r="M25" t="n">
-        <v>50297</v>
+        <v>50055.5</v>
       </c>
       <c r="N25" t="n">
-        <v>50868</v>
+        <v>50481.25</v>
       </c>
       <c r="O25" t="n">
-        <v>52067</v>
+        <v>50730</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
       </c>
-      <c r="Q25" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R25" s="6" t="n">
-        <v/>
+      <c r="Q25" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R25" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S25" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T25" s="8" t="n">
@@ -2631,64 +2635,66 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>49642</v>
+        <v>48451</v>
       </c>
       <c r="C26" t="n">
-        <v>49872</v>
+        <v>49121</v>
       </c>
       <c r="D26" t="n">
-        <v>48699</v>
+        <v>47025</v>
       </c>
       <c r="E26" t="n">
-        <v>49000</v>
+        <v>47517</v>
       </c>
       <c r="F26" t="n">
-        <v>-674</v>
+        <v>-1483</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.0136</v>
+        <v>-0.0303</v>
       </c>
       <c r="H26" t="n">
-        <v>1173</v>
+        <v>2096</v>
       </c>
       <c r="I26" t="n">
-        <v>48441</v>
+        <v>47526</v>
       </c>
       <c r="J26" t="n">
-        <v>48955.25</v>
+        <v>47684.25</v>
       </c>
       <c r="K26" t="n">
-        <v>49292.5</v>
+        <v>48413.5</v>
       </c>
       <c r="L26" t="n">
-        <v>49629.75</v>
+        <v>49142.75</v>
       </c>
       <c r="M26" t="n">
-        <v>50055.5</v>
+        <v>49586.5</v>
       </c>
       <c r="N26" t="n">
-        <v>50481.25</v>
+        <v>50030.25</v>
       </c>
       <c r="O26" t="n">
-        <v>50730</v>
-      </c>
-      <c r="P26" s="6" t="n">
-        <v/>
+        <v>51045</v>
+      </c>
+      <c r="P26" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q26" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="R26" s="6" t="inlineStr">
@@ -2710,78 +2716,70 @@
       <c r="V26" s="8" t="n">
         <v/>
       </c>
-      <c r="W26" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W26" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>48451</v>
+        <v>47177</v>
       </c>
       <c r="C27" t="n">
-        <v>49121</v>
+        <v>48266</v>
       </c>
       <c r="D27" t="n">
-        <v>47025</v>
+        <v>46333</v>
       </c>
       <c r="E27" t="n">
-        <v>47517</v>
+        <v>46592</v>
       </c>
       <c r="F27" t="n">
-        <v>-1483</v>
+        <v>-925</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.0303</v>
+        <v>-0.0195</v>
       </c>
       <c r="H27" t="n">
-        <v>2096</v>
+        <v>1933</v>
       </c>
       <c r="I27" t="n">
-        <v>47526</v>
+        <v>44929</v>
       </c>
       <c r="J27" t="n">
-        <v>47684.25</v>
+        <v>45143</v>
       </c>
       <c r="K27" t="n">
-        <v>48413.5</v>
+        <v>46469</v>
       </c>
       <c r="L27" t="n">
-        <v>49142.75</v>
+        <v>47795</v>
       </c>
       <c r="M27" t="n">
-        <v>49586.5</v>
+        <v>48565</v>
       </c>
       <c r="N27" t="n">
-        <v>50030.25</v>
+        <v>49335</v>
       </c>
       <c r="O27" t="n">
-        <v>51045</v>
-      </c>
-      <c r="P27" s="6" t="inlineStr">
+        <v>51217</v>
+      </c>
+      <c r="P27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R27" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="Q27" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R27" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S27" s="10" t="inlineStr">
@@ -2808,50 +2806,50 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>47177</v>
+        <v>46392</v>
       </c>
       <c r="C28" t="n">
-        <v>48266</v>
+        <v>47457</v>
       </c>
       <c r="D28" t="n">
-        <v>46333</v>
+        <v>45713</v>
       </c>
       <c r="E28" t="n">
-        <v>46592</v>
+        <v>45897</v>
       </c>
       <c r="F28" t="n">
-        <v>-925</v>
+        <v>-695</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.0195</v>
+        <v>-0.0149</v>
       </c>
       <c r="H28" t="n">
-        <v>1933</v>
+        <v>1744</v>
       </c>
       <c r="I28" t="n">
-        <v>44929</v>
+        <v>44400</v>
       </c>
       <c r="J28" t="n">
-        <v>45143</v>
+        <v>44305.25</v>
       </c>
       <c r="K28" t="n">
-        <v>46469</v>
+        <v>45625.5</v>
       </c>
       <c r="L28" t="n">
-        <v>47795</v>
+        <v>46945.75</v>
       </c>
       <c r="M28" t="n">
-        <v>48565</v>
+        <v>47558.5</v>
       </c>
       <c r="N28" t="n">
-        <v>49335</v>
+        <v>48171.25</v>
       </c>
       <c r="O28" t="n">
-        <v>51217</v>
+        <v>50199</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2888,50 +2886,50 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>46392</v>
+        <v>45605</v>
       </c>
       <c r="C29" t="n">
-        <v>47457</v>
+        <v>47210</v>
       </c>
       <c r="D29" t="n">
-        <v>45713</v>
+        <v>45272</v>
       </c>
       <c r="E29" t="n">
-        <v>45897</v>
+        <v>45424</v>
       </c>
       <c r="F29" t="n">
-        <v>-695</v>
+        <v>-473</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.0149</v>
+        <v>-0.0103</v>
       </c>
       <c r="H29" t="n">
-        <v>1744</v>
+        <v>1938</v>
       </c>
       <c r="I29" t="n">
-        <v>44400</v>
+        <v>43969</v>
       </c>
       <c r="J29" t="n">
-        <v>44305.25</v>
+        <v>43809</v>
       </c>
       <c r="K29" t="n">
-        <v>45625.5</v>
+        <v>45025</v>
       </c>
       <c r="L29" t="n">
-        <v>46945.75</v>
+        <v>46241</v>
       </c>
       <c r="M29" t="n">
-        <v>47558.5</v>
+        <v>46769</v>
       </c>
       <c r="N29" t="n">
-        <v>48171.25</v>
+        <v>47297</v>
       </c>
       <c r="O29" t="n">
-        <v>50199</v>
+        <v>49201</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2949,8 +2947,10 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T29" s="8" t="n">
-        <v/>
+      <c r="T29" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U29" s="8" t="n">
         <v/>
@@ -2968,50 +2968,50 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>45605</v>
+        <v>45244</v>
       </c>
       <c r="C30" t="n">
-        <v>47210</v>
+        <v>47090</v>
       </c>
       <c r="D30" t="n">
-        <v>45272</v>
+        <v>45052</v>
       </c>
       <c r="E30" t="n">
-        <v>45424</v>
+        <v>46629</v>
       </c>
       <c r="F30" t="n">
-        <v>-473</v>
+        <v>1205</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0.0103</v>
+        <v>0.0265</v>
       </c>
       <c r="H30" t="n">
-        <v>1938</v>
+        <v>2038</v>
       </c>
       <c r="I30" t="n">
-        <v>43969</v>
+        <v>43334</v>
       </c>
       <c r="J30" t="n">
-        <v>43809</v>
+        <v>43077.5</v>
       </c>
       <c r="K30" t="n">
-        <v>45025</v>
+        <v>44455</v>
       </c>
       <c r="L30" t="n">
-        <v>46241</v>
+        <v>45832.5</v>
       </c>
       <c r="M30" t="n">
-        <v>46769</v>
+        <v>46393</v>
       </c>
       <c r="N30" t="n">
-        <v>47297</v>
+        <v>46953.5</v>
       </c>
       <c r="O30" t="n">
-        <v>49201</v>
+        <v>49148</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3019,24 +3019,24 @@
       <c r="Q30" s="6" t="n">
         <v/>
       </c>
-      <c r="R30" s="6" t="inlineStr">
+      <c r="R30" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S30" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S30" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="inlineStr">
+      <c r="U30" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U30" s="8" t="n">
-        <v/>
-      </c>
       <c r="V30" s="8" t="n">
         <v/>
       </c>
@@ -3045,55 +3045,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr"/>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>45244</v>
+        <v>46569</v>
       </c>
       <c r="C31" t="n">
-        <v>47090</v>
+        <v>48555</v>
       </c>
       <c r="D31" t="n">
-        <v>45052</v>
+        <v>46362</v>
       </c>
       <c r="E31" t="n">
-        <v>46629</v>
+        <v>48129</v>
       </c>
       <c r="F31" t="n">
-        <v>1205</v>
+        <v>1500</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.0265</v>
+        <v>0.0322</v>
       </c>
       <c r="H31" t="n">
-        <v>2038</v>
+        <v>2193</v>
       </c>
       <c r="I31" t="n">
-        <v>43334</v>
+        <v>43014</v>
       </c>
       <c r="J31" t="n">
-        <v>43077.5</v>
+        <v>44870</v>
       </c>
       <c r="K31" t="n">
-        <v>44455</v>
+        <v>45610</v>
       </c>
       <c r="L31" t="n">
-        <v>45832.5</v>
+        <v>46350</v>
       </c>
       <c r="M31" t="n">
-        <v>46393</v>
+        <v>47648</v>
       </c>
       <c r="N31" t="n">
-        <v>46953.5</v>
+        <v>48946</v>
       </c>
       <c r="O31" t="n">
-        <v>49148</v>
+        <v>49128</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3114,10 +3118,8 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U31" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U31" s="8" t="n">
+        <v/>
       </c>
       <c r="V31" s="8" t="n">
         <v/>
@@ -3129,57 +3131,57 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>46569</v>
+        <v>47674</v>
       </c>
       <c r="C32" t="n">
-        <v>48555</v>
+        <v>49924</v>
       </c>
       <c r="D32" t="n">
-        <v>46362</v>
+        <v>47534</v>
       </c>
       <c r="E32" t="n">
-        <v>48129</v>
+        <v>49641</v>
       </c>
       <c r="F32" t="n">
-        <v>1500</v>
+        <v>1512</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.0322</v>
+        <v>0.0314</v>
       </c>
       <c r="H32" t="n">
-        <v>2193</v>
+        <v>2390</v>
       </c>
       <c r="I32" t="n">
-        <v>43014</v>
+        <v>44169</v>
       </c>
       <c r="J32" t="n">
-        <v>44870</v>
+        <v>46271.25</v>
       </c>
       <c r="K32" t="n">
-        <v>45610</v>
+        <v>47032.5</v>
       </c>
       <c r="L32" t="n">
-        <v>46350</v>
+        <v>47793.75</v>
       </c>
       <c r="M32" t="n">
-        <v>47648</v>
+        <v>49225.5</v>
       </c>
       <c r="N32" t="n">
-        <v>48946</v>
+        <v>50657.25</v>
       </c>
       <c r="O32" t="n">
-        <v>49128</v>
+        <v>50748</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3220,50 +3222,50 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>47674</v>
+        <v>49324</v>
       </c>
       <c r="C33" t="n">
-        <v>49924</v>
+        <v>50043</v>
       </c>
       <c r="D33" t="n">
-        <v>47534</v>
+        <v>49036</v>
       </c>
       <c r="E33" t="n">
-        <v>49641</v>
+        <v>49392</v>
       </c>
       <c r="F33" t="n">
-        <v>1512</v>
+        <v>-249</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0314</v>
+        <v>-0.005</v>
       </c>
       <c r="H33" t="n">
-        <v>2390</v>
+        <v>1007</v>
       </c>
       <c r="I33" t="n">
-        <v>44169</v>
+        <v>45144</v>
       </c>
       <c r="J33" t="n">
-        <v>46271.25</v>
+        <v>47707</v>
       </c>
       <c r="K33" t="n">
-        <v>47032.5</v>
+        <v>48446</v>
       </c>
       <c r="L33" t="n">
-        <v>47793.75</v>
+        <v>49185</v>
       </c>
       <c r="M33" t="n">
-        <v>49225.5</v>
+        <v>50836</v>
       </c>
       <c r="N33" t="n">
-        <v>50657.25</v>
+        <v>52487</v>
       </c>
       <c r="O33" t="n">
-        <v>50748</v>
+        <v>52314</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3276,13 +3278,11 @@
       </c>
       <c r="S33" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="n">
+        <v/>
       </c>
       <c r="U33" s="8" t="n">
         <v/>
@@ -3297,57 +3297,57 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>49324</v>
+        <v>49382</v>
       </c>
       <c r="C34" t="n">
-        <v>50043</v>
+        <v>50138</v>
       </c>
       <c r="D34" t="n">
-        <v>49036</v>
+        <v>48608</v>
       </c>
       <c r="E34" t="n">
-        <v>49392</v>
+        <v>49646</v>
       </c>
       <c r="F34" t="n">
-        <v>-249</v>
+        <v>254</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>-0.005</v>
+        <v>0.0051</v>
       </c>
       <c r="H34" t="n">
-        <v>1007</v>
+        <v>1530</v>
       </c>
       <c r="I34" t="n">
-        <v>45144</v>
+        <v>48029</v>
       </c>
       <c r="J34" t="n">
-        <v>47707</v>
+        <v>48311.25</v>
       </c>
       <c r="K34" t="n">
-        <v>48446</v>
+        <v>48888.5</v>
       </c>
       <c r="L34" t="n">
-        <v>49185</v>
+        <v>49465.75</v>
       </c>
       <c r="M34" t="n">
-        <v>50836</v>
+        <v>49895.5</v>
       </c>
       <c r="N34" t="n">
-        <v>52487</v>
+        <v>50325.25</v>
       </c>
       <c r="O34" t="n">
-        <v>52314</v>
+        <v>51050</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3355,16 +3355,20 @@
       <c r="Q34" s="6" t="n">
         <v/>
       </c>
-      <c r="R34" s="6" t="n">
-        <v/>
+      <c r="R34" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S34" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
       </c>
-      <c r="T34" s="8" t="n">
-        <v/>
+      <c r="T34" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U34" s="8" t="n">
         <v/>
@@ -3386,50 +3390,50 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>49382</v>
+        <v>49705</v>
       </c>
       <c r="C35" t="n">
-        <v>50138</v>
+        <v>50238</v>
       </c>
       <c r="D35" t="n">
-        <v>48608</v>
+        <v>49016</v>
       </c>
       <c r="E35" t="n">
-        <v>49646</v>
+        <v>49691</v>
       </c>
       <c r="F35" t="n">
-        <v>254</v>
+        <v>45</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.0051</v>
+        <v>0.0009</v>
       </c>
       <c r="H35" t="n">
-        <v>1530</v>
+        <v>1222</v>
       </c>
       <c r="I35" t="n">
-        <v>48029</v>
+        <v>47078</v>
       </c>
       <c r="J35" t="n">
-        <v>48311.25</v>
+        <v>48252.5</v>
       </c>
       <c r="K35" t="n">
-        <v>48888.5</v>
+        <v>48881</v>
       </c>
       <c r="L35" t="n">
-        <v>49465.75</v>
+        <v>49509.5</v>
       </c>
       <c r="M35" t="n">
-        <v>49895.5</v>
+        <v>50411</v>
       </c>
       <c r="N35" t="n">
-        <v>50325.25</v>
+        <v>51312.5</v>
       </c>
       <c r="O35" t="n">
-        <v>51050</v>
+        <v>51668</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3437,20 +3441,16 @@
       <c r="Q35" s="6" t="n">
         <v/>
       </c>
-      <c r="R35" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R35" s="6" t="n">
+        <v/>
       </c>
       <c r="S35" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
       </c>
-      <c r="T35" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T35" s="8" t="n">
+        <v/>
       </c>
       <c r="U35" s="8" t="n">
         <v/>
@@ -3465,57 +3465,57 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>49705</v>
+        <v>49640</v>
       </c>
       <c r="C36" t="n">
-        <v>50238</v>
+        <v>50292</v>
       </c>
       <c r="D36" t="n">
-        <v>49016</v>
+        <v>49397</v>
       </c>
       <c r="E36" t="n">
-        <v>49691</v>
+        <v>49617</v>
       </c>
       <c r="F36" t="n">
-        <v>45</v>
+        <v>-74</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.0009</v>
+        <v>-0.0015</v>
       </c>
       <c r="H36" t="n">
-        <v>1222</v>
+        <v>895</v>
       </c>
       <c r="I36" t="n">
-        <v>47078</v>
+        <v>47794</v>
       </c>
       <c r="J36" t="n">
-        <v>48252.5</v>
+        <v>48501</v>
       </c>
       <c r="K36" t="n">
-        <v>48881</v>
+        <v>49080</v>
       </c>
       <c r="L36" t="n">
-        <v>49509.5</v>
+        <v>49659</v>
       </c>
       <c r="M36" t="n">
-        <v>50411</v>
+        <v>50302</v>
       </c>
       <c r="N36" t="n">
-        <v>51312.5</v>
+        <v>50945</v>
       </c>
       <c r="O36" t="n">
-        <v>51668</v>
+        <v>51460</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3526,9 +3526,9 @@
       <c r="R36" s="6" t="n">
         <v/>
       </c>
-      <c r="S36" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S36" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T36" s="8" t="n">
@@ -3547,57 +3547,57 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>49640</v>
+        <v>49464</v>
       </c>
       <c r="C37" t="n">
-        <v>50292</v>
+        <v>50920</v>
       </c>
       <c r="D37" t="n">
-        <v>49397</v>
+        <v>49152</v>
       </c>
       <c r="E37" t="n">
-        <v>49617</v>
+        <v>50662</v>
       </c>
       <c r="F37" t="n">
-        <v>-74</v>
+        <v>1045</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.0015</v>
+        <v>0.0211</v>
       </c>
       <c r="H37" t="n">
-        <v>895</v>
+        <v>1768</v>
       </c>
       <c r="I37" t="n">
-        <v>47794</v>
+        <v>48502</v>
       </c>
       <c r="J37" t="n">
-        <v>48501</v>
+        <v>48608.25</v>
       </c>
       <c r="K37" t="n">
-        <v>49080</v>
+        <v>49169.5</v>
       </c>
       <c r="L37" t="n">
-        <v>49659</v>
+        <v>49730.75</v>
       </c>
       <c r="M37" t="n">
-        <v>50302</v>
+        <v>50064.5</v>
       </c>
       <c r="N37" t="n">
-        <v>50945</v>
+        <v>50398.25</v>
       </c>
       <c r="O37" t="n">
-        <v>51460</v>
+        <v>51187</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3605,81 +3605,87 @@
       <c r="Q37" s="6" t="n">
         <v/>
       </c>
-      <c r="R37" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S37" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U37" s="8" t="n">
-        <v/>
+      <c r="R37" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S37" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U37" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V37" s="8" t="n">
         <v/>
       </c>
-      <c r="W37" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W37" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>49464</v>
+        <v>50776</v>
       </c>
       <c r="C38" t="n">
-        <v>50920</v>
+        <v>51209</v>
       </c>
       <c r="D38" t="n">
-        <v>49152</v>
+        <v>50386</v>
       </c>
       <c r="E38" t="n">
-        <v>50662</v>
+        <v>51077</v>
       </c>
       <c r="F38" t="n">
-        <v>1045</v>
+        <v>415</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.0211</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="H38" t="n">
-        <v>1768</v>
+        <v>823</v>
       </c>
       <c r="I38" t="n">
-        <v>48502</v>
+        <v>47384</v>
       </c>
       <c r="J38" t="n">
-        <v>48608.25</v>
+        <v>49207</v>
       </c>
       <c r="K38" t="n">
-        <v>49169.5</v>
+        <v>49778</v>
       </c>
       <c r="L38" t="n">
-        <v>49730.75</v>
+        <v>50349</v>
       </c>
       <c r="M38" t="n">
-        <v>50064.5</v>
+        <v>51546</v>
       </c>
       <c r="N38" t="n">
-        <v>50398.25</v>
+        <v>52743</v>
       </c>
       <c r="O38" t="n">
-        <v>51187</v>
+        <v>52688</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3687,10 +3693,8 @@
       <c r="Q38" s="6" t="n">
         <v/>
       </c>
-      <c r="R38" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R38" s="6" t="n">
+        <v/>
       </c>
       <c r="S38" s="7" t="inlineStr">
         <is>
@@ -3699,14 +3703,12 @@
       </c>
       <c r="T38" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U38" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U38" s="8" t="n">
+        <v/>
+      </c>
       <c r="V38" s="8" t="n">
         <v/>
       </c>
@@ -3715,59 +3717,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>50776</v>
+        <v>51128</v>
       </c>
       <c r="C39" t="n">
-        <v>51209</v>
+        <v>51849</v>
       </c>
       <c r="D39" t="n">
-        <v>50386</v>
+        <v>50736</v>
       </c>
       <c r="E39" t="n">
-        <v>51077</v>
+        <v>50936</v>
       </c>
       <c r="F39" t="n">
-        <v>415</v>
+        <v>-141</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.008200000000000001</v>
+        <v>-0.0028</v>
       </c>
       <c r="H39" t="n">
-        <v>823</v>
+        <v>1113</v>
       </c>
       <c r="I39" t="n">
-        <v>47384</v>
+        <v>49563</v>
       </c>
       <c r="J39" t="n">
-        <v>49207</v>
+        <v>50393.75</v>
       </c>
       <c r="K39" t="n">
-        <v>49778</v>
+        <v>50665.5</v>
       </c>
       <c r="L39" t="n">
-        <v>50349</v>
+        <v>50937.25</v>
       </c>
       <c r="M39" t="n">
-        <v>51546</v>
+        <v>51488.5</v>
       </c>
       <c r="N39" t="n">
-        <v>52743</v>
+        <v>52039.75</v>
       </c>
       <c r="O39" t="n">
-        <v>52688</v>
+        <v>52032</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3778,14 +3776,14 @@
       <c r="R39" s="6" t="n">
         <v/>
       </c>
-      <c r="S39" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S39" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T39" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U39" s="8" t="n">
@@ -3799,55 +3797,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr"/>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>51128</v>
+        <v>50796</v>
       </c>
       <c r="C40" t="n">
-        <v>51849</v>
+        <v>51443</v>
       </c>
       <c r="D40" t="n">
-        <v>50736</v>
+        <v>49758</v>
       </c>
       <c r="E40" t="n">
-        <v>50936</v>
+        <v>51227</v>
       </c>
       <c r="F40" t="n">
-        <v>-141</v>
+        <v>291</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.0028</v>
+        <v>0.0057</v>
       </c>
       <c r="H40" t="n">
-        <v>1113</v>
+        <v>1685</v>
       </c>
       <c r="I40" t="n">
-        <v>49563</v>
+        <v>49623</v>
       </c>
       <c r="J40" t="n">
-        <v>50393.75</v>
+        <v>49644.75</v>
       </c>
       <c r="K40" t="n">
-        <v>50665.5</v>
+        <v>50379.5</v>
       </c>
       <c r="L40" t="n">
-        <v>50937.25</v>
+        <v>51114.25</v>
       </c>
       <c r="M40" t="n">
-        <v>51488.5</v>
+        <v>51492.5</v>
       </c>
       <c r="N40" t="n">
-        <v>52039.75</v>
+        <v>51870.75</v>
       </c>
       <c r="O40" t="n">
-        <v>52032</v>
+        <v>52962</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3855,19 +3857,19 @@
       <c r="Q40" s="6" t="n">
         <v/>
       </c>
-      <c r="R40" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S40" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="inlineStr">
+      <c r="R40" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="S40" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="n">
+        <v/>
+      </c>
       <c r="U40" s="8" t="n">
         <v/>
       </c>
@@ -3881,57 +3883,57 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>50796</v>
+        <v>51450</v>
       </c>
       <c r="C41" t="n">
-        <v>51443</v>
+        <v>52300</v>
       </c>
       <c r="D41" t="n">
-        <v>49758</v>
+        <v>51420</v>
       </c>
       <c r="E41" t="n">
-        <v>51227</v>
+        <v>51888</v>
       </c>
       <c r="F41" t="n">
-        <v>291</v>
+        <v>661</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.0057</v>
+        <v>0.0129</v>
       </c>
       <c r="H41" t="n">
-        <v>1685</v>
+        <v>880</v>
       </c>
       <c r="I41" t="n">
-        <v>49623</v>
+        <v>48073</v>
       </c>
       <c r="J41" t="n">
-        <v>49644.75</v>
+        <v>49855.25</v>
       </c>
       <c r="K41" t="n">
-        <v>50379.5</v>
+        <v>50384.5</v>
       </c>
       <c r="L41" t="n">
-        <v>51114.25</v>
+        <v>50913.75</v>
       </c>
       <c r="M41" t="n">
-        <v>51492.5</v>
+        <v>52069.5</v>
       </c>
       <c r="N41" t="n">
-        <v>51870.75</v>
+        <v>53225.25</v>
       </c>
       <c r="O41" t="n">
-        <v>52962</v>
+        <v>53128</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3939,18 +3941,18 @@
       <c r="Q41" s="6" t="n">
         <v/>
       </c>
-      <c r="R41" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R41" s="6" t="n">
+        <v/>
       </c>
       <c r="S41" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U41" s="8" t="n">
         <v/>
@@ -3963,59 +3965,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>51450</v>
+        <v>51870</v>
       </c>
       <c r="C42" t="n">
-        <v>52300</v>
+        <v>53097</v>
       </c>
       <c r="D42" t="n">
-        <v>51420</v>
+        <v>51691</v>
       </c>
       <c r="E42" t="n">
-        <v>51888</v>
+        <v>52209</v>
       </c>
       <c r="F42" t="n">
-        <v>661</v>
+        <v>321</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.0129</v>
+        <v>0.0062</v>
       </c>
       <c r="H42" t="n">
-        <v>880</v>
+        <v>1406</v>
       </c>
       <c r="I42" t="n">
-        <v>48073</v>
+        <v>50540</v>
       </c>
       <c r="J42" t="n">
-        <v>49855.25</v>
+        <v>51022</v>
       </c>
       <c r="K42" t="n">
-        <v>50384.5</v>
+        <v>51448</v>
       </c>
       <c r="L42" t="n">
-        <v>50913.75</v>
+        <v>51874</v>
       </c>
       <c r="M42" t="n">
-        <v>52069.5</v>
+        <v>52328</v>
       </c>
       <c r="N42" t="n">
-        <v>53225.25</v>
+        <v>52782</v>
       </c>
       <c r="O42" t="n">
-        <v>53128</v>
+        <v>53180</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4036,8 +4034,10 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U42" s="8" t="n">
-        <v/>
+      <c r="U42" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V42" s="8" t="n">
         <v/>
@@ -4052,50 +4052,50 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>51870</v>
+        <v>52183</v>
       </c>
       <c r="C43" t="n">
-        <v>53097</v>
+        <v>53400</v>
       </c>
       <c r="D43" t="n">
-        <v>51691</v>
+        <v>52179</v>
       </c>
       <c r="E43" t="n">
-        <v>52209</v>
+        <v>53162</v>
       </c>
       <c r="F43" t="n">
-        <v>321</v>
+        <v>953</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.0062</v>
+        <v>0.0183</v>
       </c>
       <c r="H43" t="n">
-        <v>1406</v>
+        <v>1221</v>
       </c>
       <c r="I43" t="n">
-        <v>50540</v>
+        <v>50285</v>
       </c>
       <c r="J43" t="n">
-        <v>51022</v>
+        <v>50710.5</v>
       </c>
       <c r="K43" t="n">
-        <v>51448</v>
+        <v>51506</v>
       </c>
       <c r="L43" t="n">
-        <v>51874</v>
+        <v>52301.5</v>
       </c>
       <c r="M43" t="n">
-        <v>52328</v>
+        <v>52912</v>
       </c>
       <c r="N43" t="n">
-        <v>52782</v>
+        <v>53522.5</v>
       </c>
       <c r="O43" t="n">
-        <v>53180</v>
+        <v>54503</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4116,10 +4116,8 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U43" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U43" s="8" t="n">
+        <v/>
       </c>
       <c r="V43" s="8" t="n">
         <v/>
@@ -4134,50 +4132,50 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>52183</v>
+        <v>53230</v>
       </c>
       <c r="C44" t="n">
-        <v>53400</v>
+        <v>53656</v>
       </c>
       <c r="D44" t="n">
-        <v>52179</v>
+        <v>52343</v>
       </c>
       <c r="E44" t="n">
-        <v>53162</v>
+        <v>52906</v>
       </c>
       <c r="F44" t="n">
-        <v>953</v>
+        <v>-256</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.0183</v>
+        <v>-0.0048</v>
       </c>
       <c r="H44" t="n">
-        <v>1221</v>
+        <v>1313</v>
       </c>
       <c r="I44" t="n">
-        <v>50285</v>
+        <v>50958</v>
       </c>
       <c r="J44" t="n">
-        <v>50710.5</v>
+        <v>52127.25</v>
       </c>
       <c r="K44" t="n">
-        <v>51506</v>
+        <v>52551.5</v>
       </c>
       <c r="L44" t="n">
-        <v>52301.5</v>
+        <v>52975.75</v>
       </c>
       <c r="M44" t="n">
-        <v>52912</v>
+        <v>53772.5</v>
       </c>
       <c r="N44" t="n">
-        <v>53522.5</v>
+        <v>54569.25</v>
       </c>
       <c r="O44" t="n">
-        <v>54503</v>
+        <v>54621</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4185,18 +4183,18 @@
       <c r="Q44" s="6" t="n">
         <v/>
       </c>
-      <c r="R44" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S44" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R44" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S44" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="n">
+        <v/>
       </c>
       <c r="U44" s="8" t="n">
         <v/>
@@ -4209,55 +4207,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr"/>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>53230</v>
+        <v>52844</v>
       </c>
       <c r="C45" t="n">
-        <v>53656</v>
+        <v>53113</v>
       </c>
       <c r="D45" t="n">
-        <v>52343</v>
+        <v>52174</v>
       </c>
       <c r="E45" t="n">
-        <v>52906</v>
+        <v>52375</v>
       </c>
       <c r="F45" t="n">
-        <v>-256</v>
+        <v>-531</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>-0.0048</v>
+        <v>-0.01</v>
       </c>
       <c r="H45" t="n">
-        <v>1313</v>
+        <v>939</v>
       </c>
       <c r="I45" t="n">
-        <v>50958</v>
+        <v>51030</v>
       </c>
       <c r="J45" t="n">
-        <v>52127.25</v>
+        <v>51546.25</v>
       </c>
       <c r="K45" t="n">
-        <v>52551.5</v>
+        <v>52249.5</v>
       </c>
       <c r="L45" t="n">
-        <v>52975.75</v>
+        <v>52952.75</v>
       </c>
       <c r="M45" t="n">
-        <v>53772.5</v>
+        <v>53562.5</v>
       </c>
       <c r="N45" t="n">
-        <v>54569.25</v>
+        <v>54172.25</v>
       </c>
       <c r="O45" t="n">
-        <v>54621</v>
+        <v>54969</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4267,12 +4269,12 @@
       </c>
       <c r="R45" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S45" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T45" s="8" t="n">
@@ -4291,57 +4293,57 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>52844</v>
+        <v>52300</v>
       </c>
       <c r="C46" t="n">
-        <v>53113</v>
+        <v>52721</v>
       </c>
       <c r="D46" t="n">
-        <v>52174</v>
+        <v>51720</v>
       </c>
       <c r="E46" t="n">
-        <v>52375</v>
+        <v>52124</v>
       </c>
       <c r="F46" t="n">
-        <v>-531</v>
+        <v>-251</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-0.01</v>
+        <v>-0.0048</v>
       </c>
       <c r="H46" t="n">
-        <v>939</v>
+        <v>1001</v>
       </c>
       <c r="I46" t="n">
-        <v>51030</v>
+        <v>51235</v>
       </c>
       <c r="J46" t="n">
-        <v>51546.25</v>
+        <v>51301.75</v>
       </c>
       <c r="K46" t="n">
-        <v>52249.5</v>
+        <v>51905.5</v>
       </c>
       <c r="L46" t="n">
-        <v>52952.75</v>
+        <v>52509.25</v>
       </c>
       <c r="M46" t="n">
-        <v>53562.5</v>
+        <v>52844.5</v>
       </c>
       <c r="N46" t="n">
-        <v>54172.25</v>
+        <v>53179.75</v>
       </c>
       <c r="O46" t="n">
-        <v>54969</v>
+        <v>54052</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4382,50 +4384,50 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>52300</v>
+        <v>52299</v>
       </c>
       <c r="C47" t="n">
-        <v>52721</v>
+        <v>53105</v>
       </c>
       <c r="D47" t="n">
-        <v>51720</v>
+        <v>51630</v>
       </c>
       <c r="E47" t="n">
-        <v>52124</v>
+        <v>52635</v>
       </c>
       <c r="F47" t="n">
-        <v>-251</v>
+        <v>511</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>-0.0048</v>
+        <v>0.0098</v>
       </c>
       <c r="H47" t="n">
-        <v>1001</v>
+        <v>1475</v>
       </c>
       <c r="I47" t="n">
-        <v>51235</v>
+        <v>50719</v>
       </c>
       <c r="J47" t="n">
-        <v>51301.75</v>
+        <v>51074.75</v>
       </c>
       <c r="K47" t="n">
-        <v>51905.5</v>
+        <v>51623.5</v>
       </c>
       <c r="L47" t="n">
-        <v>52509.25</v>
+        <v>52172.25</v>
       </c>
       <c r="M47" t="n">
-        <v>52844.5</v>
+        <v>52624.5</v>
       </c>
       <c r="N47" t="n">
-        <v>53179.75</v>
+        <v>53076.75</v>
       </c>
       <c r="O47" t="n">
-        <v>54052</v>
+        <v>53722</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4433,21 +4435,23 @@
       <c r="Q47" s="6" t="n">
         <v/>
       </c>
-      <c r="R47" s="6" t="inlineStr">
+      <c r="R47" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S47" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S47" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U47" s="8" t="n">
-        <v/>
+      <c r="U47" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V47" s="8" t="n">
         <v/>
@@ -4459,57 +4463,57 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>52299</v>
+        <v>52780</v>
       </c>
       <c r="C48" t="n">
-        <v>53105</v>
+        <v>54884</v>
       </c>
       <c r="D48" t="n">
-        <v>51630</v>
+        <v>52777</v>
       </c>
       <c r="E48" t="n">
-        <v>52635</v>
+        <v>54152</v>
       </c>
       <c r="F48" t="n">
-        <v>511</v>
+        <v>1517</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.0098</v>
+        <v>0.0288</v>
       </c>
       <c r="H48" t="n">
-        <v>1475</v>
+        <v>2107</v>
       </c>
       <c r="I48" t="n">
-        <v>50719</v>
+        <v>50155</v>
       </c>
       <c r="J48" t="n">
-        <v>51074.75</v>
+        <v>51293.75</v>
       </c>
       <c r="K48" t="n">
-        <v>51623.5</v>
+        <v>51897.5</v>
       </c>
       <c r="L48" t="n">
-        <v>52172.25</v>
+        <v>52501.25</v>
       </c>
       <c r="M48" t="n">
-        <v>52624.5</v>
+        <v>53372.5</v>
       </c>
       <c r="N48" t="n">
-        <v>53076.75</v>
+        <v>54243.75</v>
       </c>
       <c r="O48" t="n">
-        <v>53722</v>
+        <v>54580</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4527,75 +4531,73 @@
       </c>
       <c r="T48" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U48" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U48" s="8" t="inlineStr">
+      <c r="V48" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="V48" s="8" t="n">
-        <v/>
-      </c>
       <c r="W48" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>52780</v>
+        <v>54133</v>
       </c>
       <c r="C49" t="n">
-        <v>54884</v>
+        <v>54336</v>
       </c>
       <c r="D49" t="n">
-        <v>52777</v>
+        <v>53715</v>
       </c>
       <c r="E49" t="n">
-        <v>54152</v>
+        <v>53807</v>
       </c>
       <c r="F49" t="n">
-        <v>1517</v>
+        <v>-345</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.0288</v>
+        <v>-0.0064</v>
       </c>
       <c r="H49" t="n">
-        <v>2107</v>
+        <v>621</v>
       </c>
       <c r="I49" t="n">
-        <v>50155</v>
+        <v>50670</v>
       </c>
       <c r="J49" t="n">
-        <v>51293.75</v>
+        <v>52205.75</v>
       </c>
       <c r="K49" t="n">
-        <v>51897.5</v>
+        <v>53098.5</v>
       </c>
       <c r="L49" t="n">
-        <v>52501.25</v>
+        <v>53991.25</v>
       </c>
       <c r="M49" t="n">
-        <v>53372.5</v>
+        <v>55205.5</v>
       </c>
       <c r="N49" t="n">
-        <v>54243.75</v>
+        <v>56419.75</v>
       </c>
       <c r="O49" t="n">
-        <v>54580</v>
+        <v>56991</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4606,93 +4608,97 @@
       <c r="R49" s="6" t="n">
         <v/>
       </c>
-      <c r="S49" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T49" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U49" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V49" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S49" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U49" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V49" s="8" t="n">
+        <v/>
       </c>
       <c r="W49" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr"/>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>54133</v>
+        <v>53790</v>
       </c>
       <c r="C50" t="n">
-        <v>54336</v>
+        <v>53840</v>
       </c>
       <c r="D50" t="n">
-        <v>53715</v>
+        <v>52812</v>
       </c>
       <c r="E50" t="n">
-        <v>53807</v>
+        <v>53353</v>
       </c>
       <c r="F50" t="n">
-        <v>-345</v>
+        <v>-454</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.0064</v>
+        <v>-0.008399999999999999</v>
       </c>
       <c r="H50" t="n">
-        <v>621</v>
+        <v>1028</v>
       </c>
       <c r="I50" t="n">
-        <v>50670</v>
+        <v>53094</v>
       </c>
       <c r="J50" t="n">
-        <v>52205.75</v>
+        <v>53076.75</v>
       </c>
       <c r="K50" t="n">
-        <v>53098.5</v>
+        <v>53496.5</v>
       </c>
       <c r="L50" t="n">
-        <v>53991.25</v>
+        <v>53916.25</v>
       </c>
       <c r="M50" t="n">
-        <v>55205.5</v>
+        <v>54117.5</v>
       </c>
       <c r="N50" t="n">
-        <v>56419.75</v>
+        <v>54318.75</v>
       </c>
       <c r="O50" t="n">
-        <v>56991</v>
-      </c>
-      <c r="P50" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q50" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R50" s="6" t="n">
-        <v/>
+        <v>54957</v>
+      </c>
+      <c r="P50" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q50" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R50" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S50" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T50" s="8" t="n">
@@ -4711,76 +4717,70 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>53790</v>
+        <v>53367</v>
       </c>
       <c r="C51" t="n">
-        <v>53840</v>
+        <v>53862</v>
       </c>
       <c r="D51" t="n">
-        <v>52812</v>
+        <v>53210</v>
       </c>
       <c r="E51" t="n">
-        <v>53353</v>
+        <v>53584</v>
       </c>
       <c r="F51" t="n">
-        <v>-454</v>
+        <v>231</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.008399999999999999</v>
+        <v>0.0043</v>
       </c>
       <c r="H51" t="n">
-        <v>1028</v>
+        <v>652</v>
       </c>
       <c r="I51" t="n">
-        <v>53094</v>
+        <v>51784</v>
       </c>
       <c r="J51" t="n">
-        <v>53076.75</v>
+        <v>52338.5</v>
       </c>
       <c r="K51" t="n">
-        <v>53496.5</v>
+        <v>52839</v>
       </c>
       <c r="L51" t="n">
-        <v>53916.25</v>
+        <v>53339.5</v>
       </c>
       <c r="M51" t="n">
-        <v>54117.5</v>
+        <v>53867</v>
       </c>
       <c r="N51" t="n">
-        <v>54318.75</v>
+        <v>54394.5</v>
       </c>
       <c r="O51" t="n">
-        <v>54957</v>
-      </c>
-      <c r="P51" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q51" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R51" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S51" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>54868</v>
+      </c>
+      <c r="P51" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q51" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R51" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S51" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T51" s="8" t="n">
@@ -4797,72 +4797,72 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>53367</v>
+        <v>53664</v>
       </c>
       <c r="C52" t="n">
-        <v>53862</v>
+        <v>53827</v>
       </c>
       <c r="D52" t="n">
-        <v>53210</v>
+        <v>52720</v>
       </c>
       <c r="E52" t="n">
-        <v>53584</v>
+        <v>53440</v>
       </c>
       <c r="F52" t="n">
-        <v>231</v>
+        <v>-144</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.0043</v>
+        <v>-0.0027</v>
       </c>
       <c r="H52" t="n">
-        <v>652</v>
+        <v>1107</v>
       </c>
       <c r="I52" t="n">
-        <v>51784</v>
+        <v>52558</v>
       </c>
       <c r="J52" t="n">
-        <v>52338.5</v>
+        <v>52956</v>
       </c>
       <c r="K52" t="n">
-        <v>52839</v>
+        <v>53258</v>
       </c>
       <c r="L52" t="n">
-        <v>53339.5</v>
+        <v>53560</v>
       </c>
       <c r="M52" t="n">
-        <v>53867</v>
+        <v>53910</v>
       </c>
       <c r="N52" t="n">
-        <v>54394.5</v>
+        <v>54260</v>
       </c>
       <c r="O52" t="n">
-        <v>54868</v>
+        <v>54514</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
       </c>
-      <c r="Q52" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R52" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S52" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="Q52" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R52" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S52" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T52" s="8" t="n">
@@ -4879,72 +4879,76 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr"/>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>53664</v>
+        <v>53261</v>
       </c>
       <c r="C53" t="n">
-        <v>53827</v>
+        <v>53336</v>
       </c>
       <c r="D53" t="n">
-        <v>52720</v>
+        <v>51992</v>
       </c>
       <c r="E53" t="n">
-        <v>53440</v>
+        <v>52585</v>
       </c>
       <c r="F53" t="n">
-        <v>-144</v>
+        <v>-855</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.0027</v>
+        <v>-0.016</v>
       </c>
       <c r="H53" t="n">
-        <v>1107</v>
+        <v>1344</v>
       </c>
       <c r="I53" t="n">
-        <v>52558</v>
+        <v>51613</v>
       </c>
       <c r="J53" t="n">
-        <v>52956</v>
+        <v>52416.25</v>
       </c>
       <c r="K53" t="n">
-        <v>53258</v>
+        <v>52886.5</v>
       </c>
       <c r="L53" t="n">
-        <v>53560</v>
+        <v>53356.75</v>
       </c>
       <c r="M53" t="n">
-        <v>53910</v>
+        <v>53993.5</v>
       </c>
       <c r="N53" t="n">
-        <v>54260</v>
+        <v>54630.25</v>
       </c>
       <c r="O53" t="n">
-        <v>54514</v>
+        <v>54934</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
       </c>
       <c r="Q53" s="6" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R53" s="6" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R53" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S53" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T53" s="8" t="n">
@@ -4970,62 +4974,60 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>53261</v>
+        <v>52376</v>
       </c>
       <c r="C54" t="n">
-        <v>53336</v>
+        <v>52672</v>
       </c>
       <c r="D54" t="n">
-        <v>51992</v>
+        <v>51209</v>
       </c>
       <c r="E54" t="n">
-        <v>52585</v>
+        <v>51761</v>
       </c>
       <c r="F54" t="n">
-        <v>-855</v>
+        <v>-824</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.016</v>
+        <v>-0.0157</v>
       </c>
       <c r="H54" t="n">
-        <v>1344</v>
+        <v>1463</v>
       </c>
       <c r="I54" t="n">
-        <v>51613</v>
+        <v>50648</v>
       </c>
       <c r="J54" t="n">
-        <v>52416.25</v>
+        <v>51201.5</v>
       </c>
       <c r="K54" t="n">
-        <v>52886.5</v>
+        <v>51913</v>
       </c>
       <c r="L54" t="n">
-        <v>53356.75</v>
+        <v>52624.5</v>
       </c>
       <c r="M54" t="n">
-        <v>53993.5</v>
+        <v>53257</v>
       </c>
       <c r="N54" t="n">
-        <v>54630.25</v>
+        <v>53889.5</v>
       </c>
       <c r="O54" t="n">
-        <v>54934</v>
+        <v>54680</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
       </c>
-      <c r="Q54" s="6" t="inlineStr">
+      <c r="Q54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R54" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="R54" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S54" s="10" t="inlineStr">
@@ -5056,50 +5058,50 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>52376</v>
+        <v>52085</v>
       </c>
       <c r="C55" t="n">
-        <v>52672</v>
+        <v>52844</v>
       </c>
       <c r="D55" t="n">
-        <v>51209</v>
+        <v>51479</v>
       </c>
       <c r="E55" t="n">
-        <v>51761</v>
+        <v>52163</v>
       </c>
       <c r="F55" t="n">
-        <v>-824</v>
+        <v>402</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.0157</v>
+        <v>0.0078</v>
       </c>
       <c r="H55" t="n">
-        <v>1463</v>
+        <v>1365</v>
       </c>
       <c r="I55" t="n">
-        <v>50648</v>
+        <v>49746</v>
       </c>
       <c r="J55" t="n">
-        <v>51201.5</v>
+        <v>50208.25</v>
       </c>
       <c r="K55" t="n">
-        <v>51913</v>
+        <v>51029.5</v>
       </c>
       <c r="L55" t="n">
-        <v>52624.5</v>
+        <v>51850.75</v>
       </c>
       <c r="M55" t="n">
-        <v>53257</v>
+        <v>52492.5</v>
       </c>
       <c r="N55" t="n">
-        <v>53889.5</v>
+        <v>53134.25</v>
       </c>
       <c r="O55" t="n">
-        <v>54680</v>
+        <v>54135</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5107,18 +5109,18 @@
       <c r="Q55" s="6" t="n">
         <v/>
       </c>
-      <c r="R55" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S55" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T55" s="8" t="n">
-        <v/>
+      <c r="R55" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S55" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T55" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U55" s="8" t="n">
         <v/>
@@ -5131,59 +5133,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>52085</v>
+        <v>52140</v>
       </c>
       <c r="C56" t="n">
-        <v>52844</v>
+        <v>52153</v>
       </c>
       <c r="D56" t="n">
-        <v>51479</v>
+        <v>50859</v>
       </c>
       <c r="E56" t="n">
-        <v>52163</v>
+        <v>51477</v>
       </c>
       <c r="F56" t="n">
-        <v>402</v>
+        <v>-686</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.0078</v>
+        <v>-0.0132</v>
       </c>
       <c r="H56" t="n">
-        <v>1365</v>
+        <v>1294</v>
       </c>
       <c r="I56" t="n">
-        <v>49746</v>
+        <v>50114</v>
       </c>
       <c r="J56" t="n">
-        <v>50208.25</v>
+        <v>50798.75</v>
       </c>
       <c r="K56" t="n">
-        <v>51029.5</v>
+        <v>51480.5</v>
       </c>
       <c r="L56" t="n">
-        <v>51850.75</v>
+        <v>52162.25</v>
       </c>
       <c r="M56" t="n">
-        <v>52492.5</v>
+        <v>52845.5</v>
       </c>
       <c r="N56" t="n">
-        <v>53134.25</v>
+        <v>53528.75</v>
       </c>
       <c r="O56" t="n">
-        <v>54135</v>
+        <v>54209</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5191,18 +5189,18 @@
       <c r="Q56" s="6" t="n">
         <v/>
       </c>
-      <c r="R56" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S56" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T56" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R56" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S56" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T56" s="8" t="n">
+        <v/>
       </c>
       <c r="U56" s="8" t="n">
         <v/>
@@ -5215,55 +5213,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X56" t="inlineStr"/>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>52140</v>
+        <v>51486</v>
       </c>
       <c r="C57" t="n">
-        <v>52153</v>
+        <v>52032</v>
       </c>
       <c r="D57" t="n">
-        <v>50859</v>
+        <v>50909</v>
       </c>
       <c r="E57" t="n">
-        <v>51477</v>
+        <v>51926</v>
       </c>
       <c r="F57" t="n">
-        <v>-686</v>
+        <v>449</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0132</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="H57" t="n">
-        <v>1294</v>
+        <v>1123</v>
       </c>
       <c r="I57" t="n">
-        <v>50114</v>
+        <v>49565</v>
       </c>
       <c r="J57" t="n">
-        <v>50798.75</v>
+        <v>50168.5</v>
       </c>
       <c r="K57" t="n">
-        <v>51480.5</v>
+        <v>50830</v>
       </c>
       <c r="L57" t="n">
-        <v>52162.25</v>
+        <v>51491.5</v>
       </c>
       <c r="M57" t="n">
-        <v>52845.5</v>
+        <v>52124</v>
       </c>
       <c r="N57" t="n">
-        <v>53528.75</v>
+        <v>52756.5</v>
       </c>
       <c r="O57" t="n">
-        <v>54209</v>
+        <v>53447</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5271,19 +5273,19 @@
       <c r="Q57" s="6" t="n">
         <v/>
       </c>
-      <c r="R57" s="6" t="inlineStr">
+      <c r="R57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S57" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S57" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T57" s="8" t="n">
-        <v/>
-      </c>
       <c r="U57" s="8" t="n">
         <v/>
       </c>
@@ -5296,88 +5298,6 @@
         </is>
       </c>
       <c r="X57" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="B58" t="n">
-        <v>51486</v>
-      </c>
-      <c r="C58" t="n">
-        <v>51965</v>
-      </c>
-      <c r="D58" t="n">
-        <v>51141</v>
-      </c>
-      <c r="E58" t="n">
-        <v>51592</v>
-      </c>
-      <c r="F58" t="n">
-        <v>115</v>
-      </c>
-      <c r="G58" s="5" t="n">
-        <v>0.0022</v>
-      </c>
-      <c r="H58" t="n">
-        <v>824</v>
-      </c>
-      <c r="I58" t="n">
-        <v>49565</v>
-      </c>
-      <c r="J58" t="n">
-        <v>50168.5</v>
-      </c>
-      <c r="K58" t="n">
-        <v>50830</v>
-      </c>
-      <c r="L58" t="n">
-        <v>51491.5</v>
-      </c>
-      <c r="M58" t="n">
-        <v>52124</v>
-      </c>
-      <c r="N58" t="n">
-        <v>52756.5</v>
-      </c>
-      <c r="O58" t="n">
-        <v>53447</v>
-      </c>
-      <c r="P58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S58" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W58" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X58" t="inlineStr">
         <is>
           <t>弱警訊</t>
         </is>

--- a/three_gate/analysis/YM_weekly.xlsx
+++ b/three_gate/analysis/YM_weekly.xlsx
@@ -5229,22 +5229,22 @@
         <v>51486</v>
       </c>
       <c r="C57" t="n">
-        <v>52032</v>
+        <v>52067</v>
       </c>
       <c r="D57" t="n">
         <v>50909</v>
       </c>
       <c r="E57" t="n">
-        <v>51926</v>
+        <v>52059</v>
       </c>
       <c r="F57" t="n">
-        <v>449</v>
+        <v>582</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.008699999999999999</v>
+        <v>0.0113</v>
       </c>
       <c r="H57" t="n">
-        <v>1123</v>
+        <v>1158</v>
       </c>
       <c r="I57" t="n">
         <v>49565</v>

--- a/three_gate/analysis/YM_weekly.xlsx
+++ b/three_gate/analysis/YM_weekly.xlsx
@@ -5229,22 +5229,22 @@
         <v>51486</v>
       </c>
       <c r="C57" t="n">
-        <v>52067</v>
+        <v>52122</v>
       </c>
       <c r="D57" t="n">
         <v>50909</v>
       </c>
       <c r="E57" t="n">
-        <v>52059</v>
+        <v>52120</v>
       </c>
       <c r="F57" t="n">
-        <v>582</v>
+        <v>643</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.0113</v>
+        <v>0.0125</v>
       </c>
       <c r="H57" t="n">
-        <v>1158</v>
+        <v>1213</v>
       </c>
       <c r="I57" t="n">
         <v>49565</v>

--- a/three_gate/analysis/YM_weekly.xlsx
+++ b/three_gate/analysis/YM_weekly.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X57"/>
+  <dimension ref="A1:X58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -659,25 +659,25 @@
         <v>699</v>
       </c>
       <c r="I2" t="n">
-        <v>44466</v>
+        <v>44652</v>
       </c>
       <c r="J2" t="n">
-        <v>45051.75</v>
+        <v>45121.5</v>
       </c>
       <c r="K2" t="n">
-        <v>45426.5</v>
+        <v>45473</v>
       </c>
       <c r="L2" t="n">
-        <v>45801.25</v>
+        <v>45824.5</v>
       </c>
       <c r="M2" t="n">
-        <v>46281.5</v>
+        <v>46235</v>
       </c>
       <c r="N2" t="n">
-        <v>46761.75</v>
+        <v>46645.5</v>
       </c>
       <c r="O2" t="n">
-        <v>47031</v>
+        <v>46938</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -5229,22 +5229,22 @@
         <v>51486</v>
       </c>
       <c r="C57" t="n">
-        <v>52122</v>
+        <v>52032</v>
       </c>
       <c r="D57" t="n">
         <v>50909</v>
       </c>
       <c r="E57" t="n">
-        <v>52120</v>
+        <v>51926</v>
       </c>
       <c r="F57" t="n">
-        <v>643</v>
+        <v>449</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.0125</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="H57" t="n">
-        <v>1213</v>
+        <v>1123</v>
       </c>
       <c r="I57" t="n">
         <v>49565</v>
@@ -5302,6 +5302,86 @@
           <t>弱警訊</t>
         </is>
       </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>51972</v>
+      </c>
+      <c r="C58" t="n">
+        <v>52182</v>
+      </c>
+      <c r="D58" t="n">
+        <v>51913</v>
+      </c>
+      <c r="E58" t="n">
+        <v>52110</v>
+      </c>
+      <c r="F58" t="n">
+        <v>184</v>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v>0.0035</v>
+      </c>
+      <c r="H58" t="n">
+        <v>269</v>
+      </c>
+      <c r="I58" t="n">
+        <v>49786</v>
+      </c>
+      <c r="J58" t="n">
+        <v>51030.75</v>
+      </c>
+      <c r="K58" t="n">
+        <v>51364.5</v>
+      </c>
+      <c r="L58" t="n">
+        <v>51698.25</v>
+      </c>
+      <c r="M58" t="n">
+        <v>52487.5</v>
+      </c>
+      <c r="N58" t="n">
+        <v>53276.75</v>
+      </c>
+      <c r="O58" t="n">
+        <v>53155</v>
+      </c>
+      <c r="P58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S58" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W58" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/YM_weekly.xlsx
+++ b/three_gate/analysis/YM_weekly.xlsx
@@ -5316,19 +5316,19 @@
         <v>52182</v>
       </c>
       <c r="D58" t="n">
-        <v>51913</v>
+        <v>51873</v>
       </c>
       <c r="E58" t="n">
-        <v>52110</v>
+        <v>51916</v>
       </c>
       <c r="F58" t="n">
-        <v>184</v>
+        <v>-10</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0035</v>
+        <v>-0.0002</v>
       </c>
       <c r="H58" t="n">
-        <v>269</v>
+        <v>309</v>
       </c>
       <c r="I58" t="n">
         <v>49786</v>
@@ -5362,13 +5362,11 @@
       </c>
       <c r="S58" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="n">
+        <v/>
       </c>
       <c r="U58" s="8" t="n">
         <v/>
@@ -5381,7 +5379,11 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr"/>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/YM_weekly.xlsx
+++ b/three_gate/analysis/YM_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>699</v>
       </c>
       <c r="I2" t="n">
-        <v>44652</v>
+        <v>44830</v>
       </c>
       <c r="J2" t="n">
-        <v>45121.5</v>
+        <v>45188.25</v>
       </c>
       <c r="K2" t="n">
-        <v>45473</v>
+        <v>45517.5</v>
       </c>
       <c r="L2" t="n">
-        <v>45824.5</v>
+        <v>45846.75</v>
       </c>
       <c r="M2" t="n">
-        <v>46235</v>
+        <v>46190.5</v>
       </c>
       <c r="N2" t="n">
-        <v>46645.5</v>
+        <v>46534.25</v>
       </c>
       <c r="O2" t="n">
-        <v>46938</v>
+        <v>46849</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -5313,22 +5313,22 @@
         <v>51972</v>
       </c>
       <c r="C58" t="n">
-        <v>52182</v>
+        <v>52612</v>
       </c>
       <c r="D58" t="n">
-        <v>51873</v>
+        <v>51836</v>
       </c>
       <c r="E58" t="n">
-        <v>51916</v>
+        <v>51878</v>
       </c>
       <c r="F58" t="n">
-        <v>-10</v>
+        <v>-48</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0002</v>
+        <v>-0.0009</v>
       </c>
       <c r="H58" t="n">
-        <v>309</v>
+        <v>776</v>
       </c>
       <c r="I58" t="n">
         <v>49786</v>
@@ -5365,8 +5365,10 @@
           <t>↑C</t>
         </is>
       </c>
-      <c r="T58" s="8" t="n">
-        <v/>
+      <c r="T58" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U58" s="8" t="n">
         <v/>

--- a/three_gate/analysis/YM_weekly.xlsx
+++ b/three_gate/analysis/YM_weekly.xlsx
@@ -5316,19 +5316,19 @@
         <v>52612</v>
       </c>
       <c r="D58" t="n">
-        <v>51836</v>
+        <v>51832</v>
       </c>
       <c r="E58" t="n">
-        <v>51878</v>
+        <v>51832</v>
       </c>
       <c r="F58" t="n">
-        <v>-48</v>
+        <v>-94</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0009</v>
+        <v>-0.0018</v>
       </c>
       <c r="H58" t="n">
-        <v>776</v>
+        <v>780</v>
       </c>
       <c r="I58" t="n">
         <v>49786</v>

--- a/three_gate/analysis/YM_weekly.xlsx
+++ b/three_gate/analysis/YM_weekly.xlsx
@@ -5316,19 +5316,19 @@
         <v>52612</v>
       </c>
       <c r="D58" t="n">
-        <v>51832</v>
+        <v>51823</v>
       </c>
       <c r="E58" t="n">
-        <v>51832</v>
+        <v>51861</v>
       </c>
       <c r="F58" t="n">
-        <v>-94</v>
+        <v>-65</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0018</v>
+        <v>-0.0013</v>
       </c>
       <c r="H58" t="n">
-        <v>780</v>
+        <v>789</v>
       </c>
       <c r="I58" t="n">
         <v>49786</v>

--- a/three_gate/analysis/YM_weekly.xlsx
+++ b/three_gate/analysis/YM_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>699</v>
       </c>
       <c r="I2" t="n">
-        <v>44830</v>
+        <v>45496</v>
       </c>
       <c r="J2" t="n">
-        <v>45188.25</v>
+        <v>45446.75</v>
       </c>
       <c r="K2" t="n">
-        <v>45517.5</v>
+        <v>45686.5</v>
       </c>
       <c r="L2" t="n">
-        <v>45846.75</v>
+        <v>45926.25</v>
       </c>
       <c r="M2" t="n">
-        <v>46190.5</v>
+        <v>46021.5</v>
       </c>
       <c r="N2" t="n">
-        <v>46534.25</v>
+        <v>46116.75</v>
       </c>
       <c r="O2" t="n">
-        <v>46849</v>
+        <v>46501</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -685,8 +685,10 @@
       <c r="Q2" s="6" t="n">
         <v/>
       </c>
-      <c r="R2" s="6" t="n">
-        <v/>
+      <c r="R2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
@@ -695,21 +697,29 @@
       </c>
       <c r="T2" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U2" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V2" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U2" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V2" s="8" t="n">
-        <v/>
-      </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr"/>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -5316,19 +5326,19 @@
         <v>52612</v>
       </c>
       <c r="D58" t="n">
-        <v>51823</v>
+        <v>51602</v>
       </c>
       <c r="E58" t="n">
-        <v>51861</v>
+        <v>52460</v>
       </c>
       <c r="F58" t="n">
-        <v>-65</v>
+        <v>534</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0013</v>
+        <v>0.0103</v>
       </c>
       <c r="H58" t="n">
-        <v>789</v>
+        <v>1010</v>
       </c>
       <c r="I58" t="n">
         <v>49786</v>
@@ -5362,12 +5372,12 @@
       </c>
       <c r="S58" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T58" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U58" s="8" t="n">
@@ -5381,11 +5391,7 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X58" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/YM_weekly.xlsx
+++ b/three_gate/analysis/YM_weekly.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X58"/>
+  <dimension ref="A1:X57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,50 +634,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>45860</v>
+        <v>46605</v>
       </c>
       <c r="C2" t="n">
-        <v>46379</v>
+        <v>47055</v>
       </c>
       <c r="D2" t="n">
-        <v>45680</v>
+        <v>46098</v>
       </c>
       <c r="E2" t="n">
-        <v>46328</v>
+        <v>46556</v>
       </c>
       <c r="F2" t="n">
-        <v>474</v>
+        <v>228</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0103</v>
+        <v>0.0049</v>
       </c>
       <c r="H2" t="n">
-        <v>699</v>
+        <v>957</v>
       </c>
       <c r="I2" t="n">
-        <v>45496</v>
+        <v>44981</v>
       </c>
       <c r="J2" t="n">
-        <v>45446.75</v>
+        <v>45778.25</v>
       </c>
       <c r="K2" t="n">
-        <v>45686.5</v>
+        <v>45978.5</v>
       </c>
       <c r="L2" t="n">
-        <v>45926.25</v>
+        <v>46178.75</v>
       </c>
       <c r="M2" t="n">
-        <v>46021.5</v>
+        <v>46677.5</v>
       </c>
       <c r="N2" t="n">
-        <v>46116.75</v>
+        <v>47176.25</v>
       </c>
       <c r="O2" t="n">
-        <v>46501</v>
+        <v>47078</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -685,10 +685,8 @@
       <c r="Q2" s="6" t="n">
         <v/>
       </c>
-      <c r="R2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R2" s="6" t="n">
+        <v/>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
@@ -697,77 +695,69 @@
       </c>
       <c r="T2" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V2" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U2" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V2" s="8" t="n">
+        <v/>
+      </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>46605</v>
+        <v>46565</v>
       </c>
       <c r="C3" t="n">
-        <v>47055</v>
+        <v>47323</v>
       </c>
       <c r="D3" t="n">
-        <v>46098</v>
+        <v>46335</v>
       </c>
       <c r="E3" t="n">
-        <v>46556</v>
+        <v>47031</v>
       </c>
       <c r="F3" t="n">
-        <v>228</v>
+        <v>475</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.0049</v>
+        <v>0.0102</v>
       </c>
       <c r="H3" t="n">
-        <v>957</v>
+        <v>988</v>
       </c>
       <c r="I3" t="n">
-        <v>44981</v>
+        <v>45141</v>
       </c>
       <c r="J3" t="n">
-        <v>45778.25</v>
+        <v>45588.75</v>
       </c>
       <c r="K3" t="n">
-        <v>45978.5</v>
+        <v>46077.5</v>
       </c>
       <c r="L3" t="n">
-        <v>46178.75</v>
+        <v>46566.25</v>
       </c>
       <c r="M3" t="n">
-        <v>46677.5</v>
+        <v>47034.5</v>
       </c>
       <c r="N3" t="n">
-        <v>47176.25</v>
+        <v>47502.75</v>
       </c>
       <c r="O3" t="n">
-        <v>47078</v>
+        <v>48012</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -804,79 +794,83 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>46565</v>
+        <v>47048</v>
       </c>
       <c r="C4" t="n">
-        <v>47323</v>
+        <v>47162</v>
       </c>
       <c r="D4" t="n">
-        <v>46335</v>
+        <v>45387</v>
       </c>
       <c r="E4" t="n">
-        <v>47031</v>
+        <v>45706</v>
       </c>
       <c r="F4" t="n">
-        <v>475</v>
+        <v>-1325</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.0102</v>
+        <v>-0.0282</v>
       </c>
       <c r="H4" t="n">
-        <v>988</v>
+        <v>1775</v>
       </c>
       <c r="I4" t="n">
-        <v>45141</v>
+        <v>45347</v>
       </c>
       <c r="J4" t="n">
-        <v>45588.75</v>
+        <v>46144</v>
       </c>
       <c r="K4" t="n">
-        <v>46077.5</v>
+        <v>46537</v>
       </c>
       <c r="L4" t="n">
-        <v>46566.25</v>
+        <v>46930</v>
       </c>
       <c r="M4" t="n">
-        <v>47034.5</v>
+        <v>47525</v>
       </c>
       <c r="N4" t="n">
-        <v>47502.75</v>
+        <v>48120</v>
       </c>
       <c r="O4" t="n">
-        <v>48012</v>
-      </c>
-      <c r="P4" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q4" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R4" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S4" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="inlineStr">
+        <v>48311</v>
+      </c>
+      <c r="P4" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="Q4" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R4" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S4" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="n">
+        <v/>
+      </c>
       <c r="U4" s="8" t="n">
         <v/>
       </c>
       <c r="V4" s="8" t="n">
         <v/>
       </c>
-      <c r="W4" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W4" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X4" t="inlineStr"/>
@@ -884,74 +878,70 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>47048</v>
+        <v>45837</v>
       </c>
       <c r="C5" t="n">
-        <v>47162</v>
+        <v>46915</v>
       </c>
       <c r="D5" t="n">
-        <v>45387</v>
+        <v>45605</v>
       </c>
       <c r="E5" t="n">
-        <v>45706</v>
+        <v>46381</v>
       </c>
       <c r="F5" t="n">
-        <v>-1325</v>
+        <v>675</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.0282</v>
+        <v>0.0148</v>
       </c>
       <c r="H5" t="n">
-        <v>1775</v>
+        <v>1310</v>
       </c>
       <c r="I5" t="n">
-        <v>45347</v>
+        <v>43612</v>
       </c>
       <c r="J5" t="n">
-        <v>46144</v>
+        <v>43646.75</v>
       </c>
       <c r="K5" t="n">
-        <v>46537</v>
+        <v>44818.5</v>
       </c>
       <c r="L5" t="n">
-        <v>46930</v>
+        <v>45990.25</v>
       </c>
       <c r="M5" t="n">
-        <v>47525</v>
+        <v>46593.5</v>
       </c>
       <c r="N5" t="n">
-        <v>48120</v>
+        <v>47196.75</v>
       </c>
       <c r="O5" t="n">
-        <v>48311</v>
-      </c>
-      <c r="P5" s="6" t="inlineStr">
+        <v>48937</v>
+      </c>
+      <c r="P5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S5" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q5" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R5" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S5" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="n">
-        <v/>
-      </c>
       <c r="U5" s="8" t="n">
         <v/>
       </c>
@@ -963,55 +953,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr"/>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>45837</v>
+        <v>46489</v>
       </c>
       <c r="C6" t="n">
-        <v>46915</v>
+        <v>47508</v>
       </c>
       <c r="D6" t="n">
-        <v>45605</v>
+        <v>46316</v>
       </c>
       <c r="E6" t="n">
-        <v>46381</v>
+        <v>47396</v>
       </c>
       <c r="F6" t="n">
-        <v>675</v>
+        <v>1015</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.0148</v>
+        <v>0.0219</v>
       </c>
       <c r="H6" t="n">
-        <v>1310</v>
+        <v>1192</v>
       </c>
       <c r="I6" t="n">
-        <v>43612</v>
+        <v>44295</v>
       </c>
       <c r="J6" t="n">
-        <v>43646.75</v>
+        <v>45131.5</v>
       </c>
       <c r="K6" t="n">
-        <v>44818.5</v>
+        <v>45726</v>
       </c>
       <c r="L6" t="n">
-        <v>45990.25</v>
+        <v>46320.5</v>
       </c>
       <c r="M6" t="n">
-        <v>46593.5</v>
+        <v>47036</v>
       </c>
       <c r="N6" t="n">
-        <v>47196.75</v>
+        <v>47751.5</v>
       </c>
       <c r="O6" t="n">
-        <v>48937</v>
+        <v>48225</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1029,12 +1023,14 @@
       </c>
       <c r="T6" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U6" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U6" s="8" t="n">
-        <v/>
-      </c>
       <c r="V6" s="8" t="n">
         <v/>
       </c>
@@ -1045,57 +1041,57 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>46489</v>
+        <v>47711</v>
       </c>
       <c r="C7" t="n">
-        <v>47508</v>
+        <v>48214</v>
       </c>
       <c r="D7" t="n">
-        <v>46316</v>
+        <v>47488</v>
       </c>
       <c r="E7" t="n">
-        <v>47396</v>
+        <v>47722</v>
       </c>
       <c r="F7" t="n">
-        <v>1015</v>
+        <v>326</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.0219</v>
+        <v>0.0069</v>
       </c>
       <c r="H7" t="n">
-        <v>1192</v>
+        <v>726</v>
       </c>
       <c r="I7" t="n">
-        <v>44295</v>
+        <v>45124</v>
       </c>
       <c r="J7" t="n">
-        <v>45131.5</v>
+        <v>46446</v>
       </c>
       <c r="K7" t="n">
-        <v>45726</v>
+        <v>46800</v>
       </c>
       <c r="L7" t="n">
-        <v>46320.5</v>
+        <v>47154</v>
       </c>
       <c r="M7" t="n">
-        <v>47036</v>
+        <v>47992</v>
       </c>
       <c r="N7" t="n">
-        <v>47751.5</v>
+        <v>48830</v>
       </c>
       <c r="O7" t="n">
-        <v>48225</v>
+        <v>48700</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1113,13 +1109,11 @@
       </c>
       <c r="T7" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U7" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U7" s="8" t="n">
+        <v/>
       </c>
       <c r="V7" s="8" t="n">
         <v/>
@@ -1138,70 +1132,74 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>47711</v>
+        <v>47735</v>
       </c>
       <c r="C8" t="n">
-        <v>48214</v>
+        <v>47869</v>
       </c>
       <c r="D8" t="n">
-        <v>47488</v>
+        <v>46574</v>
       </c>
       <c r="E8" t="n">
-        <v>47722</v>
+        <v>47085</v>
       </c>
       <c r="F8" t="n">
-        <v>326</v>
+        <v>-637</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.0069</v>
+        <v>-0.0133</v>
       </c>
       <c r="H8" t="n">
-        <v>726</v>
+        <v>1295</v>
       </c>
       <c r="I8" t="n">
-        <v>45124</v>
+        <v>46762</v>
       </c>
       <c r="J8" t="n">
-        <v>46446</v>
+        <v>46931.5</v>
       </c>
       <c r="K8" t="n">
-        <v>46800</v>
+        <v>47359</v>
       </c>
       <c r="L8" t="n">
-        <v>47154</v>
+        <v>47786.5</v>
       </c>
       <c r="M8" t="n">
-        <v>47992</v>
+        <v>48085</v>
       </c>
       <c r="N8" t="n">
-        <v>48830</v>
+        <v>48383.5</v>
       </c>
       <c r="O8" t="n">
-        <v>48700</v>
-      </c>
-      <c r="P8" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q8" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R8" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S8" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="inlineStr">
+        <v>48940</v>
+      </c>
+      <c r="P8" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q8" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R8" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S8" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="n">
+        <v/>
+      </c>
       <c r="U8" s="8" t="n">
         <v/>
       </c>
@@ -1213,86 +1211,80 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>47735</v>
+        <v>47208</v>
       </c>
       <c r="C9" t="n">
-        <v>47869</v>
+        <v>48528</v>
       </c>
       <c r="D9" t="n">
-        <v>46574</v>
+        <v>46939</v>
       </c>
       <c r="E9" t="n">
-        <v>47085</v>
+        <v>47229</v>
       </c>
       <c r="F9" t="n">
-        <v>-637</v>
+        <v>144</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.0133</v>
+        <v>0.0031</v>
       </c>
       <c r="H9" t="n">
-        <v>1295</v>
+        <v>1589</v>
       </c>
       <c r="I9" t="n">
-        <v>46762</v>
+        <v>45279</v>
       </c>
       <c r="J9" t="n">
-        <v>46931.5</v>
+        <v>45721.75</v>
       </c>
       <c r="K9" t="n">
-        <v>47359</v>
+        <v>46437.5</v>
       </c>
       <c r="L9" t="n">
-        <v>47786.5</v>
+        <v>47153.25</v>
       </c>
       <c r="M9" t="n">
-        <v>48085</v>
+        <v>47732.5</v>
       </c>
       <c r="N9" t="n">
-        <v>48383.5</v>
+        <v>48311.75</v>
       </c>
       <c r="O9" t="n">
-        <v>48940</v>
-      </c>
-      <c r="P9" s="6" t="inlineStr">
+        <v>49164</v>
+      </c>
+      <c r="P9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S9" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q9" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R9" s="6" t="inlineStr">
+      <c r="U9" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S9" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U9" s="8" t="n">
-        <v/>
-      </c>
       <c r="V9" s="8" t="n">
         <v/>
       </c>
@@ -1301,55 +1293,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr"/>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>47208</v>
+        <v>47237</v>
       </c>
       <c r="C10" t="n">
-        <v>48528</v>
+        <v>47368</v>
       </c>
       <c r="D10" t="n">
-        <v>46939</v>
+        <v>45779</v>
       </c>
       <c r="E10" t="n">
-        <v>47229</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="n">
-        <v>144</v>
+        <v>-908</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.0031</v>
+        <v>-0.0192</v>
       </c>
       <c r="H10" t="n">
         <v>1589</v>
       </c>
       <c r="I10" t="n">
-        <v>45279</v>
+        <v>45350</v>
       </c>
       <c r="J10" t="n">
-        <v>45721.75</v>
+        <v>45387.75</v>
       </c>
       <c r="K10" t="n">
-        <v>46437.5</v>
+        <v>46434.5</v>
       </c>
       <c r="L10" t="n">
-        <v>47153.25</v>
+        <v>47481.25</v>
       </c>
       <c r="M10" t="n">
-        <v>47732.5</v>
+        <v>48023.5</v>
       </c>
       <c r="N10" t="n">
-        <v>48311.75</v>
+        <v>48565.75</v>
       </c>
       <c r="O10" t="n">
-        <v>49164</v>
+        <v>50117</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1357,23 +1353,21 @@
       <c r="Q10" s="6" t="n">
         <v/>
       </c>
-      <c r="R10" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S10" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U10" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R10" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S10" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U10" s="8" t="n">
+        <v/>
       </c>
       <c r="V10" s="8" t="n">
         <v/>
@@ -1383,59 +1377,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>47237</v>
+        <v>46504</v>
       </c>
       <c r="C11" t="n">
-        <v>47368</v>
+        <v>47796</v>
       </c>
       <c r="D11" t="n">
-        <v>45779</v>
+        <v>46165</v>
       </c>
       <c r="E11" t="n">
-        <v>46321</v>
+        <v>47743</v>
       </c>
       <c r="F11" t="n">
-        <v>-908</v>
+        <v>1422</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0.0192</v>
+        <v>0.0307</v>
       </c>
       <c r="H11" t="n">
-        <v>1589</v>
+        <v>1631</v>
       </c>
       <c r="I11" t="n">
-        <v>45350</v>
+        <v>44190</v>
       </c>
       <c r="J11" t="n">
-        <v>45387.75</v>
+        <v>44605.75</v>
       </c>
       <c r="K11" t="n">
-        <v>46434.5</v>
+        <v>45526.5</v>
       </c>
       <c r="L11" t="n">
-        <v>47481.25</v>
+        <v>46447.25</v>
       </c>
       <c r="M11" t="n">
-        <v>48023.5</v>
+        <v>47115.5</v>
       </c>
       <c r="N11" t="n">
-        <v>48565.75</v>
+        <v>47783.75</v>
       </c>
       <c r="O11" t="n">
-        <v>50117</v>
+        <v>48957</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1443,22 +1433,24 @@
       <c r="Q11" s="6" t="n">
         <v/>
       </c>
-      <c r="R11" s="6" t="inlineStr">
+      <c r="R11" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S11" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U11" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S11" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U11" s="8" t="n">
-        <v/>
-      </c>
       <c r="V11" s="8" t="n">
         <v/>
       </c>
@@ -1467,55 +1459,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr"/>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>46504</v>
+        <v>47741</v>
       </c>
       <c r="C12" t="n">
-        <v>47796</v>
+        <v>48184</v>
       </c>
       <c r="D12" t="n">
-        <v>46165</v>
+        <v>47269</v>
       </c>
       <c r="E12" t="n">
-        <v>47743</v>
+        <v>48001</v>
       </c>
       <c r="F12" t="n">
-        <v>1422</v>
+        <v>258</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.0307</v>
+        <v>0.0054</v>
       </c>
       <c r="H12" t="n">
-        <v>1631</v>
+        <v>915</v>
       </c>
       <c r="I12" t="n">
-        <v>44190</v>
+        <v>44534</v>
       </c>
       <c r="J12" t="n">
-        <v>44605.75</v>
+        <v>46493.25</v>
       </c>
       <c r="K12" t="n">
-        <v>45526.5</v>
+        <v>46927.5</v>
       </c>
       <c r="L12" t="n">
-        <v>46447.25</v>
+        <v>47361.75</v>
       </c>
       <c r="M12" t="n">
-        <v>47115.5</v>
+        <v>48558.5</v>
       </c>
       <c r="N12" t="n">
-        <v>47783.75</v>
+        <v>49755.25</v>
       </c>
       <c r="O12" t="n">
-        <v>48957</v>
+        <v>49427</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1533,13 +1529,11 @@
       </c>
       <c r="T12" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U12" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U12" s="8" t="n">
+        <v/>
       </c>
       <c r="V12" s="8" t="n">
         <v/>
@@ -1558,50 +1552,50 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>47741</v>
+        <v>48015</v>
       </c>
       <c r="C13" t="n">
-        <v>48184</v>
+        <v>48917</v>
       </c>
       <c r="D13" t="n">
-        <v>47269</v>
+        <v>47504</v>
       </c>
       <c r="E13" t="n">
-        <v>48001</v>
+        <v>48474</v>
       </c>
       <c r="F13" t="n">
-        <v>258</v>
+        <v>473</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.0054</v>
+        <v>0.009900000000000001</v>
       </c>
       <c r="H13" t="n">
-        <v>915</v>
+        <v>1413</v>
       </c>
       <c r="I13" t="n">
-        <v>44534</v>
+        <v>46354</v>
       </c>
       <c r="J13" t="n">
-        <v>46493.25</v>
+        <v>47223.25</v>
       </c>
       <c r="K13" t="n">
-        <v>46927.5</v>
+        <v>47543.5</v>
       </c>
       <c r="L13" t="n">
-        <v>47361.75</v>
+        <v>47863.75</v>
       </c>
       <c r="M13" t="n">
-        <v>48558.5</v>
+        <v>48458.5</v>
       </c>
       <c r="N13" t="n">
-        <v>49755.25</v>
+        <v>49053.25</v>
       </c>
       <c r="O13" t="n">
-        <v>49427</v>
+        <v>49099</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1609,8 +1603,10 @@
       <c r="Q13" s="6" t="n">
         <v/>
       </c>
-      <c r="R13" s="6" t="n">
-        <v/>
+      <c r="R13" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S13" s="7" t="inlineStr">
         <is>
@@ -1642,50 +1638,50 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>48015</v>
+        <v>48517</v>
       </c>
       <c r="C14" t="n">
-        <v>48917</v>
+        <v>48745</v>
       </c>
       <c r="D14" t="n">
-        <v>47504</v>
+        <v>47809</v>
       </c>
       <c r="E14" t="n">
-        <v>48474</v>
+        <v>48090</v>
       </c>
       <c r="F14" t="n">
-        <v>473</v>
+        <v>-384</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.009900000000000001</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="H14" t="n">
-        <v>1413</v>
+        <v>936</v>
       </c>
       <c r="I14" t="n">
-        <v>46354</v>
+        <v>46091</v>
       </c>
       <c r="J14" t="n">
-        <v>47223.25</v>
+        <v>47192.75</v>
       </c>
       <c r="K14" t="n">
-        <v>47543.5</v>
+        <v>47767.5</v>
       </c>
       <c r="L14" t="n">
-        <v>47863.75</v>
+        <v>48342.25</v>
       </c>
       <c r="M14" t="n">
-        <v>48458.5</v>
+        <v>49180.5</v>
       </c>
       <c r="N14" t="n">
-        <v>49053.25</v>
+        <v>50018.75</v>
       </c>
       <c r="O14" t="n">
-        <v>49099</v>
+        <v>50330</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1693,20 +1689,16 @@
       <c r="Q14" s="6" t="n">
         <v/>
       </c>
-      <c r="R14" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S14" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R14" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S14" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="n">
+        <v/>
       </c>
       <c r="U14" s="8" t="n">
         <v/>
@@ -1721,57 +1713,57 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>48517</v>
+        <v>48600</v>
       </c>
       <c r="C15" t="n">
-        <v>48745</v>
+        <v>49086</v>
       </c>
       <c r="D15" t="n">
-        <v>47809</v>
+        <v>48458</v>
       </c>
       <c r="E15" t="n">
-        <v>48090</v>
+        <v>48998</v>
       </c>
       <c r="F15" t="n">
-        <v>-384</v>
+        <v>908</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.007900000000000001</v>
+        <v>0.0189</v>
       </c>
       <c r="H15" t="n">
-        <v>936</v>
+        <v>628</v>
       </c>
       <c r="I15" t="n">
-        <v>46091</v>
+        <v>46873</v>
       </c>
       <c r="J15" t="n">
-        <v>47192.75</v>
+        <v>47060.5</v>
       </c>
       <c r="K15" t="n">
-        <v>47767.5</v>
+        <v>47622</v>
       </c>
       <c r="L15" t="n">
-        <v>48342.25</v>
+        <v>48183.5</v>
       </c>
       <c r="M15" t="n">
-        <v>49180.5</v>
+        <v>48558</v>
       </c>
       <c r="N15" t="n">
-        <v>50018.75</v>
+        <v>48932.5</v>
       </c>
       <c r="O15" t="n">
-        <v>50330</v>
+        <v>49681</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1782,103 +1774,103 @@
       <c r="R15" s="6" t="n">
         <v/>
       </c>
-      <c r="S15" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U15" s="8" t="n">
-        <v/>
+      <c r="S15" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U15" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V15" s="8" t="n">
         <v/>
       </c>
-      <c r="W15" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W15" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>48600</v>
+        <v>48998</v>
       </c>
       <c r="C16" t="n">
-        <v>49086</v>
+        <v>49052</v>
       </c>
       <c r="D16" t="n">
-        <v>48458</v>
+        <v>48092</v>
       </c>
       <c r="E16" t="n">
-        <v>48998</v>
+        <v>48616</v>
       </c>
       <c r="F16" t="n">
-        <v>908</v>
+        <v>-382</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0189</v>
+        <v>-0.0078</v>
       </c>
       <c r="H16" t="n">
-        <v>628</v>
+        <v>960</v>
       </c>
       <c r="I16" t="n">
-        <v>46873</v>
+        <v>47830</v>
       </c>
       <c r="J16" t="n">
-        <v>47060.5</v>
+        <v>48483</v>
       </c>
       <c r="K16" t="n">
-        <v>47622</v>
+        <v>48684</v>
       </c>
       <c r="L16" t="n">
-        <v>48183.5</v>
+        <v>48885</v>
       </c>
       <c r="M16" t="n">
-        <v>48558</v>
+        <v>49312</v>
       </c>
       <c r="N16" t="n">
-        <v>48932.5</v>
+        <v>49739</v>
       </c>
       <c r="O16" t="n">
-        <v>49681</v>
+        <v>49714</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
       </c>
-      <c r="Q16" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R16" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S16" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="inlineStr">
+      <c r="Q16" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U16" s="8" t="inlineStr">
+      <c r="R16" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S16" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U16" s="8" t="n">
+        <v/>
+      </c>
       <c r="V16" s="8" t="n">
         <v/>
       </c>
@@ -1887,80 +1879,84 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr"/>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>48998</v>
+        <v>48653</v>
       </c>
       <c r="C17" t="n">
-        <v>49052</v>
+        <v>49876</v>
       </c>
       <c r="D17" t="n">
-        <v>48092</v>
+        <v>48556</v>
       </c>
       <c r="E17" t="n">
-        <v>48616</v>
+        <v>49726</v>
       </c>
       <c r="F17" t="n">
-        <v>-382</v>
+        <v>1110</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-0.0078</v>
+        <v>0.0228</v>
       </c>
       <c r="H17" t="n">
-        <v>960</v>
+        <v>1320</v>
       </c>
       <c r="I17" t="n">
-        <v>47830</v>
+        <v>47132</v>
       </c>
       <c r="J17" t="n">
-        <v>48483</v>
+        <v>47678</v>
       </c>
       <c r="K17" t="n">
-        <v>48684</v>
+        <v>48136</v>
       </c>
       <c r="L17" t="n">
-        <v>48885</v>
+        <v>48594</v>
       </c>
       <c r="M17" t="n">
-        <v>49312</v>
+        <v>49096</v>
       </c>
       <c r="N17" t="n">
-        <v>49739</v>
+        <v>49598</v>
       </c>
       <c r="O17" t="n">
-        <v>49714</v>
+        <v>50012</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
       </c>
-      <c r="Q17" s="6" t="inlineStr">
+      <c r="Q17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S17" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R17" s="6" t="inlineStr">
+      <c r="U17" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S17" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U17" s="8" t="n">
-        <v/>
-      </c>
       <c r="V17" s="8" t="n">
         <v/>
       </c>
@@ -1969,59 +1965,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>48653</v>
+        <v>49720</v>
       </c>
       <c r="C18" t="n">
-        <v>49876</v>
+        <v>49901</v>
       </c>
       <c r="D18" t="n">
-        <v>48556</v>
+        <v>49057</v>
       </c>
       <c r="E18" t="n">
-        <v>49726</v>
+        <v>49547</v>
       </c>
       <c r="F18" t="n">
-        <v>1110</v>
+        <v>-179</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0228</v>
+        <v>-0.0036</v>
       </c>
       <c r="H18" t="n">
-        <v>1320</v>
+        <v>844</v>
       </c>
       <c r="I18" t="n">
-        <v>47132</v>
+        <v>47236</v>
       </c>
       <c r="J18" t="n">
-        <v>47678</v>
+        <v>48661</v>
       </c>
       <c r="K18" t="n">
-        <v>48136</v>
+        <v>49066</v>
       </c>
       <c r="L18" t="n">
-        <v>48594</v>
+        <v>49471</v>
       </c>
       <c r="M18" t="n">
-        <v>49096</v>
+        <v>50386</v>
       </c>
       <c r="N18" t="n">
-        <v>49598</v>
+        <v>51301</v>
       </c>
       <c r="O18" t="n">
-        <v>50012</v>
+        <v>51196</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2029,23 +2021,21 @@
       <c r="Q18" s="6" t="n">
         <v/>
       </c>
-      <c r="R18" s="6" t="n">
-        <v/>
+      <c r="R18" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S18" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U18" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U18" s="8" t="n">
+        <v/>
       </c>
       <c r="V18" s="8" t="n">
         <v/>
@@ -2055,70 +2045,76 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr"/>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>49720</v>
+        <v>49310</v>
       </c>
       <c r="C19" t="n">
-        <v>49901</v>
+        <v>49795</v>
       </c>
       <c r="D19" t="n">
-        <v>49057</v>
+        <v>48488</v>
       </c>
       <c r="E19" t="n">
-        <v>49547</v>
+        <v>49263</v>
       </c>
       <c r="F19" t="n">
-        <v>-179</v>
+        <v>-284</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-0.0036</v>
+        <v>-0.0057</v>
       </c>
       <c r="H19" t="n">
-        <v>844</v>
+        <v>1307</v>
       </c>
       <c r="I19" t="n">
-        <v>47236</v>
+        <v>48213</v>
       </c>
       <c r="J19" t="n">
-        <v>48661</v>
+        <v>48737</v>
       </c>
       <c r="K19" t="n">
-        <v>49066</v>
+        <v>49125</v>
       </c>
       <c r="L19" t="n">
-        <v>49471</v>
+        <v>49513</v>
       </c>
       <c r="M19" t="n">
-        <v>50386</v>
+        <v>49969</v>
       </c>
       <c r="N19" t="n">
-        <v>51301</v>
+        <v>50425</v>
       </c>
       <c r="O19" t="n">
-        <v>51196</v>
+        <v>50745</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
       </c>
-      <c r="Q19" s="6" t="n">
-        <v/>
+      <c r="Q19" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R19" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S19" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S19" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T19" s="8" t="n">
@@ -2137,74 +2133,72 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>49310</v>
+        <v>49036</v>
       </c>
       <c r="C20" t="n">
-        <v>49795</v>
+        <v>49644</v>
       </c>
       <c r="D20" t="n">
-        <v>48488</v>
+        <v>48571</v>
       </c>
       <c r="E20" t="n">
-        <v>49263</v>
+        <v>49008</v>
       </c>
       <c r="F20" t="n">
-        <v>-284</v>
+        <v>-255</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-0.0057</v>
+        <v>-0.0052</v>
       </c>
       <c r="H20" t="n">
-        <v>1307</v>
+        <v>1073</v>
       </c>
       <c r="I20" t="n">
-        <v>48213</v>
+        <v>47181</v>
       </c>
       <c r="J20" t="n">
-        <v>48737</v>
+        <v>48016.75</v>
       </c>
       <c r="K20" t="n">
-        <v>49125</v>
+        <v>48609.5</v>
       </c>
       <c r="L20" t="n">
-        <v>49513</v>
+        <v>49202.25</v>
       </c>
       <c r="M20" t="n">
-        <v>49969</v>
+        <v>49916.5</v>
       </c>
       <c r="N20" t="n">
-        <v>50425</v>
+        <v>50630.75</v>
       </c>
       <c r="O20" t="n">
-        <v>50745</v>
+        <v>51102</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
       </c>
-      <c r="Q20" s="6" t="inlineStr">
+      <c r="Q20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R20" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R20" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
       <c r="S20" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T20" s="8" t="n">
@@ -2223,57 +2217,57 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>49036</v>
+        <v>48864</v>
       </c>
       <c r="C21" t="n">
-        <v>49644</v>
+        <v>50263</v>
       </c>
       <c r="D21" t="n">
-        <v>48571</v>
+        <v>48506</v>
       </c>
       <c r="E21" t="n">
-        <v>49008</v>
+        <v>50205</v>
       </c>
       <c r="F21" t="n">
-        <v>-255</v>
+        <v>1197</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.0052</v>
+        <v>0.0244</v>
       </c>
       <c r="H21" t="n">
-        <v>1073</v>
+        <v>1757</v>
       </c>
       <c r="I21" t="n">
-        <v>47181</v>
+        <v>47498</v>
       </c>
       <c r="J21" t="n">
-        <v>48016.75</v>
+        <v>47885.25</v>
       </c>
       <c r="K21" t="n">
-        <v>48609.5</v>
+        <v>48471.5</v>
       </c>
       <c r="L21" t="n">
-        <v>49202.25</v>
+        <v>49057.75</v>
       </c>
       <c r="M21" t="n">
-        <v>49916.5</v>
+        <v>49544.5</v>
       </c>
       <c r="N21" t="n">
-        <v>50630.75</v>
+        <v>50031.25</v>
       </c>
       <c r="O21" t="n">
-        <v>51102</v>
+        <v>50717</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2281,21 +2275,23 @@
       <c r="Q21" s="6" t="n">
         <v/>
       </c>
-      <c r="R21" s="6" t="inlineStr">
+      <c r="R21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S21" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S21" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U21" s="8" t="n">
-        <v/>
+      <c r="U21" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V21" s="8" t="n">
         <v/>
@@ -2307,57 +2303,57 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>48864</v>
+        <v>50240</v>
       </c>
       <c r="C22" t="n">
-        <v>50263</v>
+        <v>50611</v>
       </c>
       <c r="D22" t="n">
-        <v>48506</v>
+        <v>49155</v>
       </c>
       <c r="E22" t="n">
-        <v>50205</v>
+        <v>49569</v>
       </c>
       <c r="F22" t="n">
-        <v>1197</v>
+        <v>-636</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.0244</v>
+        <v>-0.0127</v>
       </c>
       <c r="H22" t="n">
-        <v>1757</v>
+        <v>1456</v>
       </c>
       <c r="I22" t="n">
-        <v>47498</v>
+        <v>46749</v>
       </c>
       <c r="J22" t="n">
-        <v>47885.25</v>
+        <v>48858.25</v>
       </c>
       <c r="K22" t="n">
-        <v>48471.5</v>
+        <v>49326.5</v>
       </c>
       <c r="L22" t="n">
-        <v>49057.75</v>
+        <v>49794.75</v>
       </c>
       <c r="M22" t="n">
-        <v>49544.5</v>
+        <v>51083.5</v>
       </c>
       <c r="N22" t="n">
-        <v>50031.25</v>
+        <v>52372.25</v>
       </c>
       <c r="O22" t="n">
-        <v>50717</v>
+        <v>52020</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2365,23 +2361,21 @@
       <c r="Q22" s="6" t="n">
         <v/>
       </c>
-      <c r="R22" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S22" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="inlineStr">
+      <c r="R22" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U22" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S22" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U22" s="8" t="n">
+        <v/>
       </c>
       <c r="V22" s="8" t="n">
         <v/>
@@ -2400,50 +2394,50 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>50240</v>
+        <v>49549</v>
       </c>
       <c r="C23" t="n">
-        <v>50611</v>
+        <v>49967</v>
       </c>
       <c r="D23" t="n">
-        <v>49155</v>
+        <v>49204</v>
       </c>
       <c r="E23" t="n">
-        <v>49569</v>
+        <v>49674</v>
       </c>
       <c r="F23" t="n">
-        <v>-636</v>
+        <v>105</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-0.0127</v>
+        <v>0.0021</v>
       </c>
       <c r="H23" t="n">
-        <v>1456</v>
+        <v>763</v>
       </c>
       <c r="I23" t="n">
-        <v>46749</v>
+        <v>47699</v>
       </c>
       <c r="J23" t="n">
-        <v>48858.25</v>
+        <v>47956</v>
       </c>
       <c r="K23" t="n">
-        <v>49326.5</v>
+        <v>48841</v>
       </c>
       <c r="L23" t="n">
-        <v>49794.75</v>
+        <v>49726</v>
       </c>
       <c r="M23" t="n">
-        <v>51083.5</v>
+        <v>50297</v>
       </c>
       <c r="N23" t="n">
-        <v>52372.25</v>
+        <v>50868</v>
       </c>
       <c r="O23" t="n">
-        <v>52020</v>
+        <v>52067</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2451,10 +2445,8 @@
       <c r="Q23" s="6" t="n">
         <v/>
       </c>
-      <c r="R23" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R23" s="6" t="n">
+        <v/>
       </c>
       <c r="S23" s="10" t="inlineStr">
         <is>
@@ -2484,63 +2476,67 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>49549</v>
+        <v>49642</v>
       </c>
       <c r="C24" t="n">
-        <v>49967</v>
+        <v>49872</v>
       </c>
       <c r="D24" t="n">
-        <v>49204</v>
+        <v>48699</v>
       </c>
       <c r="E24" t="n">
-        <v>49674</v>
+        <v>49000</v>
       </c>
       <c r="F24" t="n">
-        <v>105</v>
+        <v>-674</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.0021</v>
+        <v>-0.0136</v>
       </c>
       <c r="H24" t="n">
-        <v>763</v>
+        <v>1173</v>
       </c>
       <c r="I24" t="n">
-        <v>47699</v>
+        <v>48441</v>
       </c>
       <c r="J24" t="n">
-        <v>47956</v>
+        <v>48955.25</v>
       </c>
       <c r="K24" t="n">
-        <v>48841</v>
+        <v>49292.5</v>
       </c>
       <c r="L24" t="n">
-        <v>49726</v>
+        <v>49629.75</v>
       </c>
       <c r="M24" t="n">
-        <v>50297</v>
+        <v>50055.5</v>
       </c>
       <c r="N24" t="n">
-        <v>50868</v>
+        <v>50481.25</v>
       </c>
       <c r="O24" t="n">
-        <v>52067</v>
+        <v>50730</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
       </c>
-      <c r="Q24" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R24" s="6" t="n">
-        <v/>
+      <c r="Q24" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R24" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S24" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T24" s="8" t="n">
@@ -2559,64 +2555,66 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>49642</v>
+        <v>48451</v>
       </c>
       <c r="C25" t="n">
-        <v>49872</v>
+        <v>49121</v>
       </c>
       <c r="D25" t="n">
-        <v>48699</v>
+        <v>47025</v>
       </c>
       <c r="E25" t="n">
-        <v>49000</v>
+        <v>47517</v>
       </c>
       <c r="F25" t="n">
-        <v>-674</v>
+        <v>-1483</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.0136</v>
+        <v>-0.0303</v>
       </c>
       <c r="H25" t="n">
-        <v>1173</v>
+        <v>2096</v>
       </c>
       <c r="I25" t="n">
-        <v>48441</v>
+        <v>47526</v>
       </c>
       <c r="J25" t="n">
-        <v>48955.25</v>
+        <v>47684.25</v>
       </c>
       <c r="K25" t="n">
-        <v>49292.5</v>
+        <v>48413.5</v>
       </c>
       <c r="L25" t="n">
-        <v>49629.75</v>
+        <v>49142.75</v>
       </c>
       <c r="M25" t="n">
-        <v>50055.5</v>
+        <v>49586.5</v>
       </c>
       <c r="N25" t="n">
-        <v>50481.25</v>
+        <v>50030.25</v>
       </c>
       <c r="O25" t="n">
-        <v>50730</v>
-      </c>
-      <c r="P25" s="6" t="n">
-        <v/>
+        <v>51045</v>
+      </c>
+      <c r="P25" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q25" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="R25" s="6" t="inlineStr">
@@ -2638,78 +2636,70 @@
       <c r="V25" s="8" t="n">
         <v/>
       </c>
-      <c r="W25" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W25" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>48451</v>
+        <v>47177</v>
       </c>
       <c r="C26" t="n">
-        <v>49121</v>
+        <v>48266</v>
       </c>
       <c r="D26" t="n">
-        <v>47025</v>
+        <v>46333</v>
       </c>
       <c r="E26" t="n">
-        <v>47517</v>
+        <v>46592</v>
       </c>
       <c r="F26" t="n">
-        <v>-1483</v>
+        <v>-925</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.0303</v>
+        <v>-0.0195</v>
       </c>
       <c r="H26" t="n">
-        <v>2096</v>
+        <v>1933</v>
       </c>
       <c r="I26" t="n">
-        <v>47526</v>
+        <v>44929</v>
       </c>
       <c r="J26" t="n">
-        <v>47684.25</v>
+        <v>45143</v>
       </c>
       <c r="K26" t="n">
-        <v>48413.5</v>
+        <v>46469</v>
       </c>
       <c r="L26" t="n">
-        <v>49142.75</v>
+        <v>47795</v>
       </c>
       <c r="M26" t="n">
-        <v>49586.5</v>
+        <v>48565</v>
       </c>
       <c r="N26" t="n">
-        <v>50030.25</v>
+        <v>49335</v>
       </c>
       <c r="O26" t="n">
-        <v>51045</v>
-      </c>
-      <c r="P26" s="6" t="inlineStr">
+        <v>51217</v>
+      </c>
+      <c r="P26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R26" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="Q26" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R26" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S26" s="10" t="inlineStr">
@@ -2736,50 +2726,50 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>47177</v>
+        <v>46392</v>
       </c>
       <c r="C27" t="n">
-        <v>48266</v>
+        <v>47457</v>
       </c>
       <c r="D27" t="n">
-        <v>46333</v>
+        <v>45713</v>
       </c>
       <c r="E27" t="n">
-        <v>46592</v>
+        <v>45897</v>
       </c>
       <c r="F27" t="n">
-        <v>-925</v>
+        <v>-695</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.0195</v>
+        <v>-0.0149</v>
       </c>
       <c r="H27" t="n">
-        <v>1933</v>
+        <v>1744</v>
       </c>
       <c r="I27" t="n">
-        <v>44929</v>
+        <v>44400</v>
       </c>
       <c r="J27" t="n">
-        <v>45143</v>
+        <v>44305.25</v>
       </c>
       <c r="K27" t="n">
-        <v>46469</v>
+        <v>45625.5</v>
       </c>
       <c r="L27" t="n">
-        <v>47795</v>
+        <v>46945.75</v>
       </c>
       <c r="M27" t="n">
-        <v>48565</v>
+        <v>47558.5</v>
       </c>
       <c r="N27" t="n">
-        <v>49335</v>
+        <v>48171.25</v>
       </c>
       <c r="O27" t="n">
-        <v>51217</v>
+        <v>50199</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2816,50 +2806,50 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>46392</v>
+        <v>45605</v>
       </c>
       <c r="C28" t="n">
-        <v>47457</v>
+        <v>47210</v>
       </c>
       <c r="D28" t="n">
-        <v>45713</v>
+        <v>45272</v>
       </c>
       <c r="E28" t="n">
-        <v>45897</v>
+        <v>45424</v>
       </c>
       <c r="F28" t="n">
-        <v>-695</v>
+        <v>-473</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.0149</v>
+        <v>-0.0103</v>
       </c>
       <c r="H28" t="n">
-        <v>1744</v>
+        <v>1938</v>
       </c>
       <c r="I28" t="n">
-        <v>44400</v>
+        <v>43969</v>
       </c>
       <c r="J28" t="n">
-        <v>44305.25</v>
+        <v>43809</v>
       </c>
       <c r="K28" t="n">
-        <v>45625.5</v>
+        <v>45025</v>
       </c>
       <c r="L28" t="n">
-        <v>46945.75</v>
+        <v>46241</v>
       </c>
       <c r="M28" t="n">
-        <v>47558.5</v>
+        <v>46769</v>
       </c>
       <c r="N28" t="n">
-        <v>48171.25</v>
+        <v>47297</v>
       </c>
       <c r="O28" t="n">
-        <v>50199</v>
+        <v>49201</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2877,8 +2867,10 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T28" s="8" t="n">
-        <v/>
+      <c r="T28" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U28" s="8" t="n">
         <v/>
@@ -2896,50 +2888,50 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>45605</v>
+        <v>45244</v>
       </c>
       <c r="C29" t="n">
-        <v>47210</v>
+        <v>47090</v>
       </c>
       <c r="D29" t="n">
-        <v>45272</v>
+        <v>45052</v>
       </c>
       <c r="E29" t="n">
-        <v>45424</v>
+        <v>46629</v>
       </c>
       <c r="F29" t="n">
-        <v>-473</v>
+        <v>1205</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.0103</v>
+        <v>0.0265</v>
       </c>
       <c r="H29" t="n">
-        <v>1938</v>
+        <v>2038</v>
       </c>
       <c r="I29" t="n">
-        <v>43969</v>
+        <v>43334</v>
       </c>
       <c r="J29" t="n">
-        <v>43809</v>
+        <v>43077.5</v>
       </c>
       <c r="K29" t="n">
-        <v>45025</v>
+        <v>44455</v>
       </c>
       <c r="L29" t="n">
-        <v>46241</v>
+        <v>45832.5</v>
       </c>
       <c r="M29" t="n">
-        <v>46769</v>
+        <v>46393</v>
       </c>
       <c r="N29" t="n">
-        <v>47297</v>
+        <v>46953.5</v>
       </c>
       <c r="O29" t="n">
-        <v>49201</v>
+        <v>49148</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2947,24 +2939,24 @@
       <c r="Q29" s="6" t="n">
         <v/>
       </c>
-      <c r="R29" s="6" t="inlineStr">
+      <c r="R29" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S29" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T29" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S29" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T29" s="8" t="inlineStr">
+      <c r="U29" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U29" s="8" t="n">
-        <v/>
-      </c>
       <c r="V29" s="8" t="n">
         <v/>
       </c>
@@ -2973,55 +2965,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr"/>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>45244</v>
+        <v>46569</v>
       </c>
       <c r="C30" t="n">
-        <v>47090</v>
+        <v>48555</v>
       </c>
       <c r="D30" t="n">
-        <v>45052</v>
+        <v>46362</v>
       </c>
       <c r="E30" t="n">
-        <v>46629</v>
+        <v>48129</v>
       </c>
       <c r="F30" t="n">
-        <v>1205</v>
+        <v>1500</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.0265</v>
+        <v>0.0322</v>
       </c>
       <c r="H30" t="n">
-        <v>2038</v>
+        <v>2193</v>
       </c>
       <c r="I30" t="n">
-        <v>43334</v>
+        <v>43014</v>
       </c>
       <c r="J30" t="n">
-        <v>43077.5</v>
+        <v>44870</v>
       </c>
       <c r="K30" t="n">
-        <v>44455</v>
+        <v>45610</v>
       </c>
       <c r="L30" t="n">
-        <v>45832.5</v>
+        <v>46350</v>
       </c>
       <c r="M30" t="n">
-        <v>46393</v>
+        <v>47648</v>
       </c>
       <c r="N30" t="n">
-        <v>46953.5</v>
+        <v>48946</v>
       </c>
       <c r="O30" t="n">
-        <v>49148</v>
+        <v>49128</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3042,10 +3038,8 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U30" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U30" s="8" t="n">
+        <v/>
       </c>
       <c r="V30" s="8" t="n">
         <v/>
@@ -3057,57 +3051,57 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>46569</v>
+        <v>47674</v>
       </c>
       <c r="C31" t="n">
-        <v>48555</v>
+        <v>49924</v>
       </c>
       <c r="D31" t="n">
-        <v>46362</v>
+        <v>47534</v>
       </c>
       <c r="E31" t="n">
-        <v>48129</v>
+        <v>49641</v>
       </c>
       <c r="F31" t="n">
-        <v>1500</v>
+        <v>1512</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.0322</v>
+        <v>0.0314</v>
       </c>
       <c r="H31" t="n">
-        <v>2193</v>
+        <v>2390</v>
       </c>
       <c r="I31" t="n">
-        <v>43014</v>
+        <v>44169</v>
       </c>
       <c r="J31" t="n">
-        <v>44870</v>
+        <v>46271.25</v>
       </c>
       <c r="K31" t="n">
-        <v>45610</v>
+        <v>47032.5</v>
       </c>
       <c r="L31" t="n">
-        <v>46350</v>
+        <v>47793.75</v>
       </c>
       <c r="M31" t="n">
-        <v>47648</v>
+        <v>49225.5</v>
       </c>
       <c r="N31" t="n">
-        <v>48946</v>
+        <v>50657.25</v>
       </c>
       <c r="O31" t="n">
-        <v>49128</v>
+        <v>50748</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3148,50 +3142,50 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>47674</v>
+        <v>49324</v>
       </c>
       <c r="C32" t="n">
-        <v>49924</v>
+        <v>50043</v>
       </c>
       <c r="D32" t="n">
-        <v>47534</v>
+        <v>49036</v>
       </c>
       <c r="E32" t="n">
-        <v>49641</v>
+        <v>49392</v>
       </c>
       <c r="F32" t="n">
-        <v>1512</v>
+        <v>-249</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.0314</v>
+        <v>-0.005</v>
       </c>
       <c r="H32" t="n">
-        <v>2390</v>
+        <v>1007</v>
       </c>
       <c r="I32" t="n">
-        <v>44169</v>
+        <v>45144</v>
       </c>
       <c r="J32" t="n">
-        <v>46271.25</v>
+        <v>47707</v>
       </c>
       <c r="K32" t="n">
-        <v>47032.5</v>
+        <v>48446</v>
       </c>
       <c r="L32" t="n">
-        <v>47793.75</v>
+        <v>49185</v>
       </c>
       <c r="M32" t="n">
-        <v>49225.5</v>
+        <v>50836</v>
       </c>
       <c r="N32" t="n">
-        <v>50657.25</v>
+        <v>52487</v>
       </c>
       <c r="O32" t="n">
-        <v>50748</v>
+        <v>52314</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3204,13 +3198,11 @@
       </c>
       <c r="S32" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="n">
+        <v/>
       </c>
       <c r="U32" s="8" t="n">
         <v/>
@@ -3225,57 +3217,57 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>49324</v>
+        <v>49382</v>
       </c>
       <c r="C33" t="n">
-        <v>50043</v>
+        <v>50138</v>
       </c>
       <c r="D33" t="n">
-        <v>49036</v>
+        <v>48608</v>
       </c>
       <c r="E33" t="n">
-        <v>49392</v>
+        <v>49646</v>
       </c>
       <c r="F33" t="n">
-        <v>-249</v>
+        <v>254</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>-0.005</v>
+        <v>0.0051</v>
       </c>
       <c r="H33" t="n">
-        <v>1007</v>
+        <v>1530</v>
       </c>
       <c r="I33" t="n">
-        <v>45144</v>
+        <v>48029</v>
       </c>
       <c r="J33" t="n">
-        <v>47707</v>
+        <v>48311.25</v>
       </c>
       <c r="K33" t="n">
-        <v>48446</v>
+        <v>48888.5</v>
       </c>
       <c r="L33" t="n">
-        <v>49185</v>
+        <v>49465.75</v>
       </c>
       <c r="M33" t="n">
-        <v>50836</v>
+        <v>49895.5</v>
       </c>
       <c r="N33" t="n">
-        <v>52487</v>
+        <v>50325.25</v>
       </c>
       <c r="O33" t="n">
-        <v>52314</v>
+        <v>51050</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3283,16 +3275,20 @@
       <c r="Q33" s="6" t="n">
         <v/>
       </c>
-      <c r="R33" s="6" t="n">
-        <v/>
+      <c r="R33" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S33" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
       </c>
-      <c r="T33" s="8" t="n">
-        <v/>
+      <c r="T33" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U33" s="8" t="n">
         <v/>
@@ -3314,50 +3310,50 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>49382</v>
+        <v>49705</v>
       </c>
       <c r="C34" t="n">
-        <v>50138</v>
+        <v>50238</v>
       </c>
       <c r="D34" t="n">
-        <v>48608</v>
+        <v>49016</v>
       </c>
       <c r="E34" t="n">
-        <v>49646</v>
+        <v>49691</v>
       </c>
       <c r="F34" t="n">
-        <v>254</v>
+        <v>45</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0051</v>
+        <v>0.0009</v>
       </c>
       <c r="H34" t="n">
-        <v>1530</v>
+        <v>1222</v>
       </c>
       <c r="I34" t="n">
-        <v>48029</v>
+        <v>47078</v>
       </c>
       <c r="J34" t="n">
-        <v>48311.25</v>
+        <v>48252.5</v>
       </c>
       <c r="K34" t="n">
-        <v>48888.5</v>
+        <v>48881</v>
       </c>
       <c r="L34" t="n">
-        <v>49465.75</v>
+        <v>49509.5</v>
       </c>
       <c r="M34" t="n">
-        <v>49895.5</v>
+        <v>50411</v>
       </c>
       <c r="N34" t="n">
-        <v>50325.25</v>
+        <v>51312.5</v>
       </c>
       <c r="O34" t="n">
-        <v>51050</v>
+        <v>51668</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3365,20 +3361,16 @@
       <c r="Q34" s="6" t="n">
         <v/>
       </c>
-      <c r="R34" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R34" s="6" t="n">
+        <v/>
       </c>
       <c r="S34" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
       </c>
-      <c r="T34" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T34" s="8" t="n">
+        <v/>
       </c>
       <c r="U34" s="8" t="n">
         <v/>
@@ -3393,57 +3385,57 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>49705</v>
+        <v>49640</v>
       </c>
       <c r="C35" t="n">
-        <v>50238</v>
+        <v>50292</v>
       </c>
       <c r="D35" t="n">
-        <v>49016</v>
+        <v>49397</v>
       </c>
       <c r="E35" t="n">
-        <v>49691</v>
+        <v>49617</v>
       </c>
       <c r="F35" t="n">
-        <v>45</v>
+        <v>-74</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.0009</v>
+        <v>-0.0015</v>
       </c>
       <c r="H35" t="n">
-        <v>1222</v>
+        <v>895</v>
       </c>
       <c r="I35" t="n">
-        <v>47078</v>
+        <v>47794</v>
       </c>
       <c r="J35" t="n">
-        <v>48252.5</v>
+        <v>48501</v>
       </c>
       <c r="K35" t="n">
-        <v>48881</v>
+        <v>49080</v>
       </c>
       <c r="L35" t="n">
-        <v>49509.5</v>
+        <v>49659</v>
       </c>
       <c r="M35" t="n">
-        <v>50411</v>
+        <v>50302</v>
       </c>
       <c r="N35" t="n">
-        <v>51312.5</v>
+        <v>50945</v>
       </c>
       <c r="O35" t="n">
-        <v>51668</v>
+        <v>51460</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3454,9 +3446,9 @@
       <c r="R35" s="6" t="n">
         <v/>
       </c>
-      <c r="S35" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S35" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T35" s="8" t="n">
@@ -3475,57 +3467,57 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>49640</v>
+        <v>49464</v>
       </c>
       <c r="C36" t="n">
-        <v>50292</v>
+        <v>50920</v>
       </c>
       <c r="D36" t="n">
-        <v>49397</v>
+        <v>49152</v>
       </c>
       <c r="E36" t="n">
-        <v>49617</v>
+        <v>50662</v>
       </c>
       <c r="F36" t="n">
-        <v>-74</v>
+        <v>1045</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>-0.0015</v>
+        <v>0.0211</v>
       </c>
       <c r="H36" t="n">
-        <v>895</v>
+        <v>1768</v>
       </c>
       <c r="I36" t="n">
-        <v>47794</v>
+        <v>48502</v>
       </c>
       <c r="J36" t="n">
-        <v>48501</v>
+        <v>48608.25</v>
       </c>
       <c r="K36" t="n">
-        <v>49080</v>
+        <v>49169.5</v>
       </c>
       <c r="L36" t="n">
-        <v>49659</v>
+        <v>49730.75</v>
       </c>
       <c r="M36" t="n">
-        <v>50302</v>
+        <v>50064.5</v>
       </c>
       <c r="N36" t="n">
-        <v>50945</v>
+        <v>50398.25</v>
       </c>
       <c r="O36" t="n">
-        <v>51460</v>
+        <v>51187</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3533,81 +3525,87 @@
       <c r="Q36" s="6" t="n">
         <v/>
       </c>
-      <c r="R36" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S36" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U36" s="8" t="n">
-        <v/>
+      <c r="R36" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S36" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U36" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V36" s="8" t="n">
         <v/>
       </c>
-      <c r="W36" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W36" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>49464</v>
+        <v>50776</v>
       </c>
       <c r="C37" t="n">
-        <v>50920</v>
+        <v>51209</v>
       </c>
       <c r="D37" t="n">
-        <v>49152</v>
+        <v>50386</v>
       </c>
       <c r="E37" t="n">
-        <v>50662</v>
+        <v>51077</v>
       </c>
       <c r="F37" t="n">
-        <v>1045</v>
+        <v>415</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.0211</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="H37" t="n">
-        <v>1768</v>
+        <v>823</v>
       </c>
       <c r="I37" t="n">
-        <v>48502</v>
+        <v>47384</v>
       </c>
       <c r="J37" t="n">
-        <v>48608.25</v>
+        <v>49207</v>
       </c>
       <c r="K37" t="n">
-        <v>49169.5</v>
+        <v>49778</v>
       </c>
       <c r="L37" t="n">
-        <v>49730.75</v>
+        <v>50349</v>
       </c>
       <c r="M37" t="n">
-        <v>50064.5</v>
+        <v>51546</v>
       </c>
       <c r="N37" t="n">
-        <v>50398.25</v>
+        <v>52743</v>
       </c>
       <c r="O37" t="n">
-        <v>51187</v>
+        <v>52688</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3615,10 +3613,8 @@
       <c r="Q37" s="6" t="n">
         <v/>
       </c>
-      <c r="R37" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R37" s="6" t="n">
+        <v/>
       </c>
       <c r="S37" s="7" t="inlineStr">
         <is>
@@ -3627,14 +3623,12 @@
       </c>
       <c r="T37" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U37" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U37" s="8" t="n">
+        <v/>
+      </c>
       <c r="V37" s="8" t="n">
         <v/>
       </c>
@@ -3643,59 +3637,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>50776</v>
+        <v>51128</v>
       </c>
       <c r="C38" t="n">
-        <v>51209</v>
+        <v>51849</v>
       </c>
       <c r="D38" t="n">
-        <v>50386</v>
+        <v>50736</v>
       </c>
       <c r="E38" t="n">
-        <v>51077</v>
+        <v>50936</v>
       </c>
       <c r="F38" t="n">
-        <v>415</v>
+        <v>-141</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.008200000000000001</v>
+        <v>-0.0028</v>
       </c>
       <c r="H38" t="n">
-        <v>823</v>
+        <v>1113</v>
       </c>
       <c r="I38" t="n">
-        <v>47384</v>
+        <v>49563</v>
       </c>
       <c r="J38" t="n">
-        <v>49207</v>
+        <v>50393.75</v>
       </c>
       <c r="K38" t="n">
-        <v>49778</v>
+        <v>50665.5</v>
       </c>
       <c r="L38" t="n">
-        <v>50349</v>
+        <v>50937.25</v>
       </c>
       <c r="M38" t="n">
-        <v>51546</v>
+        <v>51488.5</v>
       </c>
       <c r="N38" t="n">
-        <v>52743</v>
+        <v>52039.75</v>
       </c>
       <c r="O38" t="n">
-        <v>52688</v>
+        <v>52032</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3706,14 +3696,14 @@
       <c r="R38" s="6" t="n">
         <v/>
       </c>
-      <c r="S38" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S38" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T38" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U38" s="8" t="n">
@@ -3727,55 +3717,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr"/>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>51128</v>
+        <v>50796</v>
       </c>
       <c r="C39" t="n">
-        <v>51849</v>
+        <v>51443</v>
       </c>
       <c r="D39" t="n">
-        <v>50736</v>
+        <v>49758</v>
       </c>
       <c r="E39" t="n">
-        <v>50936</v>
+        <v>51227</v>
       </c>
       <c r="F39" t="n">
-        <v>-141</v>
+        <v>291</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.0028</v>
+        <v>0.0057</v>
       </c>
       <c r="H39" t="n">
-        <v>1113</v>
+        <v>1685</v>
       </c>
       <c r="I39" t="n">
-        <v>49563</v>
+        <v>49623</v>
       </c>
       <c r="J39" t="n">
-        <v>50393.75</v>
+        <v>49644.75</v>
       </c>
       <c r="K39" t="n">
-        <v>50665.5</v>
+        <v>50379.5</v>
       </c>
       <c r="L39" t="n">
-        <v>50937.25</v>
+        <v>51114.25</v>
       </c>
       <c r="M39" t="n">
-        <v>51488.5</v>
+        <v>51492.5</v>
       </c>
       <c r="N39" t="n">
-        <v>52039.75</v>
+        <v>51870.75</v>
       </c>
       <c r="O39" t="n">
-        <v>52032</v>
+        <v>52962</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3783,19 +3777,19 @@
       <c r="Q39" s="6" t="n">
         <v/>
       </c>
-      <c r="R39" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S39" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="inlineStr">
+      <c r="R39" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="S39" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="n">
+        <v/>
+      </c>
       <c r="U39" s="8" t="n">
         <v/>
       </c>
@@ -3809,57 +3803,57 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>50796</v>
+        <v>51450</v>
       </c>
       <c r="C40" t="n">
-        <v>51443</v>
+        <v>52300</v>
       </c>
       <c r="D40" t="n">
-        <v>49758</v>
+        <v>51420</v>
       </c>
       <c r="E40" t="n">
-        <v>51227</v>
+        <v>51888</v>
       </c>
       <c r="F40" t="n">
-        <v>291</v>
+        <v>661</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.0057</v>
+        <v>0.0129</v>
       </c>
       <c r="H40" t="n">
-        <v>1685</v>
+        <v>880</v>
       </c>
       <c r="I40" t="n">
-        <v>49623</v>
+        <v>48073</v>
       </c>
       <c r="J40" t="n">
-        <v>49644.75</v>
+        <v>49855.25</v>
       </c>
       <c r="K40" t="n">
-        <v>50379.5</v>
+        <v>50384.5</v>
       </c>
       <c r="L40" t="n">
-        <v>51114.25</v>
+        <v>50913.75</v>
       </c>
       <c r="M40" t="n">
-        <v>51492.5</v>
+        <v>52069.5</v>
       </c>
       <c r="N40" t="n">
-        <v>51870.75</v>
+        <v>53225.25</v>
       </c>
       <c r="O40" t="n">
-        <v>52962</v>
+        <v>53128</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3867,18 +3861,18 @@
       <c r="Q40" s="6" t="n">
         <v/>
       </c>
-      <c r="R40" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R40" s="6" t="n">
+        <v/>
       </c>
       <c r="S40" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U40" s="8" t="n">
         <v/>
@@ -3891,59 +3885,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>51450</v>
+        <v>51870</v>
       </c>
       <c r="C41" t="n">
-        <v>52300</v>
+        <v>53097</v>
       </c>
       <c r="D41" t="n">
-        <v>51420</v>
+        <v>51691</v>
       </c>
       <c r="E41" t="n">
-        <v>51888</v>
+        <v>52209</v>
       </c>
       <c r="F41" t="n">
-        <v>661</v>
+        <v>321</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.0129</v>
+        <v>0.0062</v>
       </c>
       <c r="H41" t="n">
-        <v>880</v>
+        <v>1406</v>
       </c>
       <c r="I41" t="n">
-        <v>48073</v>
+        <v>50540</v>
       </c>
       <c r="J41" t="n">
-        <v>49855.25</v>
+        <v>51022</v>
       </c>
       <c r="K41" t="n">
-        <v>50384.5</v>
+        <v>51448</v>
       </c>
       <c r="L41" t="n">
-        <v>50913.75</v>
+        <v>51874</v>
       </c>
       <c r="M41" t="n">
-        <v>52069.5</v>
+        <v>52328</v>
       </c>
       <c r="N41" t="n">
-        <v>53225.25</v>
+        <v>52782</v>
       </c>
       <c r="O41" t="n">
-        <v>53128</v>
+        <v>53180</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3964,8 +3954,10 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U41" s="8" t="n">
-        <v/>
+      <c r="U41" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V41" s="8" t="n">
         <v/>
@@ -3980,50 +3972,50 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>51870</v>
+        <v>52183</v>
       </c>
       <c r="C42" t="n">
-        <v>53097</v>
+        <v>53400</v>
       </c>
       <c r="D42" t="n">
-        <v>51691</v>
+        <v>52179</v>
       </c>
       <c r="E42" t="n">
-        <v>52209</v>
+        <v>53162</v>
       </c>
       <c r="F42" t="n">
-        <v>321</v>
+        <v>953</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.0062</v>
+        <v>0.0183</v>
       </c>
       <c r="H42" t="n">
-        <v>1406</v>
+        <v>1221</v>
       </c>
       <c r="I42" t="n">
-        <v>50540</v>
+        <v>50285</v>
       </c>
       <c r="J42" t="n">
-        <v>51022</v>
+        <v>50710.5</v>
       </c>
       <c r="K42" t="n">
-        <v>51448</v>
+        <v>51506</v>
       </c>
       <c r="L42" t="n">
-        <v>51874</v>
+        <v>52301.5</v>
       </c>
       <c r="M42" t="n">
-        <v>52328</v>
+        <v>52912</v>
       </c>
       <c r="N42" t="n">
-        <v>52782</v>
+        <v>53522.5</v>
       </c>
       <c r="O42" t="n">
-        <v>53180</v>
+        <v>54503</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4044,10 +4036,8 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U42" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U42" s="8" t="n">
+        <v/>
       </c>
       <c r="V42" s="8" t="n">
         <v/>
@@ -4062,50 +4052,50 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>52183</v>
+        <v>53230</v>
       </c>
       <c r="C43" t="n">
-        <v>53400</v>
+        <v>53656</v>
       </c>
       <c r="D43" t="n">
-        <v>52179</v>
+        <v>52343</v>
       </c>
       <c r="E43" t="n">
-        <v>53162</v>
+        <v>52906</v>
       </c>
       <c r="F43" t="n">
-        <v>953</v>
+        <v>-256</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.0183</v>
+        <v>-0.0048</v>
       </c>
       <c r="H43" t="n">
-        <v>1221</v>
+        <v>1313</v>
       </c>
       <c r="I43" t="n">
-        <v>50285</v>
+        <v>50958</v>
       </c>
       <c r="J43" t="n">
-        <v>50710.5</v>
+        <v>52127.25</v>
       </c>
       <c r="K43" t="n">
-        <v>51506</v>
+        <v>52551.5</v>
       </c>
       <c r="L43" t="n">
-        <v>52301.5</v>
+        <v>52975.75</v>
       </c>
       <c r="M43" t="n">
-        <v>52912</v>
+        <v>53772.5</v>
       </c>
       <c r="N43" t="n">
-        <v>53522.5</v>
+        <v>54569.25</v>
       </c>
       <c r="O43" t="n">
-        <v>54503</v>
+        <v>54621</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4113,18 +4103,18 @@
       <c r="Q43" s="6" t="n">
         <v/>
       </c>
-      <c r="R43" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S43" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R43" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S43" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="n">
+        <v/>
       </c>
       <c r="U43" s="8" t="n">
         <v/>
@@ -4137,55 +4127,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr"/>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>53230</v>
+        <v>52844</v>
       </c>
       <c r="C44" t="n">
-        <v>53656</v>
+        <v>53113</v>
       </c>
       <c r="D44" t="n">
-        <v>52343</v>
+        <v>52174</v>
       </c>
       <c r="E44" t="n">
-        <v>52906</v>
+        <v>52375</v>
       </c>
       <c r="F44" t="n">
-        <v>-256</v>
+        <v>-531</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.0048</v>
+        <v>-0.01</v>
       </c>
       <c r="H44" t="n">
-        <v>1313</v>
+        <v>939</v>
       </c>
       <c r="I44" t="n">
-        <v>50958</v>
+        <v>51030</v>
       </c>
       <c r="J44" t="n">
-        <v>52127.25</v>
+        <v>51546.25</v>
       </c>
       <c r="K44" t="n">
-        <v>52551.5</v>
+        <v>52249.5</v>
       </c>
       <c r="L44" t="n">
-        <v>52975.75</v>
+        <v>52952.75</v>
       </c>
       <c r="M44" t="n">
-        <v>53772.5</v>
+        <v>53562.5</v>
       </c>
       <c r="N44" t="n">
-        <v>54569.25</v>
+        <v>54172.25</v>
       </c>
       <c r="O44" t="n">
-        <v>54621</v>
+        <v>54969</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4195,12 +4189,12 @@
       </c>
       <c r="R44" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S44" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T44" s="8" t="n">
@@ -4219,57 +4213,57 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>52844</v>
+        <v>52300</v>
       </c>
       <c r="C45" t="n">
-        <v>53113</v>
+        <v>52721</v>
       </c>
       <c r="D45" t="n">
-        <v>52174</v>
+        <v>51720</v>
       </c>
       <c r="E45" t="n">
-        <v>52375</v>
+        <v>52124</v>
       </c>
       <c r="F45" t="n">
-        <v>-531</v>
+        <v>-251</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>-0.01</v>
+        <v>-0.0048</v>
       </c>
       <c r="H45" t="n">
-        <v>939</v>
+        <v>1001</v>
       </c>
       <c r="I45" t="n">
-        <v>51030</v>
+        <v>51235</v>
       </c>
       <c r="J45" t="n">
-        <v>51546.25</v>
+        <v>51301.75</v>
       </c>
       <c r="K45" t="n">
-        <v>52249.5</v>
+        <v>51905.5</v>
       </c>
       <c r="L45" t="n">
-        <v>52952.75</v>
+        <v>52509.25</v>
       </c>
       <c r="M45" t="n">
-        <v>53562.5</v>
+        <v>52844.5</v>
       </c>
       <c r="N45" t="n">
-        <v>54172.25</v>
+        <v>53179.75</v>
       </c>
       <c r="O45" t="n">
-        <v>54969</v>
+        <v>54052</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4310,50 +4304,50 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>52300</v>
+        <v>52299</v>
       </c>
       <c r="C46" t="n">
-        <v>52721</v>
+        <v>53105</v>
       </c>
       <c r="D46" t="n">
-        <v>51720</v>
+        <v>51630</v>
       </c>
       <c r="E46" t="n">
-        <v>52124</v>
+        <v>52635</v>
       </c>
       <c r="F46" t="n">
-        <v>-251</v>
+        <v>511</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-0.0048</v>
+        <v>0.0098</v>
       </c>
       <c r="H46" t="n">
-        <v>1001</v>
+        <v>1475</v>
       </c>
       <c r="I46" t="n">
-        <v>51235</v>
+        <v>50719</v>
       </c>
       <c r="J46" t="n">
-        <v>51301.75</v>
+        <v>51074.75</v>
       </c>
       <c r="K46" t="n">
-        <v>51905.5</v>
+        <v>51623.5</v>
       </c>
       <c r="L46" t="n">
-        <v>52509.25</v>
+        <v>52172.25</v>
       </c>
       <c r="M46" t="n">
-        <v>52844.5</v>
+        <v>52624.5</v>
       </c>
       <c r="N46" t="n">
-        <v>53179.75</v>
+        <v>53076.75</v>
       </c>
       <c r="O46" t="n">
-        <v>54052</v>
+        <v>53722</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4361,21 +4355,23 @@
       <c r="Q46" s="6" t="n">
         <v/>
       </c>
-      <c r="R46" s="6" t="inlineStr">
+      <c r="R46" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S46" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S46" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U46" s="8" t="n">
-        <v/>
+      <c r="U46" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V46" s="8" t="n">
         <v/>
@@ -4387,57 +4383,57 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>52299</v>
+        <v>52780</v>
       </c>
       <c r="C47" t="n">
-        <v>53105</v>
+        <v>54884</v>
       </c>
       <c r="D47" t="n">
-        <v>51630</v>
+        <v>52777</v>
       </c>
       <c r="E47" t="n">
-        <v>52635</v>
+        <v>54152</v>
       </c>
       <c r="F47" t="n">
-        <v>511</v>
+        <v>1517</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.0098</v>
+        <v>0.0288</v>
       </c>
       <c r="H47" t="n">
-        <v>1475</v>
+        <v>2107</v>
       </c>
       <c r="I47" t="n">
-        <v>50719</v>
+        <v>50155</v>
       </c>
       <c r="J47" t="n">
-        <v>51074.75</v>
+        <v>51293.75</v>
       </c>
       <c r="K47" t="n">
-        <v>51623.5</v>
+        <v>51897.5</v>
       </c>
       <c r="L47" t="n">
-        <v>52172.25</v>
+        <v>52501.25</v>
       </c>
       <c r="M47" t="n">
-        <v>52624.5</v>
+        <v>53372.5</v>
       </c>
       <c r="N47" t="n">
-        <v>53076.75</v>
+        <v>54243.75</v>
       </c>
       <c r="O47" t="n">
-        <v>53722</v>
+        <v>54580</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4455,75 +4451,73 @@
       </c>
       <c r="T47" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U47" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U47" s="8" t="inlineStr">
+      <c r="V47" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="V47" s="8" t="n">
-        <v/>
-      </c>
       <c r="W47" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>52780</v>
+        <v>54133</v>
       </c>
       <c r="C48" t="n">
-        <v>54884</v>
+        <v>54336</v>
       </c>
       <c r="D48" t="n">
-        <v>52777</v>
+        <v>53715</v>
       </c>
       <c r="E48" t="n">
-        <v>54152</v>
+        <v>53807</v>
       </c>
       <c r="F48" t="n">
-        <v>1517</v>
+        <v>-345</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.0288</v>
+        <v>-0.0064</v>
       </c>
       <c r="H48" t="n">
-        <v>2107</v>
+        <v>621</v>
       </c>
       <c r="I48" t="n">
-        <v>50155</v>
+        <v>50670</v>
       </c>
       <c r="J48" t="n">
-        <v>51293.75</v>
+        <v>52205.75</v>
       </c>
       <c r="K48" t="n">
-        <v>51897.5</v>
+        <v>53098.5</v>
       </c>
       <c r="L48" t="n">
-        <v>52501.25</v>
+        <v>53991.25</v>
       </c>
       <c r="M48" t="n">
-        <v>53372.5</v>
+        <v>55205.5</v>
       </c>
       <c r="N48" t="n">
-        <v>54243.75</v>
+        <v>56419.75</v>
       </c>
       <c r="O48" t="n">
-        <v>54580</v>
+        <v>56991</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4534,93 +4528,97 @@
       <c r="R48" s="6" t="n">
         <v/>
       </c>
-      <c r="S48" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T48" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U48" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V48" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S48" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U48" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V48" s="8" t="n">
+        <v/>
       </c>
       <c r="W48" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr"/>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>54133</v>
+        <v>53790</v>
       </c>
       <c r="C49" t="n">
-        <v>54336</v>
+        <v>53840</v>
       </c>
       <c r="D49" t="n">
-        <v>53715</v>
+        <v>52812</v>
       </c>
       <c r="E49" t="n">
-        <v>53807</v>
+        <v>53353</v>
       </c>
       <c r="F49" t="n">
-        <v>-345</v>
+        <v>-454</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.0064</v>
+        <v>-0.008399999999999999</v>
       </c>
       <c r="H49" t="n">
-        <v>621</v>
+        <v>1028</v>
       </c>
       <c r="I49" t="n">
-        <v>50670</v>
+        <v>53094</v>
       </c>
       <c r="J49" t="n">
-        <v>52205.75</v>
+        <v>53076.75</v>
       </c>
       <c r="K49" t="n">
-        <v>53098.5</v>
+        <v>53496.5</v>
       </c>
       <c r="L49" t="n">
-        <v>53991.25</v>
+        <v>53916.25</v>
       </c>
       <c r="M49" t="n">
-        <v>55205.5</v>
+        <v>54117.5</v>
       </c>
       <c r="N49" t="n">
-        <v>56419.75</v>
+        <v>54318.75</v>
       </c>
       <c r="O49" t="n">
-        <v>56991</v>
-      </c>
-      <c r="P49" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q49" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R49" s="6" t="n">
-        <v/>
+        <v>54957</v>
+      </c>
+      <c r="P49" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q49" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R49" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S49" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T49" s="8" t="n">
@@ -4639,76 +4637,70 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>53790</v>
+        <v>53367</v>
       </c>
       <c r="C50" t="n">
-        <v>53840</v>
+        <v>53862</v>
       </c>
       <c r="D50" t="n">
-        <v>52812</v>
+        <v>53210</v>
       </c>
       <c r="E50" t="n">
-        <v>53353</v>
+        <v>53584</v>
       </c>
       <c r="F50" t="n">
-        <v>-454</v>
+        <v>231</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.008399999999999999</v>
+        <v>0.0043</v>
       </c>
       <c r="H50" t="n">
-        <v>1028</v>
+        <v>652</v>
       </c>
       <c r="I50" t="n">
-        <v>53094</v>
+        <v>51784</v>
       </c>
       <c r="J50" t="n">
-        <v>53076.75</v>
+        <v>52338.5</v>
       </c>
       <c r="K50" t="n">
-        <v>53496.5</v>
+        <v>52839</v>
       </c>
       <c r="L50" t="n">
-        <v>53916.25</v>
+        <v>53339.5</v>
       </c>
       <c r="M50" t="n">
-        <v>54117.5</v>
+        <v>53867</v>
       </c>
       <c r="N50" t="n">
-        <v>54318.75</v>
+        <v>54394.5</v>
       </c>
       <c r="O50" t="n">
-        <v>54957</v>
-      </c>
-      <c r="P50" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q50" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R50" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S50" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>54868</v>
+      </c>
+      <c r="P50" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q50" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R50" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S50" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T50" s="8" t="n">
@@ -4725,72 +4717,72 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>53367</v>
+        <v>53664</v>
       </c>
       <c r="C51" t="n">
-        <v>53862</v>
+        <v>53827</v>
       </c>
       <c r="D51" t="n">
-        <v>53210</v>
+        <v>52720</v>
       </c>
       <c r="E51" t="n">
-        <v>53584</v>
+        <v>53440</v>
       </c>
       <c r="F51" t="n">
-        <v>231</v>
+        <v>-144</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.0043</v>
+        <v>-0.0027</v>
       </c>
       <c r="H51" t="n">
-        <v>652</v>
+        <v>1107</v>
       </c>
       <c r="I51" t="n">
-        <v>51784</v>
+        <v>52558</v>
       </c>
       <c r="J51" t="n">
-        <v>52338.5</v>
+        <v>52956</v>
       </c>
       <c r="K51" t="n">
-        <v>52839</v>
+        <v>53258</v>
       </c>
       <c r="L51" t="n">
-        <v>53339.5</v>
+        <v>53560</v>
       </c>
       <c r="M51" t="n">
-        <v>53867</v>
+        <v>53910</v>
       </c>
       <c r="N51" t="n">
-        <v>54394.5</v>
+        <v>54260</v>
       </c>
       <c r="O51" t="n">
-        <v>54868</v>
+        <v>54514</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
       </c>
-      <c r="Q51" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R51" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S51" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="Q51" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R51" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S51" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T51" s="8" t="n">
@@ -4807,72 +4799,76 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr"/>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>53664</v>
+        <v>53261</v>
       </c>
       <c r="C52" t="n">
-        <v>53827</v>
+        <v>53336</v>
       </c>
       <c r="D52" t="n">
-        <v>52720</v>
+        <v>51992</v>
       </c>
       <c r="E52" t="n">
-        <v>53440</v>
+        <v>52585</v>
       </c>
       <c r="F52" t="n">
-        <v>-144</v>
+        <v>-855</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.0027</v>
+        <v>-0.016</v>
       </c>
       <c r="H52" t="n">
-        <v>1107</v>
+        <v>1344</v>
       </c>
       <c r="I52" t="n">
-        <v>52558</v>
+        <v>51613</v>
       </c>
       <c r="J52" t="n">
-        <v>52956</v>
+        <v>52416.25</v>
       </c>
       <c r="K52" t="n">
-        <v>53258</v>
+        <v>52886.5</v>
       </c>
       <c r="L52" t="n">
-        <v>53560</v>
+        <v>53356.75</v>
       </c>
       <c r="M52" t="n">
-        <v>53910</v>
+        <v>53993.5</v>
       </c>
       <c r="N52" t="n">
-        <v>54260</v>
+        <v>54630.25</v>
       </c>
       <c r="O52" t="n">
-        <v>54514</v>
+        <v>54934</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
       </c>
       <c r="Q52" s="6" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R52" s="6" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R52" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S52" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T52" s="8" t="n">
@@ -4898,62 +4894,60 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>53261</v>
+        <v>52376</v>
       </c>
       <c r="C53" t="n">
-        <v>53336</v>
+        <v>52672</v>
       </c>
       <c r="D53" t="n">
-        <v>51992</v>
+        <v>51209</v>
       </c>
       <c r="E53" t="n">
-        <v>52585</v>
+        <v>51761</v>
       </c>
       <c r="F53" t="n">
-        <v>-855</v>
+        <v>-824</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.016</v>
+        <v>-0.0157</v>
       </c>
       <c r="H53" t="n">
-        <v>1344</v>
+        <v>1463</v>
       </c>
       <c r="I53" t="n">
-        <v>51613</v>
+        <v>50648</v>
       </c>
       <c r="J53" t="n">
-        <v>52416.25</v>
+        <v>51201.5</v>
       </c>
       <c r="K53" t="n">
-        <v>52886.5</v>
+        <v>51913</v>
       </c>
       <c r="L53" t="n">
-        <v>53356.75</v>
+        <v>52624.5</v>
       </c>
       <c r="M53" t="n">
-        <v>53993.5</v>
+        <v>53257</v>
       </c>
       <c r="N53" t="n">
-        <v>54630.25</v>
+        <v>53889.5</v>
       </c>
       <c r="O53" t="n">
-        <v>54934</v>
+        <v>54680</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
       </c>
-      <c r="Q53" s="6" t="inlineStr">
+      <c r="Q53" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R53" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="R53" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S53" s="10" t="inlineStr">
@@ -4984,50 +4978,50 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>52376</v>
+        <v>52085</v>
       </c>
       <c r="C54" t="n">
-        <v>52672</v>
+        <v>52844</v>
       </c>
       <c r="D54" t="n">
-        <v>51209</v>
+        <v>51479</v>
       </c>
       <c r="E54" t="n">
-        <v>51761</v>
+        <v>52163</v>
       </c>
       <c r="F54" t="n">
-        <v>-824</v>
+        <v>402</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.0157</v>
+        <v>0.0078</v>
       </c>
       <c r="H54" t="n">
-        <v>1463</v>
+        <v>1365</v>
       </c>
       <c r="I54" t="n">
-        <v>50648</v>
+        <v>49746</v>
       </c>
       <c r="J54" t="n">
-        <v>51201.5</v>
+        <v>50208.25</v>
       </c>
       <c r="K54" t="n">
-        <v>51913</v>
+        <v>51029.5</v>
       </c>
       <c r="L54" t="n">
-        <v>52624.5</v>
+        <v>51850.75</v>
       </c>
       <c r="M54" t="n">
-        <v>53257</v>
+        <v>52492.5</v>
       </c>
       <c r="N54" t="n">
-        <v>53889.5</v>
+        <v>53134.25</v>
       </c>
       <c r="O54" t="n">
-        <v>54680</v>
+        <v>54135</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5035,18 +5029,18 @@
       <c r="Q54" s="6" t="n">
         <v/>
       </c>
-      <c r="R54" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S54" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T54" s="8" t="n">
-        <v/>
+      <c r="R54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S54" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T54" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U54" s="8" t="n">
         <v/>
@@ -5059,59 +5053,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>52085</v>
+        <v>52140</v>
       </c>
       <c r="C55" t="n">
-        <v>52844</v>
+        <v>52153</v>
       </c>
       <c r="D55" t="n">
-        <v>51479</v>
+        <v>50859</v>
       </c>
       <c r="E55" t="n">
-        <v>52163</v>
+        <v>51477</v>
       </c>
       <c r="F55" t="n">
-        <v>402</v>
+        <v>-686</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.0078</v>
+        <v>-0.0132</v>
       </c>
       <c r="H55" t="n">
-        <v>1365</v>
+        <v>1294</v>
       </c>
       <c r="I55" t="n">
-        <v>49746</v>
+        <v>50114</v>
       </c>
       <c r="J55" t="n">
-        <v>50208.25</v>
+        <v>50798.75</v>
       </c>
       <c r="K55" t="n">
-        <v>51029.5</v>
+        <v>51480.5</v>
       </c>
       <c r="L55" t="n">
-        <v>51850.75</v>
+        <v>52162.25</v>
       </c>
       <c r="M55" t="n">
-        <v>52492.5</v>
+        <v>52845.5</v>
       </c>
       <c r="N55" t="n">
-        <v>53134.25</v>
+        <v>53528.75</v>
       </c>
       <c r="O55" t="n">
-        <v>54135</v>
+        <v>54209</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5119,18 +5109,18 @@
       <c r="Q55" s="6" t="n">
         <v/>
       </c>
-      <c r="R55" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S55" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T55" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R55" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S55" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T55" s="8" t="n">
+        <v/>
       </c>
       <c r="U55" s="8" t="n">
         <v/>
@@ -5143,55 +5133,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr"/>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>52140</v>
+        <v>51486</v>
       </c>
       <c r="C56" t="n">
-        <v>52153</v>
+        <v>52032</v>
       </c>
       <c r="D56" t="n">
-        <v>50859</v>
+        <v>50909</v>
       </c>
       <c r="E56" t="n">
-        <v>51477</v>
+        <v>51926</v>
       </c>
       <c r="F56" t="n">
-        <v>-686</v>
+        <v>449</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.0132</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="H56" t="n">
-        <v>1294</v>
+        <v>1123</v>
       </c>
       <c r="I56" t="n">
-        <v>50114</v>
+        <v>49565</v>
       </c>
       <c r="J56" t="n">
-        <v>50798.75</v>
+        <v>50168.5</v>
       </c>
       <c r="K56" t="n">
-        <v>51480.5</v>
+        <v>50830</v>
       </c>
       <c r="L56" t="n">
-        <v>52162.25</v>
+        <v>51491.5</v>
       </c>
       <c r="M56" t="n">
-        <v>52845.5</v>
+        <v>52124</v>
       </c>
       <c r="N56" t="n">
-        <v>53528.75</v>
+        <v>52756.5</v>
       </c>
       <c r="O56" t="n">
-        <v>54209</v>
+        <v>53447</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5199,19 +5193,19 @@
       <c r="Q56" s="6" t="n">
         <v/>
       </c>
-      <c r="R56" s="6" t="inlineStr">
+      <c r="R56" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S56" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T56" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S56" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T56" s="8" t="n">
-        <v/>
-      </c>
       <c r="U56" s="8" t="n">
         <v/>
       </c>
@@ -5225,57 +5219,57 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>51486</v>
+        <v>51972</v>
       </c>
       <c r="C57" t="n">
-        <v>52032</v>
+        <v>52823</v>
       </c>
       <c r="D57" t="n">
-        <v>50909</v>
+        <v>51602</v>
       </c>
       <c r="E57" t="n">
-        <v>51926</v>
+        <v>52200</v>
       </c>
       <c r="F57" t="n">
-        <v>449</v>
+        <v>274</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.008699999999999999</v>
+        <v>0.0053</v>
       </c>
       <c r="H57" t="n">
-        <v>1123</v>
+        <v>1221</v>
       </c>
       <c r="I57" t="n">
-        <v>49565</v>
+        <v>49786</v>
       </c>
       <c r="J57" t="n">
-        <v>50168.5</v>
+        <v>51030.75</v>
       </c>
       <c r="K57" t="n">
-        <v>50830</v>
+        <v>51364.5</v>
       </c>
       <c r="L57" t="n">
-        <v>51491.5</v>
+        <v>51698.25</v>
       </c>
       <c r="M57" t="n">
-        <v>52124</v>
+        <v>52487.5</v>
       </c>
       <c r="N57" t="n">
-        <v>52756.5</v>
+        <v>53276.75</v>
       </c>
       <c r="O57" t="n">
-        <v>53447</v>
+        <v>53155</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5307,91 +5301,7 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="B58" t="n">
-        <v>51972</v>
-      </c>
-      <c r="C58" t="n">
-        <v>52612</v>
-      </c>
-      <c r="D58" t="n">
-        <v>51602</v>
-      </c>
-      <c r="E58" t="n">
-        <v>52460</v>
-      </c>
-      <c r="F58" t="n">
-        <v>534</v>
-      </c>
-      <c r="G58" s="5" t="n">
-        <v>0.0103</v>
-      </c>
-      <c r="H58" t="n">
-        <v>1010</v>
-      </c>
-      <c r="I58" t="n">
-        <v>49786</v>
-      </c>
-      <c r="J58" t="n">
-        <v>51030.75</v>
-      </c>
-      <c r="K58" t="n">
-        <v>51364.5</v>
-      </c>
-      <c r="L58" t="n">
-        <v>51698.25</v>
-      </c>
-      <c r="M58" t="n">
-        <v>52487.5</v>
-      </c>
-      <c r="N58" t="n">
-        <v>53276.75</v>
-      </c>
-      <c r="O58" t="n">
-        <v>53155</v>
-      </c>
-      <c r="P58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S58" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W58" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X58" t="inlineStr"/>
+      <c r="X57" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/YM_weekly.xlsx
+++ b/three_gate/analysis/YM_weekly.xlsx
@@ -5239,13 +5239,13 @@
         <v>51602</v>
       </c>
       <c r="E57" t="n">
-        <v>52200</v>
+        <v>52214</v>
       </c>
       <c r="F57" t="n">
-        <v>274</v>
+        <v>288</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.0053</v>
+        <v>0.0055</v>
       </c>
       <c r="H57" t="n">
         <v>1221</v>

--- a/three_gate/analysis/YM_weekly.xlsx
+++ b/three_gate/analysis/YM_weekly.xlsx
@@ -5239,13 +5239,13 @@
         <v>51602</v>
       </c>
       <c r="E57" t="n">
-        <v>52214</v>
+        <v>52377</v>
       </c>
       <c r="F57" t="n">
-        <v>288</v>
+        <v>451</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.0055</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="H57" t="n">
         <v>1221</v>

--- a/three_gate/analysis/YM_weekly.xlsx
+++ b/three_gate/analysis/YM_weekly.xlsx
@@ -5239,13 +5239,13 @@
         <v>51602</v>
       </c>
       <c r="E57" t="n">
-        <v>52377</v>
+        <v>52350</v>
       </c>
       <c r="F57" t="n">
-        <v>451</v>
+        <v>424</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.008699999999999999</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="H57" t="n">
         <v>1221</v>

--- a/three_gate/analysis/YM_weekly.xlsx
+++ b/three_gate/analysis/YM_weekly.xlsx
@@ -86,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -115,6 +115,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -480,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X57"/>
+  <dimension ref="A1:X58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5239,13 +5242,13 @@
         <v>51602</v>
       </c>
       <c r="E57" t="n">
-        <v>52350</v>
+        <v>52214</v>
       </c>
       <c r="F57" t="n">
-        <v>424</v>
+        <v>288</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.008200000000000001</v>
+        <v>0.0055</v>
       </c>
       <c r="H57" t="n">
         <v>1221</v>
@@ -5302,6 +5305,90 @@
         </is>
       </c>
       <c r="X57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>52238</v>
+      </c>
+      <c r="C58" t="n">
+        <v>52308</v>
+      </c>
+      <c r="D58" t="n">
+        <v>52201</v>
+      </c>
+      <c r="E58" t="n">
+        <v/>
+      </c>
+      <c r="F58" t="n">
+        <v/>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v/>
+      </c>
+      <c r="H58" t="n">
+        <v>107</v>
+      </c>
+      <c r="I58" t="n">
+        <v>50381</v>
+      </c>
+      <c r="J58" t="n">
+        <v>50993.75</v>
+      </c>
+      <c r="K58" t="n">
+        <v>51603.5</v>
+      </c>
+      <c r="L58" t="n">
+        <v>52213.25</v>
+      </c>
+      <c r="M58" t="n">
+        <v>52824.5</v>
+      </c>
+      <c r="N58" t="n">
+        <v>53435.75</v>
+      </c>
+      <c r="O58" t="n">
+        <v>54044</v>
+      </c>
+      <c r="P58" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S58" s="12" t="inlineStr">
+        <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W58" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/YM_weekly.xlsx
+++ b/three_gate/analysis/YM_weekly.xlsx
@@ -5319,7 +5319,7 @@
         <v>52308</v>
       </c>
       <c r="D58" t="n">
-        <v>52201</v>
+        <v>52197</v>
       </c>
       <c r="E58" t="n">
         <v/>
@@ -5331,7 +5331,7 @@
         <v/>
       </c>
       <c r="H58" t="n">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="I58" t="n">
         <v>50381</v>

--- a/three_gate/analysis/YM_weekly.xlsx
+++ b/three_gate/analysis/YM_weekly.xlsx
@@ -86,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -115,9 +115,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -662,25 +659,25 @@
         <v>957</v>
       </c>
       <c r="I2" t="n">
-        <v>44981</v>
+        <v>45023</v>
       </c>
       <c r="J2" t="n">
-        <v>45778.25</v>
+        <v>45794</v>
       </c>
       <c r="K2" t="n">
-        <v>45978.5</v>
+        <v>45989</v>
       </c>
       <c r="L2" t="n">
-        <v>46178.75</v>
+        <v>46184</v>
       </c>
       <c r="M2" t="n">
-        <v>46677.5</v>
+        <v>46667</v>
       </c>
       <c r="N2" t="n">
-        <v>47176.25</v>
+        <v>47150</v>
       </c>
       <c r="O2" t="n">
-        <v>47078</v>
+        <v>47057</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -5313,25 +5310,25 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>52238</v>
+        <v>52070</v>
       </c>
       <c r="C58" t="n">
-        <v>52308</v>
+        <v>52826</v>
       </c>
       <c r="D58" t="n">
-        <v>52197</v>
+        <v>52034</v>
       </c>
       <c r="E58" t="n">
-        <v/>
+        <v>52714</v>
       </c>
       <c r="F58" t="n">
-        <v/>
+        <v>500</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v/>
+        <v>0.009599999999999999</v>
       </c>
       <c r="H58" t="n">
-        <v>111</v>
+        <v>792</v>
       </c>
       <c r="I58" t="n">
         <v>50381</v>
@@ -5354,25 +5351,25 @@
       <c r="O58" t="n">
         <v>54044</v>
       </c>
-      <c r="P58" s="6" t="inlineStr">
+      <c r="P58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S58" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S58" s="12" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="n">
-        <v/>
-      </c>
       <c r="U58" s="8" t="n">
         <v/>
       </c>
@@ -5384,11 +5381,7 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X58" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/YM_weekly.xlsx
+++ b/three_gate/analysis/YM_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>957</v>
       </c>
       <c r="I2" t="n">
-        <v>45023</v>
+        <v>45545</v>
       </c>
       <c r="J2" t="n">
-        <v>45794</v>
+        <v>45989.75</v>
       </c>
       <c r="K2" t="n">
-        <v>45989</v>
+        <v>46119.5</v>
       </c>
       <c r="L2" t="n">
-        <v>46184</v>
+        <v>46249.25</v>
       </c>
       <c r="M2" t="n">
-        <v>46667</v>
+        <v>46536.5</v>
       </c>
       <c r="N2" t="n">
-        <v>47150</v>
+        <v>46823.75</v>
       </c>
       <c r="O2" t="n">
-        <v>47057</v>
+        <v>46796</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -685,8 +685,10 @@
       <c r="Q2" s="6" t="n">
         <v/>
       </c>
-      <c r="R2" s="6" t="n">
-        <v/>
+      <c r="R2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
@@ -698,11 +700,15 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U2" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V2" s="8" t="n">
-        <v/>
+      <c r="U2" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V2" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
@@ -5313,22 +5319,22 @@
         <v>52070</v>
       </c>
       <c r="C58" t="n">
-        <v>52826</v>
+        <v>53085</v>
       </c>
       <c r="D58" t="n">
         <v>52034</v>
       </c>
       <c r="E58" t="n">
-        <v>52714</v>
+        <v>52894</v>
       </c>
       <c r="F58" t="n">
-        <v>500</v>
+        <v>680</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.009599999999999999</v>
+        <v>0.013</v>
       </c>
       <c r="H58" t="n">
-        <v>792</v>
+        <v>1051</v>
       </c>
       <c r="I58" t="n">
         <v>50381</v>

--- a/three_gate/analysis/YM_weekly.xlsx
+++ b/three_gate/analysis/YM_weekly.xlsx
@@ -5319,22 +5319,22 @@
         <v>52070</v>
       </c>
       <c r="C58" t="n">
-        <v>53085</v>
+        <v>53168</v>
       </c>
       <c r="D58" t="n">
         <v>52034</v>
       </c>
       <c r="E58" t="n">
-        <v>52894</v>
+        <v>52936</v>
       </c>
       <c r="F58" t="n">
-        <v>680</v>
+        <v>722</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.013</v>
+        <v>0.0138</v>
       </c>
       <c r="H58" t="n">
-        <v>1051</v>
+        <v>1134</v>
       </c>
       <c r="I58" t="n">
         <v>50381</v>

--- a/three_gate/analysis/YM_weekly.xlsx
+++ b/three_gate/analysis/YM_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>957</v>
       </c>
       <c r="I2" t="n">
-        <v>45545</v>
+        <v>45762</v>
       </c>
       <c r="J2" t="n">
-        <v>45989.75</v>
+        <v>46093</v>
       </c>
       <c r="K2" t="n">
-        <v>46119.5</v>
+        <v>46180</v>
       </c>
       <c r="L2" t="n">
-        <v>46249.25</v>
+        <v>46267</v>
       </c>
       <c r="M2" t="n">
-        <v>46536.5</v>
+        <v>46476</v>
       </c>
       <c r="N2" t="n">
-        <v>46823.75</v>
+        <v>46685</v>
       </c>
       <c r="O2" t="n">
-        <v>46796</v>
+        <v>46650</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -5325,13 +5325,13 @@
         <v>52034</v>
       </c>
       <c r="E58" t="n">
-        <v>52936</v>
+        <v>53032</v>
       </c>
       <c r="F58" t="n">
-        <v>722</v>
+        <v>818</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0138</v>
+        <v>0.0157</v>
       </c>
       <c r="H58" t="n">
         <v>1134</v>

--- a/three_gate/analysis/YM_weekly.xlsx
+++ b/three_gate/analysis/YM_weekly.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X58"/>
+  <dimension ref="A1:X57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,50 +634,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>46605</v>
+        <v>46565</v>
       </c>
       <c r="C2" t="n">
-        <v>47055</v>
+        <v>47323</v>
       </c>
       <c r="D2" t="n">
-        <v>46098</v>
+        <v>46335</v>
       </c>
       <c r="E2" t="n">
-        <v>46556</v>
+        <v>47031</v>
       </c>
       <c r="F2" t="n">
-        <v>228</v>
+        <v>475</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0049</v>
+        <v>0.0102</v>
       </c>
       <c r="H2" t="n">
-        <v>957</v>
+        <v>988</v>
       </c>
       <c r="I2" t="n">
-        <v>45762</v>
+        <v>45141</v>
       </c>
       <c r="J2" t="n">
-        <v>46093</v>
+        <v>45588.75</v>
       </c>
       <c r="K2" t="n">
-        <v>46180</v>
+        <v>46077.5</v>
       </c>
       <c r="L2" t="n">
-        <v>46267</v>
+        <v>46566.25</v>
       </c>
       <c r="M2" t="n">
-        <v>46476</v>
+        <v>47034.5</v>
       </c>
       <c r="N2" t="n">
-        <v>46685</v>
+        <v>47502.75</v>
       </c>
       <c r="O2" t="n">
-        <v>46650</v>
+        <v>48012</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -685,10 +685,8 @@
       <c r="Q2" s="6" t="n">
         <v/>
       </c>
-      <c r="R2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R2" s="6" t="n">
+        <v/>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
@@ -700,15 +698,11 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U2" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V2" s="8" t="n">
+        <v/>
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
@@ -720,79 +714,83 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>46565</v>
+        <v>47048</v>
       </c>
       <c r="C3" t="n">
-        <v>47323</v>
+        <v>47162</v>
       </c>
       <c r="D3" t="n">
-        <v>46335</v>
+        <v>45387</v>
       </c>
       <c r="E3" t="n">
-        <v>47031</v>
+        <v>45706</v>
       </c>
       <c r="F3" t="n">
-        <v>475</v>
+        <v>-1325</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.0102</v>
+        <v>-0.0282</v>
       </c>
       <c r="H3" t="n">
-        <v>988</v>
+        <v>1775</v>
       </c>
       <c r="I3" t="n">
-        <v>45141</v>
+        <v>45347</v>
       </c>
       <c r="J3" t="n">
-        <v>45588.75</v>
+        <v>46144</v>
       </c>
       <c r="K3" t="n">
-        <v>46077.5</v>
+        <v>46537</v>
       </c>
       <c r="L3" t="n">
-        <v>46566.25</v>
+        <v>46930</v>
       </c>
       <c r="M3" t="n">
-        <v>47034.5</v>
+        <v>47525</v>
       </c>
       <c r="N3" t="n">
-        <v>47502.75</v>
+        <v>48120</v>
       </c>
       <c r="O3" t="n">
-        <v>48012</v>
-      </c>
-      <c r="P3" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q3" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R3" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S3" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="inlineStr">
+        <v>48311</v>
+      </c>
+      <c r="P3" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="Q3" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R3" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S3" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="n">
+        <v/>
+      </c>
       <c r="U3" s="8" t="n">
         <v/>
       </c>
       <c r="V3" s="8" t="n">
         <v/>
       </c>
-      <c r="W3" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W3" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X3" t="inlineStr"/>
@@ -800,74 +798,70 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>47048</v>
+        <v>45837</v>
       </c>
       <c r="C4" t="n">
-        <v>47162</v>
+        <v>46915</v>
       </c>
       <c r="D4" t="n">
-        <v>45387</v>
+        <v>45605</v>
       </c>
       <c r="E4" t="n">
-        <v>45706</v>
+        <v>46381</v>
       </c>
       <c r="F4" t="n">
-        <v>-1325</v>
+        <v>675</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.0282</v>
+        <v>0.0148</v>
       </c>
       <c r="H4" t="n">
-        <v>1775</v>
+        <v>1310</v>
       </c>
       <c r="I4" t="n">
-        <v>45347</v>
+        <v>43612</v>
       </c>
       <c r="J4" t="n">
-        <v>46144</v>
+        <v>43646.75</v>
       </c>
       <c r="K4" t="n">
-        <v>46537</v>
+        <v>44818.5</v>
       </c>
       <c r="L4" t="n">
-        <v>46930</v>
+        <v>45990.25</v>
       </c>
       <c r="M4" t="n">
-        <v>47525</v>
+        <v>46593.5</v>
       </c>
       <c r="N4" t="n">
-        <v>48120</v>
+        <v>47196.75</v>
       </c>
       <c r="O4" t="n">
-        <v>48311</v>
-      </c>
-      <c r="P4" s="6" t="inlineStr">
+        <v>48937</v>
+      </c>
+      <c r="P4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S4" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q4" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R4" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S4" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="n">
-        <v/>
-      </c>
       <c r="U4" s="8" t="n">
         <v/>
       </c>
@@ -879,55 +873,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr"/>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>45837</v>
+        <v>46489</v>
       </c>
       <c r="C5" t="n">
-        <v>46915</v>
+        <v>47508</v>
       </c>
       <c r="D5" t="n">
-        <v>45605</v>
+        <v>46316</v>
       </c>
       <c r="E5" t="n">
-        <v>46381</v>
+        <v>47396</v>
       </c>
       <c r="F5" t="n">
-        <v>675</v>
+        <v>1015</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.0148</v>
+        <v>0.0219</v>
       </c>
       <c r="H5" t="n">
-        <v>1310</v>
+        <v>1192</v>
       </c>
       <c r="I5" t="n">
-        <v>43612</v>
+        <v>44295</v>
       </c>
       <c r="J5" t="n">
-        <v>43646.75</v>
+        <v>45131.5</v>
       </c>
       <c r="K5" t="n">
-        <v>44818.5</v>
+        <v>45726</v>
       </c>
       <c r="L5" t="n">
-        <v>45990.25</v>
+        <v>46320.5</v>
       </c>
       <c r="M5" t="n">
-        <v>46593.5</v>
+        <v>47036</v>
       </c>
       <c r="N5" t="n">
-        <v>47196.75</v>
+        <v>47751.5</v>
       </c>
       <c r="O5" t="n">
-        <v>48937</v>
+        <v>48225</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -945,12 +943,14 @@
       </c>
       <c r="T5" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U5" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U5" s="8" t="n">
-        <v/>
-      </c>
       <c r="V5" s="8" t="n">
         <v/>
       </c>
@@ -961,57 +961,57 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>46489</v>
+        <v>47711</v>
       </c>
       <c r="C6" t="n">
-        <v>47508</v>
+        <v>48214</v>
       </c>
       <c r="D6" t="n">
-        <v>46316</v>
+        <v>47488</v>
       </c>
       <c r="E6" t="n">
-        <v>47396</v>
+        <v>47722</v>
       </c>
       <c r="F6" t="n">
-        <v>1015</v>
+        <v>326</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.0219</v>
+        <v>0.0069</v>
       </c>
       <c r="H6" t="n">
-        <v>1192</v>
+        <v>726</v>
       </c>
       <c r="I6" t="n">
-        <v>44295</v>
+        <v>45124</v>
       </c>
       <c r="J6" t="n">
-        <v>45131.5</v>
+        <v>46446</v>
       </c>
       <c r="K6" t="n">
-        <v>45726</v>
+        <v>46800</v>
       </c>
       <c r="L6" t="n">
-        <v>46320.5</v>
+        <v>47154</v>
       </c>
       <c r="M6" t="n">
-        <v>47036</v>
+        <v>47992</v>
       </c>
       <c r="N6" t="n">
-        <v>47751.5</v>
+        <v>48830</v>
       </c>
       <c r="O6" t="n">
-        <v>48225</v>
+        <v>48700</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1029,13 +1029,11 @@
       </c>
       <c r="T6" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U6" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U6" s="8" t="n">
+        <v/>
       </c>
       <c r="V6" s="8" t="n">
         <v/>
@@ -1054,70 +1052,74 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>47711</v>
+        <v>47735</v>
       </c>
       <c r="C7" t="n">
-        <v>48214</v>
+        <v>47869</v>
       </c>
       <c r="D7" t="n">
-        <v>47488</v>
+        <v>46574</v>
       </c>
       <c r="E7" t="n">
-        <v>47722</v>
+        <v>47085</v>
       </c>
       <c r="F7" t="n">
-        <v>326</v>
+        <v>-637</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.0069</v>
+        <v>-0.0133</v>
       </c>
       <c r="H7" t="n">
-        <v>726</v>
+        <v>1295</v>
       </c>
       <c r="I7" t="n">
-        <v>45124</v>
+        <v>46762</v>
       </c>
       <c r="J7" t="n">
-        <v>46446</v>
+        <v>46931.5</v>
       </c>
       <c r="K7" t="n">
-        <v>46800</v>
+        <v>47359</v>
       </c>
       <c r="L7" t="n">
-        <v>47154</v>
+        <v>47786.5</v>
       </c>
       <c r="M7" t="n">
-        <v>47992</v>
+        <v>48085</v>
       </c>
       <c r="N7" t="n">
-        <v>48830</v>
+        <v>48383.5</v>
       </c>
       <c r="O7" t="n">
-        <v>48700</v>
-      </c>
-      <c r="P7" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q7" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R7" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S7" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="inlineStr">
+        <v>48940</v>
+      </c>
+      <c r="P7" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q7" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R7" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S7" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="n">
+        <v/>
+      </c>
       <c r="U7" s="8" t="n">
         <v/>
       </c>
@@ -1129,86 +1131,80 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>47735</v>
+        <v>47208</v>
       </c>
       <c r="C8" t="n">
-        <v>47869</v>
+        <v>48528</v>
       </c>
       <c r="D8" t="n">
-        <v>46574</v>
+        <v>46939</v>
       </c>
       <c r="E8" t="n">
-        <v>47085</v>
+        <v>47229</v>
       </c>
       <c r="F8" t="n">
-        <v>-637</v>
+        <v>144</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.0133</v>
+        <v>0.0031</v>
       </c>
       <c r="H8" t="n">
-        <v>1295</v>
+        <v>1589</v>
       </c>
       <c r="I8" t="n">
-        <v>46762</v>
+        <v>45279</v>
       </c>
       <c r="J8" t="n">
-        <v>46931.5</v>
+        <v>45721.75</v>
       </c>
       <c r="K8" t="n">
-        <v>47359</v>
+        <v>46437.5</v>
       </c>
       <c r="L8" t="n">
-        <v>47786.5</v>
+        <v>47153.25</v>
       </c>
       <c r="M8" t="n">
-        <v>48085</v>
+        <v>47732.5</v>
       </c>
       <c r="N8" t="n">
-        <v>48383.5</v>
+        <v>48311.75</v>
       </c>
       <c r="O8" t="n">
-        <v>48940</v>
-      </c>
-      <c r="P8" s="6" t="inlineStr">
+        <v>49164</v>
+      </c>
+      <c r="P8" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q8" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R8" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S8" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q8" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R8" s="6" t="inlineStr">
+      <c r="U8" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S8" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U8" s="8" t="n">
-        <v/>
-      </c>
       <c r="V8" s="8" t="n">
         <v/>
       </c>
@@ -1217,55 +1213,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr"/>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>47208</v>
+        <v>47237</v>
       </c>
       <c r="C9" t="n">
-        <v>48528</v>
+        <v>47368</v>
       </c>
       <c r="D9" t="n">
-        <v>46939</v>
+        <v>45779</v>
       </c>
       <c r="E9" t="n">
-        <v>47229</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="n">
-        <v>144</v>
+        <v>-908</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.0031</v>
+        <v>-0.0192</v>
       </c>
       <c r="H9" t="n">
         <v>1589</v>
       </c>
       <c r="I9" t="n">
-        <v>45279</v>
+        <v>45350</v>
       </c>
       <c r="J9" t="n">
-        <v>45721.75</v>
+        <v>45387.75</v>
       </c>
       <c r="K9" t="n">
-        <v>46437.5</v>
+        <v>46434.5</v>
       </c>
       <c r="L9" t="n">
-        <v>47153.25</v>
+        <v>47481.25</v>
       </c>
       <c r="M9" t="n">
-        <v>47732.5</v>
+        <v>48023.5</v>
       </c>
       <c r="N9" t="n">
-        <v>48311.75</v>
+        <v>48565.75</v>
       </c>
       <c r="O9" t="n">
-        <v>49164</v>
+        <v>50117</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1273,23 +1273,21 @@
       <c r="Q9" s="6" t="n">
         <v/>
       </c>
-      <c r="R9" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S9" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U9" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R9" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S9" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U9" s="8" t="n">
+        <v/>
       </c>
       <c r="V9" s="8" t="n">
         <v/>
@@ -1299,59 +1297,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>47237</v>
+        <v>46504</v>
       </c>
       <c r="C10" t="n">
-        <v>47368</v>
+        <v>47796</v>
       </c>
       <c r="D10" t="n">
-        <v>45779</v>
+        <v>46165</v>
       </c>
       <c r="E10" t="n">
-        <v>46321</v>
+        <v>47743</v>
       </c>
       <c r="F10" t="n">
-        <v>-908</v>
+        <v>1422</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.0192</v>
+        <v>0.0307</v>
       </c>
       <c r="H10" t="n">
-        <v>1589</v>
+        <v>1631</v>
       </c>
       <c r="I10" t="n">
-        <v>45350</v>
+        <v>44190</v>
       </c>
       <c r="J10" t="n">
-        <v>45387.75</v>
+        <v>44605.75</v>
       </c>
       <c r="K10" t="n">
-        <v>46434.5</v>
+        <v>45526.5</v>
       </c>
       <c r="L10" t="n">
-        <v>47481.25</v>
+        <v>46447.25</v>
       </c>
       <c r="M10" t="n">
-        <v>48023.5</v>
+        <v>47115.5</v>
       </c>
       <c r="N10" t="n">
-        <v>48565.75</v>
+        <v>47783.75</v>
       </c>
       <c r="O10" t="n">
-        <v>50117</v>
+        <v>48957</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1359,22 +1353,24 @@
       <c r="Q10" s="6" t="n">
         <v/>
       </c>
-      <c r="R10" s="6" t="inlineStr">
+      <c r="R10" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S10" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U10" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S10" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U10" s="8" t="n">
-        <v/>
-      </c>
       <c r="V10" s="8" t="n">
         <v/>
       </c>
@@ -1383,55 +1379,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr"/>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>46504</v>
+        <v>47741</v>
       </c>
       <c r="C11" t="n">
-        <v>47796</v>
+        <v>48184</v>
       </c>
       <c r="D11" t="n">
-        <v>46165</v>
+        <v>47269</v>
       </c>
       <c r="E11" t="n">
-        <v>47743</v>
+        <v>48001</v>
       </c>
       <c r="F11" t="n">
-        <v>1422</v>
+        <v>258</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0307</v>
+        <v>0.0054</v>
       </c>
       <c r="H11" t="n">
-        <v>1631</v>
+        <v>915</v>
       </c>
       <c r="I11" t="n">
-        <v>44190</v>
+        <v>44534</v>
       </c>
       <c r="J11" t="n">
-        <v>44605.75</v>
+        <v>46493.25</v>
       </c>
       <c r="K11" t="n">
-        <v>45526.5</v>
+        <v>46927.5</v>
       </c>
       <c r="L11" t="n">
-        <v>46447.25</v>
+        <v>47361.75</v>
       </c>
       <c r="M11" t="n">
-        <v>47115.5</v>
+        <v>48558.5</v>
       </c>
       <c r="N11" t="n">
-        <v>47783.75</v>
+        <v>49755.25</v>
       </c>
       <c r="O11" t="n">
-        <v>48957</v>
+        <v>49427</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1449,13 +1449,11 @@
       </c>
       <c r="T11" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U11" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U11" s="8" t="n">
+        <v/>
       </c>
       <c r="V11" s="8" t="n">
         <v/>
@@ -1474,50 +1472,50 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>47741</v>
+        <v>48015</v>
       </c>
       <c r="C12" t="n">
-        <v>48184</v>
+        <v>48917</v>
       </c>
       <c r="D12" t="n">
-        <v>47269</v>
+        <v>47504</v>
       </c>
       <c r="E12" t="n">
-        <v>48001</v>
+        <v>48474</v>
       </c>
       <c r="F12" t="n">
-        <v>258</v>
+        <v>473</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.0054</v>
+        <v>0.009900000000000001</v>
       </c>
       <c r="H12" t="n">
-        <v>915</v>
+        <v>1413</v>
       </c>
       <c r="I12" t="n">
-        <v>44534</v>
+        <v>46354</v>
       </c>
       <c r="J12" t="n">
-        <v>46493.25</v>
+        <v>47223.25</v>
       </c>
       <c r="K12" t="n">
-        <v>46927.5</v>
+        <v>47543.5</v>
       </c>
       <c r="L12" t="n">
-        <v>47361.75</v>
+        <v>47863.75</v>
       </c>
       <c r="M12" t="n">
-        <v>48558.5</v>
+        <v>48458.5</v>
       </c>
       <c r="N12" t="n">
-        <v>49755.25</v>
+        <v>49053.25</v>
       </c>
       <c r="O12" t="n">
-        <v>49427</v>
+        <v>49099</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1525,8 +1523,10 @@
       <c r="Q12" s="6" t="n">
         <v/>
       </c>
-      <c r="R12" s="6" t="n">
-        <v/>
+      <c r="R12" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S12" s="7" t="inlineStr">
         <is>
@@ -1558,50 +1558,50 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>48015</v>
+        <v>48517</v>
       </c>
       <c r="C13" t="n">
-        <v>48917</v>
+        <v>48745</v>
       </c>
       <c r="D13" t="n">
-        <v>47504</v>
+        <v>47809</v>
       </c>
       <c r="E13" t="n">
-        <v>48474</v>
+        <v>48090</v>
       </c>
       <c r="F13" t="n">
-        <v>473</v>
+        <v>-384</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.009900000000000001</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="H13" t="n">
-        <v>1413</v>
+        <v>936</v>
       </c>
       <c r="I13" t="n">
-        <v>46354</v>
+        <v>46091</v>
       </c>
       <c r="J13" t="n">
-        <v>47223.25</v>
+        <v>47192.75</v>
       </c>
       <c r="K13" t="n">
-        <v>47543.5</v>
+        <v>47767.5</v>
       </c>
       <c r="L13" t="n">
-        <v>47863.75</v>
+        <v>48342.25</v>
       </c>
       <c r="M13" t="n">
-        <v>48458.5</v>
+        <v>49180.5</v>
       </c>
       <c r="N13" t="n">
-        <v>49053.25</v>
+        <v>50018.75</v>
       </c>
       <c r="O13" t="n">
-        <v>49099</v>
+        <v>50330</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1609,20 +1609,16 @@
       <c r="Q13" s="6" t="n">
         <v/>
       </c>
-      <c r="R13" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S13" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S13" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="n">
+        <v/>
       </c>
       <c r="U13" s="8" t="n">
         <v/>
@@ -1637,57 +1633,57 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>48517</v>
+        <v>48600</v>
       </c>
       <c r="C14" t="n">
-        <v>48745</v>
+        <v>49086</v>
       </c>
       <c r="D14" t="n">
-        <v>47809</v>
+        <v>48458</v>
       </c>
       <c r="E14" t="n">
-        <v>48090</v>
+        <v>48998</v>
       </c>
       <c r="F14" t="n">
-        <v>-384</v>
+        <v>908</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.007900000000000001</v>
+        <v>0.0189</v>
       </c>
       <c r="H14" t="n">
-        <v>936</v>
+        <v>628</v>
       </c>
       <c r="I14" t="n">
-        <v>46091</v>
+        <v>46873</v>
       </c>
       <c r="J14" t="n">
-        <v>47192.75</v>
+        <v>47060.5</v>
       </c>
       <c r="K14" t="n">
-        <v>47767.5</v>
+        <v>47622</v>
       </c>
       <c r="L14" t="n">
-        <v>48342.25</v>
+        <v>48183.5</v>
       </c>
       <c r="M14" t="n">
-        <v>49180.5</v>
+        <v>48558</v>
       </c>
       <c r="N14" t="n">
-        <v>50018.75</v>
+        <v>48932.5</v>
       </c>
       <c r="O14" t="n">
-        <v>50330</v>
+        <v>49681</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1698,103 +1694,103 @@
       <c r="R14" s="6" t="n">
         <v/>
       </c>
-      <c r="S14" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U14" s="8" t="n">
-        <v/>
+      <c r="S14" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U14" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V14" s="8" t="n">
         <v/>
       </c>
-      <c r="W14" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W14" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>48600</v>
+        <v>48998</v>
       </c>
       <c r="C15" t="n">
-        <v>49086</v>
+        <v>49052</v>
       </c>
       <c r="D15" t="n">
-        <v>48458</v>
+        <v>48092</v>
       </c>
       <c r="E15" t="n">
-        <v>48998</v>
+        <v>48616</v>
       </c>
       <c r="F15" t="n">
-        <v>908</v>
+        <v>-382</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.0189</v>
+        <v>-0.0078</v>
       </c>
       <c r="H15" t="n">
-        <v>628</v>
+        <v>960</v>
       </c>
       <c r="I15" t="n">
-        <v>46873</v>
+        <v>47830</v>
       </c>
       <c r="J15" t="n">
-        <v>47060.5</v>
+        <v>48483</v>
       </c>
       <c r="K15" t="n">
-        <v>47622</v>
+        <v>48684</v>
       </c>
       <c r="L15" t="n">
-        <v>48183.5</v>
+        <v>48885</v>
       </c>
       <c r="M15" t="n">
-        <v>48558</v>
+        <v>49312</v>
       </c>
       <c r="N15" t="n">
-        <v>48932.5</v>
+        <v>49739</v>
       </c>
       <c r="O15" t="n">
-        <v>49681</v>
+        <v>49714</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
       </c>
-      <c r="Q15" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R15" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S15" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="inlineStr">
+      <c r="Q15" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U15" s="8" t="inlineStr">
+      <c r="R15" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S15" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U15" s="8" t="n">
+        <v/>
+      </c>
       <c r="V15" s="8" t="n">
         <v/>
       </c>
@@ -1803,80 +1799,84 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr"/>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>48998</v>
+        <v>48653</v>
       </c>
       <c r="C16" t="n">
-        <v>49052</v>
+        <v>49876</v>
       </c>
       <c r="D16" t="n">
-        <v>48092</v>
+        <v>48556</v>
       </c>
       <c r="E16" t="n">
-        <v>48616</v>
+        <v>49726</v>
       </c>
       <c r="F16" t="n">
-        <v>-382</v>
+        <v>1110</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-0.0078</v>
+        <v>0.0228</v>
       </c>
       <c r="H16" t="n">
-        <v>960</v>
+        <v>1320</v>
       </c>
       <c r="I16" t="n">
-        <v>47830</v>
+        <v>47132</v>
       </c>
       <c r="J16" t="n">
-        <v>48483</v>
+        <v>47678</v>
       </c>
       <c r="K16" t="n">
-        <v>48684</v>
+        <v>48136</v>
       </c>
       <c r="L16" t="n">
-        <v>48885</v>
+        <v>48594</v>
       </c>
       <c r="M16" t="n">
-        <v>49312</v>
+        <v>49096</v>
       </c>
       <c r="N16" t="n">
-        <v>49739</v>
+        <v>49598</v>
       </c>
       <c r="O16" t="n">
-        <v>49714</v>
+        <v>50012</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
       </c>
-      <c r="Q16" s="6" t="inlineStr">
+      <c r="Q16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S16" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R16" s="6" t="inlineStr">
+      <c r="U16" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S16" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U16" s="8" t="n">
-        <v/>
-      </c>
       <c r="V16" s="8" t="n">
         <v/>
       </c>
@@ -1885,59 +1885,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>48653</v>
+        <v>49720</v>
       </c>
       <c r="C17" t="n">
-        <v>49876</v>
+        <v>49901</v>
       </c>
       <c r="D17" t="n">
-        <v>48556</v>
+        <v>49057</v>
       </c>
       <c r="E17" t="n">
-        <v>49726</v>
+        <v>49547</v>
       </c>
       <c r="F17" t="n">
-        <v>1110</v>
+        <v>-179</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0228</v>
+        <v>-0.0036</v>
       </c>
       <c r="H17" t="n">
-        <v>1320</v>
+        <v>844</v>
       </c>
       <c r="I17" t="n">
-        <v>47132</v>
+        <v>47236</v>
       </c>
       <c r="J17" t="n">
-        <v>47678</v>
+        <v>48661</v>
       </c>
       <c r="K17" t="n">
-        <v>48136</v>
+        <v>49066</v>
       </c>
       <c r="L17" t="n">
-        <v>48594</v>
+        <v>49471</v>
       </c>
       <c r="M17" t="n">
-        <v>49096</v>
+        <v>50386</v>
       </c>
       <c r="N17" t="n">
-        <v>49598</v>
+        <v>51301</v>
       </c>
       <c r="O17" t="n">
-        <v>50012</v>
+        <v>51196</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1945,23 +1941,21 @@
       <c r="Q17" s="6" t="n">
         <v/>
       </c>
-      <c r="R17" s="6" t="n">
-        <v/>
+      <c r="R17" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S17" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U17" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U17" s="8" t="n">
+        <v/>
       </c>
       <c r="V17" s="8" t="n">
         <v/>
@@ -1971,70 +1965,76 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr"/>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>49720</v>
+        <v>49310</v>
       </c>
       <c r="C18" t="n">
-        <v>49901</v>
+        <v>49795</v>
       </c>
       <c r="D18" t="n">
-        <v>49057</v>
+        <v>48488</v>
       </c>
       <c r="E18" t="n">
-        <v>49547</v>
+        <v>49263</v>
       </c>
       <c r="F18" t="n">
-        <v>-179</v>
+        <v>-284</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-0.0036</v>
+        <v>-0.0057</v>
       </c>
       <c r="H18" t="n">
-        <v>844</v>
+        <v>1307</v>
       </c>
       <c r="I18" t="n">
-        <v>47236</v>
+        <v>48213</v>
       </c>
       <c r="J18" t="n">
-        <v>48661</v>
+        <v>48737</v>
       </c>
       <c r="K18" t="n">
-        <v>49066</v>
+        <v>49125</v>
       </c>
       <c r="L18" t="n">
-        <v>49471</v>
+        <v>49513</v>
       </c>
       <c r="M18" t="n">
-        <v>50386</v>
+        <v>49969</v>
       </c>
       <c r="N18" t="n">
-        <v>51301</v>
+        <v>50425</v>
       </c>
       <c r="O18" t="n">
-        <v>51196</v>
+        <v>50745</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
       </c>
-      <c r="Q18" s="6" t="n">
-        <v/>
+      <c r="Q18" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R18" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S18" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S18" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T18" s="8" t="n">
@@ -2053,74 +2053,72 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>49310</v>
+        <v>49036</v>
       </c>
       <c r="C19" t="n">
-        <v>49795</v>
+        <v>49644</v>
       </c>
       <c r="D19" t="n">
-        <v>48488</v>
+        <v>48571</v>
       </c>
       <c r="E19" t="n">
-        <v>49263</v>
+        <v>49008</v>
       </c>
       <c r="F19" t="n">
-        <v>-284</v>
+        <v>-255</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-0.0057</v>
+        <v>-0.0052</v>
       </c>
       <c r="H19" t="n">
-        <v>1307</v>
+        <v>1073</v>
       </c>
       <c r="I19" t="n">
-        <v>48213</v>
+        <v>47181</v>
       </c>
       <c r="J19" t="n">
-        <v>48737</v>
+        <v>48016.75</v>
       </c>
       <c r="K19" t="n">
-        <v>49125</v>
+        <v>48609.5</v>
       </c>
       <c r="L19" t="n">
-        <v>49513</v>
+        <v>49202.25</v>
       </c>
       <c r="M19" t="n">
-        <v>49969</v>
+        <v>49916.5</v>
       </c>
       <c r="N19" t="n">
-        <v>50425</v>
+        <v>50630.75</v>
       </c>
       <c r="O19" t="n">
-        <v>50745</v>
+        <v>51102</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
       </c>
-      <c r="Q19" s="6" t="inlineStr">
+      <c r="Q19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R19" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R19" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
       <c r="S19" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T19" s="8" t="n">
@@ -2139,57 +2137,57 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>49036</v>
+        <v>48864</v>
       </c>
       <c r="C20" t="n">
-        <v>49644</v>
+        <v>50263</v>
       </c>
       <c r="D20" t="n">
-        <v>48571</v>
+        <v>48506</v>
       </c>
       <c r="E20" t="n">
-        <v>49008</v>
+        <v>50205</v>
       </c>
       <c r="F20" t="n">
-        <v>-255</v>
+        <v>1197</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-0.0052</v>
+        <v>0.0244</v>
       </c>
       <c r="H20" t="n">
-        <v>1073</v>
+        <v>1757</v>
       </c>
       <c r="I20" t="n">
-        <v>47181</v>
+        <v>47498</v>
       </c>
       <c r="J20" t="n">
-        <v>48016.75</v>
+        <v>47885.25</v>
       </c>
       <c r="K20" t="n">
-        <v>48609.5</v>
+        <v>48471.5</v>
       </c>
       <c r="L20" t="n">
-        <v>49202.25</v>
+        <v>49057.75</v>
       </c>
       <c r="M20" t="n">
-        <v>49916.5</v>
+        <v>49544.5</v>
       </c>
       <c r="N20" t="n">
-        <v>50630.75</v>
+        <v>50031.25</v>
       </c>
       <c r="O20" t="n">
-        <v>51102</v>
+        <v>50717</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2197,21 +2195,23 @@
       <c r="Q20" s="6" t="n">
         <v/>
       </c>
-      <c r="R20" s="6" t="inlineStr">
+      <c r="R20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S20" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S20" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U20" s="8" t="n">
-        <v/>
+      <c r="U20" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V20" s="8" t="n">
         <v/>
@@ -2223,57 +2223,57 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>48864</v>
+        <v>50240</v>
       </c>
       <c r="C21" t="n">
-        <v>50263</v>
+        <v>50611</v>
       </c>
       <c r="D21" t="n">
-        <v>48506</v>
+        <v>49155</v>
       </c>
       <c r="E21" t="n">
-        <v>50205</v>
+        <v>49569</v>
       </c>
       <c r="F21" t="n">
-        <v>1197</v>
+        <v>-636</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.0244</v>
+        <v>-0.0127</v>
       </c>
       <c r="H21" t="n">
-        <v>1757</v>
+        <v>1456</v>
       </c>
       <c r="I21" t="n">
-        <v>47498</v>
+        <v>46749</v>
       </c>
       <c r="J21" t="n">
-        <v>47885.25</v>
+        <v>48858.25</v>
       </c>
       <c r="K21" t="n">
-        <v>48471.5</v>
+        <v>49326.5</v>
       </c>
       <c r="L21" t="n">
-        <v>49057.75</v>
+        <v>49794.75</v>
       </c>
       <c r="M21" t="n">
-        <v>49544.5</v>
+        <v>51083.5</v>
       </c>
       <c r="N21" t="n">
-        <v>50031.25</v>
+        <v>52372.25</v>
       </c>
       <c r="O21" t="n">
-        <v>50717</v>
+        <v>52020</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2281,23 +2281,21 @@
       <c r="Q21" s="6" t="n">
         <v/>
       </c>
-      <c r="R21" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S21" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="inlineStr">
+      <c r="R21" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U21" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S21" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U21" s="8" t="n">
+        <v/>
       </c>
       <c r="V21" s="8" t="n">
         <v/>
@@ -2316,50 +2314,50 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>50240</v>
+        <v>49549</v>
       </c>
       <c r="C22" t="n">
-        <v>50611</v>
+        <v>49967</v>
       </c>
       <c r="D22" t="n">
-        <v>49155</v>
+        <v>49204</v>
       </c>
       <c r="E22" t="n">
-        <v>49569</v>
+        <v>49674</v>
       </c>
       <c r="F22" t="n">
-        <v>-636</v>
+        <v>105</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.0127</v>
+        <v>0.0021</v>
       </c>
       <c r="H22" t="n">
-        <v>1456</v>
+        <v>763</v>
       </c>
       <c r="I22" t="n">
-        <v>46749</v>
+        <v>47699</v>
       </c>
       <c r="J22" t="n">
-        <v>48858.25</v>
+        <v>47956</v>
       </c>
       <c r="K22" t="n">
-        <v>49326.5</v>
+        <v>48841</v>
       </c>
       <c r="L22" t="n">
-        <v>49794.75</v>
+        <v>49726</v>
       </c>
       <c r="M22" t="n">
-        <v>51083.5</v>
+        <v>50297</v>
       </c>
       <c r="N22" t="n">
-        <v>52372.25</v>
+        <v>50868</v>
       </c>
       <c r="O22" t="n">
-        <v>52020</v>
+        <v>52067</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2367,10 +2365,8 @@
       <c r="Q22" s="6" t="n">
         <v/>
       </c>
-      <c r="R22" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R22" s="6" t="n">
+        <v/>
       </c>
       <c r="S22" s="10" t="inlineStr">
         <is>
@@ -2400,63 +2396,67 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>49549</v>
+        <v>49642</v>
       </c>
       <c r="C23" t="n">
-        <v>49967</v>
+        <v>49872</v>
       </c>
       <c r="D23" t="n">
-        <v>49204</v>
+        <v>48699</v>
       </c>
       <c r="E23" t="n">
-        <v>49674</v>
+        <v>49000</v>
       </c>
       <c r="F23" t="n">
-        <v>105</v>
+        <v>-674</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.0021</v>
+        <v>-0.0136</v>
       </c>
       <c r="H23" t="n">
-        <v>763</v>
+        <v>1173</v>
       </c>
       <c r="I23" t="n">
-        <v>47699</v>
+        <v>48441</v>
       </c>
       <c r="J23" t="n">
-        <v>47956</v>
+        <v>48955.25</v>
       </c>
       <c r="K23" t="n">
-        <v>48841</v>
+        <v>49292.5</v>
       </c>
       <c r="L23" t="n">
-        <v>49726</v>
+        <v>49629.75</v>
       </c>
       <c r="M23" t="n">
-        <v>50297</v>
+        <v>50055.5</v>
       </c>
       <c r="N23" t="n">
-        <v>50868</v>
+        <v>50481.25</v>
       </c>
       <c r="O23" t="n">
-        <v>52067</v>
+        <v>50730</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
       </c>
-      <c r="Q23" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R23" s="6" t="n">
-        <v/>
+      <c r="Q23" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R23" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S23" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T23" s="8" t="n">
@@ -2475,64 +2475,66 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>49642</v>
+        <v>48451</v>
       </c>
       <c r="C24" t="n">
-        <v>49872</v>
+        <v>49121</v>
       </c>
       <c r="D24" t="n">
-        <v>48699</v>
+        <v>47025</v>
       </c>
       <c r="E24" t="n">
-        <v>49000</v>
+        <v>47517</v>
       </c>
       <c r="F24" t="n">
-        <v>-674</v>
+        <v>-1483</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-0.0136</v>
+        <v>-0.0303</v>
       </c>
       <c r="H24" t="n">
-        <v>1173</v>
+        <v>2096</v>
       </c>
       <c r="I24" t="n">
-        <v>48441</v>
+        <v>47526</v>
       </c>
       <c r="J24" t="n">
-        <v>48955.25</v>
+        <v>47684.25</v>
       </c>
       <c r="K24" t="n">
-        <v>49292.5</v>
+        <v>48413.5</v>
       </c>
       <c r="L24" t="n">
-        <v>49629.75</v>
+        <v>49142.75</v>
       </c>
       <c r="M24" t="n">
-        <v>50055.5</v>
+        <v>49586.5</v>
       </c>
       <c r="N24" t="n">
-        <v>50481.25</v>
+        <v>50030.25</v>
       </c>
       <c r="O24" t="n">
-        <v>50730</v>
-      </c>
-      <c r="P24" s="6" t="n">
-        <v/>
+        <v>51045</v>
+      </c>
+      <c r="P24" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q24" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="R24" s="6" t="inlineStr">
@@ -2554,78 +2556,70 @@
       <c r="V24" s="8" t="n">
         <v/>
       </c>
-      <c r="W24" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W24" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>48451</v>
+        <v>47177</v>
       </c>
       <c r="C25" t="n">
-        <v>49121</v>
+        <v>48266</v>
       </c>
       <c r="D25" t="n">
-        <v>47025</v>
+        <v>46333</v>
       </c>
       <c r="E25" t="n">
-        <v>47517</v>
+        <v>46592</v>
       </c>
       <c r="F25" t="n">
-        <v>-1483</v>
+        <v>-925</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.0303</v>
+        <v>-0.0195</v>
       </c>
       <c r="H25" t="n">
-        <v>2096</v>
+        <v>1933</v>
       </c>
       <c r="I25" t="n">
-        <v>47526</v>
+        <v>44929</v>
       </c>
       <c r="J25" t="n">
-        <v>47684.25</v>
+        <v>45143</v>
       </c>
       <c r="K25" t="n">
-        <v>48413.5</v>
+        <v>46469</v>
       </c>
       <c r="L25" t="n">
-        <v>49142.75</v>
+        <v>47795</v>
       </c>
       <c r="M25" t="n">
-        <v>49586.5</v>
+        <v>48565</v>
       </c>
       <c r="N25" t="n">
-        <v>50030.25</v>
+        <v>49335</v>
       </c>
       <c r="O25" t="n">
-        <v>51045</v>
-      </c>
-      <c r="P25" s="6" t="inlineStr">
+        <v>51217</v>
+      </c>
+      <c r="P25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R25" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="Q25" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R25" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S25" s="10" t="inlineStr">
@@ -2652,50 +2646,50 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>47177</v>
+        <v>46392</v>
       </c>
       <c r="C26" t="n">
-        <v>48266</v>
+        <v>47457</v>
       </c>
       <c r="D26" t="n">
-        <v>46333</v>
+        <v>45713</v>
       </c>
       <c r="E26" t="n">
-        <v>46592</v>
+        <v>45897</v>
       </c>
       <c r="F26" t="n">
-        <v>-925</v>
+        <v>-695</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.0195</v>
+        <v>-0.0149</v>
       </c>
       <c r="H26" t="n">
-        <v>1933</v>
+        <v>1744</v>
       </c>
       <c r="I26" t="n">
-        <v>44929</v>
+        <v>44400</v>
       </c>
       <c r="J26" t="n">
-        <v>45143</v>
+        <v>44305.25</v>
       </c>
       <c r="K26" t="n">
-        <v>46469</v>
+        <v>45625.5</v>
       </c>
       <c r="L26" t="n">
-        <v>47795</v>
+        <v>46945.75</v>
       </c>
       <c r="M26" t="n">
-        <v>48565</v>
+        <v>47558.5</v>
       </c>
       <c r="N26" t="n">
-        <v>49335</v>
+        <v>48171.25</v>
       </c>
       <c r="O26" t="n">
-        <v>51217</v>
+        <v>50199</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2732,50 +2726,50 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>46392</v>
+        <v>45605</v>
       </c>
       <c r="C27" t="n">
-        <v>47457</v>
+        <v>47210</v>
       </c>
       <c r="D27" t="n">
-        <v>45713</v>
+        <v>45272</v>
       </c>
       <c r="E27" t="n">
-        <v>45897</v>
+        <v>45424</v>
       </c>
       <c r="F27" t="n">
-        <v>-695</v>
+        <v>-473</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.0149</v>
+        <v>-0.0103</v>
       </c>
       <c r="H27" t="n">
-        <v>1744</v>
+        <v>1938</v>
       </c>
       <c r="I27" t="n">
-        <v>44400</v>
+        <v>43969</v>
       </c>
       <c r="J27" t="n">
-        <v>44305.25</v>
+        <v>43809</v>
       </c>
       <c r="K27" t="n">
-        <v>45625.5</v>
+        <v>45025</v>
       </c>
       <c r="L27" t="n">
-        <v>46945.75</v>
+        <v>46241</v>
       </c>
       <c r="M27" t="n">
-        <v>47558.5</v>
+        <v>46769</v>
       </c>
       <c r="N27" t="n">
-        <v>48171.25</v>
+        <v>47297</v>
       </c>
       <c r="O27" t="n">
-        <v>50199</v>
+        <v>49201</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2793,8 +2787,10 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T27" s="8" t="n">
-        <v/>
+      <c r="T27" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U27" s="8" t="n">
         <v/>
@@ -2812,50 +2808,50 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>45605</v>
+        <v>45244</v>
       </c>
       <c r="C28" t="n">
-        <v>47210</v>
+        <v>47090</v>
       </c>
       <c r="D28" t="n">
-        <v>45272</v>
+        <v>45052</v>
       </c>
       <c r="E28" t="n">
-        <v>45424</v>
+        <v>46629</v>
       </c>
       <c r="F28" t="n">
-        <v>-473</v>
+        <v>1205</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.0103</v>
+        <v>0.0265</v>
       </c>
       <c r="H28" t="n">
-        <v>1938</v>
+        <v>2038</v>
       </c>
       <c r="I28" t="n">
-        <v>43969</v>
+        <v>43334</v>
       </c>
       <c r="J28" t="n">
-        <v>43809</v>
+        <v>43077.5</v>
       </c>
       <c r="K28" t="n">
-        <v>45025</v>
+        <v>44455</v>
       </c>
       <c r="L28" t="n">
-        <v>46241</v>
+        <v>45832.5</v>
       </c>
       <c r="M28" t="n">
-        <v>46769</v>
+        <v>46393</v>
       </c>
       <c r="N28" t="n">
-        <v>47297</v>
+        <v>46953.5</v>
       </c>
       <c r="O28" t="n">
-        <v>49201</v>
+        <v>49148</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2863,24 +2859,24 @@
       <c r="Q28" s="6" t="n">
         <v/>
       </c>
-      <c r="R28" s="6" t="inlineStr">
+      <c r="R28" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S28" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S28" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="inlineStr">
+      <c r="U28" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U28" s="8" t="n">
-        <v/>
-      </c>
       <c r="V28" s="8" t="n">
         <v/>
       </c>
@@ -2889,55 +2885,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr"/>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>45244</v>
+        <v>46569</v>
       </c>
       <c r="C29" t="n">
-        <v>47090</v>
+        <v>48555</v>
       </c>
       <c r="D29" t="n">
-        <v>45052</v>
+        <v>46362</v>
       </c>
       <c r="E29" t="n">
-        <v>46629</v>
+        <v>48129</v>
       </c>
       <c r="F29" t="n">
-        <v>1205</v>
+        <v>1500</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.0265</v>
+        <v>0.0322</v>
       </c>
       <c r="H29" t="n">
-        <v>2038</v>
+        <v>2193</v>
       </c>
       <c r="I29" t="n">
-        <v>43334</v>
+        <v>43014</v>
       </c>
       <c r="J29" t="n">
-        <v>43077.5</v>
+        <v>44870</v>
       </c>
       <c r="K29" t="n">
-        <v>44455</v>
+        <v>45610</v>
       </c>
       <c r="L29" t="n">
-        <v>45832.5</v>
+        <v>46350</v>
       </c>
       <c r="M29" t="n">
-        <v>46393</v>
+        <v>47648</v>
       </c>
       <c r="N29" t="n">
-        <v>46953.5</v>
+        <v>48946</v>
       </c>
       <c r="O29" t="n">
-        <v>49148</v>
+        <v>49128</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2958,10 +2958,8 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U29" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U29" s="8" t="n">
+        <v/>
       </c>
       <c r="V29" s="8" t="n">
         <v/>
@@ -2973,57 +2971,57 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>46569</v>
+        <v>47674</v>
       </c>
       <c r="C30" t="n">
-        <v>48555</v>
+        <v>49924</v>
       </c>
       <c r="D30" t="n">
-        <v>46362</v>
+        <v>47534</v>
       </c>
       <c r="E30" t="n">
-        <v>48129</v>
+        <v>49641</v>
       </c>
       <c r="F30" t="n">
-        <v>1500</v>
+        <v>1512</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.0322</v>
+        <v>0.0314</v>
       </c>
       <c r="H30" t="n">
-        <v>2193</v>
+        <v>2390</v>
       </c>
       <c r="I30" t="n">
-        <v>43014</v>
+        <v>44169</v>
       </c>
       <c r="J30" t="n">
-        <v>44870</v>
+        <v>46271.25</v>
       </c>
       <c r="K30" t="n">
-        <v>45610</v>
+        <v>47032.5</v>
       </c>
       <c r="L30" t="n">
-        <v>46350</v>
+        <v>47793.75</v>
       </c>
       <c r="M30" t="n">
-        <v>47648</v>
+        <v>49225.5</v>
       </c>
       <c r="N30" t="n">
-        <v>48946</v>
+        <v>50657.25</v>
       </c>
       <c r="O30" t="n">
-        <v>49128</v>
+        <v>50748</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3064,50 +3062,50 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>47674</v>
+        <v>49324</v>
       </c>
       <c r="C31" t="n">
-        <v>49924</v>
+        <v>50043</v>
       </c>
       <c r="D31" t="n">
-        <v>47534</v>
+        <v>49036</v>
       </c>
       <c r="E31" t="n">
-        <v>49641</v>
+        <v>49392</v>
       </c>
       <c r="F31" t="n">
-        <v>1512</v>
+        <v>-249</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.0314</v>
+        <v>-0.005</v>
       </c>
       <c r="H31" t="n">
-        <v>2390</v>
+        <v>1007</v>
       </c>
       <c r="I31" t="n">
-        <v>44169</v>
+        <v>45144</v>
       </c>
       <c r="J31" t="n">
-        <v>46271.25</v>
+        <v>47707</v>
       </c>
       <c r="K31" t="n">
-        <v>47032.5</v>
+        <v>48446</v>
       </c>
       <c r="L31" t="n">
-        <v>47793.75</v>
+        <v>49185</v>
       </c>
       <c r="M31" t="n">
-        <v>49225.5</v>
+        <v>50836</v>
       </c>
       <c r="N31" t="n">
-        <v>50657.25</v>
+        <v>52487</v>
       </c>
       <c r="O31" t="n">
-        <v>50748</v>
+        <v>52314</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3120,13 +3118,11 @@
       </c>
       <c r="S31" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="n">
+        <v/>
       </c>
       <c r="U31" s="8" t="n">
         <v/>
@@ -3141,57 +3137,57 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>49324</v>
+        <v>49382</v>
       </c>
       <c r="C32" t="n">
-        <v>50043</v>
+        <v>50138</v>
       </c>
       <c r="D32" t="n">
-        <v>49036</v>
+        <v>48608</v>
       </c>
       <c r="E32" t="n">
-        <v>49392</v>
+        <v>49646</v>
       </c>
       <c r="F32" t="n">
-        <v>-249</v>
+        <v>254</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>-0.005</v>
+        <v>0.0051</v>
       </c>
       <c r="H32" t="n">
-        <v>1007</v>
+        <v>1530</v>
       </c>
       <c r="I32" t="n">
-        <v>45144</v>
+        <v>48029</v>
       </c>
       <c r="J32" t="n">
-        <v>47707</v>
+        <v>48311.25</v>
       </c>
       <c r="K32" t="n">
-        <v>48446</v>
+        <v>48888.5</v>
       </c>
       <c r="L32" t="n">
-        <v>49185</v>
+        <v>49465.75</v>
       </c>
       <c r="M32" t="n">
-        <v>50836</v>
+        <v>49895.5</v>
       </c>
       <c r="N32" t="n">
-        <v>52487</v>
+        <v>50325.25</v>
       </c>
       <c r="O32" t="n">
-        <v>52314</v>
+        <v>51050</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3199,16 +3195,20 @@
       <c r="Q32" s="6" t="n">
         <v/>
       </c>
-      <c r="R32" s="6" t="n">
-        <v/>
+      <c r="R32" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S32" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
       </c>
-      <c r="T32" s="8" t="n">
-        <v/>
+      <c r="T32" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U32" s="8" t="n">
         <v/>
@@ -3230,50 +3230,50 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>49382</v>
+        <v>49705</v>
       </c>
       <c r="C33" t="n">
-        <v>50138</v>
+        <v>50238</v>
       </c>
       <c r="D33" t="n">
-        <v>48608</v>
+        <v>49016</v>
       </c>
       <c r="E33" t="n">
-        <v>49646</v>
+        <v>49691</v>
       </c>
       <c r="F33" t="n">
-        <v>254</v>
+        <v>45</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0051</v>
+        <v>0.0009</v>
       </c>
       <c r="H33" t="n">
-        <v>1530</v>
+        <v>1222</v>
       </c>
       <c r="I33" t="n">
-        <v>48029</v>
+        <v>47078</v>
       </c>
       <c r="J33" t="n">
-        <v>48311.25</v>
+        <v>48252.5</v>
       </c>
       <c r="K33" t="n">
-        <v>48888.5</v>
+        <v>48881</v>
       </c>
       <c r="L33" t="n">
-        <v>49465.75</v>
+        <v>49509.5</v>
       </c>
       <c r="M33" t="n">
-        <v>49895.5</v>
+        <v>50411</v>
       </c>
       <c r="N33" t="n">
-        <v>50325.25</v>
+        <v>51312.5</v>
       </c>
       <c r="O33" t="n">
-        <v>51050</v>
+        <v>51668</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3281,20 +3281,16 @@
       <c r="Q33" s="6" t="n">
         <v/>
       </c>
-      <c r="R33" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R33" s="6" t="n">
+        <v/>
       </c>
       <c r="S33" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
       </c>
-      <c r="T33" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T33" s="8" t="n">
+        <v/>
       </c>
       <c r="U33" s="8" t="n">
         <v/>
@@ -3309,57 +3305,57 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>49705</v>
+        <v>49640</v>
       </c>
       <c r="C34" t="n">
-        <v>50238</v>
+        <v>50292</v>
       </c>
       <c r="D34" t="n">
-        <v>49016</v>
+        <v>49397</v>
       </c>
       <c r="E34" t="n">
-        <v>49691</v>
+        <v>49617</v>
       </c>
       <c r="F34" t="n">
-        <v>45</v>
+        <v>-74</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0009</v>
+        <v>-0.0015</v>
       </c>
       <c r="H34" t="n">
-        <v>1222</v>
+        <v>895</v>
       </c>
       <c r="I34" t="n">
-        <v>47078</v>
+        <v>47794</v>
       </c>
       <c r="J34" t="n">
-        <v>48252.5</v>
+        <v>48501</v>
       </c>
       <c r="K34" t="n">
-        <v>48881</v>
+        <v>49080</v>
       </c>
       <c r="L34" t="n">
-        <v>49509.5</v>
+        <v>49659</v>
       </c>
       <c r="M34" t="n">
-        <v>50411</v>
+        <v>50302</v>
       </c>
       <c r="N34" t="n">
-        <v>51312.5</v>
+        <v>50945</v>
       </c>
       <c r="O34" t="n">
-        <v>51668</v>
+        <v>51460</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3370,9 +3366,9 @@
       <c r="R34" s="6" t="n">
         <v/>
       </c>
-      <c r="S34" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S34" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T34" s="8" t="n">
@@ -3391,57 +3387,57 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>49640</v>
+        <v>49464</v>
       </c>
       <c r="C35" t="n">
-        <v>50292</v>
+        <v>50920</v>
       </c>
       <c r="D35" t="n">
-        <v>49397</v>
+        <v>49152</v>
       </c>
       <c r="E35" t="n">
-        <v>49617</v>
+        <v>50662</v>
       </c>
       <c r="F35" t="n">
-        <v>-74</v>
+        <v>1045</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>-0.0015</v>
+        <v>0.0211</v>
       </c>
       <c r="H35" t="n">
-        <v>895</v>
+        <v>1768</v>
       </c>
       <c r="I35" t="n">
-        <v>47794</v>
+        <v>48502</v>
       </c>
       <c r="J35" t="n">
-        <v>48501</v>
+        <v>48608.25</v>
       </c>
       <c r="K35" t="n">
-        <v>49080</v>
+        <v>49169.5</v>
       </c>
       <c r="L35" t="n">
-        <v>49659</v>
+        <v>49730.75</v>
       </c>
       <c r="M35" t="n">
-        <v>50302</v>
+        <v>50064.5</v>
       </c>
       <c r="N35" t="n">
-        <v>50945</v>
+        <v>50398.25</v>
       </c>
       <c r="O35" t="n">
-        <v>51460</v>
+        <v>51187</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3449,81 +3445,87 @@
       <c r="Q35" s="6" t="n">
         <v/>
       </c>
-      <c r="R35" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S35" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U35" s="8" t="n">
-        <v/>
+      <c r="R35" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S35" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U35" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V35" s="8" t="n">
         <v/>
       </c>
-      <c r="W35" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W35" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>49464</v>
+        <v>50776</v>
       </c>
       <c r="C36" t="n">
-        <v>50920</v>
+        <v>51209</v>
       </c>
       <c r="D36" t="n">
-        <v>49152</v>
+        <v>50386</v>
       </c>
       <c r="E36" t="n">
-        <v>50662</v>
+        <v>51077</v>
       </c>
       <c r="F36" t="n">
-        <v>1045</v>
+        <v>415</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.0211</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="H36" t="n">
-        <v>1768</v>
+        <v>823</v>
       </c>
       <c r="I36" t="n">
-        <v>48502</v>
+        <v>47384</v>
       </c>
       <c r="J36" t="n">
-        <v>48608.25</v>
+        <v>49207</v>
       </c>
       <c r="K36" t="n">
-        <v>49169.5</v>
+        <v>49778</v>
       </c>
       <c r="L36" t="n">
-        <v>49730.75</v>
+        <v>50349</v>
       </c>
       <c r="M36" t="n">
-        <v>50064.5</v>
+        <v>51546</v>
       </c>
       <c r="N36" t="n">
-        <v>50398.25</v>
+        <v>52743</v>
       </c>
       <c r="O36" t="n">
-        <v>51187</v>
+        <v>52688</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3531,10 +3533,8 @@
       <c r="Q36" s="6" t="n">
         <v/>
       </c>
-      <c r="R36" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R36" s="6" t="n">
+        <v/>
       </c>
       <c r="S36" s="7" t="inlineStr">
         <is>
@@ -3543,14 +3543,12 @@
       </c>
       <c r="T36" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U36" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U36" s="8" t="n">
+        <v/>
+      </c>
       <c r="V36" s="8" t="n">
         <v/>
       </c>
@@ -3559,59 +3557,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>50776</v>
+        <v>51128</v>
       </c>
       <c r="C37" t="n">
-        <v>51209</v>
+        <v>51849</v>
       </c>
       <c r="D37" t="n">
-        <v>50386</v>
+        <v>50736</v>
       </c>
       <c r="E37" t="n">
-        <v>51077</v>
+        <v>50936</v>
       </c>
       <c r="F37" t="n">
-        <v>415</v>
+        <v>-141</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.008200000000000001</v>
+        <v>-0.0028</v>
       </c>
       <c r="H37" t="n">
-        <v>823</v>
+        <v>1113</v>
       </c>
       <c r="I37" t="n">
-        <v>47384</v>
+        <v>49563</v>
       </c>
       <c r="J37" t="n">
-        <v>49207</v>
+        <v>50393.75</v>
       </c>
       <c r="K37" t="n">
-        <v>49778</v>
+        <v>50665.5</v>
       </c>
       <c r="L37" t="n">
-        <v>50349</v>
+        <v>50937.25</v>
       </c>
       <c r="M37" t="n">
-        <v>51546</v>
+        <v>51488.5</v>
       </c>
       <c r="N37" t="n">
-        <v>52743</v>
+        <v>52039.75</v>
       </c>
       <c r="O37" t="n">
-        <v>52688</v>
+        <v>52032</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3622,14 +3616,14 @@
       <c r="R37" s="6" t="n">
         <v/>
       </c>
-      <c r="S37" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S37" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T37" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U37" s="8" t="n">
@@ -3643,55 +3637,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr"/>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>51128</v>
+        <v>50796</v>
       </c>
       <c r="C38" t="n">
-        <v>51849</v>
+        <v>51443</v>
       </c>
       <c r="D38" t="n">
-        <v>50736</v>
+        <v>49758</v>
       </c>
       <c r="E38" t="n">
-        <v>50936</v>
+        <v>51227</v>
       </c>
       <c r="F38" t="n">
-        <v>-141</v>
+        <v>291</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.0028</v>
+        <v>0.0057</v>
       </c>
       <c r="H38" t="n">
-        <v>1113</v>
+        <v>1685</v>
       </c>
       <c r="I38" t="n">
-        <v>49563</v>
+        <v>49623</v>
       </c>
       <c r="J38" t="n">
-        <v>50393.75</v>
+        <v>49644.75</v>
       </c>
       <c r="K38" t="n">
-        <v>50665.5</v>
+        <v>50379.5</v>
       </c>
       <c r="L38" t="n">
-        <v>50937.25</v>
+        <v>51114.25</v>
       </c>
       <c r="M38" t="n">
-        <v>51488.5</v>
+        <v>51492.5</v>
       </c>
       <c r="N38" t="n">
-        <v>52039.75</v>
+        <v>51870.75</v>
       </c>
       <c r="O38" t="n">
-        <v>52032</v>
+        <v>52962</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3699,19 +3697,19 @@
       <c r="Q38" s="6" t="n">
         <v/>
       </c>
-      <c r="R38" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S38" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="inlineStr">
+      <c r="R38" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="S38" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="n">
+        <v/>
+      </c>
       <c r="U38" s="8" t="n">
         <v/>
       </c>
@@ -3725,57 +3723,57 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>50796</v>
+        <v>51450</v>
       </c>
       <c r="C39" t="n">
-        <v>51443</v>
+        <v>52300</v>
       </c>
       <c r="D39" t="n">
-        <v>49758</v>
+        <v>51420</v>
       </c>
       <c r="E39" t="n">
-        <v>51227</v>
+        <v>51888</v>
       </c>
       <c r="F39" t="n">
-        <v>291</v>
+        <v>661</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.0057</v>
+        <v>0.0129</v>
       </c>
       <c r="H39" t="n">
-        <v>1685</v>
+        <v>880</v>
       </c>
       <c r="I39" t="n">
-        <v>49623</v>
+        <v>48073</v>
       </c>
       <c r="J39" t="n">
-        <v>49644.75</v>
+        <v>49855.25</v>
       </c>
       <c r="K39" t="n">
-        <v>50379.5</v>
+        <v>50384.5</v>
       </c>
       <c r="L39" t="n">
-        <v>51114.25</v>
+        <v>50913.75</v>
       </c>
       <c r="M39" t="n">
-        <v>51492.5</v>
+        <v>52069.5</v>
       </c>
       <c r="N39" t="n">
-        <v>51870.75</v>
+        <v>53225.25</v>
       </c>
       <c r="O39" t="n">
-        <v>52962</v>
+        <v>53128</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3783,18 +3781,18 @@
       <c r="Q39" s="6" t="n">
         <v/>
       </c>
-      <c r="R39" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R39" s="6" t="n">
+        <v/>
       </c>
       <c r="S39" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U39" s="8" t="n">
         <v/>
@@ -3807,59 +3805,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>51450</v>
+        <v>51870</v>
       </c>
       <c r="C40" t="n">
-        <v>52300</v>
+        <v>53097</v>
       </c>
       <c r="D40" t="n">
-        <v>51420</v>
+        <v>51691</v>
       </c>
       <c r="E40" t="n">
-        <v>51888</v>
+        <v>52209</v>
       </c>
       <c r="F40" t="n">
-        <v>661</v>
+        <v>321</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.0129</v>
+        <v>0.0062</v>
       </c>
       <c r="H40" t="n">
-        <v>880</v>
+        <v>1406</v>
       </c>
       <c r="I40" t="n">
-        <v>48073</v>
+        <v>50540</v>
       </c>
       <c r="J40" t="n">
-        <v>49855.25</v>
+        <v>51022</v>
       </c>
       <c r="K40" t="n">
-        <v>50384.5</v>
+        <v>51448</v>
       </c>
       <c r="L40" t="n">
-        <v>50913.75</v>
+        <v>51874</v>
       </c>
       <c r="M40" t="n">
-        <v>52069.5</v>
+        <v>52328</v>
       </c>
       <c r="N40" t="n">
-        <v>53225.25</v>
+        <v>52782</v>
       </c>
       <c r="O40" t="n">
-        <v>53128</v>
+        <v>53180</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3880,8 +3874,10 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U40" s="8" t="n">
-        <v/>
+      <c r="U40" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V40" s="8" t="n">
         <v/>
@@ -3896,50 +3892,50 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>51870</v>
+        <v>52183</v>
       </c>
       <c r="C41" t="n">
-        <v>53097</v>
+        <v>53400</v>
       </c>
       <c r="D41" t="n">
-        <v>51691</v>
+        <v>52179</v>
       </c>
       <c r="E41" t="n">
-        <v>52209</v>
+        <v>53162</v>
       </c>
       <c r="F41" t="n">
-        <v>321</v>
+        <v>953</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.0062</v>
+        <v>0.0183</v>
       </c>
       <c r="H41" t="n">
-        <v>1406</v>
+        <v>1221</v>
       </c>
       <c r="I41" t="n">
-        <v>50540</v>
+        <v>50285</v>
       </c>
       <c r="J41" t="n">
-        <v>51022</v>
+        <v>50710.5</v>
       </c>
       <c r="K41" t="n">
-        <v>51448</v>
+        <v>51506</v>
       </c>
       <c r="L41" t="n">
-        <v>51874</v>
+        <v>52301.5</v>
       </c>
       <c r="M41" t="n">
-        <v>52328</v>
+        <v>52912</v>
       </c>
       <c r="N41" t="n">
-        <v>52782</v>
+        <v>53522.5</v>
       </c>
       <c r="O41" t="n">
-        <v>53180</v>
+        <v>54503</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3960,10 +3956,8 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U41" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U41" s="8" t="n">
+        <v/>
       </c>
       <c r="V41" s="8" t="n">
         <v/>
@@ -3978,50 +3972,50 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>52183</v>
+        <v>53230</v>
       </c>
       <c r="C42" t="n">
-        <v>53400</v>
+        <v>53656</v>
       </c>
       <c r="D42" t="n">
-        <v>52179</v>
+        <v>52343</v>
       </c>
       <c r="E42" t="n">
-        <v>53162</v>
+        <v>52906</v>
       </c>
       <c r="F42" t="n">
-        <v>953</v>
+        <v>-256</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.0183</v>
+        <v>-0.0048</v>
       </c>
       <c r="H42" t="n">
-        <v>1221</v>
+        <v>1313</v>
       </c>
       <c r="I42" t="n">
-        <v>50285</v>
+        <v>50958</v>
       </c>
       <c r="J42" t="n">
-        <v>50710.5</v>
+        <v>52127.25</v>
       </c>
       <c r="K42" t="n">
-        <v>51506</v>
+        <v>52551.5</v>
       </c>
       <c r="L42" t="n">
-        <v>52301.5</v>
+        <v>52975.75</v>
       </c>
       <c r="M42" t="n">
-        <v>52912</v>
+        <v>53772.5</v>
       </c>
       <c r="N42" t="n">
-        <v>53522.5</v>
+        <v>54569.25</v>
       </c>
       <c r="O42" t="n">
-        <v>54503</v>
+        <v>54621</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4029,18 +4023,18 @@
       <c r="Q42" s="6" t="n">
         <v/>
       </c>
-      <c r="R42" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S42" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R42" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S42" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="n">
+        <v/>
       </c>
       <c r="U42" s="8" t="n">
         <v/>
@@ -4053,55 +4047,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr"/>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>53230</v>
+        <v>52844</v>
       </c>
       <c r="C43" t="n">
-        <v>53656</v>
+        <v>53113</v>
       </c>
       <c r="D43" t="n">
-        <v>52343</v>
+        <v>52174</v>
       </c>
       <c r="E43" t="n">
-        <v>52906</v>
+        <v>52375</v>
       </c>
       <c r="F43" t="n">
-        <v>-256</v>
+        <v>-531</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.0048</v>
+        <v>-0.01</v>
       </c>
       <c r="H43" t="n">
-        <v>1313</v>
+        <v>939</v>
       </c>
       <c r="I43" t="n">
-        <v>50958</v>
+        <v>51030</v>
       </c>
       <c r="J43" t="n">
-        <v>52127.25</v>
+        <v>51546.25</v>
       </c>
       <c r="K43" t="n">
-        <v>52551.5</v>
+        <v>52249.5</v>
       </c>
       <c r="L43" t="n">
-        <v>52975.75</v>
+        <v>52952.75</v>
       </c>
       <c r="M43" t="n">
-        <v>53772.5</v>
+        <v>53562.5</v>
       </c>
       <c r="N43" t="n">
-        <v>54569.25</v>
+        <v>54172.25</v>
       </c>
       <c r="O43" t="n">
-        <v>54621</v>
+        <v>54969</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4111,12 +4109,12 @@
       </c>
       <c r="R43" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S43" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T43" s="8" t="n">
@@ -4135,57 +4133,57 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>52844</v>
+        <v>52300</v>
       </c>
       <c r="C44" t="n">
-        <v>53113</v>
+        <v>52721</v>
       </c>
       <c r="D44" t="n">
-        <v>52174</v>
+        <v>51720</v>
       </c>
       <c r="E44" t="n">
-        <v>52375</v>
+        <v>52124</v>
       </c>
       <c r="F44" t="n">
-        <v>-531</v>
+        <v>-251</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.01</v>
+        <v>-0.0048</v>
       </c>
       <c r="H44" t="n">
-        <v>939</v>
+        <v>1001</v>
       </c>
       <c r="I44" t="n">
-        <v>51030</v>
+        <v>51235</v>
       </c>
       <c r="J44" t="n">
-        <v>51546.25</v>
+        <v>51301.75</v>
       </c>
       <c r="K44" t="n">
-        <v>52249.5</v>
+        <v>51905.5</v>
       </c>
       <c r="L44" t="n">
-        <v>52952.75</v>
+        <v>52509.25</v>
       </c>
       <c r="M44" t="n">
-        <v>53562.5</v>
+        <v>52844.5</v>
       </c>
       <c r="N44" t="n">
-        <v>54172.25</v>
+        <v>53179.75</v>
       </c>
       <c r="O44" t="n">
-        <v>54969</v>
+        <v>54052</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4226,50 +4224,50 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>52300</v>
+        <v>52299</v>
       </c>
       <c r="C45" t="n">
-        <v>52721</v>
+        <v>53105</v>
       </c>
       <c r="D45" t="n">
-        <v>51720</v>
+        <v>51630</v>
       </c>
       <c r="E45" t="n">
-        <v>52124</v>
+        <v>52635</v>
       </c>
       <c r="F45" t="n">
-        <v>-251</v>
+        <v>511</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>-0.0048</v>
+        <v>0.0098</v>
       </c>
       <c r="H45" t="n">
-        <v>1001</v>
+        <v>1475</v>
       </c>
       <c r="I45" t="n">
-        <v>51235</v>
+        <v>50719</v>
       </c>
       <c r="J45" t="n">
-        <v>51301.75</v>
+        <v>51074.75</v>
       </c>
       <c r="K45" t="n">
-        <v>51905.5</v>
+        <v>51623.5</v>
       </c>
       <c r="L45" t="n">
-        <v>52509.25</v>
+        <v>52172.25</v>
       </c>
       <c r="M45" t="n">
-        <v>52844.5</v>
+        <v>52624.5</v>
       </c>
       <c r="N45" t="n">
-        <v>53179.75</v>
+        <v>53076.75</v>
       </c>
       <c r="O45" t="n">
-        <v>54052</v>
+        <v>53722</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4277,21 +4275,23 @@
       <c r="Q45" s="6" t="n">
         <v/>
       </c>
-      <c r="R45" s="6" t="inlineStr">
+      <c r="R45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S45" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S45" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U45" s="8" t="n">
-        <v/>
+      <c r="U45" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V45" s="8" t="n">
         <v/>
@@ -4303,57 +4303,57 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>52299</v>
+        <v>52780</v>
       </c>
       <c r="C46" t="n">
-        <v>53105</v>
+        <v>54884</v>
       </c>
       <c r="D46" t="n">
-        <v>51630</v>
+        <v>52777</v>
       </c>
       <c r="E46" t="n">
-        <v>52635</v>
+        <v>54152</v>
       </c>
       <c r="F46" t="n">
-        <v>511</v>
+        <v>1517</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.0098</v>
+        <v>0.0288</v>
       </c>
       <c r="H46" t="n">
-        <v>1475</v>
+        <v>2107</v>
       </c>
       <c r="I46" t="n">
-        <v>50719</v>
+        <v>50155</v>
       </c>
       <c r="J46" t="n">
-        <v>51074.75</v>
+        <v>51293.75</v>
       </c>
       <c r="K46" t="n">
-        <v>51623.5</v>
+        <v>51897.5</v>
       </c>
       <c r="L46" t="n">
-        <v>52172.25</v>
+        <v>52501.25</v>
       </c>
       <c r="M46" t="n">
-        <v>52624.5</v>
+        <v>53372.5</v>
       </c>
       <c r="N46" t="n">
-        <v>53076.75</v>
+        <v>54243.75</v>
       </c>
       <c r="O46" t="n">
-        <v>53722</v>
+        <v>54580</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4371,75 +4371,73 @@
       </c>
       <c r="T46" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U46" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U46" s="8" t="inlineStr">
+      <c r="V46" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="V46" s="8" t="n">
-        <v/>
-      </c>
       <c r="W46" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>52780</v>
+        <v>54133</v>
       </c>
       <c r="C47" t="n">
-        <v>54884</v>
+        <v>54336</v>
       </c>
       <c r="D47" t="n">
-        <v>52777</v>
+        <v>53715</v>
       </c>
       <c r="E47" t="n">
-        <v>54152</v>
+        <v>53807</v>
       </c>
       <c r="F47" t="n">
-        <v>1517</v>
+        <v>-345</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.0288</v>
+        <v>-0.0064</v>
       </c>
       <c r="H47" t="n">
-        <v>2107</v>
+        <v>621</v>
       </c>
       <c r="I47" t="n">
-        <v>50155</v>
+        <v>50670</v>
       </c>
       <c r="J47" t="n">
-        <v>51293.75</v>
+        <v>52205.75</v>
       </c>
       <c r="K47" t="n">
-        <v>51897.5</v>
+        <v>53098.5</v>
       </c>
       <c r="L47" t="n">
-        <v>52501.25</v>
+        <v>53991.25</v>
       </c>
       <c r="M47" t="n">
-        <v>53372.5</v>
+        <v>55205.5</v>
       </c>
       <c r="N47" t="n">
-        <v>54243.75</v>
+        <v>56419.75</v>
       </c>
       <c r="O47" t="n">
-        <v>54580</v>
+        <v>56991</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4450,93 +4448,97 @@
       <c r="R47" s="6" t="n">
         <v/>
       </c>
-      <c r="S47" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U47" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V47" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S47" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U47" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V47" s="8" t="n">
+        <v/>
       </c>
       <c r="W47" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr"/>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>54133</v>
+        <v>53790</v>
       </c>
       <c r="C48" t="n">
-        <v>54336</v>
+        <v>53840</v>
       </c>
       <c r="D48" t="n">
-        <v>53715</v>
+        <v>52812</v>
       </c>
       <c r="E48" t="n">
-        <v>53807</v>
+        <v>53353</v>
       </c>
       <c r="F48" t="n">
-        <v>-345</v>
+        <v>-454</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0.0064</v>
+        <v>-0.008399999999999999</v>
       </c>
       <c r="H48" t="n">
-        <v>621</v>
+        <v>1028</v>
       </c>
       <c r="I48" t="n">
-        <v>50670</v>
+        <v>53094</v>
       </c>
       <c r="J48" t="n">
-        <v>52205.75</v>
+        <v>53076.75</v>
       </c>
       <c r="K48" t="n">
-        <v>53098.5</v>
+        <v>53496.5</v>
       </c>
       <c r="L48" t="n">
-        <v>53991.25</v>
+        <v>53916.25</v>
       </c>
       <c r="M48" t="n">
-        <v>55205.5</v>
+        <v>54117.5</v>
       </c>
       <c r="N48" t="n">
-        <v>56419.75</v>
+        <v>54318.75</v>
       </c>
       <c r="O48" t="n">
-        <v>56991</v>
-      </c>
-      <c r="P48" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q48" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R48" s="6" t="n">
-        <v/>
+        <v>54957</v>
+      </c>
+      <c r="P48" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q48" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R48" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S48" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T48" s="8" t="n">
@@ -4555,76 +4557,70 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>53790</v>
+        <v>53367</v>
       </c>
       <c r="C49" t="n">
-        <v>53840</v>
+        <v>53862</v>
       </c>
       <c r="D49" t="n">
-        <v>52812</v>
+        <v>53210</v>
       </c>
       <c r="E49" t="n">
-        <v>53353</v>
+        <v>53584</v>
       </c>
       <c r="F49" t="n">
-        <v>-454</v>
+        <v>231</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.008399999999999999</v>
+        <v>0.0043</v>
       </c>
       <c r="H49" t="n">
-        <v>1028</v>
+        <v>652</v>
       </c>
       <c r="I49" t="n">
-        <v>53094</v>
+        <v>51784</v>
       </c>
       <c r="J49" t="n">
-        <v>53076.75</v>
+        <v>52338.5</v>
       </c>
       <c r="K49" t="n">
-        <v>53496.5</v>
+        <v>52839</v>
       </c>
       <c r="L49" t="n">
-        <v>53916.25</v>
+        <v>53339.5</v>
       </c>
       <c r="M49" t="n">
-        <v>54117.5</v>
+        <v>53867</v>
       </c>
       <c r="N49" t="n">
-        <v>54318.75</v>
+        <v>54394.5</v>
       </c>
       <c r="O49" t="n">
-        <v>54957</v>
-      </c>
-      <c r="P49" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q49" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R49" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S49" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>54868</v>
+      </c>
+      <c r="P49" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q49" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R49" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S49" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T49" s="8" t="n">
@@ -4641,72 +4637,72 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>53367</v>
+        <v>53664</v>
       </c>
       <c r="C50" t="n">
-        <v>53862</v>
+        <v>53827</v>
       </c>
       <c r="D50" t="n">
-        <v>53210</v>
+        <v>52720</v>
       </c>
       <c r="E50" t="n">
-        <v>53584</v>
+        <v>53440</v>
       </c>
       <c r="F50" t="n">
-        <v>231</v>
+        <v>-144</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.0043</v>
+        <v>-0.0027</v>
       </c>
       <c r="H50" t="n">
-        <v>652</v>
+        <v>1107</v>
       </c>
       <c r="I50" t="n">
-        <v>51784</v>
+        <v>52558</v>
       </c>
       <c r="J50" t="n">
-        <v>52338.5</v>
+        <v>52956</v>
       </c>
       <c r="K50" t="n">
-        <v>52839</v>
+        <v>53258</v>
       </c>
       <c r="L50" t="n">
-        <v>53339.5</v>
+        <v>53560</v>
       </c>
       <c r="M50" t="n">
-        <v>53867</v>
+        <v>53910</v>
       </c>
       <c r="N50" t="n">
-        <v>54394.5</v>
+        <v>54260</v>
       </c>
       <c r="O50" t="n">
-        <v>54868</v>
+        <v>54514</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
       </c>
-      <c r="Q50" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R50" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S50" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="Q50" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R50" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S50" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T50" s="8" t="n">
@@ -4723,72 +4719,76 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr"/>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>53664</v>
+        <v>53261</v>
       </c>
       <c r="C51" t="n">
-        <v>53827</v>
+        <v>53336</v>
       </c>
       <c r="D51" t="n">
-        <v>52720</v>
+        <v>51992</v>
       </c>
       <c r="E51" t="n">
-        <v>53440</v>
+        <v>52585</v>
       </c>
       <c r="F51" t="n">
-        <v>-144</v>
+        <v>-855</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.0027</v>
+        <v>-0.016</v>
       </c>
       <c r="H51" t="n">
-        <v>1107</v>
+        <v>1344</v>
       </c>
       <c r="I51" t="n">
-        <v>52558</v>
+        <v>51613</v>
       </c>
       <c r="J51" t="n">
-        <v>52956</v>
+        <v>52416.25</v>
       </c>
       <c r="K51" t="n">
-        <v>53258</v>
+        <v>52886.5</v>
       </c>
       <c r="L51" t="n">
-        <v>53560</v>
+        <v>53356.75</v>
       </c>
       <c r="M51" t="n">
-        <v>53910</v>
+        <v>53993.5</v>
       </c>
       <c r="N51" t="n">
-        <v>54260</v>
+        <v>54630.25</v>
       </c>
       <c r="O51" t="n">
-        <v>54514</v>
+        <v>54934</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
       </c>
       <c r="Q51" s="6" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R51" s="6" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R51" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S51" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T51" s="8" t="n">
@@ -4814,62 +4814,60 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>53261</v>
+        <v>52376</v>
       </c>
       <c r="C52" t="n">
-        <v>53336</v>
+        <v>52672</v>
       </c>
       <c r="D52" t="n">
-        <v>51992</v>
+        <v>51209</v>
       </c>
       <c r="E52" t="n">
-        <v>52585</v>
+        <v>51761</v>
       </c>
       <c r="F52" t="n">
-        <v>-855</v>
+        <v>-824</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.016</v>
+        <v>-0.0157</v>
       </c>
       <c r="H52" t="n">
-        <v>1344</v>
+        <v>1463</v>
       </c>
       <c r="I52" t="n">
-        <v>51613</v>
+        <v>50648</v>
       </c>
       <c r="J52" t="n">
-        <v>52416.25</v>
+        <v>51201.5</v>
       </c>
       <c r="K52" t="n">
-        <v>52886.5</v>
+        <v>51913</v>
       </c>
       <c r="L52" t="n">
-        <v>53356.75</v>
+        <v>52624.5</v>
       </c>
       <c r="M52" t="n">
-        <v>53993.5</v>
+        <v>53257</v>
       </c>
       <c r="N52" t="n">
-        <v>54630.25</v>
+        <v>53889.5</v>
       </c>
       <c r="O52" t="n">
-        <v>54934</v>
+        <v>54680</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
       </c>
-      <c r="Q52" s="6" t="inlineStr">
+      <c r="Q52" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R52" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="R52" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S52" s="10" t="inlineStr">
@@ -4900,50 +4898,50 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>52376</v>
+        <v>52085</v>
       </c>
       <c r="C53" t="n">
-        <v>52672</v>
+        <v>52844</v>
       </c>
       <c r="D53" t="n">
-        <v>51209</v>
+        <v>51479</v>
       </c>
       <c r="E53" t="n">
-        <v>51761</v>
+        <v>52163</v>
       </c>
       <c r="F53" t="n">
-        <v>-824</v>
+        <v>402</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.0157</v>
+        <v>0.0078</v>
       </c>
       <c r="H53" t="n">
-        <v>1463</v>
+        <v>1365</v>
       </c>
       <c r="I53" t="n">
-        <v>50648</v>
+        <v>49746</v>
       </c>
       <c r="J53" t="n">
-        <v>51201.5</v>
+        <v>50208.25</v>
       </c>
       <c r="K53" t="n">
-        <v>51913</v>
+        <v>51029.5</v>
       </c>
       <c r="L53" t="n">
-        <v>52624.5</v>
+        <v>51850.75</v>
       </c>
       <c r="M53" t="n">
-        <v>53257</v>
+        <v>52492.5</v>
       </c>
       <c r="N53" t="n">
-        <v>53889.5</v>
+        <v>53134.25</v>
       </c>
       <c r="O53" t="n">
-        <v>54680</v>
+        <v>54135</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4951,18 +4949,18 @@
       <c r="Q53" s="6" t="n">
         <v/>
       </c>
-      <c r="R53" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S53" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T53" s="8" t="n">
-        <v/>
+      <c r="R53" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S53" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T53" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U53" s="8" t="n">
         <v/>
@@ -4975,59 +4973,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>52085</v>
+        <v>52140</v>
       </c>
       <c r="C54" t="n">
-        <v>52844</v>
+        <v>52153</v>
       </c>
       <c r="D54" t="n">
-        <v>51479</v>
+        <v>50859</v>
       </c>
       <c r="E54" t="n">
-        <v>52163</v>
+        <v>51477</v>
       </c>
       <c r="F54" t="n">
-        <v>402</v>
+        <v>-686</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.0078</v>
+        <v>-0.0132</v>
       </c>
       <c r="H54" t="n">
-        <v>1365</v>
+        <v>1294</v>
       </c>
       <c r="I54" t="n">
-        <v>49746</v>
+        <v>50114</v>
       </c>
       <c r="J54" t="n">
-        <v>50208.25</v>
+        <v>50798.75</v>
       </c>
       <c r="K54" t="n">
-        <v>51029.5</v>
+        <v>51480.5</v>
       </c>
       <c r="L54" t="n">
-        <v>51850.75</v>
+        <v>52162.25</v>
       </c>
       <c r="M54" t="n">
-        <v>52492.5</v>
+        <v>52845.5</v>
       </c>
       <c r="N54" t="n">
-        <v>53134.25</v>
+        <v>53528.75</v>
       </c>
       <c r="O54" t="n">
-        <v>54135</v>
+        <v>54209</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5035,18 +5029,18 @@
       <c r="Q54" s="6" t="n">
         <v/>
       </c>
-      <c r="R54" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S54" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T54" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R54" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S54" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T54" s="8" t="n">
+        <v/>
       </c>
       <c r="U54" s="8" t="n">
         <v/>
@@ -5059,55 +5053,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr"/>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>52140</v>
+        <v>51486</v>
       </c>
       <c r="C55" t="n">
-        <v>52153</v>
+        <v>52032</v>
       </c>
       <c r="D55" t="n">
-        <v>50859</v>
+        <v>50909</v>
       </c>
       <c r="E55" t="n">
-        <v>51477</v>
+        <v>51926</v>
       </c>
       <c r="F55" t="n">
-        <v>-686</v>
+        <v>449</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.0132</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="H55" t="n">
-        <v>1294</v>
+        <v>1123</v>
       </c>
       <c r="I55" t="n">
-        <v>50114</v>
+        <v>49565</v>
       </c>
       <c r="J55" t="n">
-        <v>50798.75</v>
+        <v>50168.5</v>
       </c>
       <c r="K55" t="n">
-        <v>51480.5</v>
+        <v>50830</v>
       </c>
       <c r="L55" t="n">
-        <v>52162.25</v>
+        <v>51491.5</v>
       </c>
       <c r="M55" t="n">
-        <v>52845.5</v>
+        <v>52124</v>
       </c>
       <c r="N55" t="n">
-        <v>53528.75</v>
+        <v>52756.5</v>
       </c>
       <c r="O55" t="n">
-        <v>54209</v>
+        <v>53447</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5115,19 +5113,19 @@
       <c r="Q55" s="6" t="n">
         <v/>
       </c>
-      <c r="R55" s="6" t="inlineStr">
+      <c r="R55" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S55" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T55" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S55" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T55" s="8" t="n">
-        <v/>
-      </c>
       <c r="U55" s="8" t="n">
         <v/>
       </c>
@@ -5141,57 +5139,57 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>51486</v>
+        <v>51972</v>
       </c>
       <c r="C56" t="n">
-        <v>52032</v>
+        <v>52823</v>
       </c>
       <c r="D56" t="n">
-        <v>50909</v>
+        <v>51602</v>
       </c>
       <c r="E56" t="n">
-        <v>51926</v>
+        <v>52214</v>
       </c>
       <c r="F56" t="n">
-        <v>449</v>
+        <v>288</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.008699999999999999</v>
+        <v>0.0055</v>
       </c>
       <c r="H56" t="n">
-        <v>1123</v>
+        <v>1221</v>
       </c>
       <c r="I56" t="n">
-        <v>49565</v>
+        <v>49786</v>
       </c>
       <c r="J56" t="n">
-        <v>50168.5</v>
+        <v>51030.75</v>
       </c>
       <c r="K56" t="n">
-        <v>50830</v>
+        <v>51364.5</v>
       </c>
       <c r="L56" t="n">
-        <v>51491.5</v>
+        <v>51698.25</v>
       </c>
       <c r="M56" t="n">
-        <v>52124</v>
+        <v>52487.5</v>
       </c>
       <c r="N56" t="n">
-        <v>52756.5</v>
+        <v>53276.75</v>
       </c>
       <c r="O56" t="n">
-        <v>53447</v>
+        <v>53155</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5223,59 +5221,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X56" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>51972</v>
+        <v>52070</v>
       </c>
       <c r="C57" t="n">
-        <v>52823</v>
+        <v>53168</v>
       </c>
       <c r="D57" t="n">
-        <v>51602</v>
+        <v>52034</v>
       </c>
       <c r="E57" t="n">
-        <v>52214</v>
+        <v>52451</v>
       </c>
       <c r="F57" t="n">
-        <v>288</v>
+        <v>237</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.0055</v>
+        <v>0.0045</v>
       </c>
       <c r="H57" t="n">
-        <v>1221</v>
+        <v>1134</v>
       </c>
       <c r="I57" t="n">
-        <v>49786</v>
+        <v>50381</v>
       </c>
       <c r="J57" t="n">
-        <v>51030.75</v>
+        <v>50993.75</v>
       </c>
       <c r="K57" t="n">
-        <v>51364.5</v>
+        <v>51603.5</v>
       </c>
       <c r="L57" t="n">
-        <v>51698.25</v>
+        <v>52213.25</v>
       </c>
       <c r="M57" t="n">
-        <v>52487.5</v>
+        <v>52824.5</v>
       </c>
       <c r="N57" t="n">
-        <v>53276.75</v>
+        <v>53435.75</v>
       </c>
       <c r="O57" t="n">
-        <v>53155</v>
+        <v>54044</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5288,12 +5282,12 @@
       </c>
       <c r="S57" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T57" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U57" s="8" t="n">
@@ -5308,86 +5302,6 @@
         </is>
       </c>
       <c r="X57" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="B58" t="n">
-        <v>52070</v>
-      </c>
-      <c r="C58" t="n">
-        <v>53168</v>
-      </c>
-      <c r="D58" t="n">
-        <v>52034</v>
-      </c>
-      <c r="E58" t="n">
-        <v>53032</v>
-      </c>
-      <c r="F58" t="n">
-        <v>818</v>
-      </c>
-      <c r="G58" s="5" t="n">
-        <v>0.0157</v>
-      </c>
-      <c r="H58" t="n">
-        <v>1134</v>
-      </c>
-      <c r="I58" t="n">
-        <v>50381</v>
-      </c>
-      <c r="J58" t="n">
-        <v>50993.75</v>
-      </c>
-      <c r="K58" t="n">
-        <v>51603.5</v>
-      </c>
-      <c r="L58" t="n">
-        <v>52213.25</v>
-      </c>
-      <c r="M58" t="n">
-        <v>52824.5</v>
-      </c>
-      <c r="N58" t="n">
-        <v>53435.75</v>
-      </c>
-      <c r="O58" t="n">
-        <v>54044</v>
-      </c>
-      <c r="P58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S58" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W58" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X58" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/YM_weekly.xlsx
+++ b/three_gate/analysis/YM_weekly.xlsx
@@ -5239,13 +5239,13 @@
         <v>52034</v>
       </c>
       <c r="E57" t="n">
-        <v>52451</v>
+        <v>52430</v>
       </c>
       <c r="F57" t="n">
-        <v>237</v>
+        <v>216</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.0045</v>
+        <v>0.0041</v>
       </c>
       <c r="H57" t="n">
         <v>1134</v>

--- a/three_gate/analysis/YM_weekly.xlsx
+++ b/three_gate/analysis/YM_weekly.xlsx
@@ -86,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -115,6 +115,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -480,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X57"/>
+  <dimension ref="A1:X58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5239,13 +5242,13 @@
         <v>52034</v>
       </c>
       <c r="E57" t="n">
-        <v>52430</v>
+        <v>52394</v>
       </c>
       <c r="F57" t="n">
-        <v>216</v>
+        <v>180</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.0041</v>
+        <v>0.0034</v>
       </c>
       <c r="H57" t="n">
         <v>1134</v>
@@ -5302,6 +5305,90 @@
         </is>
       </c>
       <c r="X57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>52528</v>
+      </c>
+      <c r="C58" t="n">
+        <v>52620</v>
+      </c>
+      <c r="D58" t="n">
+        <v>52455</v>
+      </c>
+      <c r="E58" t="n">
+        <v/>
+      </c>
+      <c r="F58" t="n">
+        <v/>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v/>
+      </c>
+      <c r="H58" t="n">
+        <v>165</v>
+      </c>
+      <c r="I58" t="n">
+        <v>50900</v>
+      </c>
+      <c r="J58" t="n">
+        <v>51156.5</v>
+      </c>
+      <c r="K58" t="n">
+        <v>51827</v>
+      </c>
+      <c r="L58" t="n">
+        <v>52497.5</v>
+      </c>
+      <c r="M58" t="n">
+        <v>52961</v>
+      </c>
+      <c r="N58" t="n">
+        <v>53424.5</v>
+      </c>
+      <c r="O58" t="n">
+        <v>54302</v>
+      </c>
+      <c r="P58" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S58" s="12" t="inlineStr">
+        <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W58" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/YM_weekly.xlsx
+++ b/three_gate/analysis/YM_weekly.xlsx
@@ -86,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -115,9 +115,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -662,25 +659,25 @@
         <v>988</v>
       </c>
       <c r="I2" t="n">
-        <v>45141</v>
+        <v>45407</v>
       </c>
       <c r="J2" t="n">
-        <v>45588.75</v>
+        <v>45921.25</v>
       </c>
       <c r="K2" t="n">
-        <v>46077.5</v>
+        <v>46210.5</v>
       </c>
       <c r="L2" t="n">
-        <v>46566.25</v>
+        <v>46499.75</v>
       </c>
       <c r="M2" t="n">
-        <v>47034.5</v>
+        <v>46901.5</v>
       </c>
       <c r="N2" t="n">
-        <v>47502.75</v>
+        <v>47303.25</v>
       </c>
       <c r="O2" t="n">
-        <v>48012</v>
+        <v>47480</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -701,8 +698,10 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U2" s="8" t="n">
-        <v/>
+      <c r="U2" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V2" s="8" t="n">
         <v/>
@@ -5313,25 +5312,25 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>52528</v>
+        <v>52492</v>
       </c>
       <c r="C58" t="n">
-        <v>52620</v>
+        <v>52818</v>
       </c>
       <c r="D58" t="n">
-        <v>52455</v>
+        <v>52378</v>
       </c>
       <c r="E58" t="n">
-        <v/>
+        <v>52457</v>
       </c>
       <c r="F58" t="n">
-        <v/>
+        <v>63</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v/>
+        <v>0.0012</v>
       </c>
       <c r="H58" t="n">
-        <v>165</v>
+        <v>440</v>
       </c>
       <c r="I58" t="n">
         <v>50900</v>
@@ -5354,10 +5353,8 @@
       <c r="O58" t="n">
         <v>54302</v>
       </c>
-      <c r="P58" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="P58" s="6" t="n">
+        <v/>
       </c>
       <c r="Q58" s="6" t="n">
         <v/>
@@ -5365,9 +5362,9 @@
       <c r="R58" s="6" t="n">
         <v/>
       </c>
-      <c r="S58" s="12" t="inlineStr">
-        <is>
-          <t>=</t>
+      <c r="S58" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">

--- a/three_gate/analysis/YM_weekly.xlsx
+++ b/three_gate/analysis/YM_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>988</v>
       </c>
       <c r="I2" t="n">
-        <v>45407</v>
+        <v>45528</v>
       </c>
       <c r="J2" t="n">
-        <v>45921.25</v>
+        <v>46072.5</v>
       </c>
       <c r="K2" t="n">
-        <v>46210.5</v>
+        <v>46271</v>
       </c>
       <c r="L2" t="n">
-        <v>46499.75</v>
+        <v>46469.5</v>
       </c>
       <c r="M2" t="n">
-        <v>46901.5</v>
+        <v>46841</v>
       </c>
       <c r="N2" t="n">
-        <v>47303.25</v>
+        <v>47212.5</v>
       </c>
       <c r="O2" t="n">
-        <v>47480</v>
+        <v>47238</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -695,16 +695,18 @@
       </c>
       <c r="T2" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U2" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U2" s="8" t="inlineStr">
+      <c r="V2" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
-      </c>
-      <c r="V2" s="8" t="n">
-        <v/>
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
@@ -5315,22 +5317,22 @@
         <v>52492</v>
       </c>
       <c r="C58" t="n">
-        <v>52818</v>
+        <v>52954</v>
       </c>
       <c r="D58" t="n">
         <v>52378</v>
       </c>
       <c r="E58" t="n">
-        <v>52457</v>
+        <v>52859</v>
       </c>
       <c r="F58" t="n">
-        <v>63</v>
+        <v>465</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0012</v>
+        <v>0.0089</v>
       </c>
       <c r="H58" t="n">
-        <v>440</v>
+        <v>576</v>
       </c>
       <c r="I58" t="n">
         <v>50900</v>
@@ -5362,13 +5364,15 @@
       <c r="R58" s="6" t="n">
         <v/>
       </c>
-      <c r="S58" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="n">
-        <v/>
+      <c r="S58" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U58" s="8" t="n">
         <v/>

--- a/three_gate/analysis/YM_weekly.xlsx
+++ b/three_gate/analysis/YM_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>988</v>
       </c>
       <c r="I2" t="n">
-        <v>45528</v>
+        <v>45800</v>
       </c>
       <c r="J2" t="n">
-        <v>46072.5</v>
+        <v>46174.5</v>
       </c>
       <c r="K2" t="n">
-        <v>46271</v>
+        <v>46339</v>
       </c>
       <c r="L2" t="n">
-        <v>46469.5</v>
+        <v>46503.5</v>
       </c>
       <c r="M2" t="n">
-        <v>46841</v>
+        <v>46773</v>
       </c>
       <c r="N2" t="n">
-        <v>47212.5</v>
+        <v>47042.5</v>
       </c>
       <c r="O2" t="n">
-        <v>47238</v>
+        <v>47102</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -685,8 +685,10 @@
       <c r="Q2" s="6" t="n">
         <v/>
       </c>
-      <c r="R2" s="6" t="n">
-        <v/>
+      <c r="R2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
@@ -5317,22 +5319,22 @@
         <v>52492</v>
       </c>
       <c r="C58" t="n">
-        <v>52954</v>
+        <v>53145</v>
       </c>
       <c r="D58" t="n">
-        <v>52378</v>
+        <v>52310</v>
       </c>
       <c r="E58" t="n">
-        <v>52859</v>
+        <v>52357</v>
       </c>
       <c r="F58" t="n">
-        <v>465</v>
+        <v>-37</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0089</v>
+        <v>-0.0007</v>
       </c>
       <c r="H58" t="n">
-        <v>576</v>
+        <v>835</v>
       </c>
       <c r="I58" t="n">
         <v>50900</v>
@@ -5364,14 +5366,14 @@
       <c r="R58" s="6" t="n">
         <v/>
       </c>
-      <c r="S58" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S58" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T58" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U58" s="8" t="n">
@@ -5387,7 +5389,7 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/YM_weekly.xlsx
+++ b/three_gate/analysis/YM_weekly.xlsx
@@ -104,17 +104,17 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X58"/>
+  <dimension ref="A1:X57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,56 +634,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>46565</v>
+        <v>47048</v>
       </c>
       <c r="C2" t="n">
-        <v>47323</v>
+        <v>47162</v>
       </c>
       <c r="D2" t="n">
-        <v>46335</v>
+        <v>45387</v>
       </c>
       <c r="E2" t="n">
-        <v>47031</v>
+        <v>45706</v>
       </c>
       <c r="F2" t="n">
-        <v>475</v>
+        <v>-1325</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0102</v>
+        <v>-0.0282</v>
       </c>
       <c r="H2" t="n">
-        <v>988</v>
+        <v>1775</v>
       </c>
       <c r="I2" t="n">
-        <v>45800</v>
+        <v>45347</v>
       </c>
       <c r="J2" t="n">
-        <v>46174.5</v>
+        <v>46144</v>
       </c>
       <c r="K2" t="n">
-        <v>46339</v>
+        <v>46537</v>
       </c>
       <c r="L2" t="n">
-        <v>46503.5</v>
+        <v>46930</v>
       </c>
       <c r="M2" t="n">
-        <v>46773</v>
+        <v>47525</v>
       </c>
       <c r="N2" t="n">
-        <v>47042.5</v>
+        <v>48120</v>
       </c>
       <c r="O2" t="n">
-        <v>47102</v>
-      </c>
-      <c r="P2" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q2" s="6" t="n">
-        <v/>
+        <v>48311</v>
+      </c>
+      <c r="P2" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R2" s="6" t="inlineStr">
         <is>
@@ -692,27 +696,21 @@
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U2" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U2" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V2" s="8" t="n">
+        <v/>
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
+          <t>空方</t>
         </is>
       </c>
       <c r="X2" t="inlineStr"/>
@@ -720,134 +718,134 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>47048</v>
+        <v>45837</v>
       </c>
       <c r="C3" t="n">
-        <v>47162</v>
+        <v>46915</v>
       </c>
       <c r="D3" t="n">
-        <v>45387</v>
+        <v>45605</v>
       </c>
       <c r="E3" t="n">
-        <v>45706</v>
+        <v>46381</v>
       </c>
       <c r="F3" t="n">
-        <v>-1325</v>
+        <v>675</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.0282</v>
+        <v>0.0148</v>
       </c>
       <c r="H3" t="n">
-        <v>1775</v>
+        <v>1310</v>
       </c>
       <c r="I3" t="n">
-        <v>45347</v>
+        <v>43612</v>
       </c>
       <c r="J3" t="n">
-        <v>46144</v>
+        <v>43646.75</v>
       </c>
       <c r="K3" t="n">
-        <v>46537</v>
+        <v>44818.5</v>
       </c>
       <c r="L3" t="n">
-        <v>46930</v>
+        <v>45990.25</v>
       </c>
       <c r="M3" t="n">
-        <v>47525</v>
+        <v>46593.5</v>
       </c>
       <c r="N3" t="n">
-        <v>48120</v>
+        <v>47196.75</v>
       </c>
       <c r="O3" t="n">
-        <v>48311</v>
-      </c>
-      <c r="P3" s="6" t="inlineStr">
+        <v>48937</v>
+      </c>
+      <c r="P3" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q3" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R3" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S3" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q3" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R3" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S3" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="n">
-        <v/>
-      </c>
       <c r="U3" s="8" t="n">
         <v/>
       </c>
       <c r="V3" s="8" t="n">
         <v/>
       </c>
-      <c r="W3" s="11" t="inlineStr">
+      <c r="W3" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr"/>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>45837</v>
+        <v>46489</v>
       </c>
       <c r="C4" t="n">
-        <v>46915</v>
+        <v>47508</v>
       </c>
       <c r="D4" t="n">
-        <v>45605</v>
+        <v>46316</v>
       </c>
       <c r="E4" t="n">
-        <v>46381</v>
+        <v>47396</v>
       </c>
       <c r="F4" t="n">
-        <v>675</v>
+        <v>1015</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.0148</v>
+        <v>0.0219</v>
       </c>
       <c r="H4" t="n">
-        <v>1310</v>
+        <v>1192</v>
       </c>
       <c r="I4" t="n">
-        <v>43612</v>
+        <v>44295</v>
       </c>
       <c r="J4" t="n">
-        <v>43646.75</v>
+        <v>45131.5</v>
       </c>
       <c r="K4" t="n">
-        <v>44818.5</v>
+        <v>45726</v>
       </c>
       <c r="L4" t="n">
-        <v>45990.25</v>
+        <v>46320.5</v>
       </c>
       <c r="M4" t="n">
-        <v>46593.5</v>
+        <v>47036</v>
       </c>
       <c r="N4" t="n">
-        <v>47196.75</v>
+        <v>47751.5</v>
       </c>
       <c r="O4" t="n">
-        <v>48937</v>
+        <v>48225</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -858,80 +856,82 @@
       <c r="R4" s="6" t="n">
         <v/>
       </c>
-      <c r="S4" s="7" t="inlineStr">
+      <c r="S4" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T4" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U4" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U4" s="8" t="n">
-        <v/>
-      </c>
       <c r="V4" s="8" t="n">
         <v/>
       </c>
-      <c r="W4" s="11" t="inlineStr">
+      <c r="W4" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>46489</v>
+        <v>47711</v>
       </c>
       <c r="C5" t="n">
-        <v>47508</v>
+        <v>48214</v>
       </c>
       <c r="D5" t="n">
-        <v>46316</v>
+        <v>47488</v>
       </c>
       <c r="E5" t="n">
-        <v>47396</v>
+        <v>47722</v>
       </c>
       <c r="F5" t="n">
-        <v>1015</v>
+        <v>326</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.0219</v>
+        <v>0.0069</v>
       </c>
       <c r="H5" t="n">
-        <v>1192</v>
+        <v>726</v>
       </c>
       <c r="I5" t="n">
-        <v>44295</v>
+        <v>45124</v>
       </c>
       <c r="J5" t="n">
-        <v>45131.5</v>
+        <v>46446</v>
       </c>
       <c r="K5" t="n">
-        <v>45726</v>
+        <v>46800</v>
       </c>
       <c r="L5" t="n">
-        <v>46320.5</v>
+        <v>47154</v>
       </c>
       <c r="M5" t="n">
-        <v>47036</v>
+        <v>47992</v>
       </c>
       <c r="N5" t="n">
-        <v>47751.5</v>
+        <v>48830</v>
       </c>
       <c r="O5" t="n">
-        <v>48225</v>
+        <v>48700</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -942,25 +942,23 @@
       <c r="R5" s="6" t="n">
         <v/>
       </c>
-      <c r="S5" s="7" t="inlineStr">
+      <c r="S5" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T5" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U5" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U5" s="8" t="n">
+        <v/>
+      </c>
       <c r="V5" s="8" t="n">
         <v/>
       </c>
-      <c r="W5" s="11" t="inlineStr">
+      <c r="W5" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -974,69 +972,73 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>47711</v>
+        <v>47735</v>
       </c>
       <c r="C6" t="n">
-        <v>48214</v>
+        <v>47869</v>
       </c>
       <c r="D6" t="n">
-        <v>47488</v>
+        <v>46574</v>
       </c>
       <c r="E6" t="n">
-        <v>47722</v>
+        <v>47085</v>
       </c>
       <c r="F6" t="n">
-        <v>326</v>
+        <v>-637</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.0069</v>
+        <v>-0.0133</v>
       </c>
       <c r="H6" t="n">
-        <v>726</v>
+        <v>1295</v>
       </c>
       <c r="I6" t="n">
-        <v>45124</v>
+        <v>46762</v>
       </c>
       <c r="J6" t="n">
-        <v>46446</v>
+        <v>46931.5</v>
       </c>
       <c r="K6" t="n">
-        <v>46800</v>
+        <v>47359</v>
       </c>
       <c r="L6" t="n">
-        <v>47154</v>
+        <v>47786.5</v>
       </c>
       <c r="M6" t="n">
-        <v>47992</v>
+        <v>48085</v>
       </c>
       <c r="N6" t="n">
-        <v>48830</v>
+        <v>48383.5</v>
       </c>
       <c r="O6" t="n">
-        <v>48700</v>
-      </c>
-      <c r="P6" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q6" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R6" s="6" t="n">
-        <v/>
+        <v>48940</v>
+      </c>
+      <c r="P6" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q6" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R6" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S6" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="n">
+        <v/>
       </c>
       <c r="U6" s="8" t="n">
         <v/>
@@ -1044,148 +1046,146 @@
       <c r="V6" s="8" t="n">
         <v/>
       </c>
-      <c r="W6" s="11" t="inlineStr">
+      <c r="W6" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>47735</v>
+        <v>47208</v>
       </c>
       <c r="C7" t="n">
-        <v>47869</v>
+        <v>48528</v>
       </c>
       <c r="D7" t="n">
-        <v>46574</v>
+        <v>46939</v>
       </c>
       <c r="E7" t="n">
-        <v>47085</v>
+        <v>47229</v>
       </c>
       <c r="F7" t="n">
-        <v>-637</v>
+        <v>144</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-0.0133</v>
+        <v>0.0031</v>
       </c>
       <c r="H7" t="n">
-        <v>1295</v>
+        <v>1589</v>
       </c>
       <c r="I7" t="n">
-        <v>46762</v>
+        <v>45279</v>
       </c>
       <c r="J7" t="n">
-        <v>46931.5</v>
+        <v>45721.75</v>
       </c>
       <c r="K7" t="n">
-        <v>47359</v>
+        <v>46437.5</v>
       </c>
       <c r="L7" t="n">
-        <v>47786.5</v>
+        <v>47153.25</v>
       </c>
       <c r="M7" t="n">
-        <v>48085</v>
+        <v>47732.5</v>
       </c>
       <c r="N7" t="n">
-        <v>48383.5</v>
+        <v>48311.75</v>
       </c>
       <c r="O7" t="n">
-        <v>48940</v>
-      </c>
-      <c r="P7" s="6" t="inlineStr">
+        <v>49164</v>
+      </c>
+      <c r="P7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S7" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q7" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R7" s="6" t="inlineStr">
+      <c r="U7" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S7" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U7" s="8" t="n">
-        <v/>
-      </c>
       <c r="V7" s="8" t="n">
         <v/>
       </c>
-      <c r="W7" s="11" t="inlineStr">
+      <c r="W7" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr"/>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>47208</v>
+        <v>47237</v>
       </c>
       <c r="C8" t="n">
-        <v>48528</v>
+        <v>47368</v>
       </c>
       <c r="D8" t="n">
-        <v>46939</v>
+        <v>45779</v>
       </c>
       <c r="E8" t="n">
-        <v>47229</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="n">
-        <v>144</v>
+        <v>-908</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.0031</v>
+        <v>-0.0192</v>
       </c>
       <c r="H8" t="n">
         <v>1589</v>
       </c>
       <c r="I8" t="n">
-        <v>45279</v>
+        <v>45350</v>
       </c>
       <c r="J8" t="n">
-        <v>45721.75</v>
+        <v>45387.75</v>
       </c>
       <c r="K8" t="n">
-        <v>46437.5</v>
+        <v>46434.5</v>
       </c>
       <c r="L8" t="n">
-        <v>47153.25</v>
+        <v>47481.25</v>
       </c>
       <c r="M8" t="n">
-        <v>47732.5</v>
+        <v>48023.5</v>
       </c>
       <c r="N8" t="n">
-        <v>48311.75</v>
+        <v>48565.75</v>
       </c>
       <c r="O8" t="n">
-        <v>49164</v>
+        <v>50117</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1193,85 +1193,79 @@
       <c r="Q8" s="6" t="n">
         <v/>
       </c>
-      <c r="R8" s="6" t="n">
-        <v/>
+      <c r="R8" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S8" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U8" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U8" s="8" t="n">
+        <v/>
       </c>
       <c r="V8" s="8" t="n">
         <v/>
       </c>
-      <c r="W8" s="11" t="inlineStr">
+      <c r="W8" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>47237</v>
+        <v>46504</v>
       </c>
       <c r="C9" t="n">
-        <v>47368</v>
+        <v>47796</v>
       </c>
       <c r="D9" t="n">
-        <v>45779</v>
+        <v>46165</v>
       </c>
       <c r="E9" t="n">
-        <v>46321</v>
+        <v>47743</v>
       </c>
       <c r="F9" t="n">
-        <v>-908</v>
+        <v>1422</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.0192</v>
+        <v>0.0307</v>
       </c>
       <c r="H9" t="n">
-        <v>1589</v>
+        <v>1631</v>
       </c>
       <c r="I9" t="n">
-        <v>45350</v>
+        <v>44190</v>
       </c>
       <c r="J9" t="n">
-        <v>45387.75</v>
+        <v>44605.75</v>
       </c>
       <c r="K9" t="n">
-        <v>46434.5</v>
+        <v>45526.5</v>
       </c>
       <c r="L9" t="n">
-        <v>47481.25</v>
+        <v>46447.25</v>
       </c>
       <c r="M9" t="n">
-        <v>48023.5</v>
+        <v>47115.5</v>
       </c>
       <c r="N9" t="n">
-        <v>48565.75</v>
+        <v>47783.75</v>
       </c>
       <c r="O9" t="n">
-        <v>50117</v>
+        <v>48957</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1279,79 +1273,85 @@
       <c r="Q9" s="6" t="n">
         <v/>
       </c>
-      <c r="R9" s="6" t="inlineStr">
+      <c r="R9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S9" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U9" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S9" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U9" s="8" t="n">
-        <v/>
-      </c>
       <c r="V9" s="8" t="n">
         <v/>
       </c>
-      <c r="W9" s="11" t="inlineStr">
+      <c r="W9" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr"/>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>46504</v>
+        <v>47741</v>
       </c>
       <c r="C10" t="n">
-        <v>47796</v>
+        <v>48184</v>
       </c>
       <c r="D10" t="n">
-        <v>46165</v>
+        <v>47269</v>
       </c>
       <c r="E10" t="n">
-        <v>47743</v>
+        <v>48001</v>
       </c>
       <c r="F10" t="n">
-        <v>1422</v>
+        <v>258</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.0307</v>
+        <v>0.0054</v>
       </c>
       <c r="H10" t="n">
-        <v>1631</v>
+        <v>915</v>
       </c>
       <c r="I10" t="n">
-        <v>44190</v>
+        <v>44534</v>
       </c>
       <c r="J10" t="n">
-        <v>44605.75</v>
+        <v>46493.25</v>
       </c>
       <c r="K10" t="n">
-        <v>45526.5</v>
+        <v>46927.5</v>
       </c>
       <c r="L10" t="n">
-        <v>46447.25</v>
+        <v>47361.75</v>
       </c>
       <c r="M10" t="n">
-        <v>47115.5</v>
+        <v>48558.5</v>
       </c>
       <c r="N10" t="n">
-        <v>47783.75</v>
+        <v>49755.25</v>
       </c>
       <c r="O10" t="n">
-        <v>48957</v>
+        <v>49427</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1362,25 +1362,23 @@
       <c r="R10" s="6" t="n">
         <v/>
       </c>
-      <c r="S10" s="7" t="inlineStr">
+      <c r="S10" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T10" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U10" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U10" s="8" t="n">
+        <v/>
+      </c>
       <c r="V10" s="8" t="n">
         <v/>
       </c>
-      <c r="W10" s="11" t="inlineStr">
+      <c r="W10" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1394,50 +1392,50 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>47741</v>
+        <v>48015</v>
       </c>
       <c r="C11" t="n">
-        <v>48184</v>
+        <v>48917</v>
       </c>
       <c r="D11" t="n">
-        <v>47269</v>
+        <v>47504</v>
       </c>
       <c r="E11" t="n">
-        <v>48001</v>
+        <v>48474</v>
       </c>
       <c r="F11" t="n">
-        <v>258</v>
+        <v>473</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0054</v>
+        <v>0.009900000000000001</v>
       </c>
       <c r="H11" t="n">
-        <v>915</v>
+        <v>1413</v>
       </c>
       <c r="I11" t="n">
-        <v>44534</v>
+        <v>46354</v>
       </c>
       <c r="J11" t="n">
-        <v>46493.25</v>
+        <v>47223.25</v>
       </c>
       <c r="K11" t="n">
-        <v>46927.5</v>
+        <v>47543.5</v>
       </c>
       <c r="L11" t="n">
-        <v>47361.75</v>
+        <v>47863.75</v>
       </c>
       <c r="M11" t="n">
-        <v>48558.5</v>
+        <v>48458.5</v>
       </c>
       <c r="N11" t="n">
-        <v>49755.25</v>
+        <v>49053.25</v>
       </c>
       <c r="O11" t="n">
-        <v>49427</v>
+        <v>49099</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1445,10 +1443,12 @@
       <c r="Q11" s="6" t="n">
         <v/>
       </c>
-      <c r="R11" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S11" s="7" t="inlineStr">
+      <c r="R11" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S11" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1464,7 +1464,7 @@
       <c r="V11" s="8" t="n">
         <v/>
       </c>
-      <c r="W11" s="11" t="inlineStr">
+      <c r="W11" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1478,50 +1478,50 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>48015</v>
+        <v>48517</v>
       </c>
       <c r="C12" t="n">
-        <v>48917</v>
+        <v>48745</v>
       </c>
       <c r="D12" t="n">
-        <v>47504</v>
+        <v>47809</v>
       </c>
       <c r="E12" t="n">
-        <v>48474</v>
+        <v>48090</v>
       </c>
       <c r="F12" t="n">
-        <v>473</v>
+        <v>-384</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.009900000000000001</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="H12" t="n">
-        <v>1413</v>
+        <v>936</v>
       </c>
       <c r="I12" t="n">
-        <v>46354</v>
+        <v>46091</v>
       </c>
       <c r="J12" t="n">
-        <v>47223.25</v>
+        <v>47192.75</v>
       </c>
       <c r="K12" t="n">
-        <v>47543.5</v>
+        <v>47767.5</v>
       </c>
       <c r="L12" t="n">
-        <v>47863.75</v>
+        <v>48342.25</v>
       </c>
       <c r="M12" t="n">
-        <v>48458.5</v>
+        <v>49180.5</v>
       </c>
       <c r="N12" t="n">
-        <v>49053.25</v>
+        <v>50018.75</v>
       </c>
       <c r="O12" t="n">
-        <v>49099</v>
+        <v>50330</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1529,20 +1529,16 @@
       <c r="Q12" s="6" t="n">
         <v/>
       </c>
-      <c r="R12" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R12" s="6" t="n">
+        <v/>
       </c>
       <c r="S12" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="n">
+        <v/>
       </c>
       <c r="U12" s="8" t="n">
         <v/>
@@ -1550,64 +1546,64 @@
       <c r="V12" s="8" t="n">
         <v/>
       </c>
-      <c r="W12" s="11" t="inlineStr">
+      <c r="W12" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>48517</v>
+        <v>48600</v>
       </c>
       <c r="C13" t="n">
-        <v>48745</v>
+        <v>49086</v>
       </c>
       <c r="D13" t="n">
-        <v>47809</v>
+        <v>48458</v>
       </c>
       <c r="E13" t="n">
-        <v>48090</v>
+        <v>48998</v>
       </c>
       <c r="F13" t="n">
-        <v>-384</v>
+        <v>908</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.007900000000000001</v>
+        <v>0.0189</v>
       </c>
       <c r="H13" t="n">
-        <v>936</v>
+        <v>628</v>
       </c>
       <c r="I13" t="n">
-        <v>46091</v>
+        <v>46873</v>
       </c>
       <c r="J13" t="n">
-        <v>47192.75</v>
+        <v>47060.5</v>
       </c>
       <c r="K13" t="n">
-        <v>47767.5</v>
+        <v>47622</v>
       </c>
       <c r="L13" t="n">
-        <v>48342.25</v>
+        <v>48183.5</v>
       </c>
       <c r="M13" t="n">
-        <v>49180.5</v>
+        <v>48558</v>
       </c>
       <c r="N13" t="n">
-        <v>50018.75</v>
+        <v>48932.5</v>
       </c>
       <c r="O13" t="n">
-        <v>50330</v>
+        <v>49681</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1620,244 +1616,244 @@
       </c>
       <c r="S13" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U13" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U13" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V13" s="8" t="n">
         <v/>
       </c>
       <c r="W13" s="11" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>48600</v>
+        <v>48998</v>
       </c>
       <c r="C14" t="n">
-        <v>49086</v>
+        <v>49052</v>
       </c>
       <c r="D14" t="n">
-        <v>48458</v>
+        <v>48092</v>
       </c>
       <c r="E14" t="n">
-        <v>48998</v>
+        <v>48616</v>
       </c>
       <c r="F14" t="n">
-        <v>908</v>
+        <v>-382</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0189</v>
+        <v>-0.0078</v>
       </c>
       <c r="H14" t="n">
-        <v>628</v>
+        <v>960</v>
       </c>
       <c r="I14" t="n">
-        <v>46873</v>
+        <v>47830</v>
       </c>
       <c r="J14" t="n">
-        <v>47060.5</v>
+        <v>48483</v>
       </c>
       <c r="K14" t="n">
-        <v>47622</v>
+        <v>48684</v>
       </c>
       <c r="L14" t="n">
-        <v>48183.5</v>
+        <v>48885</v>
       </c>
       <c r="M14" t="n">
-        <v>48558</v>
+        <v>49312</v>
       </c>
       <c r="N14" t="n">
-        <v>48932.5</v>
+        <v>49739</v>
       </c>
       <c r="O14" t="n">
-        <v>49681</v>
+        <v>49714</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
       </c>
-      <c r="Q14" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R14" s="6" t="n">
-        <v/>
+      <c r="Q14" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R14" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S14" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U14" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U14" s="8" t="n">
+        <v/>
       </c>
       <c r="V14" s="8" t="n">
         <v/>
       </c>
-      <c r="W14" s="9" t="inlineStr">
+      <c r="W14" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr"/>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>48998</v>
+        <v>48653</v>
       </c>
       <c r="C15" t="n">
-        <v>49052</v>
+        <v>49876</v>
       </c>
       <c r="D15" t="n">
-        <v>48092</v>
+        <v>48556</v>
       </c>
       <c r="E15" t="n">
-        <v>48616</v>
+        <v>49726</v>
       </c>
       <c r="F15" t="n">
-        <v>-382</v>
+        <v>1110</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.0078</v>
+        <v>0.0228</v>
       </c>
       <c r="H15" t="n">
-        <v>960</v>
+        <v>1320</v>
       </c>
       <c r="I15" t="n">
-        <v>47830</v>
+        <v>47132</v>
       </c>
       <c r="J15" t="n">
-        <v>48483</v>
+        <v>47678</v>
       </c>
       <c r="K15" t="n">
-        <v>48684</v>
+        <v>48136</v>
       </c>
       <c r="L15" t="n">
-        <v>48885</v>
+        <v>48594</v>
       </c>
       <c r="M15" t="n">
-        <v>49312</v>
+        <v>49096</v>
       </c>
       <c r="N15" t="n">
-        <v>49739</v>
+        <v>49598</v>
       </c>
       <c r="O15" t="n">
-        <v>49714</v>
+        <v>50012</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
       </c>
-      <c r="Q15" s="6" t="inlineStr">
+      <c r="Q15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S15" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R15" s="6" t="inlineStr">
+      <c r="U15" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S15" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U15" s="8" t="n">
-        <v/>
-      </c>
       <c r="V15" s="8" t="n">
         <v/>
       </c>
-      <c r="W15" s="9" t="inlineStr">
+      <c r="W15" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>48653</v>
+        <v>49720</v>
       </c>
       <c r="C16" t="n">
-        <v>49876</v>
+        <v>49901</v>
       </c>
       <c r="D16" t="n">
-        <v>48556</v>
+        <v>49057</v>
       </c>
       <c r="E16" t="n">
-        <v>49726</v>
+        <v>49547</v>
       </c>
       <c r="F16" t="n">
-        <v>1110</v>
+        <v>-179</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0228</v>
+        <v>-0.0036</v>
       </c>
       <c r="H16" t="n">
-        <v>1320</v>
+        <v>844</v>
       </c>
       <c r="I16" t="n">
-        <v>47132</v>
+        <v>47236</v>
       </c>
       <c r="J16" t="n">
-        <v>47678</v>
+        <v>48661</v>
       </c>
       <c r="K16" t="n">
-        <v>48136</v>
+        <v>49066</v>
       </c>
       <c r="L16" t="n">
-        <v>48594</v>
+        <v>49471</v>
       </c>
       <c r="M16" t="n">
-        <v>49096</v>
+        <v>50386</v>
       </c>
       <c r="N16" t="n">
-        <v>49598</v>
+        <v>51301</v>
       </c>
       <c r="O16" t="n">
-        <v>50012</v>
+        <v>51196</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1865,96 +1861,100 @@
       <c r="Q16" s="6" t="n">
         <v/>
       </c>
-      <c r="R16" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S16" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="inlineStr">
+      <c r="R16" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U16" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S16" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U16" s="8" t="n">
+        <v/>
       </c>
       <c r="V16" s="8" t="n">
         <v/>
       </c>
-      <c r="W16" s="9" t="inlineStr">
+      <c r="W16" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr"/>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>49720</v>
+        <v>49310</v>
       </c>
       <c r="C17" t="n">
-        <v>49901</v>
+        <v>49795</v>
       </c>
       <c r="D17" t="n">
-        <v>49057</v>
+        <v>48488</v>
       </c>
       <c r="E17" t="n">
-        <v>49547</v>
+        <v>49263</v>
       </c>
       <c r="F17" t="n">
-        <v>-179</v>
+        <v>-284</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-0.0036</v>
+        <v>-0.0057</v>
       </c>
       <c r="H17" t="n">
-        <v>844</v>
+        <v>1307</v>
       </c>
       <c r="I17" t="n">
-        <v>47236</v>
+        <v>48213</v>
       </c>
       <c r="J17" t="n">
-        <v>48661</v>
+        <v>48737</v>
       </c>
       <c r="K17" t="n">
-        <v>49066</v>
+        <v>49125</v>
       </c>
       <c r="L17" t="n">
-        <v>49471</v>
+        <v>49513</v>
       </c>
       <c r="M17" t="n">
-        <v>50386</v>
+        <v>49969</v>
       </c>
       <c r="N17" t="n">
-        <v>51301</v>
+        <v>50425</v>
       </c>
       <c r="O17" t="n">
-        <v>51196</v>
+        <v>50745</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
       </c>
-      <c r="Q17" s="6" t="n">
-        <v/>
+      <c r="Q17" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R17" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S17" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T17" s="8" t="n">
@@ -1966,81 +1966,79 @@
       <c r="V17" s="8" t="n">
         <v/>
       </c>
-      <c r="W17" s="9" t="inlineStr">
+      <c r="W17" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>49310</v>
+        <v>49036</v>
       </c>
       <c r="C18" t="n">
-        <v>49795</v>
+        <v>49644</v>
       </c>
       <c r="D18" t="n">
-        <v>48488</v>
+        <v>48571</v>
       </c>
       <c r="E18" t="n">
-        <v>49263</v>
+        <v>49008</v>
       </c>
       <c r="F18" t="n">
-        <v>-284</v>
+        <v>-255</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-0.0057</v>
+        <v>-0.0052</v>
       </c>
       <c r="H18" t="n">
-        <v>1307</v>
+        <v>1073</v>
       </c>
       <c r="I18" t="n">
-        <v>48213</v>
+        <v>47181</v>
       </c>
       <c r="J18" t="n">
-        <v>48737</v>
+        <v>48016.75</v>
       </c>
       <c r="K18" t="n">
-        <v>49125</v>
+        <v>48609.5</v>
       </c>
       <c r="L18" t="n">
-        <v>49513</v>
+        <v>49202.25</v>
       </c>
       <c r="M18" t="n">
-        <v>49969</v>
+        <v>49916.5</v>
       </c>
       <c r="N18" t="n">
-        <v>50425</v>
+        <v>50630.75</v>
       </c>
       <c r="O18" t="n">
-        <v>50745</v>
+        <v>51102</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
       </c>
-      <c r="Q18" s="6" t="inlineStr">
+      <c r="Q18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R18" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R18" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S18" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="S18" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T18" s="8" t="n">
@@ -2052,64 +2050,64 @@
       <c r="V18" s="8" t="n">
         <v/>
       </c>
-      <c r="W18" s="9" t="inlineStr">
+      <c r="W18" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>49036</v>
+        <v>48864</v>
       </c>
       <c r="C19" t="n">
-        <v>49644</v>
+        <v>50263</v>
       </c>
       <c r="D19" t="n">
-        <v>48571</v>
+        <v>48506</v>
       </c>
       <c r="E19" t="n">
-        <v>49008</v>
+        <v>50205</v>
       </c>
       <c r="F19" t="n">
-        <v>-255</v>
+        <v>1197</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-0.0052</v>
+        <v>0.0244</v>
       </c>
       <c r="H19" t="n">
-        <v>1073</v>
+        <v>1757</v>
       </c>
       <c r="I19" t="n">
-        <v>47181</v>
+        <v>47498</v>
       </c>
       <c r="J19" t="n">
-        <v>48016.75</v>
+        <v>47885.25</v>
       </c>
       <c r="K19" t="n">
-        <v>48609.5</v>
+        <v>48471.5</v>
       </c>
       <c r="L19" t="n">
-        <v>49202.25</v>
+        <v>49057.75</v>
       </c>
       <c r="M19" t="n">
-        <v>49916.5</v>
+        <v>49544.5</v>
       </c>
       <c r="N19" t="n">
-        <v>50630.75</v>
+        <v>50031.25</v>
       </c>
       <c r="O19" t="n">
-        <v>51102</v>
+        <v>50717</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2117,83 +2115,85 @@
       <c r="Q19" s="6" t="n">
         <v/>
       </c>
-      <c r="R19" s="6" t="inlineStr">
+      <c r="R19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S19" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S19" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U19" s="8" t="n">
-        <v/>
+      <c r="U19" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V19" s="8" t="n">
         <v/>
       </c>
-      <c r="W19" s="9" t="inlineStr">
+      <c r="W19" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>48864</v>
+        <v>50240</v>
       </c>
       <c r="C20" t="n">
-        <v>50263</v>
+        <v>50611</v>
       </c>
       <c r="D20" t="n">
-        <v>48506</v>
+        <v>49155</v>
       </c>
       <c r="E20" t="n">
-        <v>50205</v>
+        <v>49569</v>
       </c>
       <c r="F20" t="n">
-        <v>1197</v>
+        <v>-636</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.0244</v>
+        <v>-0.0127</v>
       </c>
       <c r="H20" t="n">
-        <v>1757</v>
+        <v>1456</v>
       </c>
       <c r="I20" t="n">
-        <v>47498</v>
+        <v>46749</v>
       </c>
       <c r="J20" t="n">
-        <v>47885.25</v>
+        <v>48858.25</v>
       </c>
       <c r="K20" t="n">
-        <v>48471.5</v>
+        <v>49326.5</v>
       </c>
       <c r="L20" t="n">
-        <v>49057.75</v>
+        <v>49794.75</v>
       </c>
       <c r="M20" t="n">
-        <v>49544.5</v>
+        <v>51083.5</v>
       </c>
       <c r="N20" t="n">
-        <v>50031.25</v>
+        <v>52372.25</v>
       </c>
       <c r="O20" t="n">
-        <v>50717</v>
+        <v>52020</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2201,28 +2201,26 @@
       <c r="Q20" s="6" t="n">
         <v/>
       </c>
-      <c r="R20" s="6" t="n">
-        <v/>
+      <c r="R20" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S20" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U20" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U20" s="8" t="n">
+        <v/>
       </c>
       <c r="V20" s="8" t="n">
         <v/>
       </c>
-      <c r="W20" s="9" t="inlineStr">
+      <c r="W20" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2236,50 +2234,50 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>50240</v>
+        <v>49549</v>
       </c>
       <c r="C21" t="n">
-        <v>50611</v>
+        <v>49967</v>
       </c>
       <c r="D21" t="n">
-        <v>49155</v>
+        <v>49204</v>
       </c>
       <c r="E21" t="n">
-        <v>49569</v>
+        <v>49674</v>
       </c>
       <c r="F21" t="n">
-        <v>-636</v>
+        <v>105</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.0127</v>
+        <v>0.0021</v>
       </c>
       <c r="H21" t="n">
-        <v>1456</v>
+        <v>763</v>
       </c>
       <c r="I21" t="n">
-        <v>46749</v>
+        <v>47699</v>
       </c>
       <c r="J21" t="n">
-        <v>48858.25</v>
+        <v>47956</v>
       </c>
       <c r="K21" t="n">
-        <v>49326.5</v>
+        <v>48841</v>
       </c>
       <c r="L21" t="n">
-        <v>49794.75</v>
+        <v>49726</v>
       </c>
       <c r="M21" t="n">
-        <v>51083.5</v>
+        <v>50297</v>
       </c>
       <c r="N21" t="n">
-        <v>52372.25</v>
+        <v>50868</v>
       </c>
       <c r="O21" t="n">
-        <v>52020</v>
+        <v>52067</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2287,12 +2285,10 @@
       <c r="Q21" s="6" t="n">
         <v/>
       </c>
-      <c r="R21" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S21" s="10" t="inlineStr">
+      <c r="R21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S21" s="7" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -2306,7 +2302,7 @@
       <c r="V21" s="8" t="n">
         <v/>
       </c>
-      <c r="W21" s="9" t="inlineStr">
+      <c r="W21" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2320,63 +2316,67 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>49549</v>
+        <v>49642</v>
       </c>
       <c r="C22" t="n">
-        <v>49967</v>
+        <v>49872</v>
       </c>
       <c r="D22" t="n">
-        <v>49204</v>
+        <v>48699</v>
       </c>
       <c r="E22" t="n">
-        <v>49674</v>
+        <v>49000</v>
       </c>
       <c r="F22" t="n">
-        <v>105</v>
+        <v>-674</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.0021</v>
+        <v>-0.0136</v>
       </c>
       <c r="H22" t="n">
-        <v>763</v>
+        <v>1173</v>
       </c>
       <c r="I22" t="n">
-        <v>47699</v>
+        <v>48441</v>
       </c>
       <c r="J22" t="n">
-        <v>47956</v>
+        <v>48955.25</v>
       </c>
       <c r="K22" t="n">
-        <v>48841</v>
+        <v>49292.5</v>
       </c>
       <c r="L22" t="n">
-        <v>49726</v>
+        <v>49629.75</v>
       </c>
       <c r="M22" t="n">
-        <v>50297</v>
+        <v>50055.5</v>
       </c>
       <c r="N22" t="n">
-        <v>50868</v>
+        <v>50481.25</v>
       </c>
       <c r="O22" t="n">
-        <v>52067</v>
+        <v>50730</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
       </c>
-      <c r="Q22" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R22" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S22" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="Q22" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R22" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S22" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T22" s="8" t="n">
@@ -2388,71 +2388,73 @@
       <c r="V22" s="8" t="n">
         <v/>
       </c>
-      <c r="W22" s="9" t="inlineStr">
+      <c r="W22" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>49642</v>
+        <v>48451</v>
       </c>
       <c r="C23" t="n">
-        <v>49872</v>
+        <v>49121</v>
       </c>
       <c r="D23" t="n">
-        <v>48699</v>
+        <v>47025</v>
       </c>
       <c r="E23" t="n">
-        <v>49000</v>
+        <v>47517</v>
       </c>
       <c r="F23" t="n">
-        <v>-674</v>
+        <v>-1483</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-0.0136</v>
+        <v>-0.0303</v>
       </c>
       <c r="H23" t="n">
-        <v>1173</v>
+        <v>2096</v>
       </c>
       <c r="I23" t="n">
-        <v>48441</v>
+        <v>47526</v>
       </c>
       <c r="J23" t="n">
-        <v>48955.25</v>
+        <v>47684.25</v>
       </c>
       <c r="K23" t="n">
-        <v>49292.5</v>
+        <v>48413.5</v>
       </c>
       <c r="L23" t="n">
-        <v>49629.75</v>
+        <v>49142.75</v>
       </c>
       <c r="M23" t="n">
-        <v>50055.5</v>
+        <v>49586.5</v>
       </c>
       <c r="N23" t="n">
-        <v>50481.25</v>
+        <v>50030.25</v>
       </c>
       <c r="O23" t="n">
-        <v>50730</v>
-      </c>
-      <c r="P23" s="6" t="n">
-        <v/>
+        <v>51045</v>
+      </c>
+      <c r="P23" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q23" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="R23" s="6" t="inlineStr">
@@ -2460,7 +2462,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S23" s="10" t="inlineStr">
+      <c r="S23" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -2476,79 +2478,71 @@
       </c>
       <c r="W23" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>48451</v>
+        <v>47177</v>
       </c>
       <c r="C24" t="n">
-        <v>49121</v>
+        <v>48266</v>
       </c>
       <c r="D24" t="n">
-        <v>47025</v>
+        <v>46333</v>
       </c>
       <c r="E24" t="n">
-        <v>47517</v>
+        <v>46592</v>
       </c>
       <c r="F24" t="n">
-        <v>-1483</v>
+        <v>-925</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-0.0303</v>
+        <v>-0.0195</v>
       </c>
       <c r="H24" t="n">
-        <v>2096</v>
+        <v>1933</v>
       </c>
       <c r="I24" t="n">
-        <v>47526</v>
+        <v>44929</v>
       </c>
       <c r="J24" t="n">
-        <v>47684.25</v>
+        <v>45143</v>
       </c>
       <c r="K24" t="n">
-        <v>48413.5</v>
+        <v>46469</v>
       </c>
       <c r="L24" t="n">
-        <v>49142.75</v>
+        <v>47795</v>
       </c>
       <c r="M24" t="n">
-        <v>49586.5</v>
+        <v>48565</v>
       </c>
       <c r="N24" t="n">
-        <v>50030.25</v>
+        <v>49335</v>
       </c>
       <c r="O24" t="n">
-        <v>51045</v>
-      </c>
-      <c r="P24" s="6" t="inlineStr">
+        <v>51217</v>
+      </c>
+      <c r="P24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R24" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q24" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R24" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S24" s="10" t="inlineStr">
+      <c r="S24" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -2562,7 +2556,7 @@
       <c r="V24" s="8" t="n">
         <v/>
       </c>
-      <c r="W24" s="11" t="inlineStr">
+      <c r="W24" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2572,50 +2566,50 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>47177</v>
+        <v>46392</v>
       </c>
       <c r="C25" t="n">
-        <v>48266</v>
+        <v>47457</v>
       </c>
       <c r="D25" t="n">
-        <v>46333</v>
+        <v>45713</v>
       </c>
       <c r="E25" t="n">
-        <v>46592</v>
+        <v>45897</v>
       </c>
       <c r="F25" t="n">
-        <v>-925</v>
+        <v>-695</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.0195</v>
+        <v>-0.0149</v>
       </c>
       <c r="H25" t="n">
-        <v>1933</v>
+        <v>1744</v>
       </c>
       <c r="I25" t="n">
-        <v>44929</v>
+        <v>44400</v>
       </c>
       <c r="J25" t="n">
-        <v>45143</v>
+        <v>44305.25</v>
       </c>
       <c r="K25" t="n">
-        <v>46469</v>
+        <v>45625.5</v>
       </c>
       <c r="L25" t="n">
-        <v>47795</v>
+        <v>46945.75</v>
       </c>
       <c r="M25" t="n">
-        <v>48565</v>
+        <v>47558.5</v>
       </c>
       <c r="N25" t="n">
-        <v>49335</v>
+        <v>48171.25</v>
       </c>
       <c r="O25" t="n">
-        <v>51217</v>
+        <v>50199</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2628,7 +2622,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S25" s="10" t="inlineStr">
+      <c r="S25" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -2642,7 +2636,7 @@
       <c r="V25" s="8" t="n">
         <v/>
       </c>
-      <c r="W25" s="11" t="inlineStr">
+      <c r="W25" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2652,50 +2646,50 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>46392</v>
+        <v>45605</v>
       </c>
       <c r="C26" t="n">
-        <v>47457</v>
+        <v>47210</v>
       </c>
       <c r="D26" t="n">
-        <v>45713</v>
+        <v>45272</v>
       </c>
       <c r="E26" t="n">
-        <v>45897</v>
+        <v>45424</v>
       </c>
       <c r="F26" t="n">
-        <v>-695</v>
+        <v>-473</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.0149</v>
+        <v>-0.0103</v>
       </c>
       <c r="H26" t="n">
-        <v>1744</v>
+        <v>1938</v>
       </c>
       <c r="I26" t="n">
-        <v>44400</v>
+        <v>43969</v>
       </c>
       <c r="J26" t="n">
-        <v>44305.25</v>
+        <v>43809</v>
       </c>
       <c r="K26" t="n">
-        <v>45625.5</v>
+        <v>45025</v>
       </c>
       <c r="L26" t="n">
-        <v>46945.75</v>
+        <v>46241</v>
       </c>
       <c r="M26" t="n">
-        <v>47558.5</v>
+        <v>46769</v>
       </c>
       <c r="N26" t="n">
-        <v>48171.25</v>
+        <v>47297</v>
       </c>
       <c r="O26" t="n">
-        <v>50199</v>
+        <v>49201</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2708,13 +2702,15 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S26" s="10" t="inlineStr">
+      <c r="S26" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T26" s="8" t="n">
-        <v/>
+      <c r="T26" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U26" s="8" t="n">
         <v/>
@@ -2722,7 +2718,7 @@
       <c r="V26" s="8" t="n">
         <v/>
       </c>
-      <c r="W26" s="11" t="inlineStr">
+      <c r="W26" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2732,50 +2728,50 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>45605</v>
+        <v>45244</v>
       </c>
       <c r="C27" t="n">
-        <v>47210</v>
+        <v>47090</v>
       </c>
       <c r="D27" t="n">
-        <v>45272</v>
+        <v>45052</v>
       </c>
       <c r="E27" t="n">
-        <v>45424</v>
+        <v>46629</v>
       </c>
       <c r="F27" t="n">
-        <v>-473</v>
+        <v>1205</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.0103</v>
+        <v>0.0265</v>
       </c>
       <c r="H27" t="n">
-        <v>1938</v>
+        <v>2038</v>
       </c>
       <c r="I27" t="n">
-        <v>43969</v>
+        <v>43334</v>
       </c>
       <c r="J27" t="n">
-        <v>43809</v>
+        <v>43077.5</v>
       </c>
       <c r="K27" t="n">
-        <v>45025</v>
+        <v>44455</v>
       </c>
       <c r="L27" t="n">
-        <v>46241</v>
+        <v>45832.5</v>
       </c>
       <c r="M27" t="n">
-        <v>46769</v>
+        <v>46393</v>
       </c>
       <c r="N27" t="n">
-        <v>47297</v>
+        <v>46953.5</v>
       </c>
       <c r="O27" t="n">
-        <v>49201</v>
+        <v>49148</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2783,81 +2779,85 @@
       <c r="Q27" s="6" t="n">
         <v/>
       </c>
-      <c r="R27" s="6" t="inlineStr">
+      <c r="R27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S27" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S27" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="inlineStr">
+      <c r="U27" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U27" s="8" t="n">
-        <v/>
-      </c>
       <c r="V27" s="8" t="n">
         <v/>
       </c>
-      <c r="W27" s="11" t="inlineStr">
+      <c r="W27" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr"/>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>45244</v>
+        <v>46569</v>
       </c>
       <c r="C28" t="n">
-        <v>47090</v>
+        <v>48555</v>
       </c>
       <c r="D28" t="n">
-        <v>45052</v>
+        <v>46362</v>
       </c>
       <c r="E28" t="n">
-        <v>46629</v>
+        <v>48129</v>
       </c>
       <c r="F28" t="n">
-        <v>1205</v>
+        <v>1500</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.0265</v>
+        <v>0.0322</v>
       </c>
       <c r="H28" t="n">
-        <v>2038</v>
+        <v>2193</v>
       </c>
       <c r="I28" t="n">
-        <v>43334</v>
+        <v>43014</v>
       </c>
       <c r="J28" t="n">
-        <v>43077.5</v>
+        <v>44870</v>
       </c>
       <c r="K28" t="n">
-        <v>44455</v>
+        <v>45610</v>
       </c>
       <c r="L28" t="n">
-        <v>45832.5</v>
+        <v>46350</v>
       </c>
       <c r="M28" t="n">
-        <v>46393</v>
+        <v>47648</v>
       </c>
       <c r="N28" t="n">
-        <v>46953.5</v>
+        <v>48946</v>
       </c>
       <c r="O28" t="n">
-        <v>49148</v>
+        <v>49128</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2868,7 +2868,7 @@
       <c r="R28" s="6" t="n">
         <v/>
       </c>
-      <c r="S28" s="7" t="inlineStr">
+      <c r="S28" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -2878,72 +2878,70 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U28" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U28" s="8" t="n">
+        <v/>
       </c>
       <c r="V28" s="8" t="n">
         <v/>
       </c>
-      <c r="W28" s="11" t="inlineStr">
+      <c r="W28" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>46569</v>
+        <v>47674</v>
       </c>
       <c r="C29" t="n">
-        <v>48555</v>
+        <v>49924</v>
       </c>
       <c r="D29" t="n">
-        <v>46362</v>
+        <v>47534</v>
       </c>
       <c r="E29" t="n">
-        <v>48129</v>
+        <v>49641</v>
       </c>
       <c r="F29" t="n">
-        <v>1500</v>
+        <v>1512</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.0322</v>
+        <v>0.0314</v>
       </c>
       <c r="H29" t="n">
-        <v>2193</v>
+        <v>2390</v>
       </c>
       <c r="I29" t="n">
-        <v>43014</v>
+        <v>44169</v>
       </c>
       <c r="J29" t="n">
-        <v>44870</v>
+        <v>46271.25</v>
       </c>
       <c r="K29" t="n">
-        <v>45610</v>
+        <v>47032.5</v>
       </c>
       <c r="L29" t="n">
-        <v>46350</v>
+        <v>47793.75</v>
       </c>
       <c r="M29" t="n">
-        <v>47648</v>
+        <v>49225.5</v>
       </c>
       <c r="N29" t="n">
-        <v>48946</v>
+        <v>50657.25</v>
       </c>
       <c r="O29" t="n">
-        <v>49128</v>
+        <v>50748</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2954,7 +2952,7 @@
       <c r="R29" s="6" t="n">
         <v/>
       </c>
-      <c r="S29" s="7" t="inlineStr">
+      <c r="S29" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -2970,7 +2968,7 @@
       <c r="V29" s="8" t="n">
         <v/>
       </c>
-      <c r="W29" s="11" t="inlineStr">
+      <c r="W29" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2984,50 +2982,50 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>47674</v>
+        <v>49324</v>
       </c>
       <c r="C30" t="n">
-        <v>49924</v>
+        <v>50043</v>
       </c>
       <c r="D30" t="n">
-        <v>47534</v>
+        <v>49036</v>
       </c>
       <c r="E30" t="n">
-        <v>49641</v>
+        <v>49392</v>
       </c>
       <c r="F30" t="n">
-        <v>1512</v>
+        <v>-249</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.0314</v>
+        <v>-0.005</v>
       </c>
       <c r="H30" t="n">
-        <v>2390</v>
+        <v>1007</v>
       </c>
       <c r="I30" t="n">
-        <v>44169</v>
+        <v>45144</v>
       </c>
       <c r="J30" t="n">
-        <v>46271.25</v>
+        <v>47707</v>
       </c>
       <c r="K30" t="n">
-        <v>47032.5</v>
+        <v>48446</v>
       </c>
       <c r="L30" t="n">
-        <v>47793.75</v>
+        <v>49185</v>
       </c>
       <c r="M30" t="n">
-        <v>49225.5</v>
+        <v>50836</v>
       </c>
       <c r="N30" t="n">
-        <v>50657.25</v>
+        <v>52487</v>
       </c>
       <c r="O30" t="n">
-        <v>50748</v>
+        <v>52314</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3038,15 +3036,13 @@
       <c r="R30" s="6" t="n">
         <v/>
       </c>
-      <c r="S30" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S30" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="n">
+        <v/>
       </c>
       <c r="U30" s="8" t="n">
         <v/>
@@ -3054,64 +3050,64 @@
       <c r="V30" s="8" t="n">
         <v/>
       </c>
-      <c r="W30" s="11" t="inlineStr">
+      <c r="W30" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>49324</v>
+        <v>49382</v>
       </c>
       <c r="C31" t="n">
-        <v>50043</v>
+        <v>50138</v>
       </c>
       <c r="D31" t="n">
-        <v>49036</v>
+        <v>48608</v>
       </c>
       <c r="E31" t="n">
-        <v>49392</v>
+        <v>49646</v>
       </c>
       <c r="F31" t="n">
-        <v>-249</v>
+        <v>254</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-0.005</v>
+        <v>0.0051</v>
       </c>
       <c r="H31" t="n">
-        <v>1007</v>
+        <v>1530</v>
       </c>
       <c r="I31" t="n">
-        <v>45144</v>
+        <v>48029</v>
       </c>
       <c r="J31" t="n">
-        <v>47707</v>
+        <v>48311.25</v>
       </c>
       <c r="K31" t="n">
-        <v>48446</v>
+        <v>48888.5</v>
       </c>
       <c r="L31" t="n">
-        <v>49185</v>
+        <v>49465.75</v>
       </c>
       <c r="M31" t="n">
-        <v>50836</v>
+        <v>49895.5</v>
       </c>
       <c r="N31" t="n">
-        <v>52487</v>
+        <v>50325.25</v>
       </c>
       <c r="O31" t="n">
-        <v>52314</v>
+        <v>51050</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3119,16 +3115,20 @@
       <c r="Q31" s="6" t="n">
         <v/>
       </c>
-      <c r="R31" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S31" s="7" t="inlineStr">
+      <c r="R31" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S31" s="10" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
       </c>
-      <c r="T31" s="8" t="n">
-        <v/>
+      <c r="T31" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U31" s="8" t="n">
         <v/>
@@ -3136,7 +3136,7 @@
       <c r="V31" s="8" t="n">
         <v/>
       </c>
-      <c r="W31" s="11" t="inlineStr">
+      <c r="W31" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3150,50 +3150,50 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>49382</v>
+        <v>49705</v>
       </c>
       <c r="C32" t="n">
-        <v>50138</v>
+        <v>50238</v>
       </c>
       <c r="D32" t="n">
-        <v>48608</v>
+        <v>49016</v>
       </c>
       <c r="E32" t="n">
-        <v>49646</v>
+        <v>49691</v>
       </c>
       <c r="F32" t="n">
-        <v>254</v>
+        <v>45</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.0051</v>
+        <v>0.0009</v>
       </c>
       <c r="H32" t="n">
-        <v>1530</v>
+        <v>1222</v>
       </c>
       <c r="I32" t="n">
-        <v>48029</v>
+        <v>47078</v>
       </c>
       <c r="J32" t="n">
-        <v>48311.25</v>
+        <v>48252.5</v>
       </c>
       <c r="K32" t="n">
-        <v>48888.5</v>
+        <v>48881</v>
       </c>
       <c r="L32" t="n">
-        <v>49465.75</v>
+        <v>49509.5</v>
       </c>
       <c r="M32" t="n">
-        <v>49895.5</v>
+        <v>50411</v>
       </c>
       <c r="N32" t="n">
-        <v>50325.25</v>
+        <v>51312.5</v>
       </c>
       <c r="O32" t="n">
-        <v>51050</v>
+        <v>51668</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3201,20 +3201,16 @@
       <c r="Q32" s="6" t="n">
         <v/>
       </c>
-      <c r="R32" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S32" s="7" t="inlineStr">
+      <c r="R32" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S32" s="10" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
       </c>
-      <c r="T32" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T32" s="8" t="n">
+        <v/>
       </c>
       <c r="U32" s="8" t="n">
         <v/>
@@ -3222,64 +3218,64 @@
       <c r="V32" s="8" t="n">
         <v/>
       </c>
-      <c r="W32" s="11" t="inlineStr">
+      <c r="W32" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>49705</v>
+        <v>49640</v>
       </c>
       <c r="C33" t="n">
-        <v>50238</v>
+        <v>50292</v>
       </c>
       <c r="D33" t="n">
-        <v>49016</v>
+        <v>49397</v>
       </c>
       <c r="E33" t="n">
-        <v>49691</v>
+        <v>49617</v>
       </c>
       <c r="F33" t="n">
-        <v>45</v>
+        <v>-74</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0009</v>
+        <v>-0.0015</v>
       </c>
       <c r="H33" t="n">
-        <v>1222</v>
+        <v>895</v>
       </c>
       <c r="I33" t="n">
-        <v>47078</v>
+        <v>47794</v>
       </c>
       <c r="J33" t="n">
-        <v>48252.5</v>
+        <v>48501</v>
       </c>
       <c r="K33" t="n">
-        <v>48881</v>
+        <v>49080</v>
       </c>
       <c r="L33" t="n">
-        <v>49509.5</v>
+        <v>49659</v>
       </c>
       <c r="M33" t="n">
-        <v>50411</v>
+        <v>50302</v>
       </c>
       <c r="N33" t="n">
-        <v>51312.5</v>
+        <v>50945</v>
       </c>
       <c r="O33" t="n">
-        <v>51668</v>
+        <v>51460</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3292,7 +3288,7 @@
       </c>
       <c r="S33" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T33" s="8" t="n">
@@ -3304,64 +3300,64 @@
       <c r="V33" s="8" t="n">
         <v/>
       </c>
-      <c r="W33" s="11" t="inlineStr">
+      <c r="W33" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>49640</v>
+        <v>49464</v>
       </c>
       <c r="C34" t="n">
-        <v>50292</v>
+        <v>50920</v>
       </c>
       <c r="D34" t="n">
-        <v>49397</v>
+        <v>49152</v>
       </c>
       <c r="E34" t="n">
-        <v>49617</v>
+        <v>50662</v>
       </c>
       <c r="F34" t="n">
-        <v>-74</v>
+        <v>1045</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>-0.0015</v>
+        <v>0.0211</v>
       </c>
       <c r="H34" t="n">
-        <v>895</v>
+        <v>1768</v>
       </c>
       <c r="I34" t="n">
-        <v>47794</v>
+        <v>48502</v>
       </c>
       <c r="J34" t="n">
-        <v>48501</v>
+        <v>48608.25</v>
       </c>
       <c r="K34" t="n">
-        <v>49080</v>
+        <v>49169.5</v>
       </c>
       <c r="L34" t="n">
-        <v>49659</v>
+        <v>49730.75</v>
       </c>
       <c r="M34" t="n">
-        <v>50302</v>
+        <v>50064.5</v>
       </c>
       <c r="N34" t="n">
-        <v>50945</v>
+        <v>50398.25</v>
       </c>
       <c r="O34" t="n">
-        <v>51460</v>
+        <v>51187</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3369,81 +3365,87 @@
       <c r="Q34" s="6" t="n">
         <v/>
       </c>
-      <c r="R34" s="6" t="n">
-        <v/>
+      <c r="R34" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S34" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U34" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U34" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V34" s="8" t="n">
         <v/>
       </c>
       <c r="W34" s="11" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>49464</v>
+        <v>50776</v>
       </c>
       <c r="C35" t="n">
-        <v>50920</v>
+        <v>51209</v>
       </c>
       <c r="D35" t="n">
-        <v>49152</v>
+        <v>50386</v>
       </c>
       <c r="E35" t="n">
-        <v>50662</v>
+        <v>51077</v>
       </c>
       <c r="F35" t="n">
-        <v>1045</v>
+        <v>415</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.0211</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="H35" t="n">
-        <v>1768</v>
+        <v>823</v>
       </c>
       <c r="I35" t="n">
-        <v>48502</v>
+        <v>47384</v>
       </c>
       <c r="J35" t="n">
-        <v>48608.25</v>
+        <v>49207</v>
       </c>
       <c r="K35" t="n">
-        <v>49169.5</v>
+        <v>49778</v>
       </c>
       <c r="L35" t="n">
-        <v>49730.75</v>
+        <v>50349</v>
       </c>
       <c r="M35" t="n">
-        <v>50064.5</v>
+        <v>51546</v>
       </c>
       <c r="N35" t="n">
-        <v>50398.25</v>
+        <v>52743</v>
       </c>
       <c r="O35" t="n">
-        <v>51187</v>
+        <v>52688</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3451,87 +3453,79 @@
       <c r="Q35" s="6" t="n">
         <v/>
       </c>
-      <c r="R35" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S35" s="7" t="inlineStr">
+      <c r="R35" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S35" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T35" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U35" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U35" s="8" t="n">
+        <v/>
+      </c>
       <c r="V35" s="8" t="n">
         <v/>
       </c>
-      <c r="W35" s="9" t="inlineStr">
+      <c r="W35" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>50776</v>
+        <v>51128</v>
       </c>
       <c r="C36" t="n">
-        <v>51209</v>
+        <v>51849</v>
       </c>
       <c r="D36" t="n">
-        <v>50386</v>
+        <v>50736</v>
       </c>
       <c r="E36" t="n">
-        <v>51077</v>
+        <v>50936</v>
       </c>
       <c r="F36" t="n">
-        <v>415</v>
+        <v>-141</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.008200000000000001</v>
+        <v>-0.0028</v>
       </c>
       <c r="H36" t="n">
-        <v>823</v>
+        <v>1113</v>
       </c>
       <c r="I36" t="n">
-        <v>47384</v>
+        <v>49563</v>
       </c>
       <c r="J36" t="n">
-        <v>49207</v>
+        <v>50393.75</v>
       </c>
       <c r="K36" t="n">
-        <v>49778</v>
+        <v>50665.5</v>
       </c>
       <c r="L36" t="n">
-        <v>50349</v>
+        <v>50937.25</v>
       </c>
       <c r="M36" t="n">
-        <v>51546</v>
+        <v>51488.5</v>
       </c>
       <c r="N36" t="n">
-        <v>52743</v>
+        <v>52039.75</v>
       </c>
       <c r="O36" t="n">
-        <v>52688</v>
+        <v>52032</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3544,12 +3538,12 @@
       </c>
       <c r="S36" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T36" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U36" s="8" t="n">
@@ -3558,60 +3552,64 @@
       <c r="V36" s="8" t="n">
         <v/>
       </c>
-      <c r="W36" s="9" t="inlineStr">
+      <c r="W36" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr"/>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>51128</v>
+        <v>50796</v>
       </c>
       <c r="C37" t="n">
-        <v>51849</v>
+        <v>51443</v>
       </c>
       <c r="D37" t="n">
-        <v>50736</v>
+        <v>49758</v>
       </c>
       <c r="E37" t="n">
-        <v>50936</v>
+        <v>51227</v>
       </c>
       <c r="F37" t="n">
-        <v>-141</v>
+        <v>291</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.0028</v>
+        <v>0.0057</v>
       </c>
       <c r="H37" t="n">
-        <v>1113</v>
+        <v>1685</v>
       </c>
       <c r="I37" t="n">
-        <v>49563</v>
+        <v>49623</v>
       </c>
       <c r="J37" t="n">
-        <v>50393.75</v>
+        <v>49644.75</v>
       </c>
       <c r="K37" t="n">
-        <v>50665.5</v>
+        <v>50379.5</v>
       </c>
       <c r="L37" t="n">
-        <v>50937.25</v>
+        <v>51114.25</v>
       </c>
       <c r="M37" t="n">
-        <v>51488.5</v>
+        <v>51492.5</v>
       </c>
       <c r="N37" t="n">
-        <v>52039.75</v>
+        <v>51870.75</v>
       </c>
       <c r="O37" t="n">
-        <v>52032</v>
+        <v>52962</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3619,18 +3617,18 @@
       <c r="Q37" s="6" t="n">
         <v/>
       </c>
-      <c r="R37" s="6" t="n">
-        <v/>
+      <c r="R37" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S37" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="n">
+        <v/>
       </c>
       <c r="U37" s="8" t="n">
         <v/>
@@ -3638,64 +3636,64 @@
       <c r="V37" s="8" t="n">
         <v/>
       </c>
-      <c r="W37" s="9" t="inlineStr">
+      <c r="W37" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>50796</v>
+        <v>51450</v>
       </c>
       <c r="C38" t="n">
-        <v>51443</v>
+        <v>52300</v>
       </c>
       <c r="D38" t="n">
-        <v>49758</v>
+        <v>51420</v>
       </c>
       <c r="E38" t="n">
-        <v>51227</v>
+        <v>51888</v>
       </c>
       <c r="F38" t="n">
-        <v>291</v>
+        <v>661</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.0057</v>
+        <v>0.0129</v>
       </c>
       <c r="H38" t="n">
-        <v>1685</v>
+        <v>880</v>
       </c>
       <c r="I38" t="n">
-        <v>49623</v>
+        <v>48073</v>
       </c>
       <c r="J38" t="n">
-        <v>49644.75</v>
+        <v>49855.25</v>
       </c>
       <c r="K38" t="n">
-        <v>50379.5</v>
+        <v>50384.5</v>
       </c>
       <c r="L38" t="n">
-        <v>51114.25</v>
+        <v>50913.75</v>
       </c>
       <c r="M38" t="n">
-        <v>51492.5</v>
+        <v>52069.5</v>
       </c>
       <c r="N38" t="n">
-        <v>51870.75</v>
+        <v>53225.25</v>
       </c>
       <c r="O38" t="n">
-        <v>52962</v>
+        <v>53128</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3703,18 +3701,18 @@
       <c r="Q38" s="6" t="n">
         <v/>
       </c>
-      <c r="R38" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S38" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="n">
-        <v/>
+      <c r="R38" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S38" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U38" s="8" t="n">
         <v/>
@@ -3722,64 +3720,60 @@
       <c r="V38" s="8" t="n">
         <v/>
       </c>
-      <c r="W38" s="9" t="inlineStr">
+      <c r="W38" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>51450</v>
+        <v>51870</v>
       </c>
       <c r="C39" t="n">
-        <v>52300</v>
+        <v>53097</v>
       </c>
       <c r="D39" t="n">
-        <v>51420</v>
+        <v>51691</v>
       </c>
       <c r="E39" t="n">
-        <v>51888</v>
+        <v>52209</v>
       </c>
       <c r="F39" t="n">
-        <v>661</v>
+        <v>321</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.0129</v>
+        <v>0.0062</v>
       </c>
       <c r="H39" t="n">
-        <v>880</v>
+        <v>1406</v>
       </c>
       <c r="I39" t="n">
-        <v>48073</v>
+        <v>50540</v>
       </c>
       <c r="J39" t="n">
-        <v>49855.25</v>
+        <v>51022</v>
       </c>
       <c r="K39" t="n">
-        <v>50384.5</v>
+        <v>51448</v>
       </c>
       <c r="L39" t="n">
-        <v>50913.75</v>
+        <v>51874</v>
       </c>
       <c r="M39" t="n">
-        <v>52069.5</v>
+        <v>52328</v>
       </c>
       <c r="N39" t="n">
-        <v>53225.25</v>
+        <v>52782</v>
       </c>
       <c r="O39" t="n">
-        <v>53128</v>
+        <v>53180</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3790,7 +3784,7 @@
       <c r="R39" s="6" t="n">
         <v/>
       </c>
-      <c r="S39" s="7" t="inlineStr">
+      <c r="S39" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3800,13 +3794,15 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U39" s="8" t="n">
-        <v/>
+      <c r="U39" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V39" s="8" t="n">
         <v/>
       </c>
-      <c r="W39" s="9" t="inlineStr">
+      <c r="W39" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3816,50 +3812,50 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>51870</v>
+        <v>52183</v>
       </c>
       <c r="C40" t="n">
-        <v>53097</v>
+        <v>53400</v>
       </c>
       <c r="D40" t="n">
-        <v>51691</v>
+        <v>52179</v>
       </c>
       <c r="E40" t="n">
-        <v>52209</v>
+        <v>53162</v>
       </c>
       <c r="F40" t="n">
-        <v>321</v>
+        <v>953</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.0062</v>
+        <v>0.0183</v>
       </c>
       <c r="H40" t="n">
-        <v>1406</v>
+        <v>1221</v>
       </c>
       <c r="I40" t="n">
-        <v>50540</v>
+        <v>50285</v>
       </c>
       <c r="J40" t="n">
-        <v>51022</v>
+        <v>50710.5</v>
       </c>
       <c r="K40" t="n">
-        <v>51448</v>
+        <v>51506</v>
       </c>
       <c r="L40" t="n">
-        <v>51874</v>
+        <v>52301.5</v>
       </c>
       <c r="M40" t="n">
-        <v>52328</v>
+        <v>52912</v>
       </c>
       <c r="N40" t="n">
-        <v>52782</v>
+        <v>53522.5</v>
       </c>
       <c r="O40" t="n">
-        <v>53180</v>
+        <v>54503</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3870,7 +3866,7 @@
       <c r="R40" s="6" t="n">
         <v/>
       </c>
-      <c r="S40" s="7" t="inlineStr">
+      <c r="S40" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3880,15 +3876,13 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U40" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U40" s="8" t="n">
+        <v/>
       </c>
       <c r="V40" s="8" t="n">
         <v/>
       </c>
-      <c r="W40" s="9" t="inlineStr">
+      <c r="W40" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3898,50 +3892,50 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>52183</v>
+        <v>53230</v>
       </c>
       <c r="C41" t="n">
-        <v>53400</v>
+        <v>53656</v>
       </c>
       <c r="D41" t="n">
-        <v>52179</v>
+        <v>52343</v>
       </c>
       <c r="E41" t="n">
-        <v>53162</v>
+        <v>52906</v>
       </c>
       <c r="F41" t="n">
-        <v>953</v>
+        <v>-256</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.0183</v>
+        <v>-0.0048</v>
       </c>
       <c r="H41" t="n">
-        <v>1221</v>
+        <v>1313</v>
       </c>
       <c r="I41" t="n">
-        <v>50285</v>
+        <v>50958</v>
       </c>
       <c r="J41" t="n">
-        <v>50710.5</v>
+        <v>52127.25</v>
       </c>
       <c r="K41" t="n">
-        <v>51506</v>
+        <v>52551.5</v>
       </c>
       <c r="L41" t="n">
-        <v>52301.5</v>
+        <v>52975.75</v>
       </c>
       <c r="M41" t="n">
-        <v>52912</v>
+        <v>53772.5</v>
       </c>
       <c r="N41" t="n">
-        <v>53522.5</v>
+        <v>54569.25</v>
       </c>
       <c r="O41" t="n">
-        <v>54503</v>
+        <v>54621</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3949,18 +3943,18 @@
       <c r="Q41" s="6" t="n">
         <v/>
       </c>
-      <c r="R41" s="6" t="n">
-        <v/>
+      <c r="R41" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S41" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="n">
+        <v/>
       </c>
       <c r="U41" s="8" t="n">
         <v/>
@@ -3968,60 +3962,64 @@
       <c r="V41" s="8" t="n">
         <v/>
       </c>
-      <c r="W41" s="9" t="inlineStr">
+      <c r="W41" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr"/>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>53230</v>
+        <v>52844</v>
       </c>
       <c r="C42" t="n">
-        <v>53656</v>
+        <v>53113</v>
       </c>
       <c r="D42" t="n">
-        <v>52343</v>
+        <v>52174</v>
       </c>
       <c r="E42" t="n">
-        <v>52906</v>
+        <v>52375</v>
       </c>
       <c r="F42" t="n">
-        <v>-256</v>
+        <v>-531</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.0048</v>
+        <v>-0.01</v>
       </c>
       <c r="H42" t="n">
-        <v>1313</v>
+        <v>939</v>
       </c>
       <c r="I42" t="n">
-        <v>50958</v>
+        <v>51030</v>
       </c>
       <c r="J42" t="n">
-        <v>52127.25</v>
+        <v>51546.25</v>
       </c>
       <c r="K42" t="n">
-        <v>52551.5</v>
+        <v>52249.5</v>
       </c>
       <c r="L42" t="n">
-        <v>52975.75</v>
+        <v>52952.75</v>
       </c>
       <c r="M42" t="n">
-        <v>53772.5</v>
+        <v>53562.5</v>
       </c>
       <c r="N42" t="n">
-        <v>54569.25</v>
+        <v>54172.25</v>
       </c>
       <c r="O42" t="n">
-        <v>54621</v>
+        <v>54969</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4031,12 +4029,12 @@
       </c>
       <c r="R42" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S42" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S42" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T42" s="8" t="n">
@@ -4048,64 +4046,64 @@
       <c r="V42" s="8" t="n">
         <v/>
       </c>
-      <c r="W42" s="9" t="inlineStr">
+      <c r="W42" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>52844</v>
+        <v>52300</v>
       </c>
       <c r="C43" t="n">
-        <v>53113</v>
+        <v>52721</v>
       </c>
       <c r="D43" t="n">
-        <v>52174</v>
+        <v>51720</v>
       </c>
       <c r="E43" t="n">
-        <v>52375</v>
+        <v>52124</v>
       </c>
       <c r="F43" t="n">
-        <v>-531</v>
+        <v>-251</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.01</v>
+        <v>-0.0048</v>
       </c>
       <c r="H43" t="n">
-        <v>939</v>
+        <v>1001</v>
       </c>
       <c r="I43" t="n">
-        <v>51030</v>
+        <v>51235</v>
       </c>
       <c r="J43" t="n">
-        <v>51546.25</v>
+        <v>51301.75</v>
       </c>
       <c r="K43" t="n">
-        <v>52249.5</v>
+        <v>51905.5</v>
       </c>
       <c r="L43" t="n">
-        <v>52952.75</v>
+        <v>52509.25</v>
       </c>
       <c r="M43" t="n">
-        <v>53562.5</v>
+        <v>52844.5</v>
       </c>
       <c r="N43" t="n">
-        <v>54172.25</v>
+        <v>53179.75</v>
       </c>
       <c r="O43" t="n">
-        <v>54969</v>
+        <v>54052</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4118,7 +4116,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S43" s="10" t="inlineStr">
+      <c r="S43" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4132,7 +4130,7 @@
       <c r="V43" s="8" t="n">
         <v/>
       </c>
-      <c r="W43" s="9" t="inlineStr">
+      <c r="W43" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4146,50 +4144,50 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>52300</v>
+        <v>52299</v>
       </c>
       <c r="C44" t="n">
-        <v>52721</v>
+        <v>53105</v>
       </c>
       <c r="D44" t="n">
-        <v>51720</v>
+        <v>51630</v>
       </c>
       <c r="E44" t="n">
-        <v>52124</v>
+        <v>52635</v>
       </c>
       <c r="F44" t="n">
-        <v>-251</v>
+        <v>511</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.0048</v>
+        <v>0.0098</v>
       </c>
       <c r="H44" t="n">
-        <v>1001</v>
+        <v>1475</v>
       </c>
       <c r="I44" t="n">
-        <v>51235</v>
+        <v>50719</v>
       </c>
       <c r="J44" t="n">
-        <v>51301.75</v>
+        <v>51074.75</v>
       </c>
       <c r="K44" t="n">
-        <v>51905.5</v>
+        <v>51623.5</v>
       </c>
       <c r="L44" t="n">
-        <v>52509.25</v>
+        <v>52172.25</v>
       </c>
       <c r="M44" t="n">
-        <v>52844.5</v>
+        <v>52624.5</v>
       </c>
       <c r="N44" t="n">
-        <v>53179.75</v>
+        <v>53076.75</v>
       </c>
       <c r="O44" t="n">
-        <v>54052</v>
+        <v>53722</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4197,83 +4195,85 @@
       <c r="Q44" s="6" t="n">
         <v/>
       </c>
-      <c r="R44" s="6" t="inlineStr">
+      <c r="R44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S44" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S44" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U44" s="8" t="n">
-        <v/>
+      <c r="U44" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V44" s="8" t="n">
         <v/>
       </c>
-      <c r="W44" s="9" t="inlineStr">
+      <c r="W44" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>52299</v>
+        <v>52780</v>
       </c>
       <c r="C45" t="n">
-        <v>53105</v>
+        <v>54884</v>
       </c>
       <c r="D45" t="n">
-        <v>51630</v>
+        <v>52777</v>
       </c>
       <c r="E45" t="n">
-        <v>52635</v>
+        <v>54152</v>
       </c>
       <c r="F45" t="n">
-        <v>511</v>
+        <v>1517</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.0098</v>
+        <v>0.0288</v>
       </c>
       <c r="H45" t="n">
-        <v>1475</v>
+        <v>2107</v>
       </c>
       <c r="I45" t="n">
-        <v>50719</v>
+        <v>50155</v>
       </c>
       <c r="J45" t="n">
-        <v>51074.75</v>
+        <v>51293.75</v>
       </c>
       <c r="K45" t="n">
-        <v>51623.5</v>
+        <v>51897.5</v>
       </c>
       <c r="L45" t="n">
-        <v>52172.25</v>
+        <v>52501.25</v>
       </c>
       <c r="M45" t="n">
-        <v>52624.5</v>
+        <v>53372.5</v>
       </c>
       <c r="N45" t="n">
-        <v>53076.75</v>
+        <v>54243.75</v>
       </c>
       <c r="O45" t="n">
-        <v>53722</v>
+        <v>54580</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4284,82 +4284,80 @@
       <c r="R45" s="6" t="n">
         <v/>
       </c>
-      <c r="S45" s="7" t="inlineStr">
+      <c r="S45" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T45" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U45" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U45" s="8" t="inlineStr">
+      <c r="V45" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="V45" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W45" s="9" t="inlineStr">
+      <c r="W45" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>52780</v>
+        <v>54133</v>
       </c>
       <c r="C46" t="n">
-        <v>54884</v>
+        <v>54336</v>
       </c>
       <c r="D46" t="n">
-        <v>52777</v>
+        <v>53715</v>
       </c>
       <c r="E46" t="n">
-        <v>54152</v>
+        <v>53807</v>
       </c>
       <c r="F46" t="n">
-        <v>1517</v>
+        <v>-345</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.0288</v>
+        <v>-0.0064</v>
       </c>
       <c r="H46" t="n">
-        <v>2107</v>
+        <v>621</v>
       </c>
       <c r="I46" t="n">
-        <v>50155</v>
+        <v>50670</v>
       </c>
       <c r="J46" t="n">
-        <v>51293.75</v>
+        <v>52205.75</v>
       </c>
       <c r="K46" t="n">
-        <v>51897.5</v>
+        <v>53098.5</v>
       </c>
       <c r="L46" t="n">
-        <v>52501.25</v>
+        <v>53991.25</v>
       </c>
       <c r="M46" t="n">
-        <v>53372.5</v>
+        <v>55205.5</v>
       </c>
       <c r="N46" t="n">
-        <v>54243.75</v>
+        <v>56419.75</v>
       </c>
       <c r="O46" t="n">
-        <v>54580</v>
+        <v>56991</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4372,91 +4370,95 @@
       </c>
       <c r="S46" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U46" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V46" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W46" s="9" t="inlineStr">
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U46" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V46" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W46" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr"/>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>54133</v>
+        <v>53790</v>
       </c>
       <c r="C47" t="n">
-        <v>54336</v>
+        <v>53840</v>
       </c>
       <c r="D47" t="n">
-        <v>53715</v>
+        <v>52812</v>
       </c>
       <c r="E47" t="n">
-        <v>53807</v>
+        <v>53353</v>
       </c>
       <c r="F47" t="n">
-        <v>-345</v>
+        <v>-454</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>-0.0064</v>
+        <v>-0.008399999999999999</v>
       </c>
       <c r="H47" t="n">
-        <v>621</v>
+        <v>1028</v>
       </c>
       <c r="I47" t="n">
-        <v>50670</v>
+        <v>53094</v>
       </c>
       <c r="J47" t="n">
-        <v>52205.75</v>
+        <v>53076.75</v>
       </c>
       <c r="K47" t="n">
-        <v>53098.5</v>
+        <v>53496.5</v>
       </c>
       <c r="L47" t="n">
-        <v>53991.25</v>
+        <v>53916.25</v>
       </c>
       <c r="M47" t="n">
-        <v>55205.5</v>
+        <v>54117.5</v>
       </c>
       <c r="N47" t="n">
-        <v>56419.75</v>
+        <v>54318.75</v>
       </c>
       <c r="O47" t="n">
-        <v>56991</v>
-      </c>
-      <c r="P47" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q47" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R47" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S47" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+        <v>54957</v>
+      </c>
+      <c r="P47" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q47" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R47" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S47" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T47" s="8" t="n">
@@ -4468,83 +4470,77 @@
       <c r="V47" s="8" t="n">
         <v/>
       </c>
-      <c r="W47" s="9" t="inlineStr">
+      <c r="W47" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>53790</v>
+        <v>53367</v>
       </c>
       <c r="C48" t="n">
-        <v>53840</v>
+        <v>53862</v>
       </c>
       <c r="D48" t="n">
-        <v>52812</v>
+        <v>53210</v>
       </c>
       <c r="E48" t="n">
-        <v>53353</v>
+        <v>53584</v>
       </c>
       <c r="F48" t="n">
-        <v>-454</v>
+        <v>231</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0.008399999999999999</v>
+        <v>0.0043</v>
       </c>
       <c r="H48" t="n">
-        <v>1028</v>
+        <v>652</v>
       </c>
       <c r="I48" t="n">
-        <v>53094</v>
+        <v>51784</v>
       </c>
       <c r="J48" t="n">
-        <v>53076.75</v>
+        <v>52338.5</v>
       </c>
       <c r="K48" t="n">
-        <v>53496.5</v>
+        <v>52839</v>
       </c>
       <c r="L48" t="n">
-        <v>53916.25</v>
+        <v>53339.5</v>
       </c>
       <c r="M48" t="n">
-        <v>54117.5</v>
+        <v>53867</v>
       </c>
       <c r="N48" t="n">
-        <v>54318.75</v>
+        <v>54394.5</v>
       </c>
       <c r="O48" t="n">
-        <v>54957</v>
-      </c>
-      <c r="P48" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q48" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R48" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+        <v>54868</v>
+      </c>
+      <c r="P48" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q48" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R48" s="6" t="n">
+        <v/>
       </c>
       <c r="S48" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T48" s="8" t="n">
@@ -4556,77 +4552,77 @@
       <c r="V48" s="8" t="n">
         <v/>
       </c>
-      <c r="W48" s="9" t="inlineStr">
+      <c r="W48" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>53367</v>
+        <v>53664</v>
       </c>
       <c r="C49" t="n">
-        <v>53862</v>
+        <v>53827</v>
       </c>
       <c r="D49" t="n">
-        <v>53210</v>
+        <v>52720</v>
       </c>
       <c r="E49" t="n">
-        <v>53584</v>
+        <v>53440</v>
       </c>
       <c r="F49" t="n">
-        <v>231</v>
+        <v>-144</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.0043</v>
+        <v>-0.0027</v>
       </c>
       <c r="H49" t="n">
-        <v>652</v>
+        <v>1107</v>
       </c>
       <c r="I49" t="n">
-        <v>51784</v>
+        <v>52558</v>
       </c>
       <c r="J49" t="n">
-        <v>52338.5</v>
+        <v>52956</v>
       </c>
       <c r="K49" t="n">
-        <v>52839</v>
+        <v>53258</v>
       </c>
       <c r="L49" t="n">
-        <v>53339.5</v>
+        <v>53560</v>
       </c>
       <c r="M49" t="n">
-        <v>53867</v>
+        <v>53910</v>
       </c>
       <c r="N49" t="n">
-        <v>54394.5</v>
+        <v>54260</v>
       </c>
       <c r="O49" t="n">
-        <v>54868</v>
+        <v>54514</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
       </c>
-      <c r="Q49" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R49" s="6" t="n">
-        <v/>
+      <c r="Q49" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R49" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S49" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T49" s="8" t="n">
@@ -4638,77 +4634,81 @@
       <c r="V49" s="8" t="n">
         <v/>
       </c>
-      <c r="W49" s="9" t="inlineStr">
+      <c r="W49" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr"/>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>53664</v>
+        <v>53261</v>
       </c>
       <c r="C50" t="n">
-        <v>53827</v>
+        <v>53336</v>
       </c>
       <c r="D50" t="n">
-        <v>52720</v>
+        <v>51992</v>
       </c>
       <c r="E50" t="n">
-        <v>53440</v>
+        <v>52585</v>
       </c>
       <c r="F50" t="n">
-        <v>-144</v>
+        <v>-855</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.0027</v>
+        <v>-0.016</v>
       </c>
       <c r="H50" t="n">
-        <v>1107</v>
+        <v>1344</v>
       </c>
       <c r="I50" t="n">
-        <v>52558</v>
+        <v>51613</v>
       </c>
       <c r="J50" t="n">
-        <v>52956</v>
+        <v>52416.25</v>
       </c>
       <c r="K50" t="n">
-        <v>53258</v>
+        <v>52886.5</v>
       </c>
       <c r="L50" t="n">
-        <v>53560</v>
+        <v>53356.75</v>
       </c>
       <c r="M50" t="n">
-        <v>53910</v>
+        <v>53993.5</v>
       </c>
       <c r="N50" t="n">
-        <v>54260</v>
+        <v>54630.25</v>
       </c>
       <c r="O50" t="n">
-        <v>54514</v>
+        <v>54934</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
       </c>
       <c r="Q50" s="6" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R50" s="6" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R50" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S50" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S50" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T50" s="8" t="n">
@@ -4720,7 +4720,7 @@
       <c r="V50" s="8" t="n">
         <v/>
       </c>
-      <c r="W50" s="9" t="inlineStr">
+      <c r="W50" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4734,65 +4734,63 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>53261</v>
+        <v>52376</v>
       </c>
       <c r="C51" t="n">
-        <v>53336</v>
+        <v>52672</v>
       </c>
       <c r="D51" t="n">
-        <v>51992</v>
+        <v>51209</v>
       </c>
       <c r="E51" t="n">
-        <v>52585</v>
+        <v>51761</v>
       </c>
       <c r="F51" t="n">
-        <v>-855</v>
+        <v>-824</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.016</v>
+        <v>-0.0157</v>
       </c>
       <c r="H51" t="n">
-        <v>1344</v>
+        <v>1463</v>
       </c>
       <c r="I51" t="n">
-        <v>51613</v>
+        <v>50648</v>
       </c>
       <c r="J51" t="n">
-        <v>52416.25</v>
+        <v>51201.5</v>
       </c>
       <c r="K51" t="n">
-        <v>52886.5</v>
+        <v>51913</v>
       </c>
       <c r="L51" t="n">
-        <v>53356.75</v>
+        <v>52624.5</v>
       </c>
       <c r="M51" t="n">
-        <v>53993.5</v>
+        <v>53257</v>
       </c>
       <c r="N51" t="n">
-        <v>54630.25</v>
+        <v>53889.5</v>
       </c>
       <c r="O51" t="n">
-        <v>54934</v>
+        <v>54680</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
       </c>
-      <c r="Q51" s="6" t="inlineStr">
+      <c r="Q51" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R51" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R51" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S51" s="10" t="inlineStr">
+      <c r="S51" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4806,7 +4804,7 @@
       <c r="V51" s="8" t="n">
         <v/>
       </c>
-      <c r="W51" s="9" t="inlineStr">
+      <c r="W51" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4820,50 +4818,50 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>52376</v>
+        <v>52085</v>
       </c>
       <c r="C52" t="n">
-        <v>52672</v>
+        <v>52844</v>
       </c>
       <c r="D52" t="n">
-        <v>51209</v>
+        <v>51479</v>
       </c>
       <c r="E52" t="n">
-        <v>51761</v>
+        <v>52163</v>
       </c>
       <c r="F52" t="n">
-        <v>-824</v>
+        <v>402</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.0157</v>
+        <v>0.0078</v>
       </c>
       <c r="H52" t="n">
-        <v>1463</v>
+        <v>1365</v>
       </c>
       <c r="I52" t="n">
-        <v>50648</v>
+        <v>49746</v>
       </c>
       <c r="J52" t="n">
-        <v>51201.5</v>
+        <v>50208.25</v>
       </c>
       <c r="K52" t="n">
-        <v>51913</v>
+        <v>51029.5</v>
       </c>
       <c r="L52" t="n">
-        <v>52624.5</v>
+        <v>51850.75</v>
       </c>
       <c r="M52" t="n">
-        <v>53257</v>
+        <v>52492.5</v>
       </c>
       <c r="N52" t="n">
-        <v>53889.5</v>
+        <v>53134.25</v>
       </c>
       <c r="O52" t="n">
-        <v>54680</v>
+        <v>54135</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4871,18 +4869,18 @@
       <c r="Q52" s="6" t="n">
         <v/>
       </c>
-      <c r="R52" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R52" s="6" t="n">
+        <v/>
       </c>
       <c r="S52" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T52" s="8" t="n">
-        <v/>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T52" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U52" s="8" t="n">
         <v/>
@@ -4890,64 +4888,60 @@
       <c r="V52" s="8" t="n">
         <v/>
       </c>
-      <c r="W52" s="9" t="inlineStr">
+      <c r="W52" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>52085</v>
+        <v>52140</v>
       </c>
       <c r="C53" t="n">
-        <v>52844</v>
+        <v>52153</v>
       </c>
       <c r="D53" t="n">
-        <v>51479</v>
+        <v>50859</v>
       </c>
       <c r="E53" t="n">
-        <v>52163</v>
+        <v>51477</v>
       </c>
       <c r="F53" t="n">
-        <v>402</v>
+        <v>-686</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.0078</v>
+        <v>-0.0132</v>
       </c>
       <c r="H53" t="n">
-        <v>1365</v>
+        <v>1294</v>
       </c>
       <c r="I53" t="n">
-        <v>49746</v>
+        <v>50114</v>
       </c>
       <c r="J53" t="n">
-        <v>50208.25</v>
+        <v>50798.75</v>
       </c>
       <c r="K53" t="n">
-        <v>51029.5</v>
+        <v>51480.5</v>
       </c>
       <c r="L53" t="n">
-        <v>51850.75</v>
+        <v>52162.25</v>
       </c>
       <c r="M53" t="n">
-        <v>52492.5</v>
+        <v>52845.5</v>
       </c>
       <c r="N53" t="n">
-        <v>53134.25</v>
+        <v>53528.75</v>
       </c>
       <c r="O53" t="n">
-        <v>54135</v>
+        <v>54209</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4955,18 +4949,18 @@
       <c r="Q53" s="6" t="n">
         <v/>
       </c>
-      <c r="R53" s="6" t="n">
-        <v/>
+      <c r="R53" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S53" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T53" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T53" s="8" t="n">
+        <v/>
       </c>
       <c r="U53" s="8" t="n">
         <v/>
@@ -4974,60 +4968,64 @@
       <c r="V53" s="8" t="n">
         <v/>
       </c>
-      <c r="W53" s="9" t="inlineStr">
+      <c r="W53" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr"/>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>52140</v>
+        <v>51486</v>
       </c>
       <c r="C54" t="n">
-        <v>52153</v>
+        <v>52032</v>
       </c>
       <c r="D54" t="n">
-        <v>50859</v>
+        <v>50909</v>
       </c>
       <c r="E54" t="n">
-        <v>51477</v>
+        <v>51926</v>
       </c>
       <c r="F54" t="n">
-        <v>-686</v>
+        <v>449</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.0132</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="H54" t="n">
-        <v>1294</v>
+        <v>1123</v>
       </c>
       <c r="I54" t="n">
-        <v>50114</v>
+        <v>49565</v>
       </c>
       <c r="J54" t="n">
-        <v>50798.75</v>
+        <v>50168.5</v>
       </c>
       <c r="K54" t="n">
-        <v>51480.5</v>
+        <v>50830</v>
       </c>
       <c r="L54" t="n">
-        <v>52162.25</v>
+        <v>51491.5</v>
       </c>
       <c r="M54" t="n">
-        <v>52845.5</v>
+        <v>52124</v>
       </c>
       <c r="N54" t="n">
-        <v>53528.75</v>
+        <v>52756.5</v>
       </c>
       <c r="O54" t="n">
-        <v>54209</v>
+        <v>53447</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5035,83 +5033,83 @@
       <c r="Q54" s="6" t="n">
         <v/>
       </c>
-      <c r="R54" s="6" t="inlineStr">
+      <c r="R54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S54" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T54" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S54" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T54" s="8" t="n">
-        <v/>
-      </c>
       <c r="U54" s="8" t="n">
         <v/>
       </c>
       <c r="V54" s="8" t="n">
         <v/>
       </c>
-      <c r="W54" s="9" t="inlineStr">
+      <c r="W54" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>51486</v>
+        <v>51972</v>
       </c>
       <c r="C55" t="n">
-        <v>52032</v>
+        <v>52823</v>
       </c>
       <c r="D55" t="n">
-        <v>50909</v>
+        <v>51602</v>
       </c>
       <c r="E55" t="n">
-        <v>51926</v>
+        <v>52214</v>
       </c>
       <c r="F55" t="n">
-        <v>449</v>
+        <v>288</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.008699999999999999</v>
+        <v>0.0055</v>
       </c>
       <c r="H55" t="n">
-        <v>1123</v>
+        <v>1221</v>
       </c>
       <c r="I55" t="n">
-        <v>49565</v>
+        <v>49786</v>
       </c>
       <c r="J55" t="n">
-        <v>50168.5</v>
+        <v>51030.75</v>
       </c>
       <c r="K55" t="n">
-        <v>50830</v>
+        <v>51364.5</v>
       </c>
       <c r="L55" t="n">
-        <v>51491.5</v>
+        <v>51698.25</v>
       </c>
       <c r="M55" t="n">
-        <v>52124</v>
+        <v>52487.5</v>
       </c>
       <c r="N55" t="n">
-        <v>52756.5</v>
+        <v>53276.75</v>
       </c>
       <c r="O55" t="n">
-        <v>53447</v>
+        <v>53155</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5122,7 +5120,7 @@
       <c r="R55" s="6" t="n">
         <v/>
       </c>
-      <c r="S55" s="7" t="inlineStr">
+      <c r="S55" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -5138,64 +5136,60 @@
       <c r="V55" s="8" t="n">
         <v/>
       </c>
-      <c r="W55" s="9" t="inlineStr">
+      <c r="W55" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>51972</v>
+        <v>52070</v>
       </c>
       <c r="C56" t="n">
-        <v>52823</v>
+        <v>53168</v>
       </c>
       <c r="D56" t="n">
-        <v>51602</v>
+        <v>52034</v>
       </c>
       <c r="E56" t="n">
-        <v>52214</v>
+        <v>52394</v>
       </c>
       <c r="F56" t="n">
-        <v>288</v>
+        <v>180</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.0055</v>
+        <v>0.0034</v>
       </c>
       <c r="H56" t="n">
-        <v>1221</v>
+        <v>1134</v>
       </c>
       <c r="I56" t="n">
-        <v>49786</v>
+        <v>50381</v>
       </c>
       <c r="J56" t="n">
-        <v>51030.75</v>
+        <v>50993.75</v>
       </c>
       <c r="K56" t="n">
-        <v>51364.5</v>
+        <v>51603.5</v>
       </c>
       <c r="L56" t="n">
-        <v>51698.25</v>
+        <v>52213.25</v>
       </c>
       <c r="M56" t="n">
-        <v>52487.5</v>
+        <v>52824.5</v>
       </c>
       <c r="N56" t="n">
-        <v>53276.75</v>
+        <v>53435.75</v>
       </c>
       <c r="O56" t="n">
-        <v>53155</v>
+        <v>54044</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5206,14 +5200,14 @@
       <c r="R56" s="6" t="n">
         <v/>
       </c>
-      <c r="S56" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S56" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T56" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U56" s="8" t="n">
@@ -5222,7 +5216,7 @@
       <c r="V56" s="8" t="n">
         <v/>
       </c>
-      <c r="W56" s="9" t="inlineStr">
+      <c r="W56" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -5232,50 +5226,50 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>52070</v>
+        <v>52492</v>
       </c>
       <c r="C57" t="n">
-        <v>53168</v>
+        <v>53145</v>
       </c>
       <c r="D57" t="n">
-        <v>52034</v>
+        <v>51701</v>
       </c>
       <c r="E57" t="n">
-        <v>52394</v>
+        <v>51928</v>
       </c>
       <c r="F57" t="n">
-        <v>180</v>
+        <v>-466</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.0034</v>
+        <v>-0.0089</v>
       </c>
       <c r="H57" t="n">
-        <v>1134</v>
+        <v>1444</v>
       </c>
       <c r="I57" t="n">
-        <v>50381</v>
+        <v>50900</v>
       </c>
       <c r="J57" t="n">
-        <v>50993.75</v>
+        <v>51156.5</v>
       </c>
       <c r="K57" t="n">
-        <v>51603.5</v>
+        <v>51827</v>
       </c>
       <c r="L57" t="n">
-        <v>52213.25</v>
+        <v>52497.5</v>
       </c>
       <c r="M57" t="n">
-        <v>52824.5</v>
+        <v>52961</v>
       </c>
       <c r="N57" t="n">
-        <v>53435.75</v>
+        <v>53424.5</v>
       </c>
       <c r="O57" t="n">
-        <v>54044</v>
+        <v>54302</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5283,12 +5277,14 @@
       <c r="Q57" s="6" t="n">
         <v/>
       </c>
-      <c r="R57" s="6" t="n">
-        <v/>
+      <c r="R57" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S57" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T57" s="8" t="inlineStr">
@@ -5302,94 +5298,14 @@
       <c r="V57" s="8" t="n">
         <v/>
       </c>
-      <c r="W57" s="9" t="inlineStr">
+      <c r="W57" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>2026-10-26</t>
-        </is>
-      </c>
-      <c r="B58" t="n">
-        <v>52492</v>
-      </c>
-      <c r="C58" t="n">
-        <v>53145</v>
-      </c>
-      <c r="D58" t="n">
-        <v>52310</v>
-      </c>
-      <c r="E58" t="n">
-        <v>52357</v>
-      </c>
-      <c r="F58" t="n">
-        <v>-37</v>
-      </c>
-      <c r="G58" s="5" t="n">
-        <v>-0.0007</v>
-      </c>
-      <c r="H58" t="n">
-        <v>835</v>
-      </c>
-      <c r="I58" t="n">
-        <v>50900</v>
-      </c>
-      <c r="J58" t="n">
-        <v>51156.5</v>
-      </c>
-      <c r="K58" t="n">
-        <v>51827</v>
-      </c>
-      <c r="L58" t="n">
-        <v>52497.5</v>
-      </c>
-      <c r="M58" t="n">
-        <v>52961</v>
-      </c>
-      <c r="N58" t="n">
-        <v>53424.5</v>
-      </c>
-      <c r="O58" t="n">
-        <v>54302</v>
-      </c>
-      <c r="P58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S58" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W58" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t>中警訊</t>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
